--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,10 +5,11 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Standbys" sheetId="3" r:id="rId3"/>
-    <sheet name="Groups" sheetId="4" r:id="rId4"/>
-    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
-    <sheet name="Canceled Assignments" sheetId="6" r:id="rId6"/>
+    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
+    <sheet name="Standbys" sheetId="4" r:id="rId4"/>
+    <sheet name="Groups" sheetId="5" r:id="rId5"/>
+    <sheet name="Block Types" sheetId="6" r:id="rId6"/>
+    <sheet name="Canceled Assignments" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -1988,413 +1989,416 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>6c100962-ee82-41d1-afdf-6810823ea88e</v>
+        <v>0ccaf8bc-6ade-4ad6-9537-92f9829a6502</v>
       </c>
       <c r="B38" t="str">
-        <v>Madeleine  Floros</v>
+        <v>Peter Adamidis</v>
       </c>
       <c r="C38">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D38" t="str">
-        <v>Female</v>
+        <v>Not Specified</v>
       </c>
       <c r="E38" t="str">
-        <v>mfloros@y7mail.com</v>
+        <v>peter.adamidis@gmail.com</v>
       </c>
       <c r="F38" t="str">
-        <v>413533385</v>
+        <v>498086080</v>
       </c>
       <c r="G38" t="str">
-        <v>Bundoora</v>
+        <v/>
       </c>
       <c r="H38" t="str">
-        <v>B+</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J38" t="str">
-        <v>Claudia Floros</v>
+        <v>Kathleen Reynolds, Felicity Parker-Hill</v>
       </c>
       <c r="K38" t="str">
-        <v>d31fd676-cd74-4239-9827-4bfd973cc237</v>
+        <v>5fe641da-4067-49a7-bae7-e63413b3e404</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Broken Leg</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
+        <v>6c100962-ee82-41d1-afdf-6810823ea88e</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Madeleine  Floros</v>
+      </c>
+      <c r="C39">
+        <v>25</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E39" t="str">
+        <v>mfloros@y7mail.com</v>
+      </c>
+      <c r="F39" t="str">
+        <v>413533385</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Bundoora</v>
+      </c>
+      <c r="H39" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I39" t="str">
+        <v>available</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Claudia Floros</v>
+      </c>
+      <c r="K39" t="str">
+        <v>d31fd676-cd74-4239-9827-4bfd973cc237</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
         <v>2d64b97f-64bb-4190-abdf-5a2a9d37c810</v>
       </c>
-      <c r="B39" t="str">
+      <c r="B40" t="str">
         <v>Wendy  Manton</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>67</v>
       </c>
-      <c r="D39" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E39" t="str">
+      <c r="D40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E40" t="str">
         <v>wendymantonxo7@gmail.com</v>
       </c>
-      <c r="F39" t="str">
+      <c r="F40" t="str">
         <v>439858211</v>
       </c>
-      <c r="G39" t="str">
+      <c r="G40" t="str">
         <v xml:space="preserve">Melbourne </v>
       </c>
-      <c r="H39" t="str">
-        <v>B</v>
-      </c>
-      <c r="I39" t="str">
-        <v>available</v>
-      </c>
-      <c r="J39" t="str">
+      <c r="H40" t="str">
+        <v>B</v>
+      </c>
+      <c r="I40" t="str">
+        <v>available</v>
+      </c>
+      <c r="J40" t="str">
         <v>Jodi Kett</v>
       </c>
-      <c r="K39" t="str">
+      <c r="K40" t="str">
         <v>cbf209b8-2a31-4cf9-bc54-83485fa4051d</v>
       </c>
     </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
         <v>4f8c4348-e7af-42bc-93d9-bdf0b8e1585e</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B41" t="str">
         <v>SOPHIE ARMES</v>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>54</v>
       </c>
-      <c r="D40" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E40" t="str">
+      <c r="D41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E41" t="str">
         <v>sophievaudeleau@hotmail.com</v>
       </c>
-      <c r="F40" t="str">
+      <c r="F41" t="str">
         <v>401235498</v>
       </c>
-      <c r="G40" t="str">
+      <c r="G41" t="str">
         <v>HIGHTON</v>
       </c>
-      <c r="H40" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I40" t="str">
-        <v>available</v>
-      </c>
-      <c r="J40" t="str" xml:space="preserve">
+      <c r="H41" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I41" t="str">
+        <v>available</v>
+      </c>
+      <c r="J41" t="str" xml:space="preserve">
         <v xml:space="preserve">Sophie Armes - Player_x000d_
 Edward Armes - Son_x000d_
 Pamela Stone - Friend_x000d_
 Sheila Hawe - Friend_x000d_
 </v>
       </c>
-      <c r="K40" t="str">
+      <c r="K41" t="str">
         <v>d64a0044-98eb-47c9-a610-f16b009bfcb4</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="str">
+    <row r="42">
+      <c r="A42" t="str">
         <v>4c6757f5-c98a-41a1-bc6f-783d02a7e884</v>
       </c>
-      <c r="B41" t="str">
+      <c r="B42" t="str">
         <v>Matthew Bailey</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>38</v>
       </c>
-      <c r="D41" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E41" t="str">
+      <c r="D42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E42" t="str">
         <v>m.bailey23@hotmail.com</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F42" t="str">
         <v>423462472</v>
       </c>
-      <c r="G41" t="str">
+      <c r="G42" t="str">
         <v>Craigieburn</v>
       </c>
-      <c r="H41" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I41" t="str">
-        <v>available</v>
-      </c>
-      <c r="J41" t="str">
+      <c r="H42" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I42" t="str">
+        <v>available</v>
+      </c>
+      <c r="J42" t="str">
         <v>matthew bailey, simone bailey</v>
       </c>
-      <c r="K41" t="str">
+      <c r="K42" t="str">
         <v>0d1c49df-1962-42f1-9457-855ef54578e6</v>
       </c>
     </row>
-    <row r="42" xml:space="preserve">
-      <c r="A42" t="str">
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
         <v>7ef0a863-f193-4ea2-b6b1-9f6990d9c72b</v>
       </c>
-      <c r="B42" t="str">
+      <c r="B43" t="str">
         <v>EDWARD Armes</v>
       </c>
-      <c r="C42">
+      <c r="C43">
         <v>21</v>
       </c>
-      <c r="D42" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E42" t="str">
+      <c r="D43" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E43" t="str">
         <v>edarmes99@gmail.com</v>
       </c>
-      <c r="F42" t="str">
+      <c r="F43" t="str">
         <v>439861309</v>
       </c>
-      <c r="G42" t="str">
+      <c r="G43" t="str">
         <v xml:space="preserve">Geelong </v>
       </c>
-      <c r="H42" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I42" t="str">
-        <v>available</v>
-      </c>
-      <c r="J42" t="str" xml:space="preserve">
+      <c r="H43" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I43" t="str">
+        <v>available</v>
+      </c>
+      <c r="J43" t="str" xml:space="preserve">
         <v xml:space="preserve">Sophie Armes - Player_x000d_
 Edward Armes - Son_x000d_
 Pamela Stone - Friend_x000d_
 Sheila Hawe - Friend</v>
       </c>
-      <c r="K42" t="str">
+      <c r="K43" t="str">
         <v>d64a0044-98eb-47c9-a610-f16b009bfcb4</v>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str">
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
         <v>fe448c1e-878b-4ce5-b11f-de34f1d7ad19</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B44" t="str">
         <v>Antigoni  Simmons</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <v>34</v>
       </c>
-      <c r="D43" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E43" t="str">
+      <c r="D44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E44" t="str">
         <v>antigoni_trianta@outlook.com</v>
       </c>
-      <c r="F43" t="str">
+      <c r="F44" t="str">
         <v>431186284</v>
       </c>
-      <c r="G43" t="str">
+      <c r="G44" t="str">
         <v xml:space="preserve">Melbourne </v>
       </c>
-      <c r="H43" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I43" t="str">
-        <v>available</v>
-      </c>
-      <c r="J43" t="str" xml:space="preserve">
+      <c r="H44" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I44" t="str">
+        <v>available</v>
+      </c>
+      <c r="J44" t="str" xml:space="preserve">
         <v xml:space="preserve">Jamie Simmons - Needs to Apply_x000d_
 Alex Triantafylidis - Mum (tri-anta-fell-ease)_x000d_
 </v>
       </c>
-      <c r="K43" t="str">
+      <c r="K44" t="str">
         <v>b24e1d25-603c-49cb-97d3-f44db7487a00</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>acb3e630-d526-4057-b545-aa192312bdbd</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Tejas Deshmukh</v>
-      </c>
-      <c r="C44">
-        <v>35</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E44" t="str">
-        <v>arch.tejasd@gmail.com</v>
-      </c>
-      <c r="F44" t="str">
-        <v>481988781</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Melton South</v>
-      </c>
-      <c r="H44" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I44" t="str">
-        <v>available</v>
-      </c>
-      <c r="J44" t="str">
-        <v>Tejas Deshmukh, Chaitali Bhanushali</v>
-      </c>
-      <c r="K44" t="str">
-        <v>ea07ea19-44f5-4443-8d44-890ef7a5078a</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>47072c44-a802-4d24-962c-1654f4e2b639</v>
+        <v>acb3e630-d526-4057-b545-aa192312bdbd</v>
       </c>
       <c r="B45" t="str">
-        <v>gaylene piscopo</v>
+        <v>Tejas Deshmukh</v>
       </c>
       <c r="C45">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D45" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E45" t="str">
-        <v>gayleneeepiscopo03@gmail.com</v>
+        <v>arch.tejasd@gmail.com</v>
       </c>
       <c r="F45" t="str">
-        <v>499626264</v>
+        <v>481988781</v>
       </c>
       <c r="G45" t="str">
-        <v>Victoria</v>
+        <v>Melton South</v>
       </c>
       <c r="H45" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I45" t="str">
         <v>available</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Tejas Deshmukh, Chaitali Bhanushali</v>
+      </c>
+      <c r="K45" t="str">
+        <v>ea07ea19-44f5-4443-8d44-890ef7a5078a</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>712e4c3c-2bc9-486c-9fd0-42ce55f8247f</v>
+        <v>47072c44-a802-4d24-962c-1654f4e2b639</v>
       </c>
       <c r="B46" t="str">
-        <v>Kellie Fefelic</v>
+        <v>gaylene piscopo</v>
       </c>
       <c r="C46">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D46" t="str">
         <v>Female</v>
       </c>
       <c r="E46" t="str">
-        <v>kemalafelic@gmail.com</v>
+        <v>gayleneeepiscopo03@gmail.com</v>
       </c>
       <c r="F46" t="str">
-        <v>452090905</v>
+        <v>499626264</v>
       </c>
       <c r="G46" t="str">
-        <v>Mornington</v>
+        <v>Victoria</v>
       </c>
       <c r="H46" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I46" t="str">
         <v>available</v>
-      </c>
-      <c r="J46" t="str">
-        <v>Philip Heywood</v>
-      </c>
-      <c r="K46" t="str">
-        <v>54189d4e-7afc-4225-a6cb-28a8fff1a856</v>
-      </c>
-      <c r="M46" t="str">
-        <v>NA</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>1cfa5805-2855-4ff9-9175-697120cf327a</v>
+        <v>712e4c3c-2bc9-486c-9fd0-42ce55f8247f</v>
       </c>
       <c r="B47" t="str">
-        <v>Abrar Musa</v>
+        <v>Kellie Fefelic</v>
       </c>
       <c r="C47">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D47" t="str">
         <v>Female</v>
       </c>
       <c r="E47" t="str">
-        <v>abrarmusa459@gmail.com</v>
+        <v>kemalafelic@gmail.com</v>
       </c>
       <c r="F47" t="str">
-        <v>412610736</v>
+        <v>452090905</v>
       </c>
       <c r="G47" t="str">
-        <v>SPRINGVALE SOUTH</v>
+        <v>Mornington</v>
       </c>
       <c r="H47" t="str">
         <v>B+</v>
       </c>
       <c r="I47" t="str">
         <v>available</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Philip Heywood</v>
+      </c>
+      <c r="K47" t="str">
+        <v>54189d4e-7afc-4225-a6cb-28a8fff1a856</v>
+      </c>
+      <c r="M47" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>3a3ae62d-7e17-46a1-b4ca-f3edde675c9a</v>
+        <v>1cfa5805-2855-4ff9-9175-697120cf327a</v>
       </c>
       <c r="B48" t="str">
-        <v>Huda Hayek</v>
+        <v>Abrar Musa</v>
       </c>
       <c r="C48">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D48" t="str">
         <v>Female</v>
       </c>
       <c r="E48" t="str">
-        <v>Huda_hayek@yahoo.com.au</v>
+        <v>abrarmusa459@gmail.com</v>
       </c>
       <c r="F48" t="str">
-        <v>413787207</v>
+        <v>412610736</v>
       </c>
       <c r="G48" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v>SPRINGVALE SOUTH</v>
       </c>
       <c r="H48" t="str">
         <v>B+</v>
       </c>
       <c r="I48" t="str">
         <v>available</v>
-      </c>
-      <c r="J48" t="str">
-        <v>Fadey Souied</v>
-      </c>
-      <c r="K48" t="str">
-        <v>1edf8348-87ac-4690-a22c-ef5721f32b81</v>
-      </c>
-      <c r="M48" t="str">
-        <v>NA</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>11ad6470-961f-4c41-9474-0159c23c81bd</v>
+        <v>3a3ae62d-7e17-46a1-b4ca-f3edde675c9a</v>
       </c>
       <c r="B49" t="str">
-        <v>Caron Miller</v>
+        <v>Huda Hayek</v>
       </c>
       <c r="C49">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D49" t="str">
         <v>Female</v>
       </c>
       <c r="E49" t="str">
-        <v>mistyjasper@hotmail.com</v>
+        <v>Huda_hayek@yahoo.com.au</v>
       </c>
       <c r="F49" t="str">
-        <v>417331948</v>
+        <v>413787207</v>
       </c>
       <c r="G49" t="str">
-        <v>Narre Warren East</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H49" t="str">
         <v>B+</v>
@@ -2403,173 +2407,179 @@
         <v>available</v>
       </c>
       <c r="J49" t="str">
-        <v>Victoria Morrison</v>
+        <v>Fadey Souied</v>
       </c>
       <c r="K49" t="str">
-        <v>bc5440fa-e979-4a58-9300-e0349edf8d54</v>
+        <v>1edf8348-87ac-4690-a22c-ef5721f32b81</v>
+      </c>
+      <c r="M49" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
+        <v>11ad6470-961f-4c41-9474-0159c23c81bd</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Caron Miller</v>
+      </c>
+      <c r="C50">
+        <v>62</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E50" t="str">
+        <v>mistyjasper@hotmail.com</v>
+      </c>
+      <c r="F50" t="str">
+        <v>417331948</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Narre Warren East</v>
+      </c>
+      <c r="H50" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I50" t="str">
+        <v>available</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Victoria Morrison</v>
+      </c>
+      <c r="K50" t="str">
+        <v>bc5440fa-e979-4a58-9300-e0349edf8d54</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
         <v>cff9458b-cbd8-491e-9a5f-2171891b3f66</v>
       </c>
-      <c r="B50" t="str">
+      <c r="B51" t="str">
         <v>Shana Kent</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>45</v>
       </c>
-      <c r="D50" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E50" t="str">
+      <c r="D51" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E51" t="str">
         <v>banna12sk@hotmail.com</v>
       </c>
-      <c r="F50" t="str">
+      <c r="F51" t="str">
         <v>408333616</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G51" t="str">
         <v xml:space="preserve">Hurstbridge </v>
       </c>
-      <c r="H50" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I50" t="str">
-        <v>available</v>
-      </c>
-      <c r="J50" t="str">
+      <c r="H51" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I51" t="str">
+        <v>available</v>
+      </c>
+      <c r="J51" t="str">
         <v>Daughter - Emma Kent.  - needs to apply</v>
       </c>
-      <c r="K50" t="str">
+      <c r="K51" t="str">
         <v>96b83e8d-93db-4d09-9d4f-2398e8c44538</v>
       </c>
     </row>
-    <row r="51" xml:space="preserve">
-      <c r="A51" t="str">
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
         <v>32b624eb-d8d0-4725-b366-f8c07b803eee</v>
       </c>
-      <c r="B51" t="str">
+      <c r="B52" t="str">
         <v>amy milbourne</v>
       </c>
-      <c r="C51">
+      <c r="C52">
         <v>20</v>
       </c>
-      <c r="D51" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E51" t="str">
+      <c r="D52" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E52" t="str">
         <v>amy.milbourne005@gmail.com</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F52" t="str">
         <v>474656699</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G52" t="str">
         <v>haven</v>
       </c>
-      <c r="H51" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I51" t="str">
-        <v>available</v>
-      </c>
-      <c r="J51" t="str" xml:space="preserve">
+      <c r="H52" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I52" t="str">
+        <v>available</v>
+      </c>
+      <c r="J52" t="str" xml:space="preserve">
         <v xml:space="preserve">amy milbourne (MAIN PLAYER - B+)_x000d_
 Keely Elliott (B-)_x000d_
 Kate Ryan (B+)_x000d_
 </v>
       </c>
-      <c r="K51" t="str">
+      <c r="K52" t="str">
         <v>fc1a8405-88ef-43cc-a677-2d1bdc00bb6a</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>6b9babbd-6769-4410-bb4c-e9b9c9a4e966</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Angelina Butler</v>
-      </c>
-      <c r="C52">
-        <v>23</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E52" t="str">
-        <v>Angelinab31@hotmail.com</v>
-      </c>
-      <c r="F52" t="str">
-        <v>433646367</v>
-      </c>
-      <c r="G52" t="str">
-        <v>Wangaratta</v>
-      </c>
-      <c r="H52" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I52" t="str">
-        <v>available</v>
-      </c>
-      <c r="J52" t="str">
-        <v>Angelina Butler, Ebony Norris, Caragh Butler</v>
-      </c>
-      <c r="K52" t="str">
-        <v>c5549c5d-d4f2-46cd-a749-5c78710368b5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>efeba788-8d57-40b3-a3f9-e134a40931ac</v>
+        <v>6b9babbd-6769-4410-bb4c-e9b9c9a4e966</v>
       </c>
       <c r="B53" t="str">
-        <v>Leah Diaz</v>
+        <v>Angelina Butler</v>
       </c>
       <c r="C53">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D53" t="str">
         <v>Female</v>
       </c>
       <c r="E53" t="str">
-        <v>leah.diaz22@outlook.com</v>
+        <v>Angelinab31@hotmail.com</v>
       </c>
       <c r="F53" t="str">
-        <v>(159) 664-9326</v>
+        <v>433646367</v>
       </c>
       <c r="G53" t="str">
-        <v>Glendale</v>
+        <v>Wangaratta</v>
       </c>
       <c r="H53" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I53" t="str">
         <v>available</v>
       </c>
       <c r="J53" t="str">
-        <v>Julian Nguyen, Lydia Allen</v>
+        <v>Angelina Butler, Ebony Norris, Caragh Butler</v>
+      </c>
+      <c r="K53" t="str">
+        <v>c5549c5d-d4f2-46cd-a749-5c78710368b5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>50b3a8f6-823f-477c-b52d-5b4fba4edbd2</v>
+        <v>efeba788-8d57-40b3-a3f9-e134a40931ac</v>
       </c>
       <c r="B54" t="str">
-        <v>Naomi Moore</v>
+        <v>Leah Diaz</v>
       </c>
       <c r="C54">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D54" t="str">
         <v>Female</v>
       </c>
       <c r="E54" t="str">
-        <v>naomi.moore30@gmail.com</v>
+        <v>leah.diaz22@outlook.com</v>
       </c>
       <c r="F54" t="str">
-        <v>(391) 998-1729</v>
+        <v>(159) 664-9326</v>
       </c>
       <c r="G54" t="str">
-        <v>Irvine</v>
+        <v>Glendale</v>
       </c>
       <c r="H54" t="str">
         <v>B</v>
@@ -2578,94 +2588,94 @@
         <v>available</v>
       </c>
       <c r="J54" t="str">
-        <v>Isla Wright, Cora Roberts</v>
+        <v>Julian Nguyen, Lydia Allen</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>6366884b-6583-493e-80bc-a1dff1926c59</v>
+        <v>50b3a8f6-823f-477c-b52d-5b4fba4edbd2</v>
       </c>
       <c r="B55" t="str">
-        <v>Eleanor Allen</v>
+        <v>Naomi Moore</v>
       </c>
       <c r="C55">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D55" t="str">
         <v>Female</v>
       </c>
       <c r="E55" t="str">
-        <v>eleanor.allen67@outlook.com</v>
+        <v>naomi.moore30@gmail.com</v>
       </c>
       <c r="F55" t="str">
-        <v>(510) 261-1846</v>
+        <v>(391) 998-1729</v>
       </c>
       <c r="G55" t="str">
-        <v>Los Angeles</v>
+        <v>Irvine</v>
       </c>
       <c r="H55" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I55" t="str">
         <v>available</v>
       </c>
       <c r="J55" t="str">
-        <v>Christopher Allen</v>
+        <v>Isla Wright, Cora Roberts</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>d2e4b795-48d9-43e4-8ebe-6916a61a544e</v>
+        <v>6366884b-6583-493e-80bc-a1dff1926c59</v>
       </c>
       <c r="B56" t="str">
-        <v>Ella Gutierrez</v>
+        <v>Eleanor Allen</v>
       </c>
       <c r="C56">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D56" t="str">
         <v>Female</v>
       </c>
       <c r="E56" t="str">
-        <v>ella.gutierrez43@gmail.com</v>
+        <v>eleanor.allen67@outlook.com</v>
       </c>
       <c r="F56" t="str">
-        <v>(220) 105-1876</v>
+        <v>(510) 261-1846</v>
       </c>
       <c r="G56" t="str">
-        <v>Irvine</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H56" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I56" t="str">
         <v>available</v>
       </c>
       <c r="J56" t="str">
-        <v>Nora Lee</v>
+        <v>Christopher Allen</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>b57be3ad-f74f-4f2b-aa79-6e410d2c199b</v>
+        <v>d2e4b795-48d9-43e4-8ebe-6916a61a544e</v>
       </c>
       <c r="B57" t="str">
-        <v>Sofia Williams</v>
+        <v>Ella Gutierrez</v>
       </c>
       <c r="C57">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D57" t="str">
         <v>Female</v>
       </c>
       <c r="E57" t="str">
-        <v>sofia.williams60@outlook.com</v>
+        <v>ella.gutierrez43@gmail.com</v>
       </c>
       <c r="F57" t="str">
-        <v>(745) 392-3827</v>
+        <v>(220) 105-1876</v>
       </c>
       <c r="G57" t="str">
-        <v>Newport Beach</v>
+        <v>Irvine</v>
       </c>
       <c r="H57" t="str">
         <v>B</v>
@@ -2674,62 +2684,65 @@
         <v>available</v>
       </c>
       <c r="J57" t="str">
-        <v>Colton Harris, Sebastian Edwards</v>
+        <v>Nora Lee</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>d67459ad-fda4-4535-b6a0-42cd0de69019</v>
+        <v>b57be3ad-f74f-4f2b-aa79-6e410d2c199b</v>
       </c>
       <c r="B58" t="str">
-        <v>Test Contestant 15</v>
+        <v>Sofia Williams</v>
       </c>
       <c r="C58">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D58" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E58" t="str">
-        <v>test.contestant.15@gmail.com</v>
+        <v>sofia.williams60@outlook.com</v>
       </c>
       <c r="F58" t="str">
-        <v>(555) 105-0195</v>
+        <v>(745) 392-3827</v>
       </c>
       <c r="G58" t="str">
-        <v>Oakland</v>
+        <v>Newport Beach</v>
       </c>
       <c r="H58" t="str">
         <v>B</v>
       </c>
       <c r="I58" t="str">
         <v>available</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Colton Harris, Sebastian Edwards</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>f129272c-eaaf-449c-85ce-3cd116eb1fb1</v>
+        <v>d67459ad-fda4-4535-b6a0-42cd0de69019</v>
       </c>
       <c r="B59" t="str">
-        <v>Test Contestant 16</v>
+        <v>Test Contestant 15</v>
       </c>
       <c r="C59">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D59" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E59" t="str">
-        <v>test.contestant.16@gmail.com</v>
+        <v>test.contestant.15@gmail.com</v>
       </c>
       <c r="F59" t="str">
-        <v>(555) 112-0208</v>
+        <v>(555) 105-0195</v>
       </c>
       <c r="G59" t="str">
-        <v>Long Beach</v>
+        <v>Oakland</v>
       </c>
       <c r="H59" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I59" t="str">
         <v>available</v>
@@ -2737,25 +2750,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>11a593b5-9290-4dad-9566-12807536d0ae</v>
+        <v>f129272c-eaaf-449c-85ce-3cd116eb1fb1</v>
       </c>
       <c r="B60" t="str">
-        <v>Test Contestant 17</v>
+        <v>Test Contestant 16</v>
       </c>
       <c r="C60">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D60" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E60" t="str">
-        <v>test.contestant.17@gmail.com</v>
+        <v>test.contestant.16@gmail.com</v>
       </c>
       <c r="F60" t="str">
-        <v>(555) 119-0221</v>
+        <v>(555) 112-0208</v>
       </c>
       <c r="G60" t="str">
-        <v>Bakersfield</v>
+        <v>Long Beach</v>
       </c>
       <c r="H60" t="str">
         <v>B+</v>
@@ -2766,28 +2779,28 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>4d877930-458d-463b-a8ce-44fef29d6b91</v>
+        <v>11a593b5-9290-4dad-9566-12807536d0ae</v>
       </c>
       <c r="B61" t="str">
-        <v>Test Contestant 18</v>
+        <v>Test Contestant 17</v>
       </c>
       <c r="C61">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D61" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E61" t="str">
-        <v>test.contestant.18@gmail.com</v>
+        <v>test.contestant.17@gmail.com</v>
       </c>
       <c r="F61" t="str">
-        <v>(555) 126-0234</v>
+        <v>(555) 119-0221</v>
       </c>
       <c r="G61" t="str">
-        <v>Anaheim</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H61" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I61" t="str">
         <v>available</v>
@@ -2795,25 +2808,25 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>23a7e68c-bb4c-4eff-a403-af7fb14ec03e</v>
+        <v>4d877930-458d-463b-a8ce-44fef29d6b91</v>
       </c>
       <c r="B62" t="str">
-        <v>Test Contestant 19</v>
+        <v>Test Contestant 18</v>
       </c>
       <c r="C62">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D62" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E62" t="str">
-        <v>test.contestant.19@gmail.com</v>
+        <v>test.contestant.18@gmail.com</v>
       </c>
       <c r="F62" t="str">
-        <v>(555) 133-0247</v>
+        <v>(555) 126-0234</v>
       </c>
       <c r="G62" t="str">
-        <v>Santa Ana</v>
+        <v>Anaheim</v>
       </c>
       <c r="H62" t="str">
         <v>B</v>
@@ -2824,25 +2837,25 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>af5177d7-ccd0-49ee-b400-77f7af0aa6e2</v>
+        <v>23a7e68c-bb4c-4eff-a403-af7fb14ec03e</v>
       </c>
       <c r="B63" t="str">
-        <v>Test Contestant 20</v>
+        <v>Test Contestant 19</v>
       </c>
       <c r="C63">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D63" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E63" t="str">
-        <v>test.contestant.20@gmail.com</v>
+        <v>test.contestant.19@gmail.com</v>
       </c>
       <c r="F63" t="str">
-        <v>(555) 140-0260</v>
+        <v>(555) 133-0247</v>
       </c>
       <c r="G63" t="str">
-        <v>Los Angeles</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H63" t="str">
         <v>B</v>
@@ -2853,25 +2866,25 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>c03cdd9c-30bf-48cd-9c5c-97396ee3b8a7</v>
+        <v>af5177d7-ccd0-49ee-b400-77f7af0aa6e2</v>
       </c>
       <c r="B64" t="str">
-        <v>Test Contestant 21</v>
+        <v>Test Contestant 20</v>
       </c>
       <c r="C64">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D64" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E64" t="str">
-        <v>test.contestant.21@gmail.com</v>
+        <v>test.contestant.20@gmail.com</v>
       </c>
       <c r="F64" t="str">
-        <v>(555) 147-0273</v>
+        <v>(555) 140-0260</v>
       </c>
       <c r="G64" t="str">
-        <v>San Diego</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H64" t="str">
         <v>B</v>
@@ -2882,28 +2895,28 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>81986600-11c6-4c96-b1d0-9e2ee1d9c3fb</v>
+        <v>c03cdd9c-30bf-48cd-9c5c-97396ee3b8a7</v>
       </c>
       <c r="B65" t="str">
-        <v>Test Contestant 22</v>
+        <v>Test Contestant 21</v>
       </c>
       <c r="C65">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D65" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E65" t="str">
-        <v>test.contestant.22@gmail.com</v>
+        <v>test.contestant.21@gmail.com</v>
       </c>
       <c r="F65" t="str">
-        <v>(555) 154-0286</v>
+        <v>(555) 147-0273</v>
       </c>
       <c r="G65" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H65" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I65" t="str">
         <v>available</v>
@@ -2911,25 +2924,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2a22b9a0-52e1-4e3d-8a93-95da76fa7f56</v>
+        <v>81986600-11c6-4c96-b1d0-9e2ee1d9c3fb</v>
       </c>
       <c r="B66" t="str">
-        <v>Test Contestant 23</v>
+        <v>Test Contestant 22</v>
       </c>
       <c r="C66">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D66" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E66" t="str">
-        <v>test.contestant.23@gmail.com</v>
+        <v>test.contestant.22@gmail.com</v>
       </c>
       <c r="F66" t="str">
-        <v>(555) 161-0299</v>
+        <v>(555) 154-0286</v>
       </c>
       <c r="G66" t="str">
-        <v>Sacramento</v>
+        <v>San Francisco</v>
       </c>
       <c r="H66" t="str">
         <v>B+</v>
@@ -2940,28 +2953,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>aef8e2ef-578b-4161-9964-0ae6fd3c8d96</v>
+        <v>2a22b9a0-52e1-4e3d-8a93-95da76fa7f56</v>
       </c>
       <c r="B67" t="str">
-        <v>Test Contestant 24</v>
+        <v>Test Contestant 23</v>
       </c>
       <c r="C67">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E67" t="str">
-        <v>test.contestant.24@gmail.com</v>
+        <v>test.contestant.23@gmail.com</v>
       </c>
       <c r="F67" t="str">
-        <v>(555) 168-0312</v>
+        <v>(555) 161-0299</v>
       </c>
       <c r="G67" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H67" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I67" t="str">
         <v>available</v>
@@ -2969,25 +2982,25 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>e296b971-c119-416d-8ed5-372776954e90</v>
+        <v>aef8e2ef-578b-4161-9964-0ae6fd3c8d96</v>
       </c>
       <c r="B68" t="str">
-        <v>Test Contestant 25</v>
+        <v>Test Contestant 24</v>
       </c>
       <c r="C68">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D68" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E68" t="str">
-        <v>test.contestant.25@gmail.com</v>
+        <v>test.contestant.24@gmail.com</v>
       </c>
       <c r="F68" t="str">
-        <v>(555) 175-0325</v>
+        <v>(555) 168-0312</v>
       </c>
       <c r="G68" t="str">
-        <v>Oakland</v>
+        <v>Fresno</v>
       </c>
       <c r="H68" t="str">
         <v>B</v>
@@ -2998,25 +3011,25 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>178f6bd3-36f6-41e5-a8ab-d4f0f361b123</v>
+        <v>e296b971-c119-416d-8ed5-372776954e90</v>
       </c>
       <c r="B69" t="str">
-        <v>Test Contestant 26</v>
+        <v>Test Contestant 25</v>
       </c>
       <c r="C69">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D69" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E69" t="str">
-        <v>test.contestant.26@gmail.com</v>
+        <v>test.contestant.25@gmail.com</v>
       </c>
       <c r="F69" t="str">
-        <v>(555) 182-0338</v>
+        <v>(555) 175-0325</v>
       </c>
       <c r="G69" t="str">
-        <v>Long Beach</v>
+        <v>Oakland</v>
       </c>
       <c r="H69" t="str">
         <v>B</v>
@@ -3027,25 +3040,25 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>b7ec3bba-9305-49f0-b169-52951a67fa06</v>
+        <v>178f6bd3-36f6-41e5-a8ab-d4f0f361b123</v>
       </c>
       <c r="B70" t="str">
-        <v>Test Contestant 27</v>
+        <v>Test Contestant 26</v>
       </c>
       <c r="C70">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D70" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E70" t="str">
-        <v>test.contestant.27@gmail.com</v>
+        <v>test.contestant.26@gmail.com</v>
       </c>
       <c r="F70" t="str">
-        <v>(555) 189-0351</v>
+        <v>(555) 182-0338</v>
       </c>
       <c r="G70" t="str">
-        <v>Bakersfield</v>
+        <v>Long Beach</v>
       </c>
       <c r="H70" t="str">
         <v>B</v>
@@ -3056,28 +3069,28 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>1965f71f-47d5-461d-9a52-22e32499d4c6</v>
+        <v>b7ec3bba-9305-49f0-b169-52951a67fa06</v>
       </c>
       <c r="B71" t="str">
-        <v>Test Contestant 28</v>
+        <v>Test Contestant 27</v>
       </c>
       <c r="C71">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D71" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E71" t="str">
-        <v>test.contestant.28@gmail.com</v>
+        <v>test.contestant.27@gmail.com</v>
       </c>
       <c r="F71" t="str">
-        <v>(555) 196-0364</v>
+        <v>(555) 189-0351</v>
       </c>
       <c r="G71" t="str">
-        <v>Anaheim</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H71" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I71" t="str">
         <v>available</v>
@@ -3085,25 +3098,25 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>39724328-3c91-4fcd-9647-2d39b0511e0f</v>
+        <v>1965f71f-47d5-461d-9a52-22e32499d4c6</v>
       </c>
       <c r="B72" t="str">
-        <v>Test Contestant 29</v>
+        <v>Test Contestant 28</v>
       </c>
       <c r="C72">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D72" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E72" t="str">
-        <v>test.contestant.29@gmail.com</v>
+        <v>test.contestant.28@gmail.com</v>
       </c>
       <c r="F72" t="str">
-        <v>(555) 203-0377</v>
+        <v>(555) 196-0364</v>
       </c>
       <c r="G72" t="str">
-        <v>Santa Ana</v>
+        <v>Anaheim</v>
       </c>
       <c r="H72" t="str">
         <v>B+</v>
@@ -3114,28 +3127,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>a52d5a74-b5ca-46bb-abbe-bcd181350de0</v>
+        <v>39724328-3c91-4fcd-9647-2d39b0511e0f</v>
       </c>
       <c r="B73" t="str">
-        <v>Test Contestant 30</v>
+        <v>Test Contestant 29</v>
       </c>
       <c r="C73">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D73" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E73" t="str">
-        <v>test.contestant.30@gmail.com</v>
+        <v>test.contestant.29@gmail.com</v>
       </c>
       <c r="F73" t="str">
-        <v>(555) 210-0390</v>
+        <v>(555) 203-0377</v>
       </c>
       <c r="G73" t="str">
-        <v>Los Angeles</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H73" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I73" t="str">
         <v>available</v>
@@ -3143,25 +3156,25 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>cf72c0e9-1307-4c0a-9689-790378901e59</v>
+        <v>a52d5a74-b5ca-46bb-abbe-bcd181350de0</v>
       </c>
       <c r="B74" t="str">
-        <v>Test Contestant 31</v>
+        <v>Test Contestant 30</v>
       </c>
       <c r="C74">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D74" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E74" t="str">
-        <v>test.contestant.31@gmail.com</v>
+        <v>test.contestant.30@gmail.com</v>
       </c>
       <c r="F74" t="str">
-        <v>(555) 217-0403</v>
+        <v>(555) 210-0390</v>
       </c>
       <c r="G74" t="str">
-        <v>San Diego</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H74" t="str">
         <v>B</v>
@@ -3172,25 +3185,25 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>c3933989-9fcd-4cae-afa5-75de02fe66d7</v>
+        <v>cf72c0e9-1307-4c0a-9689-790378901e59</v>
       </c>
       <c r="B75" t="str">
-        <v>Test Contestant 32</v>
+        <v>Test Contestant 31</v>
       </c>
       <c r="C75">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D75" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E75" t="str">
-        <v>test.contestant.32@gmail.com</v>
+        <v>test.contestant.31@gmail.com</v>
       </c>
       <c r="F75" t="str">
-        <v>(555) 224-0416</v>
+        <v>(555) 217-0403</v>
       </c>
       <c r="G75" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H75" t="str">
         <v>B</v>
@@ -3201,28 +3214,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>8581109d-70b2-41df-9a53-c1ff59878172</v>
+        <v>c3933989-9fcd-4cae-afa5-75de02fe66d7</v>
       </c>
       <c r="B76" t="str">
-        <v>Test Contestant 33</v>
+        <v>Test Contestant 32</v>
       </c>
       <c r="C76">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D76" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E76" t="str">
-        <v>test.contestant.33@gmail.com</v>
+        <v>test.contestant.32@gmail.com</v>
       </c>
       <c r="F76" t="str">
-        <v>(555) 231-0429</v>
+        <v>(555) 224-0416</v>
       </c>
       <c r="G76" t="str">
-        <v>Sacramento</v>
+        <v>San Francisco</v>
       </c>
       <c r="H76" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I76" t="str">
         <v>available</v>
@@ -3230,25 +3243,25 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>5bf9f71c-43d9-43bc-b31d-a6ad3ca3f629</v>
+        <v>8581109d-70b2-41df-9a53-c1ff59878172</v>
       </c>
       <c r="B77" t="str">
-        <v>Test Contestant 34</v>
+        <v>Test Contestant 33</v>
       </c>
       <c r="C77">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D77" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E77" t="str">
-        <v>test.contestant.34@gmail.com</v>
+        <v>test.contestant.33@gmail.com</v>
       </c>
       <c r="F77" t="str">
-        <v>(555) 238-0442</v>
+        <v>(555) 231-0429</v>
       </c>
       <c r="G77" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H77" t="str">
         <v>B+</v>
@@ -3259,28 +3272,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>e420122f-8e2a-4388-9824-de4d7a1f2bed</v>
+        <v>5bf9f71c-43d9-43bc-b31d-a6ad3ca3f629</v>
       </c>
       <c r="B78" t="str">
-        <v>Test Contestant 35</v>
+        <v>Test Contestant 34</v>
       </c>
       <c r="C78">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D78" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E78" t="str">
-        <v>test.contestant.35@gmail.com</v>
+        <v>test.contestant.34@gmail.com</v>
       </c>
       <c r="F78" t="str">
-        <v>(555) 245-0455</v>
+        <v>(555) 238-0442</v>
       </c>
       <c r="G78" t="str">
-        <v>Oakland</v>
+        <v>Fresno</v>
       </c>
       <c r="H78" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I78" t="str">
         <v>available</v>
@@ -3288,28 +3301,28 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0d5141d9-6ee7-4671-8e2a-1ec7f4d7c962</v>
+        <v>e420122f-8e2a-4388-9824-de4d7a1f2bed</v>
       </c>
       <c r="B79" t="str">
-        <v>Test Contestant 36</v>
+        <v>Test Contestant 35</v>
       </c>
       <c r="C79">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D79" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E79" t="str">
-        <v>test.contestant.36@gmail.com</v>
+        <v>test.contestant.35@gmail.com</v>
       </c>
       <c r="F79" t="str">
-        <v>(555) 252-0468</v>
+        <v>(555) 245-0455</v>
       </c>
       <c r="G79" t="str">
-        <v>Long Beach</v>
+        <v>Oakland</v>
       </c>
       <c r="H79" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I79" t="str">
         <v>available</v>
@@ -3317,25 +3330,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>055444e6-ef7e-472e-9dd6-fc1ece2c4d01</v>
+        <v>0d5141d9-6ee7-4671-8e2a-1ec7f4d7c962</v>
       </c>
       <c r="B80" t="str">
-        <v>Test Contestant 37</v>
+        <v>Test Contestant 36</v>
       </c>
       <c r="C80">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D80" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E80" t="str">
-        <v>test.contestant.37@gmail.com</v>
+        <v>test.contestant.36@gmail.com</v>
       </c>
       <c r="F80" t="str">
-        <v>(555) 259-0481</v>
+        <v>(555) 252-0468</v>
       </c>
       <c r="G80" t="str">
-        <v>Bakersfield</v>
+        <v>Long Beach</v>
       </c>
       <c r="H80" t="str">
         <v>B</v>
@@ -3346,25 +3359,25 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>1d6bb1f4-850c-41da-ab78-629cfe29f697</v>
+        <v>055444e6-ef7e-472e-9dd6-fc1ece2c4d01</v>
       </c>
       <c r="B81" t="str">
-        <v>Test Contestant 38</v>
+        <v>Test Contestant 37</v>
       </c>
       <c r="C81">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D81" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E81" t="str">
-        <v>test.contestant.38@gmail.com</v>
+        <v>test.contestant.37@gmail.com</v>
       </c>
       <c r="F81" t="str">
-        <v>(555) 266-0494</v>
+        <v>(555) 259-0481</v>
       </c>
       <c r="G81" t="str">
-        <v>Anaheim</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H81" t="str">
         <v>B</v>
@@ -3375,28 +3388,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>054085b9-c7ab-408b-9ed8-a0fbfa587f09</v>
+        <v>1d6bb1f4-850c-41da-ab78-629cfe29f697</v>
       </c>
       <c r="B82" t="str">
-        <v>Test Contestant 39</v>
+        <v>Test Contestant 38</v>
       </c>
       <c r="C82">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D82" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E82" t="str">
-        <v>test.contestant.39@gmail.com</v>
+        <v>test.contestant.38@gmail.com</v>
       </c>
       <c r="F82" t="str">
-        <v>(555) 273-0507</v>
+        <v>(555) 266-0494</v>
       </c>
       <c r="G82" t="str">
-        <v>Santa Ana</v>
+        <v>Anaheim</v>
       </c>
       <c r="H82" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I82" t="str">
         <v>available</v>
@@ -3404,25 +3417,25 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>470121d9-d555-4418-a469-a734a8768cef</v>
+        <v>054085b9-c7ab-408b-9ed8-a0fbfa587f09</v>
       </c>
       <c r="B83" t="str">
-        <v>Test Contestant 40</v>
+        <v>Test Contestant 39</v>
       </c>
       <c r="C83">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D83" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E83" t="str">
-        <v>test.contestant.40@gmail.com</v>
+        <v>test.contestant.39@gmail.com</v>
       </c>
       <c r="F83" t="str">
-        <v>(555) 280-0520</v>
+        <v>(555) 273-0507</v>
       </c>
       <c r="G83" t="str">
-        <v>Los Angeles</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H83" t="str">
         <v>B+</v>
@@ -3433,28 +3446,28 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>7e71810e-aa20-4a93-826b-0d935e85cb00</v>
+        <v>470121d9-d555-4418-a469-a734a8768cef</v>
       </c>
       <c r="B84" t="str">
-        <v>Test Contestant 41</v>
+        <v>Test Contestant 40</v>
       </c>
       <c r="C84">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D84" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E84" t="str">
-        <v>test.contestant.41@gmail.com</v>
+        <v>test.contestant.40@gmail.com</v>
       </c>
       <c r="F84" t="str">
-        <v>(555) 287-0533</v>
+        <v>(555) 280-0520</v>
       </c>
       <c r="G84" t="str">
-        <v>San Diego</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H84" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I84" t="str">
         <v>available</v>
@@ -3462,28 +3475,28 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>c30b0ce9-57b9-4ec9-a866-06141d239140</v>
+        <v>7e71810e-aa20-4a93-826b-0d935e85cb00</v>
       </c>
       <c r="B85" t="str">
-        <v>Test Contestant 42</v>
+        <v>Test Contestant 41</v>
       </c>
       <c r="C85">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D85" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E85" t="str">
-        <v>test.contestant.42@gmail.com</v>
+        <v>test.contestant.41@gmail.com</v>
       </c>
       <c r="F85" t="str">
-        <v>(555) 294-0546</v>
+        <v>(555) 287-0533</v>
       </c>
       <c r="G85" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H85" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I85" t="str">
         <v>available</v>
@@ -3491,25 +3504,25 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>1a0d4a78-0671-4fc3-b324-00e4fe165cd4</v>
+        <v>c30b0ce9-57b9-4ec9-a866-06141d239140</v>
       </c>
       <c r="B86" t="str">
-        <v>Test Contestant 43</v>
+        <v>Test Contestant 42</v>
       </c>
       <c r="C86">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D86" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E86" t="str">
-        <v>test.contestant.43@gmail.com</v>
+        <v>test.contestant.42@gmail.com</v>
       </c>
       <c r="F86" t="str">
-        <v>(555) 301-0559</v>
+        <v>(555) 294-0546</v>
       </c>
       <c r="G86" t="str">
-        <v>Sacramento</v>
+        <v>San Francisco</v>
       </c>
       <c r="H86" t="str">
         <v>B</v>
@@ -3520,25 +3533,25 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>c7d30695-3461-403c-9a9f-b564f18bf2db</v>
+        <v>1a0d4a78-0671-4fc3-b324-00e4fe165cd4</v>
       </c>
       <c r="B87" t="str">
-        <v>Test Contestant 44</v>
+        <v>Test Contestant 43</v>
       </c>
       <c r="C87">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D87" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E87" t="str">
-        <v>test.contestant.44@gmail.com</v>
+        <v>test.contestant.43@gmail.com</v>
       </c>
       <c r="F87" t="str">
-        <v>(555) 308-0572</v>
+        <v>(555) 301-0559</v>
       </c>
       <c r="G87" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H87" t="str">
         <v>B</v>
@@ -3549,28 +3562,28 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>c97499bb-742e-48ff-8a3e-cf1d496a9858</v>
+        <v>c7d30695-3461-403c-9a9f-b564f18bf2db</v>
       </c>
       <c r="B88" t="str">
-        <v>Test Contestant 45</v>
+        <v>Test Contestant 44</v>
       </c>
       <c r="C88">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D88" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E88" t="str">
-        <v>test.contestant.45@gmail.com</v>
+        <v>test.contestant.44@gmail.com</v>
       </c>
       <c r="F88" t="str">
-        <v>(555) 315-0585</v>
+        <v>(555) 308-0572</v>
       </c>
       <c r="G88" t="str">
-        <v>Oakland</v>
+        <v>Fresno</v>
       </c>
       <c r="H88" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I88" t="str">
         <v>available</v>
@@ -3578,25 +3591,25 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>e0f8d626-987a-4be1-9a0f-eb763a04ec37</v>
+        <v>c97499bb-742e-48ff-8a3e-cf1d496a9858</v>
       </c>
       <c r="B89" t="str">
-        <v>Test Contestant 46</v>
+        <v>Test Contestant 45</v>
       </c>
       <c r="C89">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D89" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E89" t="str">
-        <v>test.contestant.46@gmail.com</v>
+        <v>test.contestant.45@gmail.com</v>
       </c>
       <c r="F89" t="str">
-        <v>(555) 322-0598</v>
+        <v>(555) 315-0585</v>
       </c>
       <c r="G89" t="str">
-        <v>Long Beach</v>
+        <v>Oakland</v>
       </c>
       <c r="H89" t="str">
         <v>B+</v>
@@ -3607,28 +3620,28 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>25bdc5eb-e818-48fc-a794-4dc3c3b48898</v>
+        <v>e0f8d626-987a-4be1-9a0f-eb763a04ec37</v>
       </c>
       <c r="B90" t="str">
-        <v>Test Contestant 47</v>
+        <v>Test Contestant 46</v>
       </c>
       <c r="C90">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D90" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E90" t="str">
-        <v>test.contestant.47@gmail.com</v>
+        <v>test.contestant.46@gmail.com</v>
       </c>
       <c r="F90" t="str">
-        <v>(555) 329-0611</v>
+        <v>(555) 322-0598</v>
       </c>
       <c r="G90" t="str">
-        <v>Bakersfield</v>
+        <v>Long Beach</v>
       </c>
       <c r="H90" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I90" t="str">
         <v>available</v>
@@ -3636,28 +3649,28 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>3f3213dd-dd0a-4cfb-a059-e333d35ec55c</v>
+        <v>25bdc5eb-e818-48fc-a794-4dc3c3b48898</v>
       </c>
       <c r="B91" t="str">
-        <v>Test Contestant 48</v>
+        <v>Test Contestant 47</v>
       </c>
       <c r="C91">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D91" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E91" t="str">
-        <v>test.contestant.48@gmail.com</v>
+        <v>test.contestant.47@gmail.com</v>
       </c>
       <c r="F91" t="str">
-        <v>(555) 336-0624</v>
+        <v>(555) 329-0611</v>
       </c>
       <c r="G91" t="str">
-        <v>Anaheim</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H91" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I91" t="str">
         <v>available</v>
@@ -3665,25 +3678,25 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>a761fc6e-d0da-4dec-a714-88266c5a51db</v>
+        <v>3f3213dd-dd0a-4cfb-a059-e333d35ec55c</v>
       </c>
       <c r="B92" t="str">
-        <v>Test Contestant 49</v>
+        <v>Test Contestant 48</v>
       </c>
       <c r="C92">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D92" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E92" t="str">
-        <v>test.contestant.49@gmail.com</v>
+        <v>test.contestant.48@gmail.com</v>
       </c>
       <c r="F92" t="str">
-        <v>(555) 343-0637</v>
+        <v>(555) 336-0624</v>
       </c>
       <c r="G92" t="str">
-        <v>Santa Ana</v>
+        <v>Anaheim</v>
       </c>
       <c r="H92" t="str">
         <v>B</v>
@@ -3694,25 +3707,25 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>a165a103-916c-4e3f-a06a-9bee886ccba8</v>
+        <v>a761fc6e-d0da-4dec-a714-88266c5a51db</v>
       </c>
       <c r="B93" t="str">
-        <v>Test Contestant 50</v>
+        <v>Test Contestant 49</v>
       </c>
       <c r="C93">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D93" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E93" t="str">
-        <v>test.contestant.50@gmail.com</v>
+        <v>test.contestant.49@gmail.com</v>
       </c>
       <c r="F93" t="str">
-        <v>(555) 350-0650</v>
+        <v>(555) 343-0637</v>
       </c>
       <c r="G93" t="str">
-        <v>Los Angeles</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H93" t="str">
         <v>B</v>
@@ -3723,28 +3736,28 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>837f94d1-084d-4a10-9c67-10356b6f0a1b</v>
+        <v>a165a103-916c-4e3f-a06a-9bee886ccba8</v>
       </c>
       <c r="B94" t="str">
-        <v>Test Contestant 51</v>
+        <v>Test Contestant 50</v>
       </c>
       <c r="C94">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D94" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E94" t="str">
-        <v>test.contestant.51@gmail.com</v>
+        <v>test.contestant.50@gmail.com</v>
       </c>
       <c r="F94" t="str">
-        <v>(555) 357-0663</v>
+        <v>(555) 350-0650</v>
       </c>
       <c r="G94" t="str">
-        <v>San Diego</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H94" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I94" t="str">
         <v>available</v>
@@ -3752,25 +3765,25 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>39a1bf57-cf38-44df-86f5-2f5f3862c73e</v>
+        <v>837f94d1-084d-4a10-9c67-10356b6f0a1b</v>
       </c>
       <c r="B95" t="str">
-        <v>Test Contestant 52</v>
+        <v>Test Contestant 51</v>
       </c>
       <c r="C95">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D95" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E95" t="str">
-        <v>test.contestant.52@gmail.com</v>
+        <v>test.contestant.51@gmail.com</v>
       </c>
       <c r="F95" t="str">
-        <v>(555) 364-0676</v>
+        <v>(555) 357-0663</v>
       </c>
       <c r="G95" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H95" t="str">
         <v>B+</v>
@@ -3781,28 +3794,28 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>a831561c-9671-4bd0-8faf-7fd78fb58f50</v>
+        <v>39a1bf57-cf38-44df-86f5-2f5f3862c73e</v>
       </c>
       <c r="B96" t="str">
-        <v>Test Contestant 53</v>
+        <v>Test Contestant 52</v>
       </c>
       <c r="C96">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D96" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E96" t="str">
-        <v>test.contestant.53@gmail.com</v>
+        <v>test.contestant.52@gmail.com</v>
       </c>
       <c r="F96" t="str">
-        <v>(555) 371-0689</v>
+        <v>(555) 364-0676</v>
       </c>
       <c r="G96" t="str">
-        <v>Sacramento</v>
+        <v>San Francisco</v>
       </c>
       <c r="H96" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I96" t="str">
         <v>available</v>
@@ -3810,25 +3823,25 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0db74406-5063-4ca3-902b-16b080a1d557</v>
+        <v>a831561c-9671-4bd0-8faf-7fd78fb58f50</v>
       </c>
       <c r="B97" t="str">
-        <v>Test Contestant 54</v>
+        <v>Test Contestant 53</v>
       </c>
       <c r="C97">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D97" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E97" t="str">
-        <v>test.contestant.54@gmail.com</v>
+        <v>test.contestant.53@gmail.com</v>
       </c>
       <c r="F97" t="str">
-        <v>(555) 378-0702</v>
+        <v>(555) 371-0689</v>
       </c>
       <c r="G97" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H97" t="str">
         <v>B</v>
@@ -3839,25 +3852,25 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>b3d7e82b-17c2-4a9d-9127-0253a1d7cb78</v>
+        <v>0db74406-5063-4ca3-902b-16b080a1d557</v>
       </c>
       <c r="B98" t="str">
-        <v>Test Contestant 55</v>
+        <v>Test Contestant 54</v>
       </c>
       <c r="C98">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D98" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E98" t="str">
-        <v>test.contestant.55@gmail.com</v>
+        <v>test.contestant.54@gmail.com</v>
       </c>
       <c r="F98" t="str">
-        <v>(555) 385-0715</v>
+        <v>(555) 378-0702</v>
       </c>
       <c r="G98" t="str">
-        <v>Oakland</v>
+        <v>Fresno</v>
       </c>
       <c r="H98" t="str">
         <v>B</v>
@@ -3868,121 +3881,118 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>8d8070dd-3ee6-476f-aaf2-631e80f67ef7</v>
+        <v>b3d7e82b-17c2-4a9d-9127-0253a1d7cb78</v>
       </c>
       <c r="B99" t="str">
-        <v>Lydia Allen</v>
+        <v>Test Contestant 55</v>
       </c>
       <c r="C99">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D99" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E99" t="str">
-        <v>lydia.allen73@icloud.com</v>
+        <v>test.contestant.55@gmail.com</v>
       </c>
       <c r="F99" t="str">
-        <v>(363) 934-8723</v>
+        <v>(555) 385-0715</v>
       </c>
       <c r="G99" t="str">
         <v>Oakland</v>
       </c>
       <c r="H99" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I99" t="str">
         <v>available</v>
-      </c>
-      <c r="J99" t="str">
-        <v>Julian Nguyen, Leah Diaz</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>a3199cca-1aa6-4060-b6cd-0320712376ba</v>
+        <v>8d8070dd-3ee6-476f-aaf2-631e80f67ef7</v>
       </c>
       <c r="B100" t="str">
-        <v>Isla Wright</v>
+        <v>Lydia Allen</v>
       </c>
       <c r="C100">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D100" t="str">
         <v>Female</v>
       </c>
       <c r="E100" t="str">
-        <v>isla.wright1@yahoo.com</v>
+        <v>lydia.allen73@icloud.com</v>
       </c>
       <c r="F100" t="str">
-        <v>(231) 918-9825</v>
+        <v>(363) 934-8723</v>
       </c>
       <c r="G100" t="str">
-        <v>Pasadena</v>
+        <v>Oakland</v>
       </c>
       <c r="H100" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I100" t="str">
         <v>available</v>
       </c>
       <c r="J100" t="str">
-        <v>Naomi Moore, Cora Roberts</v>
+        <v>Julian Nguyen, Leah Diaz</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>36fd980a-62d1-491b-97d6-079c33195e3d</v>
+        <v>a3199cca-1aa6-4060-b6cd-0320712376ba</v>
       </c>
       <c r="B101" t="str">
-        <v>Elena Green</v>
+        <v>Isla Wright</v>
       </c>
       <c r="C101">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D101" t="str">
         <v>Female</v>
       </c>
       <c r="E101" t="str">
-        <v>elena.green83@gmail.com</v>
+        <v>isla.wright1@yahoo.com</v>
       </c>
       <c r="F101" t="str">
-        <v>(274) 515-8123</v>
+        <v>(231) 918-9825</v>
       </c>
       <c r="G101" t="str">
-        <v>San Diego</v>
+        <v>Pasadena</v>
       </c>
       <c r="H101" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I101" t="str">
         <v>available</v>
       </c>
       <c r="J101" t="str">
-        <v>Allison Torres, Christian Rivera</v>
+        <v>Naomi Moore, Cora Roberts</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>40c53847-674f-43b5-8678-2decb3d42133</v>
+        <v>36fd980a-62d1-491b-97d6-079c33195e3d</v>
       </c>
       <c r="B102" t="str">
-        <v>Eliana Green</v>
+        <v>Elena Green</v>
       </c>
       <c r="C102">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D102" t="str">
         <v>Female</v>
       </c>
       <c r="E102" t="str">
-        <v>eliana.green54@gmail.com</v>
+        <v>elena.green83@gmail.com</v>
       </c>
       <c r="F102" t="str">
-        <v>(894) 795-3178</v>
+        <v>(274) 515-8123</v>
       </c>
       <c r="G102" t="str">
-        <v>Los Angeles</v>
+        <v>San Diego</v>
       </c>
       <c r="H102" t="str">
         <v>A</v>
@@ -3991,62 +4001,65 @@
         <v>available</v>
       </c>
       <c r="J102" t="str">
-        <v>Olivia Gonzalez</v>
+        <v>Allison Torres, Christian Rivera</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>95b9e37e-cc68-405f-a428-722fa71cc674</v>
+        <v>40c53847-674f-43b5-8678-2decb3d42133</v>
       </c>
       <c r="B103" t="str">
-        <v>Test Contestant 56</v>
+        <v>Eliana Green</v>
       </c>
       <c r="C103">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D103" t="str">
         <v>Female</v>
       </c>
       <c r="E103" t="str">
-        <v>test.contestant.56@gmail.com</v>
+        <v>eliana.green54@gmail.com</v>
       </c>
       <c r="F103" t="str">
-        <v>(555) 392-0728</v>
+        <v>(894) 795-3178</v>
       </c>
       <c r="G103" t="str">
-        <v>Long Beach</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H103" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I103" t="str">
         <v>available</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Olivia Gonzalez</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>305a2226-4750-469d-93b2-751af9d6b9c8</v>
+        <v>95b9e37e-cc68-405f-a428-722fa71cc674</v>
       </c>
       <c r="B104" t="str">
-        <v>Test Contestant 57</v>
+        <v>Test Contestant 56</v>
       </c>
       <c r="C104">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D104" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E104" t="str">
-        <v>test.contestant.57@gmail.com</v>
+        <v>test.contestant.56@gmail.com</v>
       </c>
       <c r="F104" t="str">
-        <v>(555) 399-0741</v>
+        <v>(555) 392-0728</v>
       </c>
       <c r="G104" t="str">
-        <v>Bakersfield</v>
+        <v>Long Beach</v>
       </c>
       <c r="H104" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I104" t="str">
         <v>available</v>
@@ -4054,25 +4067,25 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2d2f5e65-6945-4b8e-8099-25e26f29aa20</v>
+        <v>305a2226-4750-469d-93b2-751af9d6b9c8</v>
       </c>
       <c r="B105" t="str">
-        <v>Test Contestant 58</v>
+        <v>Test Contestant 57</v>
       </c>
       <c r="C105">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D105" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E105" t="str">
-        <v>test.contestant.58@gmail.com</v>
+        <v>test.contestant.57@gmail.com</v>
       </c>
       <c r="F105" t="str">
-        <v>(555) 406-0754</v>
+        <v>(555) 399-0741</v>
       </c>
       <c r="G105" t="str">
-        <v>Anaheim</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H105" t="str">
         <v>B+</v>
@@ -4083,28 +4096,28 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>d6e22062-8c88-41b5-aac2-d8ecb0da5f91</v>
+        <v>2d2f5e65-6945-4b8e-8099-25e26f29aa20</v>
       </c>
       <c r="B106" t="str">
-        <v>Test Contestant 59</v>
+        <v>Test Contestant 58</v>
       </c>
       <c r="C106">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D106" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E106" t="str">
-        <v>test.contestant.59@gmail.com</v>
+        <v>test.contestant.58@gmail.com</v>
       </c>
       <c r="F106" t="str">
-        <v>(555) 413-0767</v>
+        <v>(555) 406-0754</v>
       </c>
       <c r="G106" t="str">
-        <v>Santa Ana</v>
+        <v>Anaheim</v>
       </c>
       <c r="H106" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I106" t="str">
         <v>available</v>
@@ -4112,25 +4125,25 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>969eb120-6235-4fcd-b4cb-5b31d43f5df5</v>
+        <v>d6e22062-8c88-41b5-aac2-d8ecb0da5f91</v>
       </c>
       <c r="B107" t="str">
-        <v>Test Contestant 60</v>
+        <v>Test Contestant 59</v>
       </c>
       <c r="C107">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D107" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E107" t="str">
-        <v>test.contestant.60@gmail.com</v>
+        <v>test.contestant.59@gmail.com</v>
       </c>
       <c r="F107" t="str">
-        <v>(555) 420-0780</v>
+        <v>(555) 413-0767</v>
       </c>
       <c r="G107" t="str">
-        <v>Los Angeles</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H107" t="str">
         <v>B</v>
@@ -4141,25 +4154,25 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>611f9537-8854-4251-8c6c-1c61381cd28e</v>
+        <v>969eb120-6235-4fcd-b4cb-5b31d43f5df5</v>
       </c>
       <c r="B108" t="str">
-        <v>Test Contestant 61</v>
+        <v>Test Contestant 60</v>
       </c>
       <c r="C108">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D108" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E108" t="str">
-        <v>test.contestant.61@gmail.com</v>
+        <v>test.contestant.60@gmail.com</v>
       </c>
       <c r="F108" t="str">
-        <v>(555) 427-0793</v>
+        <v>(555) 420-0780</v>
       </c>
       <c r="G108" t="str">
-        <v>San Diego</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H108" t="str">
         <v>B</v>
@@ -4170,25 +4183,25 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>3714c809-9a90-4708-afb9-a18144a63b19</v>
+        <v>611f9537-8854-4251-8c6c-1c61381cd28e</v>
       </c>
       <c r="B109" t="str">
-        <v>Test Contestant 62</v>
+        <v>Test Contestant 61</v>
       </c>
       <c r="C109">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D109" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E109" t="str">
-        <v>test.contestant.62@gmail.com</v>
+        <v>test.contestant.61@gmail.com</v>
       </c>
       <c r="F109" t="str">
-        <v>(555) 434-0806</v>
+        <v>(555) 427-0793</v>
       </c>
       <c r="G109" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H109" t="str">
         <v>B</v>
@@ -4199,28 +4212,28 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>d90a141d-4047-4f88-97e1-8fec2a89b185</v>
+        <v>3714c809-9a90-4708-afb9-a18144a63b19</v>
       </c>
       <c r="B110" t="str">
-        <v>Test Contestant 63</v>
+        <v>Test Contestant 62</v>
       </c>
       <c r="C110">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D110" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E110" t="str">
-        <v>test.contestant.63@gmail.com</v>
+        <v>test.contestant.62@gmail.com</v>
       </c>
       <c r="F110" t="str">
-        <v>(555) 441-0819</v>
+        <v>(555) 434-0806</v>
       </c>
       <c r="G110" t="str">
-        <v>Sacramento</v>
+        <v>San Francisco</v>
       </c>
       <c r="H110" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I110" t="str">
         <v>available</v>
@@ -4228,25 +4241,25 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>086c4a40-edf4-4e28-b3ba-4658ccac5d7e</v>
+        <v>d90a141d-4047-4f88-97e1-8fec2a89b185</v>
       </c>
       <c r="B111" t="str">
-        <v>Test Contestant 64</v>
+        <v>Test Contestant 63</v>
       </c>
       <c r="C111">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D111" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E111" t="str">
-        <v>test.contestant.64@gmail.com</v>
+        <v>test.contestant.63@gmail.com</v>
       </c>
       <c r="F111" t="str">
-        <v>(555) 448-0832</v>
+        <v>(555) 441-0819</v>
       </c>
       <c r="G111" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H111" t="str">
         <v>B+</v>
@@ -4257,28 +4270,28 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>1c90f9b6-b59d-440a-b28a-53d9d92fb090</v>
+        <v>086c4a40-edf4-4e28-b3ba-4658ccac5d7e</v>
       </c>
       <c r="B112" t="str">
-        <v>Test Contestant 65</v>
+        <v>Test Contestant 64</v>
       </c>
       <c r="C112">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D112" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E112" t="str">
-        <v>test.contestant.65@gmail.com</v>
+        <v>test.contestant.64@gmail.com</v>
       </c>
       <c r="F112" t="str">
-        <v>(555) 455-0845</v>
+        <v>(555) 448-0832</v>
       </c>
       <c r="G112" t="str">
-        <v>Oakland</v>
+        <v>Fresno</v>
       </c>
       <c r="H112" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I112" t="str">
         <v>available</v>
@@ -4286,25 +4299,25 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>55adecab-6718-45de-9a47-9817dbf5c444</v>
+        <v>1c90f9b6-b59d-440a-b28a-53d9d92fb090</v>
       </c>
       <c r="B113" t="str">
-        <v>Test Contestant 66</v>
+        <v>Test Contestant 65</v>
       </c>
       <c r="C113">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D113" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E113" t="str">
-        <v>test.contestant.66@gmail.com</v>
+        <v>test.contestant.65@gmail.com</v>
       </c>
       <c r="F113" t="str">
-        <v>(555) 462-0858</v>
+        <v>(555) 455-0845</v>
       </c>
       <c r="G113" t="str">
-        <v>Long Beach</v>
+        <v>Oakland</v>
       </c>
       <c r="H113" t="str">
         <v>B</v>
@@ -4315,25 +4328,25 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>5feb745c-7c04-4dbc-93b0-5750195337f5</v>
+        <v>55adecab-6718-45de-9a47-9817dbf5c444</v>
       </c>
       <c r="B114" t="str">
-        <v>Test Contestant 67</v>
+        <v>Test Contestant 66</v>
       </c>
       <c r="C114">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D114" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E114" t="str">
-        <v>test.contestant.67@gmail.com</v>
+        <v>test.contestant.66@gmail.com</v>
       </c>
       <c r="F114" t="str">
-        <v>(555) 469-0871</v>
+        <v>(555) 462-0858</v>
       </c>
       <c r="G114" t="str">
-        <v>Bakersfield</v>
+        <v>Long Beach</v>
       </c>
       <c r="H114" t="str">
         <v>B</v>
@@ -4344,25 +4357,25 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>30b37a9d-e988-4aab-b209-331d5acb8453</v>
+        <v>5feb745c-7c04-4dbc-93b0-5750195337f5</v>
       </c>
       <c r="B115" t="str">
-        <v>Test Contestant 68</v>
+        <v>Test Contestant 67</v>
       </c>
       <c r="C115">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D115" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E115" t="str">
-        <v>test.contestant.68@gmail.com</v>
+        <v>test.contestant.67@gmail.com</v>
       </c>
       <c r="F115" t="str">
-        <v>(555) 476-0884</v>
+        <v>(555) 469-0871</v>
       </c>
       <c r="G115" t="str">
-        <v>Anaheim</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H115" t="str">
         <v>B</v>
@@ -4373,28 +4386,28 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>4dcf69c5-2760-46a7-8755-7d7a05c8617e</v>
+        <v>30b37a9d-e988-4aab-b209-331d5acb8453</v>
       </c>
       <c r="B116" t="str">
-        <v>Test Contestant 69</v>
+        <v>Test Contestant 68</v>
       </c>
       <c r="C116">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D116" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E116" t="str">
-        <v>test.contestant.69@gmail.com</v>
+        <v>test.contestant.68@gmail.com</v>
       </c>
       <c r="F116" t="str">
-        <v>(555) 483-0897</v>
+        <v>(555) 476-0884</v>
       </c>
       <c r="G116" t="str">
-        <v>Santa Ana</v>
+        <v>Anaheim</v>
       </c>
       <c r="H116" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I116" t="str">
         <v>available</v>
@@ -4402,25 +4415,25 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>31f2300e-f88e-40de-89d6-76eda757fc7c</v>
+        <v>4dcf69c5-2760-46a7-8755-7d7a05c8617e</v>
       </c>
       <c r="B117" t="str">
-        <v>Test Contestant 70</v>
+        <v>Test Contestant 69</v>
       </c>
       <c r="C117">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D117" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E117" t="str">
-        <v>test.contestant.70@gmail.com</v>
+        <v>test.contestant.69@gmail.com</v>
       </c>
       <c r="F117" t="str">
-        <v>(555) 490-0910</v>
+        <v>(555) 483-0897</v>
       </c>
       <c r="G117" t="str">
-        <v>Los Angeles</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H117" t="str">
         <v>B+</v>
@@ -4431,86 +4444,86 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>17e4dd39-8810-472c-b1a9-52382fbe0c79</v>
+        <v>31f2300e-f88e-40de-89d6-76eda757fc7c</v>
       </c>
       <c r="B118" t="str">
-        <v>Allison Torres</v>
+        <v>Test Contestant 70</v>
       </c>
       <c r="C118">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D118" t="str">
         <v>Female</v>
       </c>
       <c r="E118" t="str">
-        <v>allison.torres94@gmail.com</v>
+        <v>test.contestant.70@gmail.com</v>
       </c>
       <c r="F118" t="str">
-        <v>(858) 153-7242</v>
+        <v>(555) 490-0910</v>
       </c>
       <c r="G118" t="str">
-        <v>Fremont</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H118" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I118" t="str">
         <v>available</v>
-      </c>
-      <c r="J118" t="str">
-        <v>Christian Rivera, Elena Green</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>b021c796-9ea9-4f53-9ec2-1da6a022df96</v>
+        <v>17e4dd39-8810-472c-b1a9-52382fbe0c79</v>
       </c>
       <c r="B119" t="str">
-        <v>Test Contestant 71</v>
+        <v>Allison Torres</v>
       </c>
       <c r="C119">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D119" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E119" t="str">
-        <v>test.contestant.71@gmail.com</v>
+        <v>allison.torres94@gmail.com</v>
       </c>
       <c r="F119" t="str">
-        <v>(555) 497-0923</v>
+        <v>(858) 153-7242</v>
       </c>
       <c r="G119" t="str">
-        <v>San Diego</v>
+        <v>Fremont</v>
       </c>
       <c r="H119" t="str">
         <v>B</v>
       </c>
       <c r="I119" t="str">
         <v>available</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Christian Rivera, Elena Green</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>bcb6ec64-1208-46ba-8617-a6dcec2c9a65</v>
+        <v>b021c796-9ea9-4f53-9ec2-1da6a022df96</v>
       </c>
       <c r="B120" t="str">
-        <v>Test Contestant 72</v>
+        <v>Test Contestant 71</v>
       </c>
       <c r="C120">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D120" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E120" t="str">
-        <v>test.contestant.72@gmail.com</v>
+        <v>test.contestant.71@gmail.com</v>
       </c>
       <c r="F120" t="str">
-        <v>(555) 504-0936</v>
+        <v>(555) 497-0923</v>
       </c>
       <c r="G120" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H120" t="str">
         <v>B</v>
@@ -4521,22 +4534,22 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>4e28a208-5278-410d-b375-d9c77ba144d7</v>
+        <v>bcb6ec64-1208-46ba-8617-a6dcec2c9a65</v>
       </c>
       <c r="B121" t="str">
-        <v>Riley Scott</v>
+        <v>Test Contestant 72</v>
       </c>
       <c r="C121">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D121" t="str">
         <v>Female</v>
       </c>
       <c r="E121" t="str">
-        <v>riley.scott58@hotmail.com</v>
+        <v>test.contestant.72@gmail.com</v>
       </c>
       <c r="F121" t="str">
-        <v>(848) 718-3465</v>
+        <v>(555) 504-0936</v>
       </c>
       <c r="G121" t="str">
         <v>San Francisco</v>
@@ -4550,28 +4563,28 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ca152dfe-8ddb-45c8-b084-8a5c9e6dacfa</v>
+        <v>4e28a208-5278-410d-b375-d9c77ba144d7</v>
       </c>
       <c r="B122" t="str">
-        <v>Ryan Lewis</v>
+        <v>Riley Scott</v>
       </c>
       <c r="C122">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D122" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E122" t="str">
-        <v>ryan.lewis85@yahoo.com</v>
+        <v>riley.scott58@hotmail.com</v>
       </c>
       <c r="F122" t="str">
-        <v>0400 187 811</v>
+        <v>(848) 718-3465</v>
       </c>
       <c r="G122" t="str">
-        <v>Canberra</v>
+        <v>San Francisco</v>
       </c>
       <c r="H122" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I122" t="str">
         <v>available</v>
@@ -4579,28 +4592,28 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>9592637d-d895-4eaa-a700-e4eeea419a8e</v>
+        <v>ca152dfe-8ddb-45c8-b084-8a5c9e6dacfa</v>
       </c>
       <c r="B123" t="str">
-        <v>Test Contestant 73</v>
+        <v>Ryan Lewis</v>
       </c>
       <c r="C123">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D123" t="str">
         <v>Male</v>
       </c>
       <c r="E123" t="str">
-        <v>test.contestant.73@gmail.com</v>
+        <v>ryan.lewis85@yahoo.com</v>
       </c>
       <c r="F123" t="str">
-        <v>(555) 511-0949</v>
+        <v>0400 187 811</v>
       </c>
       <c r="G123" t="str">
-        <v>Sacramento</v>
+        <v>Canberra</v>
       </c>
       <c r="H123" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I123" t="str">
         <v>available</v>
@@ -4608,25 +4621,25 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>9026b2df-16d2-47b5-954c-c1db95e95c8c</v>
+        <v>9592637d-d895-4eaa-a700-e4eeea419a8e</v>
       </c>
       <c r="B124" t="str">
-        <v>Test Contestant 74</v>
+        <v>Test Contestant 73</v>
       </c>
       <c r="C124">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D124" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E124" t="str">
-        <v>test.contestant.74@gmail.com</v>
+        <v>test.contestant.73@gmail.com</v>
       </c>
       <c r="F124" t="str">
-        <v>(555) 518-0962</v>
+        <v>(555) 511-0949</v>
       </c>
       <c r="G124" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H124" t="str">
         <v>B</v>
@@ -4637,28 +4650,28 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>8b302346-d164-4710-916b-8ca5c2da560e</v>
+        <v>9026b2df-16d2-47b5-954c-c1db95e95c8c</v>
       </c>
       <c r="B125" t="str">
-        <v>Test Contestant 75</v>
+        <v>Test Contestant 74</v>
       </c>
       <c r="C125">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D125" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E125" t="str">
-        <v>test.contestant.75@gmail.com</v>
+        <v>test.contestant.74@gmail.com</v>
       </c>
       <c r="F125" t="str">
-        <v>(555) 525-0975</v>
+        <v>(555) 518-0962</v>
       </c>
       <c r="G125" t="str">
-        <v>Oakland</v>
+        <v>Fresno</v>
       </c>
       <c r="H125" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I125" t="str">
         <v>available</v>
@@ -4666,89 +4679,86 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>bf1fc0b1-7d88-41a5-ab6f-ee4c085fd344</v>
+        <v>8b302346-d164-4710-916b-8ca5c2da560e</v>
       </c>
       <c r="B126" t="str">
-        <v>Brooklyn Nguyen</v>
+        <v>Test Contestant 75</v>
       </c>
       <c r="C126">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D126" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E126" t="str">
-        <v>brooklyn.nguyen77@yahoo.com</v>
+        <v>test.contestant.75@gmail.com</v>
       </c>
       <c r="F126" t="str">
-        <v>(142) 872-1855</v>
+        <v>(555) 525-0975</v>
       </c>
       <c r="G126" t="str">
-        <v>Los Angeles</v>
+        <v>Oakland</v>
       </c>
       <c r="H126" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I126" t="str">
         <v>available</v>
-      </c>
-      <c r="J126" t="str">
-        <v>Naomi Brown</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>50b098db-86f4-4a21-8425-ab03df8f7a40</v>
+        <v>bf1fc0b1-7d88-41a5-ab6f-ee4c085fd344</v>
       </c>
       <c r="B127" t="str">
-        <v>Lillian Campbell</v>
+        <v>Brooklyn Nguyen</v>
       </c>
       <c r="C127">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D127" t="str">
         <v>Female</v>
       </c>
       <c r="E127" t="str">
-        <v>lillian.campbell41@yahoo.com</v>
+        <v>brooklyn.nguyen77@yahoo.com</v>
       </c>
       <c r="F127" t="str">
-        <v>(945) 213-8284</v>
+        <v>(142) 872-1855</v>
       </c>
       <c r="G127" t="str">
-        <v>Pasadena</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H127" t="str">
-        <v>A+</v>
+        <v>A</v>
       </c>
       <c r="I127" t="str">
         <v>available</v>
       </c>
       <c r="J127" t="str">
-        <v>Amelia Lopez</v>
+        <v>Naomi Brown</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e9a3f4c7-c9ed-4fd1-a5a9-d3763ae52a55</v>
+        <v>50b098db-86f4-4a21-8425-ab03df8f7a40</v>
       </c>
       <c r="B128" t="str">
-        <v>Victoria Anderson</v>
+        <v>Lillian Campbell</v>
       </c>
       <c r="C128">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D128" t="str">
         <v>Female</v>
       </c>
       <c r="E128" t="str">
-        <v>victoria.anderson1@outlook.com</v>
+        <v>lillian.campbell41@yahoo.com</v>
       </c>
       <c r="F128" t="str">
-        <v>(622) 987-4829</v>
+        <v>(945) 213-8284</v>
       </c>
       <c r="G128" t="str">
-        <v>Sacramento</v>
+        <v>Pasadena</v>
       </c>
       <c r="H128" t="str">
         <v>A+</v>
@@ -4757,59 +4767,62 @@
         <v>available</v>
       </c>
       <c r="J128" t="str">
-        <v>Sophia Reyes</v>
+        <v>Amelia Lopez</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>af09efbe-e83d-4046-8dc8-e6a06dfc0c40</v>
+        <v>e9a3f4c7-c9ed-4fd1-a5a9-d3763ae52a55</v>
       </c>
       <c r="B129" t="str">
-        <v>Paisley Evans</v>
+        <v>Victoria Anderson</v>
       </c>
       <c r="C129">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D129" t="str">
         <v>Female</v>
       </c>
       <c r="E129" t="str">
-        <v>paisley.evans52@yahoo.com</v>
+        <v>victoria.anderson1@outlook.com</v>
       </c>
       <c r="F129" t="str">
-        <v>(894) 250-9501</v>
+        <v>(622) 987-4829</v>
       </c>
       <c r="G129" t="str">
-        <v>Torrance</v>
+        <v>Sacramento</v>
       </c>
       <c r="H129" t="str">
-        <v>B+</v>
+        <v>A+</v>
       </c>
       <c r="I129" t="str">
         <v>available</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Sophia Reyes</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>451ce844-6939-423f-afd1-3962317eb399</v>
+        <v>af09efbe-e83d-4046-8dc8-e6a06dfc0c40</v>
       </c>
       <c r="B130" t="str">
-        <v>Test Contestant 76</v>
+        <v>Paisley Evans</v>
       </c>
       <c r="C130">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D130" t="str">
         <v>Female</v>
       </c>
       <c r="E130" t="str">
-        <v>test.contestant.76@gmail.com</v>
+        <v>paisley.evans52@yahoo.com</v>
       </c>
       <c r="F130" t="str">
-        <v>(555) 532-0988</v>
+        <v>(894) 250-9501</v>
       </c>
       <c r="G130" t="str">
-        <v>Long Beach</v>
+        <v>Torrance</v>
       </c>
       <c r="H130" t="str">
         <v>B+</v>
@@ -4820,89 +4833,86 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>e7129d06-9fe4-44dd-afce-e4faeebfe1a9</v>
+        <v>451ce844-6939-423f-afd1-3962317eb399</v>
       </c>
       <c r="B131" t="str">
-        <v>Piper Green</v>
+        <v>Test Contestant 76</v>
       </c>
       <c r="C131">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D131" t="str">
         <v>Female</v>
       </c>
       <c r="E131" t="str">
-        <v>piper.green82@hotmail.com</v>
+        <v>test.contestant.76@gmail.com</v>
       </c>
       <c r="F131" t="str">
-        <v>(678) 816-2263</v>
+        <v>(555) 532-0988</v>
       </c>
       <c r="G131" t="str">
-        <v>Burbank</v>
+        <v>Long Beach</v>
       </c>
       <c r="H131" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I131" t="str">
         <v>available</v>
-      </c>
-      <c r="J131" t="str">
-        <v>Josiah Brown</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>a8f50ac0-29e0-4209-a524-83ca7878b0ca</v>
+        <v>e7129d06-9fe4-44dd-afce-e4faeebfe1a9</v>
       </c>
       <c r="B132" t="str">
-        <v>Avery Taylor</v>
+        <v>Piper Green</v>
       </c>
       <c r="C132">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D132" t="str">
         <v>Female</v>
       </c>
       <c r="E132" t="str">
-        <v>avery.taylor87@outlook.com</v>
+        <v>piper.green82@hotmail.com</v>
       </c>
       <c r="F132" t="str">
-        <v>(299) 491-7680</v>
+        <v>(678) 816-2263</v>
       </c>
       <c r="G132" t="str">
-        <v>Los Angeles</v>
+        <v>Burbank</v>
       </c>
       <c r="H132" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I132" t="str">
         <v>available</v>
       </c>
       <c r="J132" t="str">
-        <v>Audrey Hill</v>
+        <v>Josiah Brown</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>443fcd0e-727d-4035-ab6a-c3df01515271</v>
+        <v>a8f50ac0-29e0-4209-a524-83ca7878b0ca</v>
       </c>
       <c r="B133" t="str">
-        <v>Lydia Torres</v>
+        <v>Avery Taylor</v>
       </c>
       <c r="C133">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D133" t="str">
         <v>Female</v>
       </c>
       <c r="E133" t="str">
-        <v>lydia.torres72@yahoo.com</v>
+        <v>avery.taylor87@outlook.com</v>
       </c>
       <c r="F133" t="str">
-        <v>(828) 773-4386</v>
+        <v>(299) 491-7680</v>
       </c>
       <c r="G133" t="str">
-        <v>Anaheim</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H133" t="str">
         <v>B+</v>
@@ -4911,123 +4921,123 @@
         <v>available</v>
       </c>
       <c r="J133" t="str">
-        <v>Avery Cruz, Mia Anderson</v>
+        <v>Audrey Hill</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>53ee847e-7806-44ed-ba11-776baaf0214b</v>
+        <v>443fcd0e-727d-4035-ab6a-c3df01515271</v>
       </c>
       <c r="B134" t="str">
-        <v>Test Contestant 77</v>
+        <v>Lydia Torres</v>
       </c>
       <c r="C134">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D134" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E134" t="str">
-        <v>test.contestant.77@gmail.com</v>
+        <v>lydia.torres72@yahoo.com</v>
       </c>
       <c r="F134" t="str">
-        <v>(555) 539-1001</v>
+        <v>(828) 773-4386</v>
       </c>
       <c r="G134" t="str">
-        <v>Bakersfield</v>
+        <v>Anaheim</v>
       </c>
       <c r="H134" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I134" t="str">
         <v>available</v>
+      </c>
+      <c r="J134" t="str">
+        <v>Avery Cruz, Mia Anderson</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>567e589d-b232-43c2-9d30-3ff1e359f372</v>
+        <v>53ee847e-7806-44ed-ba11-776baaf0214b</v>
       </c>
       <c r="B135" t="str">
-        <v>Hazel Mitchell</v>
+        <v>Test Contestant 77</v>
       </c>
       <c r="C135">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D135" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E135" t="str">
-        <v>hazel.mitchell91@gmail.com</v>
+        <v>test.contestant.77@gmail.com</v>
       </c>
       <c r="F135" t="str">
-        <v>0400 683 761</v>
+        <v>(555) 539-1001</v>
       </c>
       <c r="G135" t="str">
-        <v>Perth</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H135" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I135" t="str">
         <v>available</v>
-      </c>
-      <c r="J135" t="str">
-        <v>Caroline Taylor</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>d4340206-46f8-4128-a64d-b1a7ca7bbdb5</v>
+        <v>567e589d-b232-43c2-9d30-3ff1e359f372</v>
       </c>
       <c r="B136" t="str">
-        <v>Serenity Campbell</v>
+        <v>Hazel Mitchell</v>
       </c>
       <c r="C136">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D136" t="str">
         <v>Female</v>
       </c>
       <c r="E136" t="str">
-        <v>serenity.campbell1@yahoo.com</v>
+        <v>hazel.mitchell91@gmail.com</v>
       </c>
       <c r="F136" t="str">
-        <v>(479) 565-5966</v>
+        <v>0400 683 761</v>
       </c>
       <c r="G136" t="str">
-        <v>Irvine</v>
+        <v>Perth</v>
       </c>
       <c r="H136" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I136" t="str">
         <v>available</v>
       </c>
       <c r="J136" t="str">
-        <v>Jackson Jackson, Isaiah Green</v>
+        <v>Caroline Taylor</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>b498fd02-c816-4b07-976f-1100495bf38b</v>
+        <v>d4340206-46f8-4128-a64d-b1a7ca7bbdb5</v>
       </c>
       <c r="B137" t="str">
-        <v>Valentina Morales</v>
+        <v>Serenity Campbell</v>
       </c>
       <c r="C137">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D137" t="str">
         <v>Female</v>
       </c>
       <c r="E137" t="str">
-        <v>valentina.morales27@icloud.com</v>
+        <v>serenity.campbell1@yahoo.com</v>
       </c>
       <c r="F137" t="str">
-        <v>(896) 204-3978</v>
+        <v>(479) 565-5966</v>
       </c>
       <c r="G137" t="str">
-        <v>San Jose</v>
+        <v>Irvine</v>
       </c>
       <c r="H137" t="str">
         <v>B+</v>
@@ -5036,56 +5046,59 @@
         <v>available</v>
       </c>
       <c r="J137" t="str">
-        <v>Adam Hall, Grayson Morgan</v>
+        <v>Jackson Jackson, Isaiah Green</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>0dfbc11c-2318-45b7-9411-3c9aa9b41af3</v>
+        <v>b498fd02-c816-4b07-976f-1100495bf38b</v>
       </c>
       <c r="B138" t="str">
-        <v>Test Contestant 78</v>
+        <v>Valentina Morales</v>
       </c>
       <c r="C138">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D138" t="str">
         <v>Female</v>
       </c>
       <c r="E138" t="str">
-        <v>test.contestant.78@gmail.com</v>
+        <v>valentina.morales27@icloud.com</v>
       </c>
       <c r="F138" t="str">
-        <v>(555) 546-1014</v>
+        <v>(896) 204-3978</v>
       </c>
       <c r="G138" t="str">
-        <v>Anaheim</v>
+        <v>San Jose</v>
       </c>
       <c r="H138" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I138" t="str">
         <v>available</v>
+      </c>
+      <c r="J138" t="str">
+        <v>Adam Hall, Grayson Morgan</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>9f873871-29cc-45f0-894c-c54745230689</v>
+        <v>0dfbc11c-2318-45b7-9411-3c9aa9b41af3</v>
       </c>
       <c r="B139" t="str">
-        <v>Sadie Wright</v>
+        <v>Test Contestant 78</v>
       </c>
       <c r="C139">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D139" t="str">
         <v>Female</v>
       </c>
       <c r="E139" t="str">
-        <v>sadie.wright75@hotmail.com</v>
+        <v>test.contestant.78@gmail.com</v>
       </c>
       <c r="F139" t="str">
-        <v>(617) 145-9784</v>
+        <v>(555) 546-1014</v>
       </c>
       <c r="G139" t="str">
         <v>Anaheim</v>
@@ -5099,28 +5112,28 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>24928131-51b3-46f8-b43f-2cf989696f62</v>
+        <v>9f873871-29cc-45f0-894c-c54745230689</v>
       </c>
       <c r="B140" t="str">
-        <v>Amelia Garcia</v>
+        <v>Sadie Wright</v>
       </c>
       <c r="C140">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D140" t="str">
         <v>Female</v>
       </c>
       <c r="E140" t="str">
-        <v>amelia.garcia16@gmail.com</v>
+        <v>sadie.wright75@hotmail.com</v>
       </c>
       <c r="F140" t="str">
-        <v>(331) 367-3904</v>
+        <v>(617) 145-9784</v>
       </c>
       <c r="G140" t="str">
         <v>Anaheim</v>
       </c>
       <c r="H140" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I140" t="str">
         <v>available</v>
@@ -5128,121 +5141,121 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>94d903d4-dbc0-4052-87a8-ca32773ca839</v>
+        <v>24928131-51b3-46f8-b43f-2cf989696f62</v>
       </c>
       <c r="B141" t="str">
-        <v>Hannah Jones</v>
+        <v>Amelia Garcia</v>
       </c>
       <c r="C141">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D141" t="str">
         <v>Female</v>
       </c>
       <c r="E141" t="str">
-        <v>hannah.jones85@yahoo.com</v>
+        <v>amelia.garcia16@gmail.com</v>
       </c>
       <c r="F141" t="str">
-        <v>(644) 877-6251</v>
+        <v>(331) 367-3904</v>
       </c>
       <c r="G141" t="str">
-        <v>Sacramento</v>
+        <v>Anaheim</v>
       </c>
       <c r="H141" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I141" t="str">
         <v>available</v>
-      </c>
-      <c r="J141" t="str">
-        <v>Thomas Nguyen, Henry Roberts</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>3dcd887e-9357-49a1-be20-96ba912e33bf</v>
+        <v>94d903d4-dbc0-4052-87a8-ca32773ca839</v>
       </c>
       <c r="B142" t="str">
-        <v>Cora Mitchell</v>
+        <v>Hannah Jones</v>
       </c>
       <c r="C142">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D142" t="str">
         <v>Female</v>
       </c>
       <c r="E142" t="str">
-        <v>cora.mitchell80@icloud.com</v>
+        <v>hannah.jones85@yahoo.com</v>
       </c>
       <c r="F142" t="str">
-        <v>(929) 139-3875</v>
+        <v>(644) 877-6251</v>
       </c>
       <c r="G142" t="str">
-        <v>Newport Beach</v>
+        <v>Sacramento</v>
       </c>
       <c r="H142" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I142" t="str">
         <v>available</v>
       </c>
       <c r="J142" t="str">
-        <v>Christopher Carter</v>
+        <v>Thomas Nguyen, Henry Roberts</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>04993d9a-3a65-4d61-a0c8-591aabb2e72c</v>
+        <v>3dcd887e-9357-49a1-be20-96ba912e33bf</v>
       </c>
       <c r="B143" t="str">
-        <v>Eliza Martinez</v>
+        <v>Cora Mitchell</v>
       </c>
       <c r="C143">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D143" t="str">
         <v>Female</v>
       </c>
       <c r="E143" t="str">
-        <v>eliza.martinez8@hotmail.com</v>
+        <v>cora.mitchell80@icloud.com</v>
       </c>
       <c r="F143" t="str">
-        <v>(881) 895-2168</v>
+        <v>(929) 139-3875</v>
       </c>
       <c r="G143" t="str">
-        <v>Torrance</v>
+        <v>Newport Beach</v>
       </c>
       <c r="H143" t="str">
         <v>B+</v>
       </c>
       <c r="I143" t="str">
         <v>available</v>
+      </c>
+      <c r="J143" t="str">
+        <v>Christopher Carter</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>0fa47948-ca05-48a1-917a-bce2c13237ed</v>
+        <v>04993d9a-3a65-4d61-a0c8-591aabb2e72c</v>
       </c>
       <c r="B144" t="str">
-        <v>Isabella Taylor</v>
+        <v>Eliza Martinez</v>
       </c>
       <c r="C144">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D144" t="str">
         <v>Female</v>
       </c>
       <c r="E144" t="str">
-        <v>isabella.taylor65@yahoo.com</v>
+        <v>eliza.martinez8@hotmail.com</v>
       </c>
       <c r="F144" t="str">
-        <v>(997) 957-4171</v>
+        <v>(881) 895-2168</v>
       </c>
       <c r="G144" t="str">
-        <v>Chula Vista</v>
+        <v>Torrance</v>
       </c>
       <c r="H144" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I144" t="str">
         <v>available</v>
@@ -5250,25 +5263,25 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>0d8894f6-9a60-421c-a7c0-144fe2f8c85f</v>
+        <v>0fa47948-ca05-48a1-917a-bce2c13237ed</v>
       </c>
       <c r="B145" t="str">
-        <v>Lydia Morris</v>
+        <v>Isabella Taylor</v>
       </c>
       <c r="C145">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D145" t="str">
         <v>Female</v>
       </c>
       <c r="E145" t="str">
-        <v>lydia.morris1@gmail.com</v>
+        <v>isabella.taylor65@yahoo.com</v>
       </c>
       <c r="F145" t="str">
-        <v>(565) 806-3217</v>
+        <v>(997) 957-4171</v>
       </c>
       <c r="G145" t="str">
-        <v>Burbank</v>
+        <v>Chula Vista</v>
       </c>
       <c r="H145" t="str">
         <v>A</v>
@@ -5276,92 +5289,89 @@
       <c r="I145" t="str">
         <v>available</v>
       </c>
-      <c r="J145" t="str">
-        <v>Logan Gomez</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>700fc657-988b-4d49-9814-25b1df35cefc</v>
+        <v>0d8894f6-9a60-421c-a7c0-144fe2f8c85f</v>
       </c>
       <c r="B146" t="str">
-        <v>Victoria Thompson</v>
+        <v>Lydia Morris</v>
       </c>
       <c r="C146">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D146" t="str">
         <v>Female</v>
       </c>
       <c r="E146" t="str">
-        <v>victoria.thompson68@yahoo.com</v>
+        <v>lydia.morris1@gmail.com</v>
       </c>
       <c r="F146" t="str">
-        <v>(793) 601-6884</v>
+        <v>(565) 806-3217</v>
       </c>
       <c r="G146" t="str">
-        <v>San Jose</v>
+        <v>Burbank</v>
       </c>
       <c r="H146" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I146" t="str">
         <v>available</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Logan Gomez</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>1c24b746-78a8-49cd-9c4d-3d22726dbc1b</v>
+        <v>700fc657-988b-4d49-9814-25b1df35cefc</v>
       </c>
       <c r="B147" t="str">
-        <v>Eleanor Hall</v>
+        <v>Victoria Thompson</v>
       </c>
       <c r="C147">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D147" t="str">
         <v>Female</v>
       </c>
       <c r="E147" t="str">
-        <v>eleanor.hall7@yahoo.com</v>
+        <v>victoria.thompson68@yahoo.com</v>
       </c>
       <c r="F147" t="str">
-        <v>(627) 443-5972</v>
+        <v>(793) 601-6884</v>
       </c>
       <c r="G147" t="str">
-        <v>Stockton</v>
+        <v>San Jose</v>
       </c>
       <c r="H147" t="str">
         <v>B</v>
       </c>
       <c r="I147" t="str">
         <v>available</v>
-      </c>
-      <c r="J147" t="str">
-        <v>Michael Campbell, Sadie Williams</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>5addacf0-a31c-4412-982a-3f0d8f1c6d07</v>
+        <v>1c24b746-78a8-49cd-9c4d-3d22726dbc1b</v>
       </c>
       <c r="B148" t="str">
-        <v>Layla Lopez</v>
+        <v>Eleanor Hall</v>
       </c>
       <c r="C148">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D148" t="str">
         <v>Female</v>
       </c>
       <c r="E148" t="str">
-        <v>layla.lopez23@yahoo.com</v>
+        <v>eleanor.hall7@yahoo.com</v>
       </c>
       <c r="F148" t="str">
-        <v>(607) 496-6102</v>
+        <v>(627) 443-5972</v>
       </c>
       <c r="G148" t="str">
-        <v>Los Angeles</v>
+        <v>Stockton</v>
       </c>
       <c r="H148" t="str">
         <v>B</v>
@@ -5370,30 +5380,30 @@
         <v>available</v>
       </c>
       <c r="J148" t="str">
-        <v>Cora Lee</v>
+        <v>Michael Campbell, Sadie Williams</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>f6a281bb-caec-44cf-a596-a6e92d6e2610</v>
+        <v>5addacf0-a31c-4412-982a-3f0d8f1c6d07</v>
       </c>
       <c r="B149" t="str">
-        <v>Leah Scott</v>
+        <v>Layla Lopez</v>
       </c>
       <c r="C149">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D149" t="str">
         <v>Female</v>
       </c>
       <c r="E149" t="str">
-        <v>leah.scott74@gmail.com</v>
+        <v>layla.lopez23@yahoo.com</v>
       </c>
       <c r="F149" t="str">
-        <v>0402 414 358</v>
+        <v>(607) 496-6102</v>
       </c>
       <c r="G149" t="str">
-        <v>Perth</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H149" t="str">
         <v>B</v>
@@ -5402,65 +5412,68 @@
         <v>available</v>
       </c>
       <c r="J149" t="str">
-        <v>Harper Sanchez</v>
-      </c>
-      <c r="M149" t="str">
-        <v>Limited mobility - prefers ground floor seating</v>
+        <v>Cora Lee</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>fec80989-ab0f-471a-a4de-6c207e334f80</v>
+        <v>f6a281bb-caec-44cf-a596-a6e92d6e2610</v>
       </c>
       <c r="B150" t="str">
-        <v>Eliza Rivera</v>
+        <v>Leah Scott</v>
       </c>
       <c r="C150">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D150" t="str">
         <v>Female</v>
       </c>
       <c r="E150" t="str">
-        <v>eliza.rivera29@yahoo.com</v>
+        <v>leah.scott74@gmail.com</v>
       </c>
       <c r="F150" t="str">
-        <v>(836) 154-6362</v>
+        <v>0402 414 358</v>
       </c>
       <c r="G150" t="str">
-        <v>Newport Beach</v>
+        <v>Perth</v>
       </c>
       <c r="H150" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I150" t="str">
         <v>available</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Harper Sanchez</v>
+      </c>
+      <c r="M150" t="str">
+        <v>Limited mobility - prefers ground floor seating</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>b8042508-0f64-416b-b67c-10b2290d8cf6</v>
+        <v>fec80989-ab0f-471a-a4de-6c207e334f80</v>
       </c>
       <c r="B151" t="str">
-        <v>Test Contestant 79</v>
+        <v>Eliza Rivera</v>
       </c>
       <c r="C151">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D151" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E151" t="str">
-        <v>test.contestant.79@gmail.com</v>
+        <v>eliza.rivera29@yahoo.com</v>
       </c>
       <c r="F151" t="str">
-        <v>(555) 553-1027</v>
+        <v>(836) 154-6362</v>
       </c>
       <c r="G151" t="str">
-        <v>Santa Ana</v>
+        <v>Newport Beach</v>
       </c>
       <c r="H151" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I151" t="str">
         <v>available</v>
@@ -5468,28 +5481,28 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>63e94439-aec8-418c-8b69-f213ab7536a7</v>
+        <v>b8042508-0f64-416b-b67c-10b2290d8cf6</v>
       </c>
       <c r="B152" t="str">
-        <v>Test Contestant 80</v>
+        <v>Test Contestant 79</v>
       </c>
       <c r="C152">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D152" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E152" t="str">
-        <v>test.contestant.80@gmail.com</v>
+        <v>test.contestant.79@gmail.com</v>
       </c>
       <c r="F152" t="str">
-        <v>(555) 560-1040</v>
+        <v>(555) 553-1027</v>
       </c>
       <c r="G152" t="str">
-        <v>Los Angeles</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H152" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I152" t="str">
         <v>available</v>
@@ -5497,147 +5510,147 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>a614b69c-4f6c-49fa-a490-24d7e4a60da9</v>
+        <v>63e94439-aec8-418c-8b69-f213ab7536a7</v>
       </c>
       <c r="B153" t="str">
-        <v>Nora Lee</v>
+        <v>Test Contestant 80</v>
       </c>
       <c r="C153">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D153" t="str">
         <v>Female</v>
       </c>
       <c r="E153" t="str">
-        <v>nora.lee56@hotmail.com</v>
+        <v>test.contestant.80@gmail.com</v>
       </c>
       <c r="F153" t="str">
-        <v>(171) 825-3697</v>
+        <v>(555) 560-1040</v>
       </c>
       <c r="G153" t="str">
-        <v>Pasadena</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H153" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I153" t="str">
         <v>available</v>
-      </c>
-      <c r="J153" t="str">
-        <v>Ella Gutierrez</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>d6c29b29-46c2-458d-9ed6-9955afb17b95</v>
+        <v>a614b69c-4f6c-49fa-a490-24d7e4a60da9</v>
       </c>
       <c r="B154" t="str">
-        <v>Ethan Taylor</v>
+        <v>Nora Lee</v>
       </c>
       <c r="C154">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D154" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E154" t="str">
-        <v>ethan.taylor22@yahoo.com</v>
+        <v>nora.lee56@hotmail.com</v>
       </c>
       <c r="F154" t="str">
-        <v>0410 363 173</v>
+        <v>(171) 825-3697</v>
       </c>
       <c r="G154" t="str">
-        <v>Adelaide</v>
+        <v>Pasadena</v>
       </c>
       <c r="H154" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I154" t="str">
         <v>available</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Ella Gutierrez</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>81759c6b-da11-4c0e-9e96-92aa20964b06</v>
+        <v>d6c29b29-46c2-458d-9ed6-9955afb17b95</v>
       </c>
       <c r="B155" t="str">
-        <v>Cora Roberts</v>
+        <v>Ethan Taylor</v>
       </c>
       <c r="C155">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D155" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E155" t="str">
-        <v>cora.roberts57@hotmail.com</v>
+        <v>ethan.taylor22@yahoo.com</v>
       </c>
       <c r="F155" t="str">
-        <v>(141) 743-6838</v>
+        <v>0410 363 173</v>
       </c>
       <c r="G155" t="str">
-        <v>Bakersfield</v>
+        <v>Adelaide</v>
       </c>
       <c r="H155" t="str">
         <v>B</v>
       </c>
       <c r="I155" t="str">
         <v>available</v>
-      </c>
-      <c r="J155" t="str">
-        <v>Isla Wright, Naomi Moore</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>0617e7d4-564d-4f00-a0e5-951fa17268be</v>
+        <v>81759c6b-da11-4c0e-9e96-92aa20964b06</v>
       </c>
       <c r="B156" t="str">
-        <v>Test Contestant 81</v>
+        <v>Cora Roberts</v>
       </c>
       <c r="C156">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D156" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E156" t="str">
-        <v>test.contestant.81@gmail.com</v>
+        <v>cora.roberts57@hotmail.com</v>
       </c>
       <c r="F156" t="str">
-        <v>(555) 567-1053</v>
+        <v>(141) 743-6838</v>
       </c>
       <c r="G156" t="str">
-        <v>San Diego</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H156" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I156" t="str">
         <v>available</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Isla Wright, Naomi Moore</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>e2890ff0-278a-41f9-bdb3-43f63398fbb7</v>
+        <v>0617e7d4-564d-4f00-a0e5-951fa17268be</v>
       </c>
       <c r="B157" t="str">
-        <v>Test Contestant 82</v>
+        <v>Test Contestant 81</v>
       </c>
       <c r="C157">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D157" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E157" t="str">
-        <v>test.contestant.82@gmail.com</v>
+        <v>test.contestant.81@gmail.com</v>
       </c>
       <c r="F157" t="str">
-        <v>(555) 574-1066</v>
+        <v>(555) 567-1053</v>
       </c>
       <c r="G157" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H157" t="str">
         <v>B+</v>
@@ -5648,28 +5661,28 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>02c8a73b-48fe-4228-9ee0-44489b6682b3</v>
+        <v>e2890ff0-278a-41f9-bdb3-43f63398fbb7</v>
       </c>
       <c r="B158" t="str">
-        <v>Test Contestant 83</v>
+        <v>Test Contestant 82</v>
       </c>
       <c r="C158">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D158" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E158" t="str">
-        <v>test.contestant.83@gmail.com</v>
+        <v>test.contestant.82@gmail.com</v>
       </c>
       <c r="F158" t="str">
-        <v>(555) 581-1079</v>
+        <v>(555) 574-1066</v>
       </c>
       <c r="G158" t="str">
-        <v>Sacramento</v>
+        <v>San Francisco</v>
       </c>
       <c r="H158" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I158" t="str">
         <v>available</v>
@@ -5677,211 +5690,211 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>d3db689e-5aed-4049-9588-adf3d1a49ae0</v>
+        <v>02c8a73b-48fe-4228-9ee0-44489b6682b3</v>
       </c>
       <c r="B159" t="str">
-        <v>Madelyn Martinez</v>
+        <v>Test Contestant 83</v>
       </c>
       <c r="C159">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D159" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E159" t="str">
-        <v>madelyn.martinez94@gmail.com</v>
+        <v>test.contestant.83@gmail.com</v>
       </c>
       <c r="F159" t="str">
-        <v>(576) 468-3300</v>
+        <v>(555) 581-1079</v>
       </c>
       <c r="G159" t="str">
-        <v>Pasadena</v>
+        <v>Sacramento</v>
       </c>
       <c r="H159" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I159" t="str">
         <v>available</v>
-      </c>
-      <c r="J159" t="str">
-        <v>Olivia Nelson, Joseph Stewart</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>ad836319-db56-4a08-bca6-a8e3f19c37a8</v>
+        <v>d3db689e-5aed-4049-9588-adf3d1a49ae0</v>
       </c>
       <c r="B160" t="str">
-        <v>Emily Johnson</v>
+        <v>Madelyn Martinez</v>
       </c>
       <c r="C160">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D160" t="str">
         <v>Female</v>
       </c>
       <c r="E160" t="str">
-        <v>emily.johnson58@hotmail.com</v>
+        <v>madelyn.martinez94@gmail.com</v>
       </c>
       <c r="F160" t="str">
-        <v>0412 663 939</v>
+        <v>(576) 468-3300</v>
       </c>
       <c r="G160" t="str">
-        <v>Perth</v>
+        <v>Pasadena</v>
       </c>
       <c r="H160" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I160" t="str">
         <v>available</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Olivia Nelson, Joseph Stewart</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>e2f70c5c-0a8d-4055-8281-2ad2ae2e0cd6</v>
+        <v>ad836319-db56-4a08-bca6-a8e3f19c37a8</v>
       </c>
       <c r="B161" t="str">
-        <v>Stella Green</v>
+        <v>Emily Johnson</v>
       </c>
       <c r="C161">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D161" t="str">
         <v>Female</v>
       </c>
       <c r="E161" t="str">
-        <v>stella.green92@gmail.com</v>
+        <v>emily.johnson58@hotmail.com</v>
       </c>
       <c r="F161" t="str">
-        <v>0404 230 858</v>
+        <v>0412 663 939</v>
       </c>
       <c r="G161" t="str">
-        <v>Wollongong</v>
+        <v>Perth</v>
       </c>
       <c r="H161" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I161" t="str">
         <v>available</v>
-      </c>
-      <c r="J161" t="str">
-        <v>Everly Torres</v>
-      </c>
-      <c r="M161" t="str">
-        <v>Vision impaired - needs assistance</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>8774a9f4-b951-41cc-b6bd-809a709cb6ea</v>
+        <v>e2f70c5c-0a8d-4055-8281-2ad2ae2e0cd6</v>
       </c>
       <c r="B162" t="str">
-        <v>Lily Walker</v>
+        <v>Stella Green</v>
       </c>
       <c r="C162">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D162" t="str">
         <v>Female</v>
       </c>
       <c r="E162" t="str">
-        <v>lily.walker96@outlook.com</v>
+        <v>stella.green92@gmail.com</v>
       </c>
       <c r="F162" t="str">
-        <v>0410 155 426</v>
+        <v>0404 230 858</v>
       </c>
       <c r="G162" t="str">
-        <v>Hobart</v>
+        <v>Wollongong</v>
       </c>
       <c r="H162" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I162" t="str">
         <v>available</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Everly Torres</v>
+      </c>
+      <c r="M162" t="str">
+        <v>Vision impaired - needs assistance</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>e15c67b6-0680-4284-a8aa-a525b34c592d</v>
+        <v>8774a9f4-b951-41cc-b6bd-809a709cb6ea</v>
       </c>
       <c r="B163" t="str">
-        <v>Aurora Williams</v>
+        <v>Lily Walker</v>
       </c>
       <c r="C163">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D163" t="str">
         <v>Female</v>
       </c>
       <c r="E163" t="str">
-        <v>aurora.williams76@outlook.com</v>
+        <v>lily.walker96@outlook.com</v>
       </c>
       <c r="F163" t="str">
-        <v>0401 416 170</v>
+        <v>0410 155 426</v>
       </c>
       <c r="G163" t="str">
-        <v>Darwin</v>
+        <v>Hobart</v>
       </c>
       <c r="H163" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I163" t="str">
         <v>available</v>
-      </c>
-      <c r="M163" t="str">
-        <v>Uses walking cane</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>bf5a6984-f656-4e23-9646-85829e9daffe</v>
+        <v>e15c67b6-0680-4284-a8aa-a525b34c592d</v>
       </c>
       <c r="B164" t="str">
-        <v>Scarlett Lopez</v>
+        <v>Aurora Williams</v>
       </c>
       <c r="C164">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D164" t="str">
         <v>Female</v>
       </c>
       <c r="E164" t="str">
-        <v>scarlett.lopez53@yahoo.com</v>
+        <v>aurora.williams76@outlook.com</v>
       </c>
       <c r="F164" t="str">
-        <v>0400 509 641</v>
+        <v>0401 416 170</v>
       </c>
       <c r="G164" t="str">
-        <v>Sydney</v>
+        <v>Darwin</v>
       </c>
       <c r="H164" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I164" t="str">
         <v>available</v>
+      </c>
+      <c r="M164" t="str">
+        <v>Uses walking cane</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>e166fd4f-73eb-4bea-b8be-3acdee4f9fdc</v>
+        <v>bf5a6984-f656-4e23-9646-85829e9daffe</v>
       </c>
       <c r="B165" t="str">
-        <v>Liam Lewis</v>
+        <v>Scarlett Lopez</v>
       </c>
       <c r="C165">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D165" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E165" t="str">
-        <v>liam.lewis79@yahoo.com</v>
+        <v>scarlett.lopez53@yahoo.com</v>
       </c>
       <c r="F165" t="str">
-        <v>0404 203 198</v>
+        <v>0400 509 641</v>
       </c>
       <c r="G165" t="str">
-        <v>Hobart</v>
+        <v>Sydney</v>
       </c>
       <c r="H165" t="str">
         <v>B+</v>
@@ -5892,28 +5905,28 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>6ddd3228-f125-4d3e-88e2-157cd730b552</v>
+        <v>e166fd4f-73eb-4bea-b8be-3acdee4f9fdc</v>
       </c>
       <c r="B166" t="str">
-        <v>Theodore Nelson</v>
+        <v>Liam Lewis</v>
       </c>
       <c r="C166">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D166" t="str">
         <v>Male</v>
       </c>
       <c r="E166" t="str">
-        <v>theodore.nelson79@gmail.com</v>
+        <v>liam.lewis79@yahoo.com</v>
       </c>
       <c r="F166" t="str">
-        <v>0403 813 793</v>
+        <v>0404 203 198</v>
       </c>
       <c r="G166" t="str">
-        <v>Canberra</v>
+        <v>Hobart</v>
       </c>
       <c r="H166" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I166" t="str">
         <v>available</v>
@@ -5921,25 +5934,25 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>adb0c362-d095-4bfd-98dc-c93920fd22d6</v>
+        <v>6ddd3228-f125-4d3e-88e2-157cd730b552</v>
       </c>
       <c r="B167" t="str">
-        <v>Victoria Torres</v>
+        <v>Theodore Nelson</v>
       </c>
       <c r="C167">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D167" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E167" t="str">
-        <v>victoria.torres48@outlook.com</v>
+        <v>theodore.nelson79@gmail.com</v>
       </c>
       <c r="F167" t="str">
-        <v>0411 539 271</v>
+        <v>0403 813 793</v>
       </c>
       <c r="G167" t="str">
-        <v>Geelong</v>
+        <v>Canberra</v>
       </c>
       <c r="H167" t="str">
         <v>B</v>
@@ -5950,25 +5963,25 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>0e8f635e-8f06-4224-a2cc-4263ac307ba2</v>
+        <v>adb0c362-d095-4bfd-98dc-c93920fd22d6</v>
       </c>
       <c r="B168" t="str">
-        <v>Joshua Jones</v>
+        <v>Victoria Torres</v>
       </c>
       <c r="C168">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D168" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E168" t="str">
-        <v>joshua.jones82@yahoo.com</v>
+        <v>victoria.torres48@outlook.com</v>
       </c>
       <c r="F168" t="str">
-        <v>0400 652 840</v>
+        <v>0411 539 271</v>
       </c>
       <c r="G168" t="str">
-        <v>Toowoomba</v>
+        <v>Geelong</v>
       </c>
       <c r="H168" t="str">
         <v>B</v>
@@ -5979,25 +5992,25 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>40727c14-a30e-4e3b-8b64-0359d25efc0c</v>
+        <v>0e8f635e-8f06-4224-a2cc-4263ac307ba2</v>
       </c>
       <c r="B169" t="str">
-        <v>Joshua Scott</v>
+        <v>Joshua Jones</v>
       </c>
       <c r="C169">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D169" t="str">
         <v>Male</v>
       </c>
       <c r="E169" t="str">
-        <v>joshua.scott95@outlook.com</v>
+        <v>joshua.jones82@yahoo.com</v>
       </c>
       <c r="F169" t="str">
-        <v>0410 137 561</v>
+        <v>0400 652 840</v>
       </c>
       <c r="G169" t="str">
-        <v>Canberra</v>
+        <v>Toowoomba</v>
       </c>
       <c r="H169" t="str">
         <v>B</v>
@@ -6008,25 +6021,25 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>d7b0dd51-8aea-4b32-bb8d-8b60271fc6c9</v>
+        <v>40727c14-a30e-4e3b-8b64-0359d25efc0c</v>
       </c>
       <c r="B170" t="str">
-        <v>Jayden Nguyen</v>
+        <v>Joshua Scott</v>
       </c>
       <c r="C170">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D170" t="str">
         <v>Male</v>
       </c>
       <c r="E170" t="str">
-        <v>jayden.nguyen88@hotmail.com</v>
+        <v>joshua.scott95@outlook.com</v>
       </c>
       <c r="F170" t="str">
-        <v>0401 108 628</v>
+        <v>0410 137 561</v>
       </c>
       <c r="G170" t="str">
-        <v>Hobart</v>
+        <v>Canberra</v>
       </c>
       <c r="H170" t="str">
         <v>B</v>
@@ -6037,57 +6050,54 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>c1783cdf-a656-46b4-9331-4d9d18d40b51</v>
+        <v>d7b0dd51-8aea-4b32-bb8d-8b60271fc6c9</v>
       </c>
       <c r="B171" t="str">
-        <v>Aurora Walker</v>
+        <v>Jayden Nguyen</v>
       </c>
       <c r="C171">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D171" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E171" t="str">
-        <v>aurora.walker1@outlook.com</v>
+        <v>jayden.nguyen88@hotmail.com</v>
       </c>
       <c r="F171" t="str">
-        <v>0403 522 404</v>
+        <v>0401 108 628</v>
       </c>
       <c r="G171" t="str">
-        <v>Darwin</v>
+        <v>Hobart</v>
       </c>
       <c r="H171" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I171" t="str">
         <v>available</v>
-      </c>
-      <c r="M171" t="str">
-        <v>Vision impaired - needs assistance</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>5e93a4d1-9d7c-4b53-9898-a1ae2a0319c1</v>
+        <v>c1783cdf-a656-46b4-9331-4d9d18d40b51</v>
       </c>
       <c r="B172" t="str">
-        <v>Amelia Nguyen</v>
+        <v>Aurora Walker</v>
       </c>
       <c r="C172">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D172" t="str">
         <v>Female</v>
       </c>
       <c r="E172" t="str">
-        <v>amelia.nguyen43@outlook.com</v>
+        <v>aurora.walker1@outlook.com</v>
       </c>
       <c r="F172" t="str">
-        <v>(164) 220-7002</v>
+        <v>0403 522 404</v>
       </c>
       <c r="G172" t="str">
-        <v>Sacramento</v>
+        <v>Darwin</v>
       </c>
       <c r="H172" t="str">
         <v>B+</v>
@@ -6095,60 +6105,63 @@
       <c r="I172" t="str">
         <v>available</v>
       </c>
-      <c r="J172" t="str">
-        <v>Paisley Brown</v>
+      <c r="M172" t="str">
+        <v>Vision impaired - needs assistance</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>418f2e6f-57a6-4a4c-a386-eb9409ae0a84</v>
+        <v>5e93a4d1-9d7c-4b53-9898-a1ae2a0319c1</v>
       </c>
       <c r="B173" t="str">
-        <v>Test Contestant 84</v>
+        <v>Amelia Nguyen</v>
       </c>
       <c r="C173">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D173" t="str">
         <v>Female</v>
       </c>
       <c r="E173" t="str">
-        <v>test.contestant.84@gmail.com</v>
+        <v>amelia.nguyen43@outlook.com</v>
       </c>
       <c r="F173" t="str">
-        <v>(555) 588-1092</v>
+        <v>(164) 220-7002</v>
       </c>
       <c r="G173" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H173" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I173" t="str">
         <v>available</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Paisley Brown</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>59bae9a1-93b9-471d-a2b7-074918634f6b</v>
+        <v>418f2e6f-57a6-4a4c-a386-eb9409ae0a84</v>
       </c>
       <c r="B174" t="str">
-        <v>Joshua Clark</v>
+        <v>Test Contestant 84</v>
       </c>
       <c r="C174">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D174" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E174" t="str">
-        <v>joshua.clark16@outlook.com</v>
+        <v>test.contestant.84@gmail.com</v>
       </c>
       <c r="F174" t="str">
-        <v>0403 901 485</v>
+        <v>(555) 588-1092</v>
       </c>
       <c r="G174" t="str">
-        <v>Sydney</v>
+        <v>Fresno</v>
       </c>
       <c r="H174" t="str">
         <v>B</v>
@@ -6159,25 +6172,25 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>ef94ff15-5215-4ecd-9ad1-9ac44fd0e56a</v>
+        <v>59bae9a1-93b9-471d-a2b7-074918634f6b</v>
       </c>
       <c r="B175" t="str">
-        <v>Luke Flores</v>
+        <v>Joshua Clark</v>
       </c>
       <c r="C175">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D175" t="str">
         <v>Male</v>
       </c>
       <c r="E175" t="str">
-        <v>luke.flores39@hotmail.com</v>
+        <v>joshua.clark16@outlook.com</v>
       </c>
       <c r="F175" t="str">
-        <v>0403 225 544</v>
+        <v>0403 901 485</v>
       </c>
       <c r="G175" t="str">
-        <v>Melbourne</v>
+        <v>Sydney</v>
       </c>
       <c r="H175" t="str">
         <v>B</v>
@@ -6188,25 +6201,25 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>1bc2ade3-8640-4045-bdfd-aa318c5df6ae</v>
+        <v>ef94ff15-5215-4ecd-9ad1-9ac44fd0e56a</v>
       </c>
       <c r="B176" t="str">
-        <v>Test Contestant 85</v>
+        <v>Luke Flores</v>
       </c>
       <c r="C176">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D176" t="str">
         <v>Male</v>
       </c>
       <c r="E176" t="str">
-        <v>test.contestant.85@gmail.com</v>
+        <v>luke.flores39@hotmail.com</v>
       </c>
       <c r="F176" t="str">
-        <v>(555) 595-1105</v>
+        <v>0403 225 544</v>
       </c>
       <c r="G176" t="str">
-        <v>Oakland</v>
+        <v>Melbourne</v>
       </c>
       <c r="H176" t="str">
         <v>B</v>
@@ -6217,25 +6230,25 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>2811bf99-369b-4c0a-b5d6-4ff46cd7aa5e</v>
+        <v>1bc2ade3-8640-4045-bdfd-aa318c5df6ae</v>
       </c>
       <c r="B177" t="str">
-        <v>Lucas Thomas</v>
+        <v>Test Contestant 85</v>
       </c>
       <c r="C177">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D177" t="str">
         <v>Male</v>
       </c>
       <c r="E177" t="str">
-        <v>lucas.thomas30@yahoo.com</v>
+        <v>test.contestant.85@gmail.com</v>
       </c>
       <c r="F177" t="str">
-        <v>0412 527 117</v>
+        <v>(555) 595-1105</v>
       </c>
       <c r="G177" t="str">
-        <v>Brisbane</v>
+        <v>Oakland</v>
       </c>
       <c r="H177" t="str">
         <v>B</v>
@@ -6246,25 +6259,25 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>45c0fc2b-415d-475a-998d-934235565d6b</v>
+        <v>2811bf99-369b-4c0a-b5d6-4ff46cd7aa5e</v>
       </c>
       <c r="B178" t="str">
-        <v>Scarlett Wright</v>
+        <v>Lucas Thomas</v>
       </c>
       <c r="C178">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D178" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E178" t="str">
-        <v>scarlett.wright68@outlook.com</v>
+        <v>lucas.thomas30@yahoo.com</v>
       </c>
       <c r="F178" t="str">
-        <v>0412 487 763</v>
+        <v>0412 527 117</v>
       </c>
       <c r="G178" t="str">
-        <v>Newcastle</v>
+        <v>Brisbane</v>
       </c>
       <c r="H178" t="str">
         <v>B</v>
@@ -6275,95 +6288,95 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>d698b1de-6641-45c6-aa63-f577d2b634bb</v>
+        <v>45c0fc2b-415d-475a-998d-934235565d6b</v>
       </c>
       <c r="B179" t="str">
-        <v>Kathleen Reynolds</v>
+        <v>Scarlett Wright</v>
       </c>
       <c r="C179">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D179" t="str">
-        <v>Not Specified</v>
+        <v>Female</v>
       </c>
       <c r="E179" t="str">
-        <v>kathleenmonicareynolds@gmail.com</v>
+        <v>scarlett.wright68@outlook.com</v>
       </c>
       <c r="F179" t="str">
-        <v>498086080</v>
+        <v>0412 487 763</v>
       </c>
       <c r="G179" t="str">
-        <v>Footscray</v>
+        <v>Newcastle</v>
       </c>
       <c r="H179" t="str">
-        <v/>
+        <v>B</v>
       </c>
       <c r="I179" t="str">
         <v>available</v>
-      </c>
-      <c r="J179" t="str">
-        <v>Peter Adamidis, Felicity Parker-Hill</v>
-      </c>
-      <c r="K179" t="str">
-        <v>5fe641da-4067-49a7-bae7-e63413b3e404</v>
-      </c>
-      <c r="L179" t="str">
-        <v>N</v>
-      </c>
-      <c r="M179" t="str">
-        <v>N/A</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>39b7a0a4-be8b-49f1-a5af-c5a105e0ab58</v>
+        <v>d698b1de-6641-45c6-aa63-f577d2b634bb</v>
       </c>
       <c r="B180" t="str">
-        <v>Joshua Carter</v>
+        <v>Kathleen Reynolds</v>
       </c>
       <c r="C180">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D180" t="str">
-        <v>Male</v>
+        <v>Not Specified</v>
       </c>
       <c r="E180" t="str">
-        <v>joshua.carter41@hotmail.com</v>
+        <v>kathleenmonicareynolds@gmail.com</v>
       </c>
       <c r="F180" t="str">
-        <v>0404 538 442</v>
+        <v>498086080</v>
       </c>
       <c r="G180" t="str">
-        <v>Wollongong</v>
+        <v>Footscray</v>
       </c>
       <c r="H180" t="str">
-        <v>B</v>
+        <v/>
       </c>
       <c r="I180" t="str">
         <v>available</v>
+      </c>
+      <c r="J180" t="str">
+        <v>Peter Adamidis, Felicity Parker-Hill</v>
+      </c>
+      <c r="K180" t="str">
+        <v>5fe641da-4067-49a7-bae7-e63413b3e404</v>
+      </c>
+      <c r="L180" t="str">
+        <v>N</v>
+      </c>
+      <c r="M180" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>a8fa9125-28f1-47e1-adba-784701975e68</v>
+        <v>39b7a0a4-be8b-49f1-a5af-c5a105e0ab58</v>
       </c>
       <c r="B181" t="str">
-        <v>Abigail Williams</v>
+        <v>Joshua Carter</v>
       </c>
       <c r="C181">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D181" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E181" t="str">
-        <v>abigail.williams45@yahoo.com</v>
+        <v>joshua.carter41@hotmail.com</v>
       </c>
       <c r="F181" t="str">
-        <v>0403 497 445</v>
+        <v>0404 538 442</v>
       </c>
       <c r="G181" t="str">
-        <v>Toowoomba</v>
+        <v>Wollongong</v>
       </c>
       <c r="H181" t="str">
         <v>B</v>
@@ -6374,28 +6387,28 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>7664257a-dce4-407a-8f24-692043d568be</v>
+        <v>a8fa9125-28f1-47e1-adba-784701975e68</v>
       </c>
       <c r="B182" t="str">
-        <v>Nora Jackson</v>
+        <v>Abigail Williams</v>
       </c>
       <c r="C182">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D182" t="str">
         <v>Female</v>
       </c>
       <c r="E182" t="str">
-        <v>nora.jackson83@hotmail.com</v>
+        <v>abigail.williams45@yahoo.com</v>
       </c>
       <c r="F182" t="str">
-        <v>0404 434 899</v>
+        <v>0403 497 445</v>
       </c>
       <c r="G182" t="str">
-        <v>Wollongong</v>
+        <v>Toowoomba</v>
       </c>
       <c r="H182" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I182" t="str">
         <v>available</v>
@@ -6403,25 +6416,25 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>df6c0d97-fd38-4b65-8765-b11a4939bd3b</v>
+        <v>7664257a-dce4-407a-8f24-692043d568be</v>
       </c>
       <c r="B183" t="str">
-        <v>Julian Rivera</v>
+        <v>Nora Jackson</v>
       </c>
       <c r="C183">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D183" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E183" t="str">
-        <v>julian.rivera31@outlook.com</v>
+        <v>nora.jackson83@hotmail.com</v>
       </c>
       <c r="F183" t="str">
-        <v>0401 414 502</v>
+        <v>0404 434 899</v>
       </c>
       <c r="G183" t="str">
-        <v>Perth</v>
+        <v>Wollongong</v>
       </c>
       <c r="H183" t="str">
         <v>B+</v>
@@ -6432,25 +6445,25 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>8956e289-91e9-4c15-bf2b-a13dee2fa476</v>
+        <v>df6c0d97-fd38-4b65-8765-b11a4939bd3b</v>
       </c>
       <c r="B184" t="str">
-        <v>Landon Wright</v>
+        <v>Julian Rivera</v>
       </c>
       <c r="C184">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D184" t="str">
         <v>Male</v>
       </c>
       <c r="E184" t="str">
-        <v>landon.wright36@outlook.com</v>
+        <v>julian.rivera31@outlook.com</v>
       </c>
       <c r="F184" t="str">
-        <v>0402 415 597</v>
+        <v>0401 414 502</v>
       </c>
       <c r="G184" t="str">
-        <v>Cairns</v>
+        <v>Perth</v>
       </c>
       <c r="H184" t="str">
         <v>B+</v>
@@ -6461,25 +6474,25 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>2fa810c7-61d0-4519-a314-824cf0873e30</v>
+        <v>8956e289-91e9-4c15-bf2b-a13dee2fa476</v>
       </c>
       <c r="B185" t="str">
-        <v>Theodore Allen</v>
+        <v>Landon Wright</v>
       </c>
       <c r="C185">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D185" t="str">
         <v>Male</v>
       </c>
       <c r="E185" t="str">
-        <v>theodore.allen25@outlook.com</v>
+        <v>landon.wright36@outlook.com</v>
       </c>
       <c r="F185" t="str">
-        <v>0400 438 819</v>
+        <v>0402 415 597</v>
       </c>
       <c r="G185" t="str">
-        <v>Newcastle</v>
+        <v>Cairns</v>
       </c>
       <c r="H185" t="str">
         <v>B+</v>
@@ -6490,121 +6503,121 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>5b3becf0-21ae-46a2-b70b-722762d230ff</v>
+        <v>2fa810c7-61d0-4519-a314-824cf0873e30</v>
       </c>
       <c r="B186" t="str">
-        <v>Evelyn Ortiz</v>
+        <v>Theodore Allen</v>
       </c>
       <c r="C186">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D186" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E186" t="str">
-        <v>evelyn.ortiz49@hotmail.com</v>
+        <v>theodore.allen25@outlook.com</v>
       </c>
       <c r="F186" t="str">
-        <v>(142) 759-4931</v>
+        <v>0400 438 819</v>
       </c>
       <c r="G186" t="str">
-        <v>Long Beach</v>
+        <v>Newcastle</v>
       </c>
       <c r="H186" t="str">
-        <v>A+</v>
+        <v>B+</v>
       </c>
       <c r="I186" t="str">
         <v>available</v>
-      </c>
-      <c r="J186" t="str">
-        <v>Mia Carter</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>b22d1d02-9344-4922-9be8-d8d05a79b0b0</v>
+        <v>5b3becf0-21ae-46a2-b70b-722762d230ff</v>
       </c>
       <c r="B187" t="str">
-        <v>Julian Nguyen</v>
+        <v>Evelyn Ortiz</v>
       </c>
       <c r="C187">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D187" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E187" t="str">
-        <v>julian.nguyen22@outlook.com</v>
+        <v>evelyn.ortiz49@hotmail.com</v>
       </c>
       <c r="F187" t="str">
-        <v>(382) 722-8118</v>
+        <v>(142) 759-4931</v>
       </c>
       <c r="G187" t="str">
         <v>Long Beach</v>
       </c>
       <c r="H187" t="str">
-        <v>B</v>
+        <v>A+</v>
       </c>
       <c r="I187" t="str">
         <v>available</v>
       </c>
       <c r="J187" t="str">
-        <v>Leah Diaz, Lydia Allen</v>
+        <v>Mia Carter</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>395b385e-b723-4e5e-ae0b-bedcb065931e</v>
+        <v>b22d1d02-9344-4922-9be8-d8d05a79b0b0</v>
       </c>
       <c r="B188" t="str">
-        <v>Test Contestant 86</v>
+        <v>Julian Nguyen</v>
       </c>
       <c r="C188">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D188" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E188" t="str">
-        <v>test.contestant.86@gmail.com</v>
+        <v>julian.nguyen22@outlook.com</v>
       </c>
       <c r="F188" t="str">
-        <v>(555) 602-1118</v>
+        <v>(382) 722-8118</v>
       </c>
       <c r="G188" t="str">
         <v>Long Beach</v>
       </c>
       <c r="H188" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I188" t="str">
         <v>available</v>
+      </c>
+      <c r="J188" t="str">
+        <v>Leah Diaz, Lydia Allen</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>cc9dcc8f-9593-4b7e-b4dd-723de93b6b04</v>
+        <v>395b385e-b723-4e5e-ae0b-bedcb065931e</v>
       </c>
       <c r="B189" t="str">
-        <v>Aiden Cook</v>
+        <v>Test Contestant 86</v>
       </c>
       <c r="C189">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D189" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E189" t="str">
-        <v>aiden.cook93@yahoo.com</v>
+        <v>test.contestant.86@gmail.com</v>
       </c>
       <c r="F189" t="str">
-        <v>(959) 986-7207</v>
+        <v>(555) 602-1118</v>
       </c>
       <c r="G189" t="str">
-        <v>Pomona</v>
+        <v>Long Beach</v>
       </c>
       <c r="H189" t="str">
-        <v>A+</v>
+        <v>B+</v>
       </c>
       <c r="I189" t="str">
         <v>available</v>
@@ -6612,28 +6625,28 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>14153d3f-36cb-428f-b6f4-b42597fae28a</v>
+        <v>cc9dcc8f-9593-4b7e-b4dd-723de93b6b04</v>
       </c>
       <c r="B190" t="str">
-        <v>Test Contestant 87</v>
+        <v>Aiden Cook</v>
       </c>
       <c r="C190">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D190" t="str">
         <v>Male</v>
       </c>
       <c r="E190" t="str">
-        <v>test.contestant.87@gmail.com</v>
+        <v>aiden.cook93@yahoo.com</v>
       </c>
       <c r="F190" t="str">
-        <v>(555) 609-1131</v>
+        <v>(959) 986-7207</v>
       </c>
       <c r="G190" t="str">
-        <v>Bakersfield</v>
+        <v>Pomona</v>
       </c>
       <c r="H190" t="str">
-        <v>B+</v>
+        <v>A+</v>
       </c>
       <c r="I190" t="str">
         <v>available</v>
@@ -6641,28 +6654,28 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>35dfd5bc-5bf2-4576-b279-afcbf6a8b090</v>
+        <v>14153d3f-36cb-428f-b6f4-b42597fae28a</v>
       </c>
       <c r="B191" t="str">
-        <v>Test Contestant 88</v>
+        <v>Test Contestant 87</v>
       </c>
       <c r="C191">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D191" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E191" t="str">
-        <v>test.contestant.88@gmail.com</v>
+        <v>test.contestant.87@gmail.com</v>
       </c>
       <c r="F191" t="str">
-        <v>(555) 616-1144</v>
+        <v>(555) 609-1131</v>
       </c>
       <c r="G191" t="str">
-        <v>Anaheim</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H191" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I191" t="str">
         <v>available</v>
@@ -6670,28 +6683,28 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>7a0a1a0e-a2dd-4f19-94ff-54601fcfb0e1</v>
+        <v>35dfd5bc-5bf2-4576-b279-afcbf6a8b090</v>
       </c>
       <c r="B192" t="str">
-        <v>Alexander Reyes</v>
+        <v>Test Contestant 88</v>
       </c>
       <c r="C192">
         <v>28</v>
       </c>
       <c r="D192" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E192" t="str">
-        <v>alexander.reyes92@icloud.com</v>
+        <v>test.contestant.88@gmail.com</v>
       </c>
       <c r="F192" t="str">
-        <v>(434) 933-1740</v>
+        <v>(555) 616-1144</v>
       </c>
       <c r="G192" t="str">
-        <v>Newport Beach</v>
+        <v>Anaheim</v>
       </c>
       <c r="H192" t="str">
-        <v>A+</v>
+        <v>A</v>
       </c>
       <c r="I192" t="str">
         <v>available</v>
@@ -6699,28 +6712,28 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>7e03dcdf-4f06-45bd-87f9-ef423cf4bf0f</v>
+        <v>7a0a1a0e-a2dd-4f19-94ff-54601fcfb0e1</v>
       </c>
       <c r="B193" t="str">
-        <v>Test Contestant 89</v>
+        <v>Alexander Reyes</v>
       </c>
       <c r="C193">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D193" t="str">
         <v>Male</v>
       </c>
       <c r="E193" t="str">
-        <v>test.contestant.89@gmail.com</v>
+        <v>alexander.reyes92@icloud.com</v>
       </c>
       <c r="F193" t="str">
-        <v>(555) 623-1157</v>
+        <v>(434) 933-1740</v>
       </c>
       <c r="G193" t="str">
-        <v>Santa Ana</v>
+        <v>Newport Beach</v>
       </c>
       <c r="H193" t="str">
-        <v>B</v>
+        <v>A+</v>
       </c>
       <c r="I193" t="str">
         <v>available</v>
@@ -6728,121 +6741,121 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>3f9d95b9-bedc-4620-9aa3-9bc8669de2af</v>
+        <v>7e03dcdf-4f06-45bd-87f9-ef423cf4bf0f</v>
       </c>
       <c r="B194" t="str">
-        <v>Christopher Allen</v>
+        <v>Test Contestant 89</v>
       </c>
       <c r="C194">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D194" t="str">
         <v>Male</v>
       </c>
       <c r="E194" t="str">
-        <v>christopher.allen60@yahoo.com</v>
+        <v>test.contestant.89@gmail.com</v>
       </c>
       <c r="F194" t="str">
-        <v>(529) 787-8147</v>
+        <v>(555) 623-1157</v>
       </c>
       <c r="G194" t="str">
-        <v>Torrance</v>
+        <v>Santa Ana</v>
       </c>
       <c r="H194" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I194" t="str">
         <v>available</v>
-      </c>
-      <c r="J194" t="str">
-        <v>Eleanor Allen</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>9e0ff879-df04-4a3f-b572-8633acb77cee</v>
+        <v>3f9d95b9-bedc-4620-9aa3-9bc8669de2af</v>
       </c>
       <c r="B195" t="str">
-        <v>Jackson Jackson</v>
+        <v>Christopher Allen</v>
       </c>
       <c r="C195">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D195" t="str">
         <v>Male</v>
       </c>
       <c r="E195" t="str">
-        <v>jackson.jackson86@icloud.com</v>
+        <v>christopher.allen60@yahoo.com</v>
       </c>
       <c r="F195" t="str">
-        <v>(858) 306-7989</v>
+        <v>(529) 787-8147</v>
       </c>
       <c r="G195" t="str">
-        <v>Oakland</v>
+        <v>Torrance</v>
       </c>
       <c r="H195" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I195" t="str">
         <v>available</v>
       </c>
       <c r="J195" t="str">
-        <v>Serenity Campbell, Isaiah Green</v>
+        <v>Eleanor Allen</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>c52bca5a-6a7f-4d77-9ec5-7859579e1c11</v>
+        <v>9e0ff879-df04-4a3f-b572-8633acb77cee</v>
       </c>
       <c r="B196" t="str">
-        <v>Test Contestant 90</v>
+        <v>Jackson Jackson</v>
       </c>
       <c r="C196">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D196" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E196" t="str">
-        <v>test.contestant.90@gmail.com</v>
+        <v>jackson.jackson86@icloud.com</v>
       </c>
       <c r="F196" t="str">
-        <v>(555) 630-1170</v>
+        <v>(858) 306-7989</v>
       </c>
       <c r="G196" t="str">
-        <v>Los Angeles</v>
+        <v>Oakland</v>
       </c>
       <c r="H196" t="str">
         <v>B</v>
       </c>
       <c r="I196" t="str">
         <v>available</v>
+      </c>
+      <c r="J196" t="str">
+        <v>Serenity Campbell, Isaiah Green</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>258eb0f3-5b73-4b6f-abb9-86c6ccb99d1f</v>
+        <v>c52bca5a-6a7f-4d77-9ec5-7859579e1c11</v>
       </c>
       <c r="B197" t="str">
-        <v>Mateo Phillips</v>
+        <v>Test Contestant 90</v>
       </c>
       <c r="C197">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D197" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E197" t="str">
-        <v>mateo.phillips59@outlook.com</v>
+        <v>test.contestant.90@gmail.com</v>
       </c>
       <c r="F197" t="str">
-        <v>(155) 680-1162</v>
+        <v>(555) 630-1170</v>
       </c>
       <c r="G197" t="str">
-        <v>Sacramento</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H197" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I197" t="str">
         <v>available</v>
@@ -6850,25 +6863,25 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>c2103c22-c825-4633-a461-495c55747ed3</v>
+        <v>258eb0f3-5b73-4b6f-abb9-86c6ccb99d1f</v>
       </c>
       <c r="B198" t="str">
-        <v>Alice Robinson</v>
+        <v>Mateo Phillips</v>
       </c>
       <c r="C198">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D198" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E198" t="str">
-        <v>alice.robinson56@hotmail.com</v>
+        <v>mateo.phillips59@outlook.com</v>
       </c>
       <c r="F198" t="str">
-        <v>(251) 325-5554</v>
+        <v>(155) 680-1162</v>
       </c>
       <c r="G198" t="str">
-        <v>Anaheim</v>
+        <v>Sacramento</v>
       </c>
       <c r="H198" t="str">
         <v>B+</v>
@@ -6879,89 +6892,86 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>4fba0674-c979-4177-b29d-9a882e08ad0d</v>
+        <v>c2103c22-c825-4633-a461-495c55747ed3</v>
       </c>
       <c r="B199" t="str">
-        <v>Autumn Lewis</v>
+        <v>Alice Robinson</v>
       </c>
       <c r="C199">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D199" t="str">
         <v>Female</v>
       </c>
       <c r="E199" t="str">
-        <v>autumn.lewis97@outlook.com</v>
+        <v>alice.robinson56@hotmail.com</v>
       </c>
       <c r="F199" t="str">
-        <v>(841) 837-8640</v>
+        <v>(251) 325-5554</v>
       </c>
       <c r="G199" t="str">
-        <v>San Francisco</v>
+        <v>Anaheim</v>
       </c>
       <c r="H199" t="str">
         <v>B+</v>
       </c>
       <c r="I199" t="str">
         <v>available</v>
-      </c>
-      <c r="J199" t="str">
-        <v>Noah Martinez</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>224212bc-76fd-40f4-903d-8a0a1d6163e3</v>
+        <v>4fba0674-c979-4177-b29d-9a882e08ad0d</v>
       </c>
       <c r="B200" t="str">
-        <v>Grayson Edwards</v>
+        <v>Autumn Lewis</v>
       </c>
       <c r="C200">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D200" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E200" t="str">
-        <v>grayson.edwards22@gmail.com</v>
+        <v>autumn.lewis97@outlook.com</v>
       </c>
       <c r="F200" t="str">
-        <v>(215) 129-3913</v>
+        <v>(841) 837-8640</v>
       </c>
       <c r="G200" t="str">
-        <v>Torrance</v>
+        <v>San Francisco</v>
       </c>
       <c r="H200" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I200" t="str">
         <v>available</v>
       </c>
       <c r="J200" t="str">
-        <v>Elizabeth Nelson, Joseph Anderson</v>
+        <v>Noah Martinez</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>bede75d6-a4ec-4fe3-907f-35108a2b4b10</v>
+        <v>224212bc-76fd-40f4-903d-8a0a1d6163e3</v>
       </c>
       <c r="B201" t="str">
-        <v>Cameron Evans</v>
+        <v>Grayson Edwards</v>
       </c>
       <c r="C201">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D201" t="str">
         <v>Male</v>
       </c>
       <c r="E201" t="str">
-        <v>cameron.evans55@outlook.com</v>
+        <v>grayson.edwards22@gmail.com</v>
       </c>
       <c r="F201" t="str">
-        <v>(535) 743-7467</v>
+        <v>(215) 129-3913</v>
       </c>
       <c r="G201" t="str">
-        <v>Fremont</v>
+        <v>Torrance</v>
       </c>
       <c r="H201" t="str">
         <v>B</v>
@@ -6970,216 +6980,216 @@
         <v>available</v>
       </c>
       <c r="J201" t="str">
-        <v>Michael Johnson, Anthony Garcia</v>
+        <v>Elizabeth Nelson, Joseph Anderson</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>10ec31e6-c6da-4957-9768-c5fcefe79c6b</v>
+        <v>bede75d6-a4ec-4fe3-907f-35108a2b4b10</v>
       </c>
       <c r="B202" t="str">
-        <v>Emma Turner</v>
+        <v>Cameron Evans</v>
       </c>
       <c r="C202">
         <v>33</v>
       </c>
       <c r="D202" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E202" t="str">
-        <v>emma.turner16@outlook.com</v>
+        <v>cameron.evans55@outlook.com</v>
       </c>
       <c r="F202" t="str">
-        <v>(656) 213-9003</v>
+        <v>(535) 743-7467</v>
       </c>
       <c r="G202" t="str">
-        <v>Pomona</v>
+        <v>Fremont</v>
       </c>
       <c r="H202" t="str">
         <v>B</v>
       </c>
       <c r="I202" t="str">
         <v>available</v>
+      </c>
+      <c r="J202" t="str">
+        <v>Michael Johnson, Anthony Garcia</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>a1895f97-a947-4cf3-9bc3-6aa43cdc1339</v>
+        <v>10ec31e6-c6da-4957-9768-c5fcefe79c6b</v>
       </c>
       <c r="B203" t="str">
-        <v>Gabriella Smith</v>
+        <v>Emma Turner</v>
       </c>
       <c r="C203">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D203" t="str">
         <v>Female</v>
       </c>
       <c r="E203" t="str">
-        <v>gabriella.smith91@hotmail.com</v>
+        <v>emma.turner16@outlook.com</v>
       </c>
       <c r="F203" t="str">
-        <v>(550) 121-2897</v>
+        <v>(656) 213-9003</v>
       </c>
       <c r="G203" t="str">
-        <v>Sacramento</v>
+        <v>Pomona</v>
       </c>
       <c r="H203" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I203" t="str">
         <v>available</v>
-      </c>
-      <c r="J203" t="str">
-        <v>Julian Rivera</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>4501044d-6fd4-4a45-83a0-416599928b1f</v>
+        <v>a1895f97-a947-4cf3-9bc3-6aa43cdc1339</v>
       </c>
       <c r="B204" t="str">
-        <v>Audrey Hill</v>
+        <v>Gabriella Smith</v>
       </c>
       <c r="C204">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D204" t="str">
         <v>Female</v>
       </c>
       <c r="E204" t="str">
-        <v>audrey.hill20@outlook.com</v>
+        <v>gabriella.smith91@hotmail.com</v>
       </c>
       <c r="F204" t="str">
-        <v>(688) 524-4712</v>
+        <v>(550) 121-2897</v>
       </c>
       <c r="G204" t="str">
-        <v>San Jose</v>
+        <v>Sacramento</v>
       </c>
       <c r="H204" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I204" t="str">
         <v>available</v>
       </c>
       <c r="J204" t="str">
-        <v>Avery Taylor</v>
+        <v>Julian Rivera</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>2450bd3d-4940-477d-8a08-abc3363fdc3a</v>
+        <v>4501044d-6fd4-4a45-83a0-416599928b1f</v>
       </c>
       <c r="B205" t="str">
-        <v>Ella Lopez</v>
+        <v>Audrey Hill</v>
       </c>
       <c r="C205">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D205" t="str">
         <v>Female</v>
       </c>
       <c r="E205" t="str">
-        <v>ella.lopez65@outlook.com</v>
+        <v>audrey.hill20@outlook.com</v>
       </c>
       <c r="F205" t="str">
-        <v>(192) 887-5779</v>
+        <v>(688) 524-4712</v>
       </c>
       <c r="G205" t="str">
-        <v>Riverside</v>
+        <v>San Jose</v>
       </c>
       <c r="H205" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I205" t="str">
         <v>available</v>
       </c>
       <c r="J205" t="str">
-        <v>Adam Edwards</v>
+        <v>Avery Taylor</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>f85f167d-7dd5-420d-86b5-ec8861b2bc1a</v>
+        <v>2450bd3d-4940-477d-8a08-abc3363fdc3a</v>
       </c>
       <c r="B206" t="str">
-        <v>Michael Carter</v>
+        <v>Ella Lopez</v>
       </c>
       <c r="C206">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D206" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E206" t="str">
-        <v>michael.carter90@outlook.com</v>
+        <v>ella.lopez65@outlook.com</v>
       </c>
       <c r="F206" t="str">
-        <v>(377) 714-4320</v>
+        <v>(192) 887-5779</v>
       </c>
       <c r="G206" t="str">
-        <v>Burbank</v>
+        <v>Riverside</v>
       </c>
       <c r="H206" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I206" t="str">
         <v>available</v>
+      </c>
+      <c r="J206" t="str">
+        <v>Adam Edwards</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>9d8995c7-d5a1-4644-848d-dca4e81371af</v>
+        <v>f85f167d-7dd5-420d-86b5-ec8861b2bc1a</v>
       </c>
       <c r="B207" t="str">
-        <v>Michael Campbell</v>
+        <v>Michael Carter</v>
       </c>
       <c r="C207">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D207" t="str">
         <v>Male</v>
       </c>
       <c r="E207" t="str">
-        <v>michael.campbell9@outlook.com</v>
+        <v>michael.carter90@outlook.com</v>
       </c>
       <c r="F207" t="str">
-        <v>(176) 164-6950</v>
+        <v>(377) 714-4320</v>
       </c>
       <c r="G207" t="str">
-        <v>Glendale</v>
+        <v>Burbank</v>
       </c>
       <c r="H207" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I207" t="str">
         <v>available</v>
-      </c>
-      <c r="J207" t="str">
-        <v>Sadie Williams, Eleanor Hall</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>ea1b059a-dde4-49c1-92b8-b9fd09c84bb7</v>
+        <v>9d8995c7-d5a1-4644-848d-dca4e81371af</v>
       </c>
       <c r="B208" t="str">
-        <v>Sadie Cook</v>
+        <v>Michael Campbell</v>
       </c>
       <c r="C208">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D208" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E208" t="str">
-        <v>sadie.cook9@yahoo.com</v>
+        <v>michael.campbell9@outlook.com</v>
       </c>
       <c r="F208" t="str">
-        <v>(382) 126-7672</v>
+        <v>(176) 164-6950</v>
       </c>
       <c r="G208" t="str">
-        <v>Santa Monica</v>
+        <v>Glendale</v>
       </c>
       <c r="H208" t="str">
         <v>B+</v>
@@ -7188,219 +7198,219 @@
         <v>available</v>
       </c>
       <c r="J208" t="str">
-        <v>William Allen, Alexa Hall</v>
+        <v>Sadie Williams, Eleanor Hall</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>cacb8de7-16c5-4332-9d25-a6794d8a23b3</v>
+        <v>ea1b059a-dde4-49c1-92b8-b9fd09c84bb7</v>
       </c>
       <c r="B209" t="str">
-        <v>Anthony Garcia</v>
+        <v>Sadie Cook</v>
       </c>
       <c r="C209">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D209" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E209" t="str">
-        <v>anthony.garcia31@yahoo.com</v>
+        <v>sadie.cook9@yahoo.com</v>
       </c>
       <c r="F209" t="str">
-        <v>(249) 774-7265</v>
+        <v>(382) 126-7672</v>
       </c>
       <c r="G209" t="str">
         <v>Santa Monica</v>
       </c>
       <c r="H209" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I209" t="str">
         <v>available</v>
       </c>
       <c r="J209" t="str">
-        <v>Michael Johnson, Cameron Evans</v>
+        <v>William Allen, Alexa Hall</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>921da7b6-596c-4a0e-a647-022bbd8cef26</v>
+        <v>cacb8de7-16c5-4332-9d25-a6794d8a23b3</v>
       </c>
       <c r="B210" t="str">
-        <v>John Diaz</v>
+        <v>Anthony Garcia</v>
       </c>
       <c r="C210">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="D210" t="str">
         <v>Male</v>
       </c>
       <c r="E210" t="str">
-        <v>john.diaz17@icloud.com</v>
+        <v>anthony.garcia31@yahoo.com</v>
       </c>
       <c r="F210" t="str">
-        <v>(251) 432-3565</v>
+        <v>(249) 774-7265</v>
       </c>
       <c r="G210" t="str">
-        <v>Pomona</v>
+        <v>Santa Monica</v>
       </c>
       <c r="H210" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I210" t="str">
         <v>available</v>
       </c>
       <c r="J210" t="str">
-        <v>Cameron Anderson</v>
+        <v>Michael Johnson, Cameron Evans</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>c03a116f-7b88-4c23-a9cc-04d14d2df186</v>
+        <v>921da7b6-596c-4a0e-a647-022bbd8cef26</v>
       </c>
       <c r="B211" t="str">
-        <v>Sofia Martin</v>
+        <v>John Diaz</v>
       </c>
       <c r="C211">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D211" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E211" t="str">
-        <v>sofia.martin17@yahoo.com</v>
+        <v>john.diaz17@icloud.com</v>
       </c>
       <c r="F211" t="str">
-        <v>(319) 272-7772</v>
+        <v>(251) 432-3565</v>
       </c>
       <c r="G211" t="str">
-        <v>Fresno</v>
+        <v>Pomona</v>
       </c>
       <c r="H211" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I211" t="str">
         <v>available</v>
+      </c>
+      <c r="J211" t="str">
+        <v>Cameron Anderson</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>97620f89-d506-4934-89b6-c60208f0bb45</v>
+        <v>c03a116f-7b88-4c23-a9cc-04d14d2df186</v>
       </c>
       <c r="B212" t="str">
-        <v>Charlotte Hernandez</v>
+        <v>Sofia Martin</v>
       </c>
       <c r="C212">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D212" t="str">
         <v>Female</v>
       </c>
       <c r="E212" t="str">
-        <v>charlotte.hernandez88@gmail.com</v>
+        <v>sofia.martin17@yahoo.com</v>
       </c>
       <c r="F212" t="str">
-        <v>(131) 448-5858</v>
+        <v>(319) 272-7772</v>
       </c>
       <c r="G212" t="str">
-        <v>San Jose</v>
+        <v>Fresno</v>
       </c>
       <c r="H212" t="str">
         <v>B</v>
       </c>
       <c r="I212" t="str">
         <v>available</v>
-      </c>
-      <c r="J212" t="str">
-        <v>Ellie Allen, Emma Torres</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>49fbe592-0995-4321-b8af-fbe859ca414c</v>
+        <v>97620f89-d506-4934-89b6-c60208f0bb45</v>
       </c>
       <c r="B213" t="str">
-        <v>Grayson Morgan</v>
+        <v>Charlotte Hernandez</v>
       </c>
       <c r="C213">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D213" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E213" t="str">
-        <v>grayson.morgan95@outlook.com</v>
+        <v>charlotte.hernandez88@gmail.com</v>
       </c>
       <c r="F213" t="str">
-        <v>(524) 127-2584</v>
+        <v>(131) 448-5858</v>
       </c>
       <c r="G213" t="str">
-        <v>Irvine</v>
+        <v>San Jose</v>
       </c>
       <c r="H213" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I213" t="str">
         <v>available</v>
       </c>
       <c r="J213" t="str">
-        <v>Adam Hall, Valentina Morales</v>
+        <v>Ellie Allen, Emma Torres</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>c284df19-568f-44d7-9ddf-b63e5af17f4a</v>
+        <v>49fbe592-0995-4321-b8af-fbe859ca414c</v>
       </c>
       <c r="B214" t="str">
-        <v>Hannah Moore</v>
+        <v>Grayson Morgan</v>
       </c>
       <c r="C214">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D214" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E214" t="str">
-        <v>hannah.moore60@outlook.com</v>
+        <v>grayson.morgan95@outlook.com</v>
       </c>
       <c r="F214" t="str">
-        <v>(173) 685-3587</v>
+        <v>(524) 127-2584</v>
       </c>
       <c r="G214" t="str">
-        <v>Torrance</v>
+        <v>Irvine</v>
       </c>
       <c r="H214" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I214" t="str">
         <v>available</v>
       </c>
       <c r="J214" t="str">
-        <v>Alexander Campbell, Logan Nguyen</v>
+        <v>Adam Hall, Valentina Morales</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>d1a4099f-cc65-41a4-8aa3-72e7788e4944</v>
+        <v>c284df19-568f-44d7-9ddf-b63e5af17f4a</v>
       </c>
       <c r="B215" t="str">
-        <v>Sophia Reyes</v>
+        <v>Hannah Moore</v>
       </c>
       <c r="C215">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D215" t="str">
         <v>Female</v>
       </c>
       <c r="E215" t="str">
-        <v>sophia.reyes82@outlook.com</v>
+        <v>hannah.moore60@outlook.com</v>
       </c>
       <c r="F215" t="str">
-        <v>(759) 966-2783</v>
+        <v>(173) 685-3587</v>
       </c>
       <c r="G215" t="str">
-        <v>Long Beach</v>
+        <v>Torrance</v>
       </c>
       <c r="H215" t="str">
         <v>B</v>
@@ -7409,30 +7419,30 @@
         <v>available</v>
       </c>
       <c r="J215" t="str">
-        <v>Victoria Anderson</v>
+        <v>Alexander Campbell, Logan Nguyen</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>783b418b-9b0d-482c-a01b-75072978141f</v>
+        <v>d1a4099f-cc65-41a4-8aa3-72e7788e4944</v>
       </c>
       <c r="B216" t="str">
-        <v>Joshua Martinez</v>
+        <v>Sophia Reyes</v>
       </c>
       <c r="C216">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D216" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E216" t="str">
-        <v>joshua.martinez94@icloud.com</v>
+        <v>sophia.reyes82@outlook.com</v>
       </c>
       <c r="F216" t="str">
-        <v>(539) 856-7158</v>
+        <v>(759) 966-2783</v>
       </c>
       <c r="G216" t="str">
-        <v>San Diego</v>
+        <v>Long Beach</v>
       </c>
       <c r="H216" t="str">
         <v>B</v>
@@ -7441,30 +7451,30 @@
         <v>available</v>
       </c>
       <c r="J216" t="str">
-        <v>Avery Clark</v>
+        <v>Victoria Anderson</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>1e334800-6e70-4273-b1ff-ee3ce5738b57</v>
+        <v>783b418b-9b0d-482c-a01b-75072978141f</v>
       </c>
       <c r="B217" t="str">
-        <v>Adam Edwards</v>
+        <v>Joshua Martinez</v>
       </c>
       <c r="C217">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D217" t="str">
         <v>Male</v>
       </c>
       <c r="E217" t="str">
-        <v>adam.edwards41@hotmail.com</v>
+        <v>joshua.martinez94@icloud.com</v>
       </c>
       <c r="F217" t="str">
-        <v>(439) 906-3390</v>
+        <v>(539) 856-7158</v>
       </c>
       <c r="G217" t="str">
-        <v>Burbank</v>
+        <v>San Diego</v>
       </c>
       <c r="H217" t="str">
         <v>B</v>
@@ -7473,59 +7483,62 @@
         <v>available</v>
       </c>
       <c r="J217" t="str">
-        <v>Ella Lopez</v>
+        <v>Avery Clark</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>55c196e0-f9b8-42fe-8113-ce9d2ac76116</v>
+        <v>1e334800-6e70-4273-b1ff-ee3ce5738b57</v>
       </c>
       <c r="B218" t="str">
-        <v>Natalie Ortiz</v>
+        <v>Adam Edwards</v>
       </c>
       <c r="C218">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D218" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E218" t="str">
-        <v>natalie.ortiz89@yahoo.com</v>
+        <v>adam.edwards41@hotmail.com</v>
       </c>
       <c r="F218" t="str">
-        <v>(986) 277-9331</v>
+        <v>(439) 906-3390</v>
       </c>
       <c r="G218" t="str">
-        <v>San Francisco</v>
+        <v>Burbank</v>
       </c>
       <c r="H218" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I218" t="str">
         <v>available</v>
+      </c>
+      <c r="J218" t="str">
+        <v>Ella Lopez</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>25fd249f-3802-4717-8a4d-4da36897b280</v>
+        <v>55c196e0-f9b8-42fe-8113-ce9d2ac76116</v>
       </c>
       <c r="B219" t="str">
-        <v>Nathan Taylor</v>
+        <v>Natalie Ortiz</v>
       </c>
       <c r="C219">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D219" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E219" t="str">
-        <v>nathan.taylor65@outlook.com</v>
+        <v>natalie.ortiz89@yahoo.com</v>
       </c>
       <c r="F219" t="str">
-        <v>(250) 584-7117</v>
+        <v>(986) 277-9331</v>
       </c>
       <c r="G219" t="str">
-        <v>Stockton</v>
+        <v>San Francisco</v>
       </c>
       <c r="H219" t="str">
         <v>B+</v>
@@ -7536,57 +7549,54 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>8819a806-f5b1-4b58-95f5-91489df570ac</v>
+        <v>25fd249f-3802-4717-8a4d-4da36897b280</v>
       </c>
       <c r="B220" t="str">
-        <v>Colton Harris</v>
+        <v>Nathan Taylor</v>
       </c>
       <c r="C220">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D220" t="str">
         <v>Male</v>
       </c>
       <c r="E220" t="str">
-        <v>colton.harris98@icloud.com</v>
+        <v>nathan.taylor65@outlook.com</v>
       </c>
       <c r="F220" t="str">
-        <v>(583) 900-3294</v>
+        <v>(250) 584-7117</v>
       </c>
       <c r="G220" t="str">
-        <v>Newport Beach</v>
+        <v>Stockton</v>
       </c>
       <c r="H220" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I220" t="str">
         <v>available</v>
-      </c>
-      <c r="J220" t="str">
-        <v>Sebastian Edwards, Sofia Williams</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>6116506f-31f1-444e-bd83-2991a5335470</v>
+        <v>8819a806-f5b1-4b58-95f5-91489df570ac</v>
       </c>
       <c r="B221" t="str">
-        <v>Sebastian Edwards</v>
+        <v>Colton Harris</v>
       </c>
       <c r="C221">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D221" t="str">
         <v>Male</v>
       </c>
       <c r="E221" t="str">
-        <v>sebastian.edwards97@icloud.com</v>
+        <v>colton.harris98@icloud.com</v>
       </c>
       <c r="F221" t="str">
-        <v>(348) 408-1134</v>
+        <v>(583) 900-3294</v>
       </c>
       <c r="G221" t="str">
-        <v>Los Angeles</v>
+        <v>Newport Beach</v>
       </c>
       <c r="H221" t="str">
         <v>B</v>
@@ -7595,62 +7605,65 @@
         <v>available</v>
       </c>
       <c r="J221" t="str">
-        <v>Colton Harris, Sofia Williams</v>
+        <v>Sebastian Edwards, Sofia Williams</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>cd39ae02-9f54-44f2-a679-42c6c5b329f4</v>
+        <v>6116506f-31f1-444e-bd83-2991a5335470</v>
       </c>
       <c r="B222" t="str">
-        <v>Test Contestant 91</v>
+        <v>Sebastian Edwards</v>
       </c>
       <c r="C222">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D222" t="str">
         <v>Male</v>
       </c>
       <c r="E222" t="str">
-        <v>test.contestant.91@gmail.com</v>
+        <v>sebastian.edwards97@icloud.com</v>
       </c>
       <c r="F222" t="str">
-        <v>(555) 637-1183</v>
+        <v>(348) 408-1134</v>
       </c>
       <c r="G222" t="str">
-        <v>San Diego</v>
+        <v>Los Angeles</v>
       </c>
       <c r="H222" t="str">
         <v>B</v>
       </c>
       <c r="I222" t="str">
         <v>available</v>
+      </c>
+      <c r="J222" t="str">
+        <v>Colton Harris, Sofia Williams</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>3af86d4e-b0b2-48a5-a377-37c0e5bc0e55</v>
+        <v>cd39ae02-9f54-44f2-a679-42c6c5b329f4</v>
       </c>
       <c r="B223" t="str">
-        <v>Test Contestant 92</v>
+        <v>Test Contestant 91</v>
       </c>
       <c r="C223">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D223" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E223" t="str">
-        <v>test.contestant.92@gmail.com</v>
+        <v>test.contestant.91@gmail.com</v>
       </c>
       <c r="F223" t="str">
-        <v>(555) 644-1196</v>
+        <v>(555) 637-1183</v>
       </c>
       <c r="G223" t="str">
-        <v>San Francisco</v>
+        <v>San Diego</v>
       </c>
       <c r="H223" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I223" t="str">
         <v>available</v>
@@ -7658,28 +7671,28 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>c6c464e0-123d-4cc9-8b28-0ecbd0a6ce5f</v>
+        <v>3af86d4e-b0b2-48a5-a377-37c0e5bc0e55</v>
       </c>
       <c r="B224" t="str">
-        <v>Matthew Anderson</v>
+        <v>Test Contestant 92</v>
       </c>
       <c r="C224">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D224" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E224" t="str">
-        <v>matthew.anderson56@icloud.com</v>
+        <v>test.contestant.92@gmail.com</v>
       </c>
       <c r="F224" t="str">
-        <v>(853) 972-9742</v>
+        <v>(555) 644-1196</v>
       </c>
       <c r="G224" t="str">
-        <v>Irvine</v>
+        <v>San Francisco</v>
       </c>
       <c r="H224" t="str">
-        <v>A+</v>
+        <v>B+</v>
       </c>
       <c r="I224" t="str">
         <v>available</v>
@@ -7687,28 +7700,28 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>6cf6d988-31a4-4dd2-91c8-6b1f5adb2989</v>
+        <v>c6c464e0-123d-4cc9-8b28-0ecbd0a6ce5f</v>
       </c>
       <c r="B225" t="str">
-        <v>Test Contestant 93</v>
+        <v>Matthew Anderson</v>
       </c>
       <c r="C225">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D225" t="str">
         <v>Male</v>
       </c>
       <c r="E225" t="str">
-        <v>test.contestant.93@gmail.com</v>
+        <v>matthew.anderson56@icloud.com</v>
       </c>
       <c r="F225" t="str">
-        <v>(555) 651-1209</v>
+        <v>(853) 972-9742</v>
       </c>
       <c r="G225" t="str">
-        <v>Sacramento</v>
+        <v>Irvine</v>
       </c>
       <c r="H225" t="str">
-        <v>B+</v>
+        <v>A+</v>
       </c>
       <c r="I225" t="str">
         <v>available</v>
@@ -7716,28 +7729,28 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>c993ea19-e004-473d-930c-ece99be098ec</v>
+        <v>6cf6d988-31a4-4dd2-91c8-6b1f5adb2989</v>
       </c>
       <c r="B226" t="str">
-        <v>Test Contestant 94</v>
+        <v>Test Contestant 93</v>
       </c>
       <c r="C226">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D226" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E226" t="str">
-        <v>test.contestant.94@gmail.com</v>
+        <v>test.contestant.93@gmail.com</v>
       </c>
       <c r="F226" t="str">
-        <v>(555) 658-1222</v>
+        <v>(555) 651-1209</v>
       </c>
       <c r="G226" t="str">
-        <v>Fresno</v>
+        <v>Sacramento</v>
       </c>
       <c r="H226" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I226" t="str">
         <v>available</v>
@@ -7745,57 +7758,54 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>0497247b-bf9a-4f46-a562-05f1892687ce</v>
+        <v>c993ea19-e004-473d-930c-ece99be098ec</v>
       </c>
       <c r="B227" t="str">
-        <v>Henry Roberts</v>
+        <v>Test Contestant 94</v>
       </c>
       <c r="C227">
         <v>34</v>
       </c>
       <c r="D227" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E227" t="str">
-        <v>henry.roberts93@outlook.com</v>
+        <v>test.contestant.94@gmail.com</v>
       </c>
       <c r="F227" t="str">
-        <v>(654) 727-7734</v>
+        <v>(555) 658-1222</v>
       </c>
       <c r="G227" t="str">
-        <v>Burbank</v>
+        <v>Fresno</v>
       </c>
       <c r="H227" t="str">
-        <v>A+</v>
+        <v>A</v>
       </c>
       <c r="I227" t="str">
         <v>available</v>
-      </c>
-      <c r="J227" t="str">
-        <v>Thomas Nguyen, Hannah Jones</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>5260c12e-e864-4bff-bd02-32d2c84a9a95</v>
+        <v>0497247b-bf9a-4f46-a562-05f1892687ce</v>
       </c>
       <c r="B228" t="str">
-        <v>Alexander Baker</v>
+        <v>Henry Roberts</v>
       </c>
       <c r="C228">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D228" t="str">
         <v>Male</v>
       </c>
       <c r="E228" t="str">
-        <v>alexander.baker64@hotmail.com</v>
+        <v>henry.roberts93@outlook.com</v>
       </c>
       <c r="F228" t="str">
-        <v>(434) 373-1503</v>
+        <v>(654) 727-7734</v>
       </c>
       <c r="G228" t="str">
-        <v>Stockton</v>
+        <v>Burbank</v>
       </c>
       <c r="H228" t="str">
         <v>A+</v>
@@ -7803,31 +7813,34 @@
       <c r="I228" t="str">
         <v>available</v>
       </c>
+      <c r="J228" t="str">
+        <v>Thomas Nguyen, Hannah Jones</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>70b6dd13-c3db-4d3c-ae6c-f5cd6a3013a7</v>
+        <v>5260c12e-e864-4bff-bd02-32d2c84a9a95</v>
       </c>
       <c r="B229" t="str">
-        <v>Test Contestant 95</v>
+        <v>Alexander Baker</v>
       </c>
       <c r="C229">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D229" t="str">
         <v>Male</v>
       </c>
       <c r="E229" t="str">
-        <v>test.contestant.95@gmail.com</v>
+        <v>alexander.baker64@hotmail.com</v>
       </c>
       <c r="F229" t="str">
-        <v>(555) 665-1235</v>
+        <v>(434) 373-1503</v>
       </c>
       <c r="G229" t="str">
-        <v>Oakland</v>
+        <v>Stockton</v>
       </c>
       <c r="H229" t="str">
-        <v>B</v>
+        <v>A+</v>
       </c>
       <c r="I229" t="str">
         <v>available</v>
@@ -7835,25 +7848,25 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>38bd2620-84e1-4cae-bd1f-472cfcf5b90a</v>
+        <v>70b6dd13-c3db-4d3c-ae6c-f5cd6a3013a7</v>
       </c>
       <c r="B230" t="str">
-        <v>Test Contestant 96</v>
+        <v>Test Contestant 95</v>
       </c>
       <c r="C230">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D230" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E230" t="str">
-        <v>test.contestant.96@gmail.com</v>
+        <v>test.contestant.95@gmail.com</v>
       </c>
       <c r="F230" t="str">
-        <v>(555) 672-1248</v>
+        <v>(555) 665-1235</v>
       </c>
       <c r="G230" t="str">
-        <v>Long Beach</v>
+        <v>Oakland</v>
       </c>
       <c r="H230" t="str">
         <v>B</v>
@@ -7864,182 +7877,182 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>06d38f0c-6780-4d6a-97b8-f28ec52ced34</v>
+        <v>38bd2620-84e1-4cae-bd1f-472cfcf5b90a</v>
       </c>
       <c r="B231" t="str">
-        <v>William Taylor</v>
+        <v>Test Contestant 96</v>
       </c>
       <c r="C231">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D231" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E231" t="str">
-        <v>william.taylor84@hotmail.com</v>
+        <v>test.contestant.96@gmail.com</v>
       </c>
       <c r="F231" t="str">
-        <v>(276) 538-1731</v>
+        <v>(555) 672-1248</v>
       </c>
       <c r="G231" t="str">
-        <v>Newport Beach</v>
+        <v>Long Beach</v>
       </c>
       <c r="H231" t="str">
         <v>B</v>
       </c>
       <c r="I231" t="str">
         <v>available</v>
-      </c>
-      <c r="J231" t="str">
-        <v>Victoria Scott</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>ce7b894b-705d-49f7-a6a3-e0a7fe953a10</v>
+        <v>06d38f0c-6780-4d6a-97b8-f28ec52ced34</v>
       </c>
       <c r="B232" t="str">
-        <v>Christian Rivera</v>
+        <v>William Taylor</v>
       </c>
       <c r="C232">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D232" t="str">
         <v>Male</v>
       </c>
       <c r="E232" t="str">
-        <v>christian.rivera21@outlook.com</v>
+        <v>william.taylor84@hotmail.com</v>
       </c>
       <c r="F232" t="str">
-        <v>(913) 900-2520</v>
+        <v>(276) 538-1731</v>
       </c>
       <c r="G232" t="str">
-        <v>Burbank</v>
+        <v>Newport Beach</v>
       </c>
       <c r="H232" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I232" t="str">
         <v>available</v>
       </c>
       <c r="J232" t="str">
-        <v>Allison Torres, Elena Green</v>
+        <v>Victoria Scott</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>d1a89d8f-bd2f-40db-a5d5-ef8dc3e3aa54</v>
+        <v>ce7b894b-705d-49f7-a6a3-e0a7fe953a10</v>
       </c>
       <c r="B233" t="str">
-        <v>Mason Hernandez</v>
+        <v>Christian Rivera</v>
       </c>
       <c r="C233">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D233" t="str">
         <v>Male</v>
       </c>
       <c r="E233" t="str">
-        <v>mason.hernandez15@gmail.com</v>
+        <v>christian.rivera21@outlook.com</v>
       </c>
       <c r="F233" t="str">
-        <v>(880) 425-4186</v>
+        <v>(913) 900-2520</v>
       </c>
       <c r="G233" t="str">
-        <v>San Jose</v>
+        <v>Burbank</v>
       </c>
       <c r="H233" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I233" t="str">
         <v>available</v>
+      </c>
+      <c r="J233" t="str">
+        <v>Allison Torres, Elena Green</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>e2c7fa0a-1d97-4430-b83c-5099c5831757</v>
+        <v>d1a89d8f-bd2f-40db-a5d5-ef8dc3e3aa54</v>
       </c>
       <c r="B234" t="str">
-        <v>John Carter</v>
+        <v>Mason Hernandez</v>
       </c>
       <c r="C234">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D234" t="str">
         <v>Male</v>
       </c>
       <c r="E234" t="str">
-        <v>john.carter42@outlook.com</v>
+        <v>mason.hernandez15@gmail.com</v>
       </c>
       <c r="F234" t="str">
-        <v>(160) 507-8767</v>
+        <v>(880) 425-4186</v>
       </c>
       <c r="G234" t="str">
-        <v>Pasadena</v>
+        <v>San Jose</v>
       </c>
       <c r="H234" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I234" t="str">
         <v>available</v>
-      </c>
-      <c r="J234" t="str">
-        <v>Brooklyn Rivera</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>0bb2a1aa-a74d-4711-a2ea-609663a77b4d</v>
+        <v>e2c7fa0a-1d97-4430-b83c-5099c5831757</v>
       </c>
       <c r="B235" t="str">
-        <v>Carter Harris</v>
+        <v>John Carter</v>
       </c>
       <c r="C235">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D235" t="str">
         <v>Male</v>
       </c>
       <c r="E235" t="str">
-        <v>carter.harris82@yahoo.com</v>
+        <v>john.carter42@outlook.com</v>
       </c>
       <c r="F235" t="str">
-        <v>0412 175 744</v>
+        <v>(160) 507-8767</v>
       </c>
       <c r="G235" t="str">
-        <v>Geelong</v>
+        <v>Pasadena</v>
       </c>
       <c r="H235" t="str">
         <v>B</v>
       </c>
       <c r="I235" t="str">
         <v>available</v>
+      </c>
+      <c r="J235" t="str">
+        <v>Brooklyn Rivera</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>340ad2e5-95a9-4eb5-a113-e7f9f0e5d704</v>
+        <v>0bb2a1aa-a74d-4711-a2ea-609663a77b4d</v>
       </c>
       <c r="B236" t="str">
-        <v>Jaxon Cook</v>
+        <v>Carter Harris</v>
       </c>
       <c r="C236">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D236" t="str">
         <v>Male</v>
       </c>
       <c r="E236" t="str">
-        <v>jaxon.cook73@yahoo.com</v>
+        <v>carter.harris82@yahoo.com</v>
       </c>
       <c r="F236" t="str">
-        <v>(190) 120-3429</v>
+        <v>0412 175 744</v>
       </c>
       <c r="G236" t="str">
-        <v>Fresno</v>
+        <v>Geelong</v>
       </c>
       <c r="H236" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I236" t="str">
         <v>available</v>
@@ -8047,22 +8060,22 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>9ad191d8-a3b3-478d-9318-781d3156afaa</v>
+        <v>340ad2e5-95a9-4eb5-a113-e7f9f0e5d704</v>
       </c>
       <c r="B237" t="str">
-        <v>Alexander Campbell</v>
+        <v>Jaxon Cook</v>
       </c>
       <c r="C237">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D237" t="str">
         <v>Male</v>
       </c>
       <c r="E237" t="str">
-        <v>alexander.campbell71@gmail.com</v>
+        <v>jaxon.cook73@yahoo.com</v>
       </c>
       <c r="F237" t="str">
-        <v>(131) 840-1169</v>
+        <v>(190) 120-3429</v>
       </c>
       <c r="G237" t="str">
         <v>Fresno</v>
@@ -8073,16 +8086,13 @@
       <c r="I237" t="str">
         <v>available</v>
       </c>
-      <c r="J237" t="str">
-        <v>Logan Nguyen, Hannah Moore</v>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>e8c7986a-699a-4e43-9b2d-52ca42510a36</v>
+        <v>9ad191d8-a3b3-478d-9318-781d3156afaa</v>
       </c>
       <c r="B238" t="str">
-        <v>Matthew Torres</v>
+        <v>Alexander Campbell</v>
       </c>
       <c r="C238">
         <v>34</v>
@@ -8091,13 +8101,13 @@
         <v>Male</v>
       </c>
       <c r="E238" t="str">
-        <v>matthew.torres76@yahoo.com</v>
+        <v>alexander.campbell71@gmail.com</v>
       </c>
       <c r="F238" t="str">
-        <v>(432) 516-9920</v>
+        <v>(131) 840-1169</v>
       </c>
       <c r="G238" t="str">
-        <v>Sacramento</v>
+        <v>Fresno</v>
       </c>
       <c r="H238" t="str">
         <v>A</v>
@@ -8105,31 +8115,34 @@
       <c r="I238" t="str">
         <v>available</v>
       </c>
+      <c r="J238" t="str">
+        <v>Logan Nguyen, Hannah Moore</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>9efd8ec8-0e91-45d9-804b-518939fbac76</v>
+        <v>e8c7986a-699a-4e43-9b2d-52ca42510a36</v>
       </c>
       <c r="B239" t="str">
-        <v>Noah Hernandez</v>
+        <v>Matthew Torres</v>
       </c>
       <c r="C239">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D239" t="str">
         <v>Male</v>
       </c>
       <c r="E239" t="str">
-        <v>noah.hernandez9@hotmail.com</v>
+        <v>matthew.torres76@yahoo.com</v>
       </c>
       <c r="F239" t="str">
-        <v>0404 855 230</v>
+        <v>(432) 516-9920</v>
       </c>
       <c r="G239" t="str">
-        <v>Cairns</v>
+        <v>Sacramento</v>
       </c>
       <c r="H239" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I239" t="str">
         <v>available</v>
@@ -8137,57 +8150,54 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>8dfd710f-c1f0-43ee-b26d-13d05de4598b</v>
+        <v>9efd8ec8-0e91-45d9-804b-518939fbac76</v>
       </c>
       <c r="B240" t="str">
-        <v>Josiah Lopez</v>
+        <v>Noah Hernandez</v>
       </c>
       <c r="C240">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D240" t="str">
         <v>Male</v>
       </c>
       <c r="E240" t="str">
-        <v>josiah.lopez65@gmail.com</v>
+        <v>noah.hernandez9@hotmail.com</v>
       </c>
       <c r="F240" t="str">
-        <v>(305) 140-9212</v>
+        <v>0404 855 230</v>
       </c>
       <c r="G240" t="str">
-        <v>Chula Vista</v>
+        <v>Cairns</v>
       </c>
       <c r="H240" t="str">
         <v>B</v>
       </c>
       <c r="I240" t="str">
         <v>available</v>
-      </c>
-      <c r="J240" t="str">
-        <v>Victoria Carter, Ella Martinez</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>924c70dd-25ce-4725-8a88-173a3af33a7f</v>
+        <v>8dfd710f-c1f0-43ee-b26d-13d05de4598b</v>
       </c>
       <c r="B241" t="str">
-        <v>Mia Anderson</v>
+        <v>Josiah Lopez</v>
       </c>
       <c r="C241">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D241" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E241" t="str">
-        <v>mia.anderson0@yahoo.com</v>
+        <v>josiah.lopez65@gmail.com</v>
       </c>
       <c r="F241" t="str">
-        <v>(574) 806-3609</v>
+        <v>(305) 140-9212</v>
       </c>
       <c r="G241" t="str">
-        <v>Stockton</v>
+        <v>Chula Vista</v>
       </c>
       <c r="H241" t="str">
         <v>B</v>
@@ -8196,30 +8206,30 @@
         <v>available</v>
       </c>
       <c r="J241" t="str">
-        <v>Avery Cruz, Lydia Torres</v>
+        <v>Victoria Carter, Ella Martinez</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>93e72347-d9bf-4fb1-b06c-7cb5a2edcc2a</v>
+        <v>924c70dd-25ce-4725-8a88-173a3af33a7f</v>
       </c>
       <c r="B242" t="str">
-        <v>Grace King</v>
+        <v>Mia Anderson</v>
       </c>
       <c r="C242">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D242" t="str">
         <v>Female</v>
       </c>
       <c r="E242" t="str">
-        <v>grace.king1@yahoo.com</v>
+        <v>mia.anderson0@yahoo.com</v>
       </c>
       <c r="F242" t="str">
-        <v>(217) 721-5651</v>
+        <v>(574) 806-3609</v>
       </c>
       <c r="G242" t="str">
-        <v>Oakland</v>
+        <v>Stockton</v>
       </c>
       <c r="H242" t="str">
         <v>B</v>
@@ -8228,219 +8238,219 @@
         <v>available</v>
       </c>
       <c r="J242" t="str">
-        <v>Gianna Hill</v>
+        <v>Avery Cruz, Lydia Torres</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>f26a0638-511f-4440-ae1a-2ae052df470f</v>
+        <v>93e72347-d9bf-4fb1-b06c-7cb5a2edcc2a</v>
       </c>
       <c r="B243" t="str">
-        <v>Caleb Brown</v>
+        <v>Grace King</v>
       </c>
       <c r="C243">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D243" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E243" t="str">
-        <v>caleb.brown13@yahoo.com</v>
+        <v>grace.king1@yahoo.com</v>
       </c>
       <c r="F243" t="str">
-        <v>(130) 920-6765</v>
+        <v>(217) 721-5651</v>
       </c>
       <c r="G243" t="str">
-        <v>Irvine</v>
+        <v>Oakland</v>
       </c>
       <c r="H243" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I243" t="str">
         <v>available</v>
       </c>
       <c r="J243" t="str">
-        <v>Jackson Murphy</v>
+        <v>Gianna Hill</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>d035c0a6-d30e-4ca3-b8c2-9becb2842da7</v>
+        <v>f26a0638-511f-4440-ae1a-2ae052df470f</v>
       </c>
       <c r="B244" t="str">
-        <v>Thomas Rivera</v>
+        <v>Caleb Brown</v>
       </c>
       <c r="C244">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D244" t="str">
         <v>Male</v>
       </c>
       <c r="E244" t="str">
-        <v>thomas.rivera13@yahoo.com</v>
+        <v>caleb.brown13@yahoo.com</v>
       </c>
       <c r="F244" t="str">
-        <v>(539) 243-6118</v>
+        <v>(130) 920-6765</v>
       </c>
       <c r="G244" t="str">
-        <v>Long Beach</v>
+        <v>Irvine</v>
       </c>
       <c r="H244" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I244" t="str">
         <v>available</v>
       </c>
       <c r="J244" t="str">
-        <v>Hannah Murphy</v>
+        <v>Jackson Murphy</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>befe2d5d-0583-45ac-939e-ab57370e2d4f</v>
+        <v>d035c0a6-d30e-4ca3-b8c2-9becb2842da7</v>
       </c>
       <c r="B245" t="str">
-        <v>Daniel Taylor</v>
+        <v>Thomas Rivera</v>
       </c>
       <c r="C245">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D245" t="str">
         <v>Male</v>
       </c>
       <c r="E245" t="str">
-        <v>daniel.taylor53@gmail.com</v>
+        <v>thomas.rivera13@yahoo.com</v>
       </c>
       <c r="F245" t="str">
-        <v>(543) 329-4768</v>
+        <v>(539) 243-6118</v>
       </c>
       <c r="G245" t="str">
-        <v>Pomona</v>
+        <v>Long Beach</v>
       </c>
       <c r="H245" t="str">
         <v>B</v>
       </c>
       <c r="I245" t="str">
         <v>available</v>
+      </c>
+      <c r="J245" t="str">
+        <v>Hannah Murphy</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>5cb68000-430e-4dc3-9afa-c9c5cca864c0</v>
+        <v>befe2d5d-0583-45ac-939e-ab57370e2d4f</v>
       </c>
       <c r="B246" t="str">
-        <v>Logan Nguyen</v>
+        <v>Daniel Taylor</v>
       </c>
       <c r="C246">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D246" t="str">
         <v>Male</v>
       </c>
       <c r="E246" t="str">
-        <v>logan.nguyen23@hotmail.com</v>
+        <v>daniel.taylor53@gmail.com</v>
       </c>
       <c r="F246" t="str">
-        <v>(278) 620-7089</v>
+        <v>(543) 329-4768</v>
       </c>
       <c r="G246" t="str">
-        <v>Torrance</v>
+        <v>Pomona</v>
       </c>
       <c r="H246" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I246" t="str">
         <v>available</v>
-      </c>
-      <c r="J246" t="str">
-        <v>Alexander Campbell, Hannah Moore</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>7772949f-f87d-480b-87ab-71f7500e8bd3</v>
+        <v>5cb68000-430e-4dc3-9afa-c9c5cca864c0</v>
       </c>
       <c r="B247" t="str">
-        <v>Elijah Miller</v>
+        <v>Logan Nguyen</v>
       </c>
       <c r="C247">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D247" t="str">
         <v>Male</v>
       </c>
       <c r="E247" t="str">
-        <v>elijah.miller73@outlook.com</v>
+        <v>logan.nguyen23@hotmail.com</v>
       </c>
       <c r="F247" t="str">
-        <v>(967) 645-5202</v>
+        <v>(278) 620-7089</v>
       </c>
       <c r="G247" t="str">
-        <v>Pasadena</v>
+        <v>Torrance</v>
       </c>
       <c r="H247" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I247" t="str">
         <v>available</v>
       </c>
       <c r="J247" t="str">
-        <v>Sophia Flores</v>
+        <v>Alexander Campbell, Hannah Moore</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>6aa67d72-8123-41b4-9298-7f5d1e89aef7</v>
+        <v>7772949f-f87d-480b-87ab-71f7500e8bd3</v>
       </c>
       <c r="B248" t="str">
-        <v>Thomas Nguyen</v>
+        <v>Elijah Miller</v>
       </c>
       <c r="C248">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D248" t="str">
         <v>Male</v>
       </c>
       <c r="E248" t="str">
-        <v>thomas.nguyen88@yahoo.com</v>
+        <v>elijah.miller73@outlook.com</v>
       </c>
       <c r="F248" t="str">
-        <v>(163) 406-8750</v>
+        <v>(967) 645-5202</v>
       </c>
       <c r="G248" t="str">
-        <v>Pomona</v>
+        <v>Pasadena</v>
       </c>
       <c r="H248" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I248" t="str">
         <v>available</v>
       </c>
       <c r="J248" t="str">
-        <v>Henry Roberts, Hannah Jones</v>
+        <v>Sophia Flores</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>29b3a5cd-ea7d-4673-9db4-7886660a791f</v>
+        <v>6aa67d72-8123-41b4-9298-7f5d1e89aef7</v>
       </c>
       <c r="B249" t="str">
-        <v>Joseph Stewart</v>
+        <v>Thomas Nguyen</v>
       </c>
       <c r="C249">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D249" t="str">
         <v>Male</v>
       </c>
       <c r="E249" t="str">
-        <v>joseph.stewart94@outlook.com</v>
+        <v>thomas.nguyen88@yahoo.com</v>
       </c>
       <c r="F249" t="str">
-        <v>(101) 920-4176</v>
+        <v>(163) 406-8750</v>
       </c>
       <c r="G249" t="str">
-        <v>Stockton</v>
+        <v>Pomona</v>
       </c>
       <c r="H249" t="str">
         <v>B</v>
@@ -8449,30 +8459,30 @@
         <v>available</v>
       </c>
       <c r="J249" t="str">
-        <v>Olivia Nelson, Madelyn Martinez</v>
+        <v>Henry Roberts, Hannah Jones</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>35c73937-3dd5-4fb3-a5df-d900cabdacba</v>
+        <v>29b3a5cd-ea7d-4673-9db4-7886660a791f</v>
       </c>
       <c r="B250" t="str">
-        <v>Jackson Murphy</v>
+        <v>Joseph Stewart</v>
       </c>
       <c r="C250">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D250" t="str">
         <v>Male</v>
       </c>
       <c r="E250" t="str">
-        <v>jackson.murphy91@yahoo.com</v>
+        <v>joseph.stewart94@outlook.com</v>
       </c>
       <c r="F250" t="str">
-        <v>(572) 305-7237</v>
+        <v>(101) 920-4176</v>
       </c>
       <c r="G250" t="str">
-        <v>Riverside</v>
+        <v>Stockton</v>
       </c>
       <c r="H250" t="str">
         <v>B</v>
@@ -8481,30 +8491,30 @@
         <v>available</v>
       </c>
       <c r="J250" t="str">
-        <v>Caleb Brown</v>
+        <v>Olivia Nelson, Madelyn Martinez</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>feb78ceb-dd95-455d-8b7d-fc0019ae54c8</v>
+        <v>35c73937-3dd5-4fb3-a5df-d900cabdacba</v>
       </c>
       <c r="B251" t="str">
-        <v>Isaiah Green</v>
+        <v>Jackson Murphy</v>
       </c>
       <c r="C251">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D251" t="str">
         <v>Male</v>
       </c>
       <c r="E251" t="str">
-        <v>isaiah.green52@icloud.com</v>
+        <v>jackson.murphy91@yahoo.com</v>
       </c>
       <c r="F251" t="str">
-        <v>(236) 625-9751</v>
+        <v>(572) 305-7237</v>
       </c>
       <c r="G251" t="str">
-        <v>Glendale</v>
+        <v>Riverside</v>
       </c>
       <c r="H251" t="str">
         <v>B</v>
@@ -8513,187 +8523,187 @@
         <v>available</v>
       </c>
       <c r="J251" t="str">
-        <v>Serenity Campbell, Jackson Jackson</v>
+        <v>Caleb Brown</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>e4b4c1c5-d581-43e6-89d9-d3cee5153165</v>
+        <v>feb78ceb-dd95-455d-8b7d-fc0019ae54c8</v>
       </c>
       <c r="B252" t="str">
-        <v>Josiah Brown</v>
+        <v>Isaiah Green</v>
       </c>
       <c r="C252">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D252" t="str">
         <v>Male</v>
       </c>
       <c r="E252" t="str">
-        <v>josiah.brown19@hotmail.com</v>
+        <v>isaiah.green52@icloud.com</v>
       </c>
       <c r="F252" t="str">
-        <v>(678) 449-3168</v>
+        <v>(236) 625-9751</v>
       </c>
       <c r="G252" t="str">
-        <v>Fresno</v>
+        <v>Glendale</v>
       </c>
       <c r="H252" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I252" t="str">
         <v>available</v>
       </c>
       <c r="J252" t="str">
-        <v>Piper Green</v>
+        <v>Serenity Campbell, Jackson Jackson</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>851b55ee-dbcd-4ef5-a339-de65c5176b45</v>
+        <v>e4b4c1c5-d581-43e6-89d9-d3cee5153165</v>
       </c>
       <c r="B253" t="str">
-        <v>Test Contestant 97</v>
+        <v>Josiah Brown</v>
       </c>
       <c r="C253">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D253" t="str">
         <v>Male</v>
       </c>
       <c r="E253" t="str">
-        <v>test.contestant.97@gmail.com</v>
+        <v>josiah.brown19@hotmail.com</v>
       </c>
       <c r="F253" t="str">
-        <v>(555) 679-1261</v>
+        <v>(678) 449-3168</v>
       </c>
       <c r="G253" t="str">
-        <v>Bakersfield</v>
+        <v>Fresno</v>
       </c>
       <c r="H253" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I253" t="str">
         <v>available</v>
+      </c>
+      <c r="J253" t="str">
+        <v>Piper Green</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>b28a73f8-5094-4b00-be67-223342b0e1d5</v>
+        <v>851b55ee-dbcd-4ef5-a339-de65c5176b45</v>
       </c>
       <c r="B254" t="str">
-        <v>Cora Lee</v>
+        <v>Test Contestant 97</v>
       </c>
       <c r="C254">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D254" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E254" t="str">
-        <v>cora.lee40@hotmail.com</v>
+        <v>test.contestant.97@gmail.com</v>
       </c>
       <c r="F254" t="str">
-        <v>(406) 886-5180</v>
+        <v>(555) 679-1261</v>
       </c>
       <c r="G254" t="str">
-        <v>Fresno</v>
+        <v>Bakersfield</v>
       </c>
       <c r="H254" t="str">
         <v>B</v>
       </c>
       <c r="I254" t="str">
         <v>available</v>
-      </c>
-      <c r="J254" t="str">
-        <v>Layla Lopez</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>f878ab7f-ae59-4af0-b19a-e9bf4573c116</v>
+        <v>b28a73f8-5094-4b00-be67-223342b0e1d5</v>
       </c>
       <c r="B255" t="str">
-        <v>William Allen</v>
+        <v>Cora Lee</v>
       </c>
       <c r="C255">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D255" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E255" t="str">
-        <v>william.allen62@hotmail.com</v>
+        <v>cora.lee40@hotmail.com</v>
       </c>
       <c r="F255" t="str">
-        <v>(267) 463-7481</v>
+        <v>(406) 886-5180</v>
       </c>
       <c r="G255" t="str">
-        <v>San Jose</v>
+        <v>Fresno</v>
       </c>
       <c r="H255" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I255" t="str">
         <v>available</v>
       </c>
       <c r="J255" t="str">
-        <v>Sadie Cook, Alexa Hall</v>
+        <v>Layla Lopez</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>ef837da0-c81f-4113-a389-db5e46ffaf4d</v>
+        <v>f878ab7f-ae59-4af0-b19a-e9bf4573c116</v>
       </c>
       <c r="B256" t="str">
-        <v>Aria Scott</v>
+        <v>William Allen</v>
       </c>
       <c r="C256">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D256" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E256" t="str">
-        <v>aria.scott42@outlook.com</v>
+        <v>william.allen62@hotmail.com</v>
       </c>
       <c r="F256" t="str">
-        <v>0401 330 548</v>
+        <v>(267) 463-7481</v>
       </c>
       <c r="G256" t="str">
-        <v>Hobart</v>
+        <v>San Jose</v>
       </c>
       <c r="H256" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I256" t="str">
         <v>available</v>
       </c>
       <c r="J256" t="str">
-        <v>Maya Hernandez</v>
+        <v>Sadie Cook, Alexa Hall</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>dd2de8e6-e7c9-40e4-8308-27a14e5f00da</v>
+        <v>ef837da0-c81f-4113-a389-db5e46ffaf4d</v>
       </c>
       <c r="B257" t="str">
-        <v>Chloe Jones</v>
+        <v>Aria Scott</v>
       </c>
       <c r="C257">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D257" t="str">
         <v>Female</v>
       </c>
       <c r="E257" t="str">
-        <v>chloe.jones20@outlook.com</v>
+        <v>aria.scott42@outlook.com</v>
       </c>
       <c r="F257" t="str">
-        <v>0411 294 635</v>
+        <v>0401 330 548</v>
       </c>
       <c r="G257" t="str">
-        <v>Toowoomba</v>
+        <v>Hobart</v>
       </c>
       <c r="H257" t="str">
         <v>B</v>
@@ -8702,62 +8712,65 @@
         <v>available</v>
       </c>
       <c r="J257" t="str">
-        <v>Zoe Brown</v>
+        <v>Maya Hernandez</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>7bfb9432-4b59-4ceb-895d-e03ae4837f91</v>
+        <v>dd2de8e6-e7c9-40e4-8308-27a14e5f00da</v>
       </c>
       <c r="B258" t="str">
-        <v>Joshua Walker</v>
+        <v>Chloe Jones</v>
       </c>
       <c r="C258">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D258" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E258" t="str">
-        <v>joshua.walker97@gmail.com</v>
+        <v>chloe.jones20@outlook.com</v>
       </c>
       <c r="F258" t="str">
-        <v>0402 640 379</v>
+        <v>0411 294 635</v>
       </c>
       <c r="G258" t="str">
-        <v>Darwin</v>
+        <v>Toowoomba</v>
       </c>
       <c r="H258" t="str">
         <v>B</v>
       </c>
       <c r="I258" t="str">
         <v>available</v>
+      </c>
+      <c r="J258" t="str">
+        <v>Zoe Brown</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>efe20d3d-2162-4ff8-a8ff-4102e5d3f3ab</v>
+        <v>7bfb9432-4b59-4ceb-895d-e03ae4837f91</v>
       </c>
       <c r="B259" t="str">
-        <v>Cameron Lee</v>
+        <v>Joshua Walker</v>
       </c>
       <c r="C259">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D259" t="str">
         <v>Male</v>
       </c>
       <c r="E259" t="str">
-        <v>cameron.lee78@yahoo.com</v>
+        <v>joshua.walker97@gmail.com</v>
       </c>
       <c r="F259" t="str">
-        <v>0404 821 708</v>
+        <v>0402 640 379</v>
       </c>
       <c r="G259" t="str">
-        <v>Cairns</v>
+        <v>Darwin</v>
       </c>
       <c r="H259" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I259" t="str">
         <v>available</v>
@@ -8765,89 +8778,86 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>8e30e99d-0594-4a73-840e-1f5ef32387ae</v>
+        <v>efe20d3d-2162-4ff8-a8ff-4102e5d3f3ab</v>
       </c>
       <c r="B260" t="str">
-        <v>Cameron Anderson</v>
+        <v>Cameron Lee</v>
       </c>
       <c r="C260">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D260" t="str">
         <v>Male</v>
       </c>
       <c r="E260" t="str">
-        <v>cameron.anderson85@hotmail.com</v>
+        <v>cameron.lee78@yahoo.com</v>
       </c>
       <c r="F260" t="str">
-        <v>(960) 363-1976</v>
+        <v>0404 821 708</v>
       </c>
       <c r="G260" t="str">
-        <v>Glendale</v>
+        <v>Cairns</v>
       </c>
       <c r="H260" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I260" t="str">
         <v>available</v>
-      </c>
-      <c r="J260" t="str">
-        <v>John Diaz</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>ba63a5c0-c76e-4c1b-b6e4-afed15dfdcd4</v>
+        <v>8e30e99d-0594-4a73-840e-1f5ef32387ae</v>
       </c>
       <c r="B261" t="str">
-        <v>Joseph Anderson</v>
+        <v>Cameron Anderson</v>
       </c>
       <c r="C261">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D261" t="str">
         <v>Male</v>
       </c>
       <c r="E261" t="str">
-        <v>joseph.anderson2@outlook.com</v>
+        <v>cameron.anderson85@hotmail.com</v>
       </c>
       <c r="F261" t="str">
-        <v>(433) 142-2338</v>
+        <v>(960) 363-1976</v>
       </c>
       <c r="G261" t="str">
-        <v>Chula Vista</v>
+        <v>Glendale</v>
       </c>
       <c r="H261" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I261" t="str">
         <v>available</v>
       </c>
       <c r="J261" t="str">
-        <v>Elizabeth Nelson, Grayson Edwards</v>
+        <v>John Diaz</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>1b5fc1ce-1ed8-4255-a8a4-b02892b2b03a</v>
+        <v>ba63a5c0-c76e-4c1b-b6e4-afed15dfdcd4</v>
       </c>
       <c r="B262" t="str">
-        <v>Ava Mitchell</v>
+        <v>Joseph Anderson</v>
       </c>
       <c r="C262">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D262" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E262" t="str">
-        <v>ava.mitchell87@icloud.com</v>
+        <v>joseph.anderson2@outlook.com</v>
       </c>
       <c r="F262" t="str">
-        <v>(211) 525-6721</v>
+        <v>(433) 142-2338</v>
       </c>
       <c r="G262" t="str">
-        <v>Santa Monica</v>
+        <v>Chula Vista</v>
       </c>
       <c r="H262" t="str">
         <v>B+</v>
@@ -8856,62 +8866,62 @@
         <v>available</v>
       </c>
       <c r="J262" t="str">
-        <v>Logan Lopez</v>
+        <v>Elizabeth Nelson, Grayson Edwards</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>1a539e8e-7b02-422a-991f-99fdb84688f5</v>
+        <v>1b5fc1ce-1ed8-4255-a8a4-b02892b2b03a</v>
       </c>
       <c r="B263" t="str">
+        <v>Ava Mitchell</v>
+      </c>
+      <c r="C263">
+        <v>56</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E263" t="str">
+        <v>ava.mitchell87@icloud.com</v>
+      </c>
+      <c r="F263" t="str">
+        <v>(211) 525-6721</v>
+      </c>
+      <c r="G263" t="str">
+        <v>Santa Monica</v>
+      </c>
+      <c r="H263" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I263" t="str">
+        <v>available</v>
+      </c>
+      <c r="J263" t="str">
         <v>Logan Lopez</v>
-      </c>
-      <c r="C263">
-        <v>50</v>
-      </c>
-      <c r="D263" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E263" t="str">
-        <v>logan.lopez66@icloud.com</v>
-      </c>
-      <c r="F263" t="str">
-        <v>(283) 498-3157</v>
-      </c>
-      <c r="G263" t="str">
-        <v>Burbank</v>
-      </c>
-      <c r="H263" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I263" t="str">
-        <v>available</v>
-      </c>
-      <c r="J263" t="str">
-        <v>Ava Mitchell</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>4f5756e4-c006-4d04-a9bc-7a2de0fdf149</v>
+        <v>1a539e8e-7b02-422a-991f-99fdb84688f5</v>
       </c>
       <c r="B264" t="str">
-        <v>Michael Johnson</v>
+        <v>Logan Lopez</v>
       </c>
       <c r="C264">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D264" t="str">
         <v>Male</v>
       </c>
       <c r="E264" t="str">
-        <v>michael.johnson96@gmail.com</v>
+        <v>logan.lopez66@icloud.com</v>
       </c>
       <c r="F264" t="str">
-        <v>(878) 132-4532</v>
+        <v>(283) 498-3157</v>
       </c>
       <c r="G264" t="str">
-        <v>Long Beach</v>
+        <v>Burbank</v>
       </c>
       <c r="H264" t="str">
         <v>B+</v>
@@ -8920,48 +8930,39 @@
         <v>available</v>
       </c>
       <c r="J264" t="str">
-        <v>Anthony Garcia, Cameron Evans</v>
+        <v>Ava Mitchell</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>0ccaf8bc-6ade-4ad6-9537-92f9829a6502</v>
+        <v>4f5756e4-c006-4d04-a9bc-7a2de0fdf149</v>
       </c>
       <c r="B265" t="str">
-        <v>Peter Adamidis</v>
+        <v>Michael Johnson</v>
       </c>
       <c r="C265">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D265" t="str">
-        <v>Not Specified</v>
+        <v>Male</v>
       </c>
       <c r="E265" t="str">
-        <v>peter.adamidis@gmail.com</v>
+        <v>michael.johnson96@gmail.com</v>
       </c>
       <c r="F265" t="str">
-        <v>498086080</v>
+        <v>(878) 132-4532</v>
       </c>
       <c r="G265" t="str">
-        <v/>
+        <v>Long Beach</v>
       </c>
       <c r="H265" t="str">
-        <v/>
+        <v>B+</v>
       </c>
       <c r="I265" t="str">
         <v>available</v>
       </c>
       <c r="J265" t="str">
-        <v>Kathleen Reynolds, Felicity Parker-Hill</v>
-      </c>
-      <c r="K265" t="str">
-        <v>5fe641da-4067-49a7-bae7-e63413b3e404</v>
-      </c>
-      <c r="L265" t="str">
-        <v>Y</v>
-      </c>
-      <c r="M265" t="str">
-        <v>Broken Leg</v>
+        <v>Anthony Garcia, Cameron Evans</v>
       </c>
     </row>
     <row r="266">
@@ -11402,6 +11403,60 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RecordDayID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ContestantID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Block</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Seat</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BookingEmailSent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ConfirmedRSVP</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>45e8f96c-780b-4952-8f47-967b01c54f1a</v>
+      </c>
+      <c r="B2" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>0ccaf8bc-6ade-4ad6-9537-92f9829a6502</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>A5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
@@ -11442,7 +11497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B39"/>
   <sheetData>
@@ -11765,7 +11820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>
@@ -12154,7 +12209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
-    <sheet name="Groups" sheetId="2" r:id="rId2"/>
-    <sheet name="Block Types" sheetId="3" r:id="rId3"/>
+    <sheet name="Contestants" sheetId="2" r:id="rId2"/>
+    <sheet name="Groups" sheetId="3" r:id="rId3"/>
+    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -665,33 +666,1764 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:M51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>ReferenceNumber</v>
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Age</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Location</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Rating</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>AttendingWith</v>
+      </c>
+      <c r="K1" t="str">
+        <v>GroupID</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MedicalInfo</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MobilityNotes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>f25a6094-c1a5-4eb4-a709-1cc3d9b3ab5e</v>
+        <v>efd8ab2e-988b-4afb-9374-3c3e3676f43a</v>
       </c>
       <c r="B2" t="str">
-        <v>GRP001</v>
+        <v>Matilda Sutherland</v>
+      </c>
+      <c r="C2">
+        <v>26</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E2" t="str">
+        <v>matilda.sutherland@hotmail.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0467 165 012</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Bundoora</v>
+      </c>
+      <c r="H2" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I2" t="str">
+        <v>available</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Grace Mann</v>
+      </c>
+      <c r="M2" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Brent Barnett</v>
+      </c>
+      <c r="C3">
+        <v>37</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E3" t="str">
+        <v>brentbarnett88@gmail.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v>423530043</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Preston</v>
+      </c>
+      <c r="H3" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I3" t="str">
+        <v>available</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Stephanie Squillacioti</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Tara Saltzman</v>
+      </c>
+      <c r="C4">
+        <v>29</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E4" t="str">
+        <v>tarasaltzman@bigpond.com</v>
+      </c>
+      <c r="F4" t="str">
+        <v>448545599</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H4" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I4" t="str">
+        <v>available</v>
+      </c>
+      <c r="J4" t="str">
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+      </c>
+      <c r="M4" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>96d2c8ad-1e67-4659-b3d0-a3bbd4fe40cb</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Karina  Richmond</v>
+      </c>
+      <c r="C5">
+        <v>38</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E5" t="str">
+        <v>richmondkarina@yahoo.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>400554609</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Newcomb</v>
+      </c>
+      <c r="H5" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I5" t="str">
+        <v>available</v>
+      </c>
+      <c r="J5" t="str">
+        <v>AMY DILLON</v>
+      </c>
+      <c r="M5" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Troy Smith</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Troyssmith94@gmail.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>429354308</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H6" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I6" t="str">
+        <v>available</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="K6" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L6" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M6" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Taylahuxtable@gmail.com</v>
+      </c>
+      <c r="F7" t="str">
+        <v>435320280</v>
+      </c>
+      <c r="G7" t="str">
+        <v>FERNTREE GULLY</v>
+      </c>
+      <c r="I7" t="str">
+        <v>available</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Troy Smith</v>
+      </c>
+      <c r="K7" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>7a05a613-1880-40c5-ab6a-cc078b418b6e</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Deb  Jones</v>
+      </c>
+      <c r="C8">
+        <v>66</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E8" t="str">
+        <v>fullhouse5@optusnet.com.au</v>
+      </c>
+      <c r="F8" t="str">
+        <v>438561474</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Bayswater North</v>
+      </c>
+      <c r="H8" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I8" t="str">
+        <v>available</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Daryl Jones</v>
+      </c>
+      <c r="M8" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Jeanette Quy</v>
+      </c>
+      <c r="C9">
+        <v>74</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E9" t="str">
+        <v>quyfamily@tpg.com.au</v>
+      </c>
+      <c r="F9" t="str">
+        <v>402902273</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Rowville</v>
+      </c>
+      <c r="H9" t="str">
+        <v>C</v>
+      </c>
+      <c r="I9" t="str">
+        <v>available</v>
+      </c>
+      <c r="M9" t="str">
+        <v xml:space="preserve">nothing of note </v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Philip Natoli</v>
+      </c>
+      <c r="C10">
+        <v>29</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Philip.natoli@outlook.com</v>
+      </c>
+      <c r="F10" t="str">
+        <v>466021882</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Caulfield South</v>
+      </c>
+      <c r="H10" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I10" t="str">
+        <v>available</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Hayley Wright</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Donna Collins</v>
+      </c>
+      <c r="C11">
+        <v>65</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Donna0@hotmail.com</v>
+      </c>
+      <c r="F11" t="str">
+        <v>408122305</v>
+      </c>
+      <c r="G11" t="str">
+        <v xml:space="preserve">Coburg </v>
+      </c>
+      <c r="H11" t="str">
+        <v>B</v>
+      </c>
+      <c r="I11" t="str">
+        <v>available</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Donna Collins, Tom Collins</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Thomas Mckenna</v>
+      </c>
+      <c r="C12">
+        <v>36</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E12" t="str">
+        <v>mckenna.6@yahoo.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>421758700</v>
+      </c>
+      <c r="G12" t="str">
+        <v xml:space="preserve">Officer South </v>
+      </c>
+      <c r="H12" t="str">
+        <v>B</v>
+      </c>
+      <c r="I12" t="str">
+        <v>available</v>
+      </c>
+      <c r="J12" t="str">
+        <v>thomas mckenna, Carolyn (Caz) Wilby</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Natasha Devers</v>
+      </c>
+      <c r="C13">
+        <v>22</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E13" t="str">
+        <v>natashadevers@gmail.com</v>
+      </c>
+      <c r="F13" t="str">
+        <v>484003770</v>
+      </c>
+      <c r="G13" t="str">
+        <v xml:space="preserve">Waterways </v>
+      </c>
+      <c r="H13" t="str">
+        <v>B</v>
+      </c>
+      <c r="I13" t="str">
+        <v>available</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Oliver Moran</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>fb6dd634-cefe-4cce-a1cc-af5d1677fdcb</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Elizabeth Schembri</v>
+      </c>
+      <c r="C14">
+        <v>69</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E14" t="str">
+        <v>e-schembri@hotmail.com</v>
+      </c>
+      <c r="F14" t="str">
+        <v>452177157</v>
+      </c>
+      <c r="G14" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H14" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I14" t="str">
+        <v>available</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Elizabeth Schembri, Gerard Hayward</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>dcd305dd-c710-4a1e-859c-835031154035</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Nicholas Boicos</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E15" t="str">
+        <v>nboicos@hotmail.com</v>
+      </c>
+      <c r="F15" t="str">
+        <v>429556400</v>
+      </c>
+      <c r="G15" t="str">
+        <v xml:space="preserve">Altona Meadows </v>
+      </c>
+      <c r="H15" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I15" t="str">
+        <v>available</v>
+      </c>
+      <c r="J15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nick Boicos 
+Matthew Boicos
+Brothers</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>09dbfbb4-9f89-44a1-95f3-10cc82ec732a</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Gianni De Pasquale</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E16" t="str">
+        <v>gdp762.0@gmail.com</v>
+      </c>
+      <c r="F16" t="str">
+        <v>481978762</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Werribee</v>
+      </c>
+      <c r="H16" t="str">
+        <v>A</v>
+      </c>
+      <c r="I16" t="str">
+        <v>available</v>
+      </c>
+      <c r="J16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Gianni De Pasquale
+Carmela De Pasquale
+Francesco De Pasquale</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Ricky Steve</v>
+      </c>
+      <c r="C17">
+        <v>31</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E17" t="str">
+        <v>tj-c-a@hotmail.com</v>
+      </c>
+      <c r="F17" t="str">
+        <v>411360449</v>
+      </c>
+      <c r="G17" t="str">
+        <v xml:space="preserve">Wangaratta </v>
+      </c>
+      <c r="H17" t="str">
+        <v>A</v>
+      </c>
+      <c r="I17" t="str">
+        <v>available</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Taylah-Jayne Lockery</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sharon King</v>
+      </c>
+      <c r="C18">
+        <v>58</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E18" t="str">
+        <v>dreamweaversixtyseven@gmail.com</v>
+      </c>
+      <c r="F18" t="str">
+        <v>611488000000</v>
+      </c>
+      <c r="G18" t="str">
+        <v xml:space="preserve">Mooroopna </v>
+      </c>
+      <c r="H18" t="str">
+        <v>A</v>
+      </c>
+      <c r="I18" t="str">
+        <v>available</v>
+      </c>
+      <c r="J18" t="str" xml:space="preserve">
+        <v xml:space="preserve">
+Friend :Jacinda Austin
+ID:b6042a-1-1936475</v>
+      </c>
+      <c r="M18" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sarah Desira</v>
+      </c>
+      <c r="C19">
+        <v>38</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E19" t="str">
+        <v>unicornwolf11@gmail.com</v>
+      </c>
+      <c r="F19" t="str">
+        <v>450765125</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Lara</v>
+      </c>
+      <c r="H19" t="str">
+        <v>B</v>
+      </c>
+      <c r="I19" t="str">
+        <v>available</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Husband Daniel Desira b6042a-1-1936280</v>
+      </c>
+      <c r="M19" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+      </c>
+      <c r="B20" t="str">
+        <v>David Fenwick</v>
+      </c>
+      <c r="C20">
+        <v>36</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E20" t="str">
+        <v>David.s.fenwick@gmail.com</v>
+      </c>
+      <c r="F20" t="str">
+        <v>429811171</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Teesdale</v>
+      </c>
+      <c r="H20" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I20" t="str">
+        <v>available</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Anna Fonua</v>
+      </c>
+      <c r="C21">
+        <v>36</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Annawallace89@hotmail.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v>452452442</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Truganina</v>
+      </c>
+      <c r="H21" t="str">
+        <v>A</v>
+      </c>
+      <c r="I21" t="str">
+        <v>available</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Dad Michael Wallace - b6042a-1-1936372</v>
+      </c>
+      <c r="M21" t="str">
+        <v xml:space="preserve">no </v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>1d96e742-18bb-4fc0-b741-154d1a4d9487</v>
+      </c>
+      <c r="B22" t="str">
+        <v>James Butler</v>
+      </c>
+      <c r="C22">
+        <v>42</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E22" t="str">
+        <v>butlerjg1509@gmail.com</v>
+      </c>
+      <c r="F22" t="str">
+        <v>428400584</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Mentone</v>
+      </c>
+      <c r="H22" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I22" t="str">
+        <v>available</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Issy McReynolds</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Mara Baumgardner</v>
+      </c>
+      <c r="C23">
+        <v>40</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Granic@hotmail.com</v>
+      </c>
+      <c r="F23" t="str">
+        <v>407364450</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Cockatoo</v>
+      </c>
+      <c r="H23" t="str">
+        <v>B</v>
+      </c>
+      <c r="I23" t="str">
+        <v>available</v>
+      </c>
+      <c r="J23" t="str">
+        <v xml:space="preserve">Mum - Mira Granic </v>
+      </c>
+      <c r="M23" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Eden Hayes</v>
+      </c>
+      <c r="C24">
+        <v>21</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E24" t="str">
+        <v>edenhayes19@gmail.com</v>
+      </c>
+      <c r="F24" t="str">
+        <v>448096139</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Elwood</v>
+      </c>
+      <c r="H24" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I24" t="str">
+        <v>available</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Jackson Harris</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Antonio Freno</v>
+      </c>
+      <c r="C25">
+        <v>39</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E25" t="str">
+        <v>frenoantonio@hotmail.it</v>
+      </c>
+      <c r="F25" t="str">
+        <v>422177371</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Glenroy</v>
+      </c>
+      <c r="H25" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I25" t="str">
+        <v>available</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Kiran Rao</v>
+      </c>
+      <c r="C26">
+        <v>35</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E26" t="str">
+        <v>kiran.rao07@gmail.com</v>
+      </c>
+      <c r="F26" t="str">
+        <v>420486042</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Southbank</v>
+      </c>
+      <c r="H26" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I26" t="str">
+        <v>available</v>
+      </c>
+      <c r="J26" t="str">
+        <v>SOLO</v>
+      </c>
+      <c r="M26" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Kerrie Donald</v>
+      </c>
+      <c r="C27">
+        <v>47</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E27" t="str">
+        <v>kerrieldonald@hotmail.com</v>
+      </c>
+      <c r="F27" t="str">
+        <v>61400826565</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Mailor's Flat</v>
+      </c>
+      <c r="H27" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I27" t="str">
+        <v>available</v>
+      </c>
+      <c r="J27" t="str">
+        <v>kerrie donald, alistair donald</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Tamara Mifsud</v>
+      </c>
+      <c r="C28">
+        <v>32</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E28" t="str">
+        <v>tamara.mifsud@hotmail.com</v>
+      </c>
+      <c r="F28" t="str">
+        <v>416552122</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Aintree</v>
+      </c>
+      <c r="H28" t="str">
+        <v>B</v>
+      </c>
+      <c r="I28" t="str">
+        <v>available</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Aliye Abcilar</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Linda Browne</v>
+      </c>
+      <c r="C29">
+        <v>54</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Lindabrowne@iprimus.com.au</v>
+      </c>
+      <c r="F29" t="str">
+        <v>429570177</v>
+      </c>
+      <c r="G29" t="str">
+        <v>OFFICER</v>
+      </c>
+      <c r="H29" t="str">
+        <v>B</v>
+      </c>
+      <c r="I29" t="str">
+        <v>available</v>
+      </c>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Natalie Browne
+Linda Browne
+Aidan Miler</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Meenakshi  Mehra</v>
+      </c>
+      <c r="C30">
+        <v>62</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E30" t="str">
+        <v>meenu.mehra@bigpond.com</v>
+      </c>
+      <c r="F30" t="str">
+        <v>420353322</v>
+      </c>
+      <c r="G30" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H30" t="str">
+        <v>B</v>
+      </c>
+      <c r="I30" t="str">
+        <v>available</v>
+      </c>
+      <c r="J30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Meenakshi Mehra
+Dhananjay Mehra</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>8a905dfd-647c-4d96-a741-f7f1517a5136</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Deanna Hay</v>
+      </c>
+      <c r="C31">
+        <v>38</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E31" t="str">
+        <v>dee_hay24@hotmail.com</v>
+      </c>
+      <c r="F31" t="str">
+        <v>424504430</v>
+      </c>
+      <c r="G31" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H31" t="str">
+        <v>DNU</v>
+      </c>
+      <c r="I31" t="str">
+        <v>available</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Lynetta Shan Faoa</v>
+      </c>
+      <c r="L31" t="str">
+        <v xml:space="preserve">Cerebral palsy in a wheelchair </v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Kayla Lorenzini</v>
+      </c>
+      <c r="C32">
+        <v>29</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E32" t="str">
+        <v>kaylalorenzini_@hotmail.com</v>
+      </c>
+      <c r="F32" t="str">
+        <v>430517653</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H32" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I32" t="str">
+        <v>available</v>
+      </c>
+      <c r="J32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Kayla Lorenzini
+James Lorenzini
+Deanna Gramola</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Mozgda  Alime</v>
+      </c>
+      <c r="C33">
+        <v>39</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E33" t="str">
+        <v>smalimi@hotmail.com</v>
+      </c>
+      <c r="F33" t="str">
+        <v>402010235</v>
+      </c>
+      <c r="G33" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H33" t="str">
+        <v>C</v>
+      </c>
+      <c r="I33" t="str">
+        <v>available</v>
+      </c>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Sadaf Almini - I believe this is her cousin 
+Lida Alime - I believe this is her cousin or sister 
+Ahmad Alime - Ahmad is Lina's husband </v>
+      </c>
+      <c r="M33" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>94b19240-6aee-4af6-ac66-0ebdb5e4403c</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Scott Clark</v>
+      </c>
+      <c r="C34">
+        <v>54</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E34" t="str">
+        <v>sclarkfitness@optusnet.com.au</v>
+      </c>
+      <c r="F34" t="str">
+        <v>448073035</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H34" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I34" t="str">
+        <v>available</v>
+      </c>
+      <c r="J34" t="str">
+        <v xml:space="preserve">Would bring someone </v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Angela Verspay</v>
+      </c>
+      <c r="C35">
+        <v>45</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E35" t="str">
+        <v>angelarileysmyth@hotmail.com</v>
+      </c>
+      <c r="F35" t="str">
+        <v>477660119</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Warrnambool</v>
+      </c>
+      <c r="H35" t="str">
+        <v>B</v>
+      </c>
+      <c r="I35" t="str">
+        <v>available</v>
+      </c>
+      <c r="J35" t="str">
+        <v>SOLO</v>
+      </c>
+      <c r="M35" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>eb3b2a7d-e6b0-421b-8987-00bfff95dda9</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Jasmine Miller</v>
+      </c>
+      <c r="C36">
+        <v>32</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E36" t="str">
+        <v>jasmine_courtney@hotmail.com</v>
+      </c>
+      <c r="F36" t="str">
+        <v>0432 387 712</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Hughesdale</v>
+      </c>
+      <c r="H36" t="str">
+        <v>C</v>
+      </c>
+      <c r="I36" t="str">
+        <v>available</v>
+      </c>
+      <c r="J36" t="str">
+        <v>ablo - partner</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Sherif Haggag</v>
+      </c>
+      <c r="C37">
+        <v>38</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Shaggag87@gmail.com</v>
+      </c>
+      <c r="F37" t="str">
+        <v>426233449</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Belmont</v>
+      </c>
+      <c r="H37" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I37" t="str">
+        <v>available</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>300ac025-db3a-42ba-a9dd-777f02fb3454</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Jeanette Quy</v>
+      </c>
+      <c r="C38">
+        <v>74</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E38" t="str">
+        <v>koalaleaf@hotmail.com</v>
+      </c>
+      <c r="F38" t="str">
+        <v>402902273</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Rowville</v>
+      </c>
+      <c r="H38" t="str">
+        <v>C</v>
+      </c>
+      <c r="I38" t="str">
+        <v>available</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Husband Ted Quy b6042a-1-1872960</v>
+      </c>
+      <c r="M38" t="str">
+        <v xml:space="preserve">Nothing of note </v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>0ea22efb-f85f-400a-b28d-d1312568ba67</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Jess Cossari</v>
+      </c>
+      <c r="C39">
+        <v>35</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Jcossari@hotmail.com</v>
+      </c>
+      <c r="F39" t="str">
+        <v xml:space="preserve">0458 746 551 </v>
+      </c>
+      <c r="G39" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H39" t="str">
+        <v>C</v>
+      </c>
+      <c r="I39" t="str">
+        <v>available</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Andrea Cocco</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Leanne Bryant</v>
+      </c>
+      <c r="C40">
+        <v>63</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E40" t="str">
+        <v>blazeandcougar@gmail.com</v>
+      </c>
+      <c r="F40" t="str">
+        <v>61415438228</v>
+      </c>
+      <c r="G40" t="str">
+        <v xml:space="preserve">Hampton Park </v>
+      </c>
+      <c r="H40" t="str">
+        <v>B</v>
+      </c>
+      <c r="I40" t="str">
+        <v>available</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Bashar Mona</v>
+      </c>
+      <c r="C41">
+        <v>33</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E41" t="str">
+        <v>bashar.mona92@gmail.com</v>
+      </c>
+      <c r="F41" t="str">
+        <v>490871416</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Roxburgh park</v>
+      </c>
+      <c r="H41" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I41" t="str">
+        <v>available</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Alexander Leonard</v>
+      </c>
+      <c r="C42">
+        <v>38</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E42" t="str">
+        <v>alexleonardedit@gmail.com</v>
+      </c>
+      <c r="F42" t="str">
+        <v>421834476</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Croydon</v>
+      </c>
+      <c r="H42" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I42" t="str">
+        <v>available</v>
+      </c>
+      <c r="J42" t="str">
+        <v>melissa francis, Alexander Leonard</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Kadisha  Bruton</v>
+      </c>
+      <c r="C43">
+        <v>23</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E43" t="str">
+        <v>kadishaann@icloud.com</v>
+      </c>
+      <c r="F43" t="str">
+        <v>434829249</v>
+      </c>
+      <c r="G43" t="str">
+        <v xml:space="preserve">Kurunjang </v>
+      </c>
+      <c r="H43" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I43" t="str">
+        <v>available</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Jacob Steele</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Sharyn  McKinnis</v>
+      </c>
+      <c r="C44">
+        <v>50</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E44" t="str">
+        <v>s.lmckinnis@bigpond.com</v>
+      </c>
+      <c r="F44" t="str">
+        <v>419880873</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Newtown</v>
+      </c>
+      <c r="H44" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I44" t="str">
+        <v>available</v>
+      </c>
+      <c r="J44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Isabelle McKinnis, Sharyn McKinnis
+</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Paige Greig</v>
+      </c>
+      <c r="C45">
+        <v>31</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E45" t="str">
+        <v>paigegreig@hotmail.com</v>
+      </c>
+      <c r="F45" t="str">
+        <v>406598552</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Mooroolbark</v>
+      </c>
+      <c r="H45" t="str">
+        <v>C</v>
+      </c>
+      <c r="I45" t="str">
+        <v>available</v>
+      </c>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Erin
+Morgan (sister) - need to do application</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>cfd3f567-ab69-4fa9-8a35-ca9c949fba91</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Michael Stevens</v>
+      </c>
+      <c r="C46">
+        <v>32</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E46" t="str">
+        <v>mjstevens1306@gmail.com</v>
+      </c>
+      <c r="F46" t="str">
+        <v>424659733</v>
+      </c>
+      <c r="G46" t="str">
+        <v xml:space="preserve">Heathcote Junction </v>
+      </c>
+      <c r="H46" t="str">
+        <v>A</v>
+      </c>
+      <c r="I46" t="str">
+        <v>available</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Libby Dunbar</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>f50d5074-9b3e-4386-9039-5e4cbd121267</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Keera Bell</v>
+      </c>
+      <c r="C47">
+        <v>44</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Keera_b@hotmail.com</v>
+      </c>
+      <c r="F47" t="str">
+        <v>404754383</v>
+      </c>
+      <c r="G47" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H47" t="str">
+        <v>B</v>
+      </c>
+      <c r="I47" t="str">
+        <v>available</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Dek Bell</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Tamika Colville</v>
+      </c>
+      <c r="C48">
+        <v>31</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E48" t="str">
+        <v>tamika.colville@gmail.com</v>
+      </c>
+      <c r="F48" t="str">
+        <v>409132141</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Golden square</v>
+      </c>
+      <c r="H48" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I48" t="str">
+        <v>available</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Shinae Colville</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Diagnosed with MS in 2018</v>
+      </c>
+      <c r="M48" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>0b96f877-e1c4-4c17-aa89-21b4a5f7f002</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Stephen Deacon</v>
+      </c>
+      <c r="C49">
+        <v>67</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E49" t="str">
+        <v>StephenDeacon@duck.com</v>
+      </c>
+      <c r="F49" t="str">
+        <v>435353108</v>
+      </c>
+      <c r="G49" t="str">
+        <v>St Kilda</v>
+      </c>
+      <c r="H49" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I49" t="str">
+        <v>available</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Chanyapach Deacon</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Dhananjay  Mehra</v>
+      </c>
+      <c r="C50">
+        <v>68</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Dmehra@bigpond.net.au</v>
+      </c>
+      <c r="F50" t="str">
+        <v>419353328</v>
+      </c>
+      <c r="G50" t="str">
+        <v xml:space="preserve">Point Cook </v>
+      </c>
+      <c r="H50" t="str">
+        <v>B</v>
+      </c>
+      <c r="I50" t="str">
+        <v>available</v>
+      </c>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">Meenakshi Mehra
+Dhananjay Mehra</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Bronwyn Parsons</v>
+      </c>
+      <c r="C51">
+        <v>72</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Babybear61153@gmail.com</v>
+      </c>
+      <c r="F51" t="str">
+        <v>432543647</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Rosebud</v>
+      </c>
+      <c r="H51" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I51" t="str">
+        <v>available</v>
+      </c>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yolette Huon - yol-et Hue on
+Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ReferenceNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>f25a6094-c1a5-4eb4-a709-1cc3d9b3ab5e</v>
+      </c>
+      <c r="B2" t="str">
+        <v>GRP001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="B3" t="str">
+        <v>GRP002</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>
     <row r="1">

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -711,235 +711,229 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>efd8ab2e-988b-4afb-9374-3c3e3676f43a</v>
+        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
       </c>
       <c r="B2" t="str">
-        <v>Matilda Sutherland</v>
+        <v>Donna Collins</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D2" t="str">
         <v>Female</v>
       </c>
       <c r="E2" t="str">
-        <v>matilda.sutherland@hotmail.com</v>
+        <v>Donna0@hotmail.com</v>
       </c>
       <c r="F2" t="str">
-        <v>0467 165 012</v>
+        <v>408122305</v>
       </c>
       <c r="G2" t="str">
-        <v>Bundoora</v>
+        <v xml:space="preserve">Coburg </v>
       </c>
       <c r="H2" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I2" t="str">
         <v>available</v>
       </c>
       <c r="J2" t="str">
-        <v>Grace Mann</v>
-      </c>
-      <c r="M2" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>Donna Collins, Tom Collins</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
       </c>
       <c r="B3" t="str">
-        <v>Brent Barnett</v>
+        <v>Meenakshi  Mehra</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D3" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E3" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>meenu.mehra@bigpond.com</v>
       </c>
       <c r="F3" t="str">
-        <v>423530043</v>
+        <v>420353322</v>
       </c>
       <c r="G3" t="str">
-        <v>Preston</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H3" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I3" t="str">
         <v>available</v>
       </c>
-      <c r="J3" t="str">
-        <v>Stephanie Squillacioti</v>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Meenakshi Mehra
+Dhananjay Mehra</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B4" t="str">
-        <v>Tara Saltzman</v>
+        <v>Tayla Huxtable</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="str">
         <v>Female</v>
       </c>
       <c r="E4" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>Taylahuxtable@gmail.com</v>
       </c>
       <c r="F4" t="str">
-        <v>448545599</v>
+        <v>435320280</v>
       </c>
       <c r="G4" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H4" t="str">
-        <v>B+</v>
+        <v>FERNTREE GULLY</v>
       </c>
       <c r="I4" t="str">
         <v>available</v>
       </c>
       <c r="J4" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
-      </c>
-      <c r="M4" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>Troy Smith</v>
+      </c>
+      <c r="K4" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>96d2c8ad-1e67-4659-b3d0-a3bbd4fe40cb</v>
+        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
       </c>
       <c r="B5" t="str">
-        <v>Karina  Richmond</v>
+        <v>Sharon King</v>
       </c>
       <c r="C5">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D5" t="str">
         <v>Female</v>
       </c>
       <c r="E5" t="str">
-        <v>richmondkarina@yahoo.com</v>
+        <v>dreamweaversixtyseven@gmail.com</v>
       </c>
       <c r="F5" t="str">
-        <v>400554609</v>
+        <v>611488000000</v>
       </c>
       <c r="G5" t="str">
-        <v>Newcomb</v>
+        <v xml:space="preserve">Mooroopna </v>
       </c>
       <c r="H5" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I5" t="str">
         <v>available</v>
       </c>
-      <c r="J5" t="str">
-        <v>AMY DILLON</v>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">
+Friend :Jacinda Austin
+ID:b6042a-1-1936475</v>
       </c>
       <c r="M5" t="str">
-        <v>NA</v>
+        <v xml:space="preserve">No </v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>8a905dfd-647c-4d96-a741-f7f1517a5136</v>
       </c>
       <c r="B6" t="str">
-        <v>Troy Smith</v>
+        <v>Deanna Hay</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D6" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E6" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>dee_hay24@hotmail.com</v>
       </c>
       <c r="F6" t="str">
-        <v>429354308</v>
+        <v>424504430</v>
       </c>
       <c r="G6" t="str">
-        <v>Melbourne</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H6" t="str">
-        <v>B+</v>
+        <v>DNU</v>
       </c>
       <c r="I6" t="str">
         <v>available</v>
       </c>
       <c r="J6" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="K6" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+        <v>Lynetta Shan Faoa</v>
       </c>
       <c r="L6" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
-      </c>
-      <c r="M6" t="str">
-        <v>NA</v>
+        <v xml:space="preserve">Cerebral palsy in a wheelchair </v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>efd8ab2e-988b-4afb-9374-3c3e3676f43a</v>
       </c>
       <c r="B7" t="str">
-        <v>Tayla Huxtable</v>
+        <v>Matilda Sutherland</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" t="str">
         <v>Female</v>
       </c>
       <c r="E7" t="str">
-        <v>Taylahuxtable@gmail.com</v>
+        <v>matilda.sutherland@hotmail.com</v>
       </c>
       <c r="F7" t="str">
-        <v>435320280</v>
+        <v>0467 165 012</v>
       </c>
       <c r="G7" t="str">
-        <v>FERNTREE GULLY</v>
+        <v>Bundoora</v>
+      </c>
+      <c r="H7" t="str">
+        <v>B+</v>
       </c>
       <c r="I7" t="str">
         <v>available</v>
       </c>
       <c r="J7" t="str">
-        <v>Troy Smith</v>
-      </c>
-      <c r="K7" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+        <v>Grace Mann</v>
+      </c>
+      <c r="M7" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7a05a613-1880-40c5-ab6a-cc078b418b6e</v>
+        <v>96d2c8ad-1e67-4659-b3d0-a3bbd4fe40cb</v>
       </c>
       <c r="B8" t="str">
-        <v>Deb  Jones</v>
+        <v>Karina  Richmond</v>
       </c>
       <c r="C8">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="D8" t="str">
         <v>Female</v>
       </c>
       <c r="E8" t="str">
-        <v>fullhouse5@optusnet.com.au</v>
+        <v>richmondkarina@yahoo.com</v>
       </c>
       <c r="F8" t="str">
-        <v>438561474</v>
+        <v>400554609</v>
       </c>
       <c r="G8" t="str">
-        <v>Bayswater North</v>
+        <v>Newcomb</v>
       </c>
       <c r="H8" t="str">
         <v>B+</v>
@@ -948,65 +942,68 @@
         <v>available</v>
       </c>
       <c r="J8" t="str">
-        <v>Daryl Jones</v>
+        <v>AMY DILLON</v>
       </c>
       <c r="M8" t="str">
-        <v>No</v>
+        <v>NA</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
+        <v>7a05a613-1880-40c5-ab6a-cc078b418b6e</v>
       </c>
       <c r="B9" t="str">
-        <v>Jeanette Quy</v>
+        <v>Deb  Jones</v>
       </c>
       <c r="C9">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D9" t="str">
         <v>Female</v>
       </c>
       <c r="E9" t="str">
-        <v>quyfamily@tpg.com.au</v>
+        <v>fullhouse5@optusnet.com.au</v>
       </c>
       <c r="F9" t="str">
-        <v>402902273</v>
+        <v>438561474</v>
       </c>
       <c r="G9" t="str">
-        <v>Rowville</v>
+        <v>Bayswater North</v>
       </c>
       <c r="H9" t="str">
-        <v>C</v>
+        <v>B+</v>
       </c>
       <c r="I9" t="str">
         <v>available</v>
       </c>
+      <c r="J9" t="str">
+        <v>Daryl Jones</v>
+      </c>
       <c r="M9" t="str">
-        <v xml:space="preserve">nothing of note </v>
+        <v>No</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
       </c>
       <c r="B10" t="str">
-        <v>Philip Natoli</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C10">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D10" t="str">
         <v>Male</v>
       </c>
       <c r="E10" t="str">
-        <v>Philip.natoli@outlook.com</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>466021882</v>
+        <v>423530043</v>
       </c>
       <c r="G10" t="str">
-        <v>Caulfield South</v>
+        <v>Preston</v>
       </c>
       <c r="H10" t="str">
         <v>B+</v>
@@ -1015,1169 +1012,1177 @@
         <v>available</v>
       </c>
       <c r="J10" t="str">
-        <v>Hayley Wright</v>
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
       </c>
       <c r="B11" t="str">
-        <v>Donna Collins</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C11">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D11" t="str">
         <v>Female</v>
       </c>
       <c r="E11" t="str">
-        <v>Donna0@hotmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F11" t="str">
-        <v>408122305</v>
+        <v>448545599</v>
       </c>
       <c r="G11" t="str">
-        <v xml:space="preserve">Coburg </v>
+        <v>Melbourne</v>
       </c>
       <c r="H11" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I11" t="str">
         <v>available</v>
       </c>
       <c r="J11" t="str">
-        <v>Donna Collins, Tom Collins</v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+      </c>
+      <c r="M11" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B12" t="str">
-        <v>Thomas Mckenna</v>
+        <v>Troy Smith</v>
       </c>
       <c r="C12">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D12" t="str">
         <v>Male</v>
       </c>
       <c r="E12" t="str">
-        <v>mckenna.6@yahoo.com</v>
+        <v>Troyssmith94@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>421758700</v>
+        <v>429354308</v>
       </c>
       <c r="G12" t="str">
-        <v xml:space="preserve">Officer South </v>
+        <v>Melbourne</v>
       </c>
       <c r="H12" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I12" t="str">
         <v>available</v>
       </c>
       <c r="J12" t="str">
-        <v>thomas mckenna, Carolyn (Caz) Wilby</v>
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="K12" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L12" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M12" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
+        <v>fb6dd634-cefe-4cce-a1cc-af5d1677fdcb</v>
       </c>
       <c r="B13" t="str">
-        <v>Natasha Devers</v>
+        <v>Elizabeth Schembri</v>
       </c>
       <c r="C13">
+        <v>69</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E13" t="str">
+        <v>e-schembri@hotmail.com</v>
+      </c>
+      <c r="F13" t="str">
+        <v>452177157</v>
+      </c>
+      <c r="G13" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H13" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I13" t="str">
+        <v>available</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Elizabeth Schembri, Gerard Hayward</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>09dbfbb4-9f89-44a1-95f3-10cc82ec732a</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Gianni De Pasquale</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E14" t="str">
+        <v>gdp762.0@gmail.com</v>
+      </c>
+      <c r="F14" t="str">
+        <v>481978762</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Werribee</v>
+      </c>
+      <c r="H14" t="str">
+        <v>A</v>
+      </c>
+      <c r="I14" t="str">
+        <v>available</v>
+      </c>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Gianni De Pasquale
+Carmela De Pasquale
+Francesco De Pasquale</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sarah Desira</v>
+      </c>
+      <c r="C15">
+        <v>38</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E15" t="str">
+        <v>unicornwolf11@gmail.com</v>
+      </c>
+      <c r="F15" t="str">
+        <v>450765125</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Lara</v>
+      </c>
+      <c r="H15" t="str">
+        <v>B</v>
+      </c>
+      <c r="I15" t="str">
+        <v>available</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Husband Daniel Desira b6042a-1-1936280</v>
+      </c>
+      <c r="M15" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Anna Fonua</v>
+      </c>
+      <c r="C16">
+        <v>36</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Annawallace89@hotmail.com</v>
+      </c>
+      <c r="F16" t="str">
+        <v>452452442</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Truganina</v>
+      </c>
+      <c r="H16" t="str">
+        <v>A</v>
+      </c>
+      <c r="I16" t="str">
+        <v>available</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Dad Michael Wallace - b6042a-1-1936372</v>
+      </c>
+      <c r="M16" t="str">
+        <v xml:space="preserve">no </v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+      </c>
+      <c r="B17" t="str">
+        <v>David Fenwick</v>
+      </c>
+      <c r="C17">
+        <v>36</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E17" t="str">
+        <v>David.s.fenwick@gmail.com</v>
+      </c>
+      <c r="F17" t="str">
+        <v>429811171</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Teesdale</v>
+      </c>
+      <c r="H17" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I17" t="str">
+        <v>available</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>1d96e742-18bb-4fc0-b741-154d1a4d9487</v>
+      </c>
+      <c r="B18" t="str">
+        <v>James Butler</v>
+      </c>
+      <c r="C18">
+        <v>42</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E18" t="str">
+        <v>butlerjg1509@gmail.com</v>
+      </c>
+      <c r="F18" t="str">
+        <v>428400584</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Mentone</v>
+      </c>
+      <c r="H18" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I18" t="str">
+        <v>available</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Issy McReynolds</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Mara Baumgardner</v>
+      </c>
+      <c r="C19">
+        <v>40</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Granic@hotmail.com</v>
+      </c>
+      <c r="F19" t="str">
+        <v>407364450</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Cockatoo</v>
+      </c>
+      <c r="H19" t="str">
+        <v>B</v>
+      </c>
+      <c r="I19" t="str">
+        <v>available</v>
+      </c>
+      <c r="J19" t="str">
+        <v xml:space="preserve">Mum - Mira Granic </v>
+      </c>
+      <c r="M19" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Eden Hayes</v>
+      </c>
+      <c r="C20">
+        <v>21</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E20" t="str">
+        <v>edenhayes19@gmail.com</v>
+      </c>
+      <c r="F20" t="str">
+        <v>448096139</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Elwood</v>
+      </c>
+      <c r="H20" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I20" t="str">
+        <v>available</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Jackson Harris</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Kiran Rao</v>
+      </c>
+      <c r="C21">
+        <v>35</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E21" t="str">
+        <v>kiran.rao07@gmail.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v>420486042</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Southbank</v>
+      </c>
+      <c r="H21" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I21" t="str">
+        <v>available</v>
+      </c>
+      <c r="J21" t="str">
+        <v>SOLO</v>
+      </c>
+      <c r="M21" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Kayla Lorenzini</v>
+      </c>
+      <c r="C22">
+        <v>29</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E22" t="str">
+        <v>kaylalorenzini_@hotmail.com</v>
+      </c>
+      <c r="F22" t="str">
+        <v>430517653</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H22" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I22" t="str">
+        <v>available</v>
+      </c>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Kayla Lorenzini
+James Lorenzini
+Deanna Gramola</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Kerrie Donald</v>
+      </c>
+      <c r="C23">
+        <v>47</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E23" t="str">
+        <v>kerrieldonald@hotmail.com</v>
+      </c>
+      <c r="F23" t="str">
+        <v>61400826565</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Mailor's Flat</v>
+      </c>
+      <c r="H23" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I23" t="str">
+        <v>available</v>
+      </c>
+      <c r="J23" t="str">
+        <v>kerrie donald, alistair donald</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Tamara Mifsud</v>
+      </c>
+      <c r="C24">
+        <v>32</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E24" t="str">
+        <v>tamara.mifsud@hotmail.com</v>
+      </c>
+      <c r="F24" t="str">
+        <v>416552122</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Aintree</v>
+      </c>
+      <c r="H24" t="str">
+        <v>B</v>
+      </c>
+      <c r="I24" t="str">
+        <v>available</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Aliye Abcilar</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Philip Natoli</v>
+      </c>
+      <c r="C25">
+        <v>29</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Philip.natoli@outlook.com</v>
+      </c>
+      <c r="F25" t="str">
+        <v>466021882</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Caulfield South</v>
+      </c>
+      <c r="H25" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I25" t="str">
+        <v>available</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Hayley Wright</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Jeanette Quy</v>
+      </c>
+      <c r="C26">
+        <v>74</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E26" t="str">
+        <v>quyfamily@tpg.com.au</v>
+      </c>
+      <c r="F26" t="str">
+        <v>402902273</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Rowville</v>
+      </c>
+      <c r="H26" t="str">
+        <v>C</v>
+      </c>
+      <c r="I26" t="str">
+        <v>available</v>
+      </c>
+      <c r="M26" t="str">
+        <v xml:space="preserve">nothing of note </v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>dcd305dd-c710-4a1e-859c-835031154035</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Nicholas Boicos</v>
+      </c>
+      <c r="C27">
         <v>22</v>
       </c>
-      <c r="D13" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E13" t="str">
-        <v>natashadevers@gmail.com</v>
-      </c>
-      <c r="F13" t="str">
-        <v>484003770</v>
-      </c>
-      <c r="G13" t="str">
-        <v xml:space="preserve">Waterways </v>
-      </c>
-      <c r="H13" t="str">
-        <v>B</v>
-      </c>
-      <c r="I13" t="str">
-        <v>available</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Oliver Moran</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>fb6dd634-cefe-4cce-a1cc-af5d1677fdcb</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Elizabeth Schembri</v>
-      </c>
-      <c r="C14">
-        <v>69</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E14" t="str">
-        <v>e-schembri@hotmail.com</v>
-      </c>
-      <c r="F14" t="str">
-        <v>452177157</v>
-      </c>
-      <c r="G14" t="str">
-        <v xml:space="preserve">Melbourne </v>
-      </c>
-      <c r="H14" t="str">
+      <c r="D27" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E27" t="str">
+        <v>nboicos@hotmail.com</v>
+      </c>
+      <c r="F27" t="str">
+        <v>429556400</v>
+      </c>
+      <c r="G27" t="str">
+        <v xml:space="preserve">Altona Meadows </v>
+      </c>
+      <c r="H27" t="str">
         <v>B+</v>
       </c>
-      <c r="I14" t="str">
-        <v>available</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Elizabeth Schembri, Gerard Hayward</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str">
-        <v>dcd305dd-c710-4a1e-859c-835031154035</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Nicholas Boicos</v>
-      </c>
-      <c r="C15">
-        <v>22</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E15" t="str">
-        <v>nboicos@hotmail.com</v>
-      </c>
-      <c r="F15" t="str">
-        <v>429556400</v>
-      </c>
-      <c r="G15" t="str">
-        <v xml:space="preserve">Altona Meadows </v>
-      </c>
-      <c r="H15" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I15" t="str">
-        <v>available</v>
-      </c>
-      <c r="J15" t="str" xml:space="preserve">
+      <c r="I27" t="str">
+        <v>available</v>
+      </c>
+      <c r="J27" t="str" xml:space="preserve">
         <v xml:space="preserve">Nick Boicos 
 Matthew Boicos
 Brothers</v>
       </c>
     </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
-        <v>09dbfbb4-9f89-44a1-95f3-10cc82ec732a</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Gianni De Pasquale</v>
-      </c>
-      <c r="C16">
-        <v>20</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E16" t="str">
-        <v>gdp762.0@gmail.com</v>
-      </c>
-      <c r="F16" t="str">
-        <v>481978762</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Werribee</v>
-      </c>
-      <c r="H16" t="str">
-        <v>A</v>
-      </c>
-      <c r="I16" t="str">
-        <v>available</v>
-      </c>
-      <c r="J16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Gianni De Pasquale
-Carmela De Pasquale
-Francesco De Pasquale</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Ricky Steve</v>
-      </c>
-      <c r="C17">
-        <v>31</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E17" t="str">
-        <v>tj-c-a@hotmail.com</v>
-      </c>
-      <c r="F17" t="str">
-        <v>411360449</v>
-      </c>
-      <c r="G17" t="str">
-        <v xml:space="preserve">Wangaratta </v>
-      </c>
-      <c r="H17" t="str">
-        <v>A</v>
-      </c>
-      <c r="I17" t="str">
-        <v>available</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Taylah-Jayne Lockery</v>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
-        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Sharon King</v>
-      </c>
-      <c r="C18">
-        <v>58</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E18" t="str">
-        <v>dreamweaversixtyseven@gmail.com</v>
-      </c>
-      <c r="F18" t="str">
-        <v>611488000000</v>
-      </c>
-      <c r="G18" t="str">
-        <v xml:space="preserve">Mooroopna </v>
-      </c>
-      <c r="H18" t="str">
-        <v>A</v>
-      </c>
-      <c r="I18" t="str">
-        <v>available</v>
-      </c>
-      <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-Friend :Jacinda Austin
-ID:b6042a-1-1936475</v>
-      </c>
-      <c r="M18" t="str">
-        <v xml:space="preserve">No </v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Sarah Desira</v>
-      </c>
-      <c r="C19">
-        <v>38</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E19" t="str">
-        <v>unicornwolf11@gmail.com</v>
-      </c>
-      <c r="F19" t="str">
-        <v>450765125</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Lara</v>
-      </c>
-      <c r="H19" t="str">
-        <v>B</v>
-      </c>
-      <c r="I19" t="str">
-        <v>available</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Husband Daniel Desira b6042a-1-1936280</v>
-      </c>
-      <c r="M19" t="str">
-        <v xml:space="preserve">No </v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
-      </c>
-      <c r="B20" t="str">
-        <v>David Fenwick</v>
-      </c>
-      <c r="C20">
-        <v>36</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E20" t="str">
-        <v>David.s.fenwick@gmail.com</v>
-      </c>
-      <c r="F20" t="str">
-        <v>429811171</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Teesdale</v>
-      </c>
-      <c r="H20" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I20" t="str">
-        <v>available</v>
-      </c>
-      <c r="J20" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Anna Fonua</v>
-      </c>
-      <c r="C21">
-        <v>36</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Annawallace89@hotmail.com</v>
-      </c>
-      <c r="F21" t="str">
-        <v>452452442</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Truganina</v>
-      </c>
-      <c r="H21" t="str">
-        <v>A</v>
-      </c>
-      <c r="I21" t="str">
-        <v>available</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Dad Michael Wallace - b6042a-1-1936372</v>
-      </c>
-      <c r="M21" t="str">
-        <v xml:space="preserve">no </v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>1d96e742-18bb-4fc0-b741-154d1a4d9487</v>
-      </c>
-      <c r="B22" t="str">
-        <v>James Butler</v>
-      </c>
-      <c r="C22">
-        <v>42</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E22" t="str">
-        <v>butlerjg1509@gmail.com</v>
-      </c>
-      <c r="F22" t="str">
-        <v>428400584</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Mentone</v>
-      </c>
-      <c r="H22" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I22" t="str">
-        <v>available</v>
-      </c>
-      <c r="J22" t="str">
-        <v>Issy McReynolds</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Mara Baumgardner</v>
-      </c>
-      <c r="C23">
-        <v>40</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E23" t="str">
-        <v>Granic@hotmail.com</v>
-      </c>
-      <c r="F23" t="str">
-        <v>407364450</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Cockatoo</v>
-      </c>
-      <c r="H23" t="str">
-        <v>B</v>
-      </c>
-      <c r="I23" t="str">
-        <v>available</v>
-      </c>
-      <c r="J23" t="str">
-        <v xml:space="preserve">Mum - Mira Granic </v>
-      </c>
-      <c r="M23" t="str">
-        <v xml:space="preserve">No </v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Eden Hayes</v>
-      </c>
-      <c r="C24">
-        <v>21</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E24" t="str">
-        <v>edenhayes19@gmail.com</v>
-      </c>
-      <c r="F24" t="str">
-        <v>448096139</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Elwood</v>
-      </c>
-      <c r="H24" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I24" t="str">
-        <v>available</v>
-      </c>
-      <c r="J24" t="str">
-        <v>Jackson Harris</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Antonio Freno</v>
-      </c>
-      <c r="C25">
-        <v>39</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E25" t="str">
-        <v>frenoantonio@hotmail.it</v>
-      </c>
-      <c r="F25" t="str">
-        <v>422177371</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Glenroy</v>
-      </c>
-      <c r="H25" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I25" t="str">
-        <v>available</v>
-      </c>
-      <c r="J25" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Kiran Rao</v>
-      </c>
-      <c r="C26">
-        <v>35</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E26" t="str">
-        <v>kiran.rao07@gmail.com</v>
-      </c>
-      <c r="F26" t="str">
-        <v>420486042</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Southbank</v>
-      </c>
-      <c r="H26" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I26" t="str">
-        <v>available</v>
-      </c>
-      <c r="J26" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M26" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Kerrie Donald</v>
-      </c>
-      <c r="C27">
-        <v>47</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E27" t="str">
-        <v>kerrieldonald@hotmail.com</v>
-      </c>
-      <c r="F27" t="str">
-        <v>61400826565</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Mailor's Flat</v>
-      </c>
-      <c r="H27" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I27" t="str">
-        <v>available</v>
-      </c>
-      <c r="J27" t="str">
-        <v>kerrie donald, alistair donald</v>
-      </c>
-    </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
+        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
       </c>
       <c r="B28" t="str">
-        <v>Tamara Mifsud</v>
+        <v>Ricky Steve</v>
       </c>
       <c r="C28">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="str">
         <v>Female</v>
       </c>
       <c r="E28" t="str">
-        <v>tamara.mifsud@hotmail.com</v>
+        <v>tj-c-a@hotmail.com</v>
       </c>
       <c r="F28" t="str">
-        <v>416552122</v>
+        <v>411360449</v>
       </c>
       <c r="G28" t="str">
-        <v>Aintree</v>
+        <v xml:space="preserve">Wangaratta </v>
       </c>
       <c r="H28" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I28" t="str">
         <v>available</v>
       </c>
       <c r="J28" t="str">
-        <v>Aliye Abcilar</v>
+        <v>Taylah-Jayne Lockery</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29" t="str">
+        <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Mozgda  Alime</v>
+      </c>
+      <c r="C29">
+        <v>39</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E29" t="str">
+        <v>smalimi@hotmail.com</v>
+      </c>
+      <c r="F29" t="str">
+        <v>402010235</v>
+      </c>
+      <c r="G29" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H29" t="str">
+        <v>C</v>
+      </c>
+      <c r="I29" t="str">
+        <v>available</v>
+      </c>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Sadaf Almini - I believe this is her cousin 
+Lida Alime - I believe this is her cousin or sister 
+Ahmad Alime - Ahmad is Lina's husband </v>
+      </c>
+      <c r="M29" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Thomas Mckenna</v>
+      </c>
+      <c r="C30">
+        <v>36</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E30" t="str">
+        <v>mckenna.6@yahoo.com</v>
+      </c>
+      <c r="F30" t="str">
+        <v>421758700</v>
+      </c>
+      <c r="G30" t="str">
+        <v xml:space="preserve">Officer South </v>
+      </c>
+      <c r="H30" t="str">
+        <v>B</v>
+      </c>
+      <c r="I30" t="str">
+        <v>available</v>
+      </c>
+      <c r="J30" t="str">
+        <v>thomas mckenna, Carolyn (Caz) Wilby</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Natasha Devers</v>
+      </c>
+      <c r="C31">
+        <v>22</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E31" t="str">
+        <v>natashadevers@gmail.com</v>
+      </c>
+      <c r="F31" t="str">
+        <v>484003770</v>
+      </c>
+      <c r="G31" t="str">
+        <v xml:space="preserve">Waterways </v>
+      </c>
+      <c r="H31" t="str">
+        <v>B</v>
+      </c>
+      <c r="I31" t="str">
+        <v>available</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Oliver Moran</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Antonio Freno</v>
+      </c>
+      <c r="C32">
+        <v>39</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E32" t="str">
+        <v>frenoantonio@hotmail.it</v>
+      </c>
+      <c r="F32" t="str">
+        <v>422177371</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Glenroy</v>
+      </c>
+      <c r="H32" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I32" t="str">
+        <v>available</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>94b19240-6aee-4af6-ac66-0ebdb5e4403c</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Scott Clark</v>
+      </c>
+      <c r="C33">
+        <v>54</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E33" t="str">
+        <v>sclarkfitness@optusnet.com.au</v>
+      </c>
+      <c r="F33" t="str">
+        <v>448073035</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H33" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I33" t="str">
+        <v>available</v>
+      </c>
+      <c r="J33" t="str">
+        <v xml:space="preserve">Would bring someone </v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Sherif Haggag</v>
+      </c>
+      <c r="C34">
+        <v>38</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Shaggag87@gmail.com</v>
+      </c>
+      <c r="F34" t="str">
+        <v>426233449</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Belmont</v>
+      </c>
+      <c r="H34" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I34" t="str">
+        <v>available</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Alexander Leonard</v>
+      </c>
+      <c r="C35">
+        <v>38</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E35" t="str">
+        <v>alexleonardedit@gmail.com</v>
+      </c>
+      <c r="F35" t="str">
+        <v>421834476</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Croydon</v>
+      </c>
+      <c r="H35" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I35" t="str">
+        <v>available</v>
+      </c>
+      <c r="J35" t="str">
+        <v>melissa francis, Alexander Leonard</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Leanne Bryant</v>
+      </c>
+      <c r="C36">
+        <v>63</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E36" t="str">
+        <v>blazeandcougar@gmail.com</v>
+      </c>
+      <c r="F36" t="str">
+        <v>61415438228</v>
+      </c>
+      <c r="G36" t="str">
+        <v xml:space="preserve">Hampton Park </v>
+      </c>
+      <c r="H36" t="str">
+        <v>B</v>
+      </c>
+      <c r="I36" t="str">
+        <v>available</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Bronwyn Parsons</v>
+      </c>
+      <c r="C37">
+        <v>72</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Babybear61153@gmail.com</v>
+      </c>
+      <c r="F37" t="str">
+        <v>432543647</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Rosebud</v>
+      </c>
+      <c r="H37" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I37" t="str">
+        <v>available</v>
+      </c>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yolette Huon - yol-et Hue on
+Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Tamika Colville</v>
+      </c>
+      <c r="C38">
+        <v>31</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E38" t="str">
+        <v>tamika.colville@gmail.com</v>
+      </c>
+      <c r="F38" t="str">
+        <v>409132141</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Golden square</v>
+      </c>
+      <c r="H38" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I38" t="str">
+        <v>available</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Shinae Colville</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Diagnosed with MS in 2018</v>
+      </c>
+      <c r="M38" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Paige Greig</v>
+      </c>
+      <c r="C39">
+        <v>31</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E39" t="str">
+        <v>paigegreig@hotmail.com</v>
+      </c>
+      <c r="F39" t="str">
+        <v>406598552</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Mooroolbark</v>
+      </c>
+      <c r="H39" t="str">
+        <v>C</v>
+      </c>
+      <c r="I39" t="str">
+        <v>available</v>
+      </c>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Erin
+Morgan (sister) - need to do application</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
         <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B40" t="str">
         <v>Linda Browne</v>
       </c>
-      <c r="C29">
+      <c r="C40">
         <v>54</v>
       </c>
-      <c r="D29" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E29" t="str">
+      <c r="D40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E40" t="str">
         <v>Lindabrowne@iprimus.com.au</v>
       </c>
-      <c r="F29" t="str">
+      <c r="F40" t="str">
         <v>429570177</v>
       </c>
-      <c r="G29" t="str">
+      <c r="G40" t="str">
         <v>OFFICER</v>
       </c>
-      <c r="H29" t="str">
+      <c r="H40" t="str">
         <v>B</v>
       </c>
-      <c r="I29" t="str">
-        <v>available</v>
-      </c>
-      <c r="J29" t="str" xml:space="preserve">
+      <c r="I40" t="str">
+        <v>available</v>
+      </c>
+      <c r="J40" t="str" xml:space="preserve">
         <v xml:space="preserve">Natalie Browne
 Linda Browne
 Aidan Miler</v>
       </c>
     </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str">
-        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Meenakshi  Mehra</v>
-      </c>
-      <c r="C30">
-        <v>62</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E30" t="str">
-        <v>meenu.mehra@bigpond.com</v>
-      </c>
-      <c r="F30" t="str">
-        <v>420353322</v>
-      </c>
-      <c r="G30" t="str">
-        <v xml:space="preserve">Melbourne </v>
-      </c>
-      <c r="H30" t="str">
+    <row r="41">
+      <c r="A41" t="str">
+        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Kadisha  Bruton</v>
+      </c>
+      <c r="C41">
+        <v>23</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E41" t="str">
+        <v>kadishaann@icloud.com</v>
+      </c>
+      <c r="F41" t="str">
+        <v>434829249</v>
+      </c>
+      <c r="G41" t="str">
+        <v xml:space="preserve">Kurunjang </v>
+      </c>
+      <c r="H41" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I41" t="str">
+        <v>available</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Jacob Steele</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Bashar Mona</v>
+      </c>
+      <c r="C42">
+        <v>33</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E42" t="str">
+        <v>bashar.mona92@gmail.com</v>
+      </c>
+      <c r="F42" t="str">
+        <v>490871416</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Roxburgh park</v>
+      </c>
+      <c r="H42" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I42" t="str">
+        <v>available</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Sharyn  McKinnis</v>
+      </c>
+      <c r="C43">
+        <v>50</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E43" t="str">
+        <v>s.lmckinnis@bigpond.com</v>
+      </c>
+      <c r="F43" t="str">
+        <v>419880873</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Newtown</v>
+      </c>
+      <c r="H43" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I43" t="str">
+        <v>available</v>
+      </c>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Isabelle McKinnis, Sharyn McKinnis
+</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Angela Verspay</v>
+      </c>
+      <c r="C44">
+        <v>45</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E44" t="str">
+        <v>angelarileysmyth@hotmail.com</v>
+      </c>
+      <c r="F44" t="str">
+        <v>477660119</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Warrnambool</v>
+      </c>
+      <c r="H44" t="str">
         <v>B</v>
       </c>
-      <c r="I30" t="str">
-        <v>available</v>
-      </c>
-      <c r="J30" t="str" xml:space="preserve">
+      <c r="I44" t="str">
+        <v>available</v>
+      </c>
+      <c r="J44" t="str">
+        <v>SOLO</v>
+      </c>
+      <c r="M44" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Dhananjay  Mehra</v>
+      </c>
+      <c r="C45">
+        <v>68</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Dmehra@bigpond.net.au</v>
+      </c>
+      <c r="F45" t="str">
+        <v>419353328</v>
+      </c>
+      <c r="G45" t="str">
+        <v xml:space="preserve">Point Cook </v>
+      </c>
+      <c r="H45" t="str">
+        <v>B</v>
+      </c>
+      <c r="I45" t="str">
+        <v>available</v>
+      </c>
+      <c r="J45" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
 Dhananjay Mehra</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>8a905dfd-647c-4d96-a741-f7f1517a5136</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Deanna Hay</v>
-      </c>
-      <c r="C31">
-        <v>38</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E31" t="str">
-        <v>dee_hay24@hotmail.com</v>
-      </c>
-      <c r="F31" t="str">
-        <v>424504430</v>
-      </c>
-      <c r="G31" t="str">
-        <v xml:space="preserve">Melbourne </v>
-      </c>
-      <c r="H31" t="str">
-        <v>DNU</v>
-      </c>
-      <c r="I31" t="str">
-        <v>available</v>
-      </c>
-      <c r="J31" t="str">
-        <v>Lynetta Shan Faoa</v>
-      </c>
-      <c r="L31" t="str">
-        <v xml:space="preserve">Cerebral palsy in a wheelchair </v>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32" t="str">
-        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Kayla Lorenzini</v>
-      </c>
-      <c r="C32">
-        <v>29</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E32" t="str">
-        <v>kaylalorenzini_@hotmail.com</v>
-      </c>
-      <c r="F32" t="str">
-        <v>430517653</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H32" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I32" t="str">
-        <v>available</v>
-      </c>
-      <c r="J32" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kayla Lorenzini
-James Lorenzini
-Deanna Gramola</v>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str">
-        <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Mozgda  Alime</v>
-      </c>
-      <c r="C33">
-        <v>39</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E33" t="str">
-        <v>smalimi@hotmail.com</v>
-      </c>
-      <c r="F33" t="str">
-        <v>402010235</v>
-      </c>
-      <c r="G33" t="str">
-        <v xml:space="preserve">Melbourne </v>
-      </c>
-      <c r="H33" t="str">
-        <v>C</v>
-      </c>
-      <c r="I33" t="str">
-        <v>available</v>
-      </c>
-      <c r="J33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Sadaf Almini - I believe this is her cousin 
-Lida Alime - I believe this is her cousin or sister 
-Ahmad Alime - Ahmad is Lina's husband </v>
-      </c>
-      <c r="M33" t="str">
-        <v xml:space="preserve">No </v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>94b19240-6aee-4af6-ac66-0ebdb5e4403c</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Scott Clark</v>
-      </c>
-      <c r="C34">
-        <v>54</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E34" t="str">
-        <v>sclarkfitness@optusnet.com.au</v>
-      </c>
-      <c r="F34" t="str">
-        <v>448073035</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H34" t="str">
-        <v>A+</v>
-      </c>
-      <c r="I34" t="str">
-        <v>available</v>
-      </c>
-      <c r="J34" t="str">
-        <v xml:space="preserve">Would bring someone </v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Angela Verspay</v>
-      </c>
-      <c r="C35">
-        <v>45</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E35" t="str">
-        <v>angelarileysmyth@hotmail.com</v>
-      </c>
-      <c r="F35" t="str">
-        <v>477660119</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Warrnambool</v>
-      </c>
-      <c r="H35" t="str">
-        <v>B</v>
-      </c>
-      <c r="I35" t="str">
-        <v>available</v>
-      </c>
-      <c r="J35" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M35" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>eb3b2a7d-e6b0-421b-8987-00bfff95dda9</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Jasmine Miller</v>
-      </c>
-      <c r="C36">
-        <v>32</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E36" t="str">
-        <v>jasmine_courtney@hotmail.com</v>
-      </c>
-      <c r="F36" t="str">
-        <v>0432 387 712</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Hughesdale</v>
-      </c>
-      <c r="H36" t="str">
-        <v>C</v>
-      </c>
-      <c r="I36" t="str">
-        <v>available</v>
-      </c>
-      <c r="J36" t="str">
-        <v>ablo - partner</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Sherif Haggag</v>
-      </c>
-      <c r="C37">
-        <v>38</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E37" t="str">
-        <v>Shaggag87@gmail.com</v>
-      </c>
-      <c r="F37" t="str">
-        <v>426233449</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Belmont</v>
-      </c>
-      <c r="H37" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I37" t="str">
-        <v>available</v>
-      </c>
-      <c r="J37" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>300ac025-db3a-42ba-a9dd-777f02fb3454</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Jeanette Quy</v>
-      </c>
-      <c r="C38">
-        <v>74</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E38" t="str">
-        <v>koalaleaf@hotmail.com</v>
-      </c>
-      <c r="F38" t="str">
-        <v>402902273</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Rowville</v>
-      </c>
-      <c r="H38" t="str">
-        <v>C</v>
-      </c>
-      <c r="I38" t="str">
-        <v>available</v>
-      </c>
-      <c r="J38" t="str">
-        <v>Husband Ted Quy b6042a-1-1872960</v>
-      </c>
-      <c r="M38" t="str">
-        <v xml:space="preserve">Nothing of note </v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>0ea22efb-f85f-400a-b28d-d1312568ba67</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Jess Cossari</v>
-      </c>
-      <c r="C39">
-        <v>35</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E39" t="str">
-        <v>Jcossari@hotmail.com</v>
-      </c>
-      <c r="F39" t="str">
-        <v xml:space="preserve">0458 746 551 </v>
-      </c>
-      <c r="G39" t="str">
-        <v xml:space="preserve">Melbourne </v>
-      </c>
-      <c r="H39" t="str">
-        <v>C</v>
-      </c>
-      <c r="I39" t="str">
-        <v>available</v>
-      </c>
-      <c r="J39" t="str">
-        <v>Andrea Cocco</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Leanne Bryant</v>
-      </c>
-      <c r="C40">
-        <v>63</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E40" t="str">
-        <v>blazeandcougar@gmail.com</v>
-      </c>
-      <c r="F40" t="str">
-        <v>61415438228</v>
-      </c>
-      <c r="G40" t="str">
-        <v xml:space="preserve">Hampton Park </v>
-      </c>
-      <c r="H40" t="str">
-        <v>B</v>
-      </c>
-      <c r="I40" t="str">
-        <v>available</v>
-      </c>
-      <c r="J40" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Bashar Mona</v>
-      </c>
-      <c r="C41">
-        <v>33</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E41" t="str">
-        <v>bashar.mona92@gmail.com</v>
-      </c>
-      <c r="F41" t="str">
-        <v>490871416</v>
-      </c>
-      <c r="G41" t="str">
-        <v>Roxburgh park</v>
-      </c>
-      <c r="H41" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I41" t="str">
-        <v>available</v>
-      </c>
-      <c r="J41" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Alexander Leonard</v>
-      </c>
-      <c r="C42">
-        <v>38</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E42" t="str">
-        <v>alexleonardedit@gmail.com</v>
-      </c>
-      <c r="F42" t="str">
-        <v>421834476</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Croydon</v>
-      </c>
-      <c r="H42" t="str">
-        <v>A+</v>
-      </c>
-      <c r="I42" t="str">
-        <v>available</v>
-      </c>
-      <c r="J42" t="str">
-        <v>melissa francis, Alexander Leonard</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Kadisha  Bruton</v>
-      </c>
-      <c r="C43">
-        <v>23</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E43" t="str">
-        <v>kadishaann@icloud.com</v>
-      </c>
-      <c r="F43" t="str">
-        <v>434829249</v>
-      </c>
-      <c r="G43" t="str">
-        <v xml:space="preserve">Kurunjang </v>
-      </c>
-      <c r="H43" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I43" t="str">
-        <v>available</v>
-      </c>
-      <c r="J43" t="str">
-        <v>Jacob Steele</v>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
-      <c r="A44" t="str">
-        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Sharyn  McKinnis</v>
-      </c>
-      <c r="C44">
-        <v>50</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E44" t="str">
-        <v>s.lmckinnis@bigpond.com</v>
-      </c>
-      <c r="F44" t="str">
-        <v>419880873</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Newtown</v>
-      </c>
-      <c r="H44" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I44" t="str">
-        <v>available</v>
-      </c>
-      <c r="J44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Isabelle McKinnis, Sharyn McKinnis
-</v>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45" t="str">
-        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Paige Greig</v>
-      </c>
-      <c r="C45">
-        <v>31</v>
-      </c>
-      <c r="D45" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E45" t="str">
-        <v>paigegreig@hotmail.com</v>
-      </c>
-      <c r="F45" t="str">
-        <v>406598552</v>
-      </c>
-      <c r="G45" t="str">
-        <v>Mooroolbark</v>
-      </c>
-      <c r="H45" t="str">
-        <v>C</v>
-      </c>
-      <c r="I45" t="str">
-        <v>available</v>
-      </c>
-      <c r="J45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Erin
-Morgan (sister) - need to do application</v>
       </c>
     </row>
     <row r="46">
@@ -2246,25 +2251,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+        <v>0b96f877-e1c4-4c17-aa89-21b4a5f7f002</v>
       </c>
       <c r="B48" t="str">
-        <v>Tamika Colville</v>
+        <v>Stephen Deacon</v>
       </c>
       <c r="C48">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D48" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E48" t="str">
-        <v>tamika.colville@gmail.com</v>
+        <v>StephenDeacon@duck.com</v>
       </c>
       <c r="F48" t="str">
-        <v>409132141</v>
+        <v>435353108</v>
       </c>
       <c r="G48" t="str">
-        <v>Golden square</v>
+        <v>St Kilda</v>
       </c>
       <c r="H48" t="str">
         <v>B+</v>
@@ -2273,111 +2278,106 @@
         <v>available</v>
       </c>
       <c r="J48" t="str">
-        <v>Shinae Colville</v>
-      </c>
-      <c r="L48" t="str">
-        <v>Diagnosed with MS in 2018</v>
-      </c>
-      <c r="M48" t="str">
-        <v>NA</v>
+        <v>Chanyapach Deacon</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0b96f877-e1c4-4c17-aa89-21b4a5f7f002</v>
+        <v>eb3b2a7d-e6b0-421b-8987-00bfff95dda9</v>
       </c>
       <c r="B49" t="str">
-        <v>Stephen Deacon</v>
+        <v>Jasmine Miller</v>
       </c>
       <c r="C49">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D49" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E49" t="str">
-        <v>StephenDeacon@duck.com</v>
+        <v>jasmine_courtney@hotmail.com</v>
       </c>
       <c r="F49" t="str">
-        <v>435353108</v>
+        <v>0432 387 712</v>
       </c>
       <c r="G49" t="str">
-        <v>St Kilda</v>
+        <v>Hughesdale</v>
       </c>
       <c r="H49" t="str">
-        <v>B+</v>
+        <v>C</v>
       </c>
       <c r="I49" t="str">
         <v>available</v>
       </c>
       <c r="J49" t="str">
-        <v>Chanyapach Deacon</v>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
+        <v>ablo - partner</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" t="str">
-        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
+        <v>300ac025-db3a-42ba-a9dd-777f02fb3454</v>
       </c>
       <c r="B50" t="str">
-        <v>Dhananjay  Mehra</v>
+        <v>Jeanette Quy</v>
       </c>
       <c r="C50">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D50" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E50" t="str">
-        <v>Dmehra@bigpond.net.au</v>
+        <v>koalaleaf@hotmail.com</v>
       </c>
       <c r="F50" t="str">
-        <v>419353328</v>
+        <v>402902273</v>
       </c>
       <c r="G50" t="str">
-        <v xml:space="preserve">Point Cook </v>
+        <v>Rowville</v>
       </c>
       <c r="H50" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="I50" t="str">
         <v>available</v>
       </c>
-      <c r="J50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Meenakshi Mehra
-Dhananjay Mehra</v>
-      </c>
-    </row>
-    <row r="51" xml:space="preserve">
+      <c r="J50" t="str">
+        <v>Husband Ted Quy b6042a-1-1872960</v>
+      </c>
+      <c r="M50" t="str">
+        <v xml:space="preserve">Nothing of note </v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="str">
-        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+        <v>0ea22efb-f85f-400a-b28d-d1312568ba67</v>
       </c>
       <c r="B51" t="str">
-        <v>Bronwyn Parsons</v>
+        <v>Jess Cossari</v>
       </c>
       <c r="C51">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D51" t="str">
         <v>Female</v>
       </c>
       <c r="E51" t="str">
-        <v>Babybear61153@gmail.com</v>
+        <v>Jcossari@hotmail.com</v>
       </c>
       <c r="F51" t="str">
-        <v>432543647</v>
+        <v xml:space="preserve">0458 746 551 </v>
       </c>
       <c r="G51" t="str">
-        <v>Rosebud</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H51" t="str">
-        <v>A+</v>
+        <v>C</v>
       </c>
       <c r="I51" t="str">
         <v>available</v>
       </c>
-      <c r="J51" t="str" xml:space="preserve">
-        <v xml:space="preserve">Yolette Huon - yol-et Hue on
-Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
+      <c r="J51" t="str">
+        <v>Andrea Cocco</v>
       </c>
     </row>
   </sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,8 +5,9 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" r:id="rId3"/>
-    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
+    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
+    <sheet name="Groups" sheetId="4" r:id="rId4"/>
+    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -709,27 +710,27 @@
         <v>MobilityNotes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
+        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
       </c>
       <c r="B2" t="str">
-        <v>Donna Collins</v>
+        <v>Meenakshi  Mehra</v>
       </c>
       <c r="C2">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D2" t="str">
         <v>Female</v>
       </c>
       <c r="E2" t="str">
-        <v>Donna0@hotmail.com</v>
+        <v>meenu.mehra@bigpond.com</v>
       </c>
       <c r="F2" t="str">
-        <v>408122305</v>
+        <v>420353322</v>
       </c>
       <c r="G2" t="str">
-        <v xml:space="preserve">Coburg </v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H2" t="str">
         <v>B</v>
@@ -737,41 +738,41 @@
       <c r="I2" t="str">
         <v>available</v>
       </c>
-      <c r="J2" t="str">
-        <v>Donna Collins, Tom Collins</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
+      <c r="J2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Meenakshi Mehra
+Dhananjay Mehra</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="str">
-        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
+        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
       </c>
       <c r="B3" t="str">
-        <v>Meenakshi  Mehra</v>
+        <v>Donna Collins</v>
       </c>
       <c r="C3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D3" t="str">
         <v>Female</v>
       </c>
       <c r="E3" t="str">
-        <v>meenu.mehra@bigpond.com</v>
+        <v>Donna0@hotmail.com</v>
       </c>
       <c r="F3" t="str">
-        <v>420353322</v>
+        <v>408122305</v>
       </c>
       <c r="G3" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v xml:space="preserve">Coburg </v>
       </c>
       <c r="H3" t="str">
         <v>B</v>
       </c>
       <c r="I3" t="str">
-        <v>available</v>
-      </c>
-      <c r="J3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Meenakshi Mehra
-Dhananjay Mehra</v>
+        <v>assigned</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Donna Collins, Tom Collins</v>
       </c>
     </row>
     <row r="4">
@@ -2389,6 +2390,60 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RecordDayID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ContestantID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Block</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Seat</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BookingEmailSent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ConfirmedRSVP</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1208c385-b9b8-47af-b3d2-f30717990aef</v>
+      </c>
+      <c r="B2" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>E1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
@@ -2422,7 +2477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,9 +5,8 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
-    <sheet name="Groups" sheetId="4" r:id="rId4"/>
-    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
+    <sheet name="Groups" sheetId="3" r:id="rId3"/>
+    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -769,7 +768,7 @@
         <v>B</v>
       </c>
       <c r="I3" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J3" t="str">
         <v>Donna Collins, Tom Collins</v>
@@ -2390,60 +2389,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>RecordDayID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>ContestantID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Block</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Seat</v>
-      </c>
-      <c r="F1" t="str">
-        <v>BookingEmailSent</v>
-      </c>
-      <c r="G1" t="str">
-        <v>ConfirmedRSVP</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1208c385-b9b8-47af-b3d2-f30717990aef</v>
-      </c>
-      <c r="B2" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C2" t="str">
-        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>E1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
@@ -2477,7 +2422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -774,131 +774,134 @@
         <v>Donna Collins, Tom Collins</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
       </c>
       <c r="B4" t="str">
-        <v>Tayla Huxtable</v>
+        <v>Sharon King</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D4" t="str">
         <v>Female</v>
       </c>
       <c r="E4" t="str">
-        <v>Taylahuxtable@gmail.com</v>
+        <v>dreamweaversixtyseven@gmail.com</v>
       </c>
       <c r="F4" t="str">
-        <v>435320280</v>
+        <v>611488000000</v>
       </c>
       <c r="G4" t="str">
-        <v>FERNTREE GULLY</v>
+        <v xml:space="preserve">Mooroopna </v>
+      </c>
+      <c r="H4" t="str">
+        <v>A</v>
       </c>
       <c r="I4" t="str">
         <v>available</v>
       </c>
-      <c r="J4" t="str">
-        <v>Troy Smith</v>
-      </c>
-      <c r="K4" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
-        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Sharon King</v>
-      </c>
-      <c r="C5">
-        <v>58</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E5" t="str">
-        <v>dreamweaversixtyseven@gmail.com</v>
-      </c>
-      <c r="F5" t="str">
-        <v>611488000000</v>
-      </c>
-      <c r="G5" t="str">
-        <v xml:space="preserve">Mooroopna </v>
-      </c>
-      <c r="H5" t="str">
-        <v>A</v>
-      </c>
-      <c r="I5" t="str">
-        <v>available</v>
-      </c>
-      <c r="J5" t="str" xml:space="preserve">
+      <c r="J4" t="str" xml:space="preserve">
         <v xml:space="preserve">
 Friend :Jacinda Austin
 ID:b6042a-1-1936475</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M4" t="str">
         <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>8a905dfd-647c-4d96-a741-f7f1517a5136</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Deanna Hay</v>
+      </c>
+      <c r="C5">
+        <v>38</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E5" t="str">
+        <v>dee_hay24@hotmail.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>424504430</v>
+      </c>
+      <c r="G5" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H5" t="str">
+        <v>DNU</v>
+      </c>
+      <c r="I5" t="str">
+        <v>available</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Lynetta Shan Faoa</v>
+      </c>
+      <c r="L5" t="str">
+        <v xml:space="preserve">Cerebral palsy in a wheelchair </v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>8a905dfd-647c-4d96-a741-f7f1517a5136</v>
+        <v>efd8ab2e-988b-4afb-9374-3c3e3676f43a</v>
       </c>
       <c r="B6" t="str">
-        <v>Deanna Hay</v>
+        <v>Matilda Sutherland</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D6" t="str">
         <v>Female</v>
       </c>
       <c r="E6" t="str">
-        <v>dee_hay24@hotmail.com</v>
+        <v>matilda.sutherland@hotmail.com</v>
       </c>
       <c r="F6" t="str">
-        <v>424504430</v>
+        <v>0467 165 012</v>
       </c>
       <c r="G6" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v>Bundoora</v>
       </c>
       <c r="H6" t="str">
-        <v>DNU</v>
+        <v>B+</v>
       </c>
       <c r="I6" t="str">
         <v>available</v>
       </c>
       <c r="J6" t="str">
-        <v>Lynetta Shan Faoa</v>
-      </c>
-      <c r="L6" t="str">
-        <v xml:space="preserve">Cerebral palsy in a wheelchair </v>
+        <v>Grace Mann</v>
+      </c>
+      <c r="M6" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>efd8ab2e-988b-4afb-9374-3c3e3676f43a</v>
+        <v>96d2c8ad-1e67-4659-b3d0-a3bbd4fe40cb</v>
       </c>
       <c r="B7" t="str">
-        <v>Matilda Sutherland</v>
+        <v>Karina  Richmond</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D7" t="str">
         <v>Female</v>
       </c>
       <c r="E7" t="str">
-        <v>matilda.sutherland@hotmail.com</v>
+        <v>richmondkarina@yahoo.com</v>
       </c>
       <c r="F7" t="str">
-        <v>0467 165 012</v>
+        <v>400554609</v>
       </c>
       <c r="G7" t="str">
-        <v>Bundoora</v>
+        <v>Newcomb</v>
       </c>
       <c r="H7" t="str">
         <v>B+</v>
@@ -907,7 +910,7 @@
         <v>available</v>
       </c>
       <c r="J7" t="str">
-        <v>Grace Mann</v>
+        <v>AMY DILLON</v>
       </c>
       <c r="M7" t="str">
         <v>NA</v>
@@ -915,25 +918,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>96d2c8ad-1e67-4659-b3d0-a3bbd4fe40cb</v>
+        <v>7a05a613-1880-40c5-ab6a-cc078b418b6e</v>
       </c>
       <c r="B8" t="str">
-        <v>Karina  Richmond</v>
+        <v>Deb  Jones</v>
       </c>
       <c r="C8">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D8" t="str">
         <v>Female</v>
       </c>
       <c r="E8" t="str">
-        <v>richmondkarina@yahoo.com</v>
+        <v>fullhouse5@optusnet.com.au</v>
       </c>
       <c r="F8" t="str">
-        <v>400554609</v>
+        <v>438561474</v>
       </c>
       <c r="G8" t="str">
-        <v>Newcomb</v>
+        <v>Bayswater North</v>
       </c>
       <c r="H8" t="str">
         <v>B+</v>
@@ -942,33 +945,33 @@
         <v>available</v>
       </c>
       <c r="J8" t="str">
-        <v>AMY DILLON</v>
+        <v>Daryl Jones</v>
       </c>
       <c r="M8" t="str">
-        <v>NA</v>
+        <v>No</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>7a05a613-1880-40c5-ab6a-cc078b418b6e</v>
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
       </c>
       <c r="B9" t="str">
-        <v>Deb  Jones</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C9">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D9" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E9" t="str">
-        <v>fullhouse5@optusnet.com.au</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F9" t="str">
-        <v>438561474</v>
+        <v>423530043</v>
       </c>
       <c r="G9" t="str">
-        <v>Bayswater North</v>
+        <v>Preston</v>
       </c>
       <c r="H9" t="str">
         <v>B+</v>
@@ -977,33 +980,30 @@
         <v>available</v>
       </c>
       <c r="J9" t="str">
-        <v>Daryl Jones</v>
-      </c>
-      <c r="M9" t="str">
-        <v>No</v>
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
       </c>
       <c r="B10" t="str">
-        <v>Brent Barnett</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C10">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D10" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E10" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F10" t="str">
-        <v>423530043</v>
+        <v>448545599</v>
       </c>
       <c r="G10" t="str">
-        <v>Preston</v>
+        <v>Melbourne</v>
       </c>
       <c r="H10" t="str">
         <v>B+</v>
@@ -1012,27 +1012,30 @@
         <v>available</v>
       </c>
       <c r="J10" t="str">
-        <v>Stephanie Squillacioti</v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+      </c>
+      <c r="M10" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B11" t="str">
-        <v>Tara Saltzman</v>
+        <v>Troy Smith</v>
       </c>
       <c r="C11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E11" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>Troyssmith94@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>448545599</v>
+        <v>429354308</v>
       </c>
       <c r="G11" t="str">
         <v>Melbourne</v>
@@ -1044,7 +1047,13 @@
         <v>available</v>
       </c>
       <c r="J11" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="K11" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L11" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
       </c>
       <c r="M11" t="str">
         <v>NA</v>
@@ -1052,43 +1061,34 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B12" t="str">
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="C12">
+        <v>28</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Taylahuxtable@gmail.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>435320280</v>
+      </c>
+      <c r="G12" t="str">
+        <v>FERNTREE GULLY</v>
+      </c>
+      <c r="I12" t="str">
+        <v>available</v>
+      </c>
+      <c r="J12" t="str">
         <v>Troy Smith</v>
-      </c>
-      <c r="C12">
-        <v>31</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Troyssmith94@gmail.com</v>
-      </c>
-      <c r="F12" t="str">
-        <v>429354308</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H12" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I12" t="str">
-        <v>available</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Tayla Huxtable</v>
       </c>
       <c r="K12" t="str">
         <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-      <c r="L12" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
-      </c>
-      <c r="M12" t="str">
-        <v>NA</v>
       </c>
     </row>
     <row r="13">

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,8 +5,9 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" r:id="rId3"/>
-    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
+    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
+    <sheet name="Groups" sheetId="4" r:id="rId4"/>
+    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -953,57 +954,57 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B9" t="str">
-        <v>Brent Barnett</v>
+        <v>Tayla Huxtable</v>
       </c>
       <c r="C9">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D9" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E9" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>Taylahuxtable@gmail.com</v>
       </c>
       <c r="F9" t="str">
-        <v>423530043</v>
+        <v>435320280</v>
       </c>
       <c r="G9" t="str">
-        <v>Preston</v>
-      </c>
-      <c r="H9" t="str">
-        <v>B+</v>
+        <v>FERNTREE GULLY</v>
       </c>
       <c r="I9" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J9" t="str">
-        <v>Stephanie Squillacioti</v>
+        <v>Troy Smith</v>
+      </c>
+      <c r="K9" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
       </c>
       <c r="B10" t="str">
-        <v>Tara Saltzman</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C10">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D10" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E10" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>448545599</v>
+        <v>423530043</v>
       </c>
       <c r="G10" t="str">
-        <v>Melbourne</v>
+        <v>Preston</v>
       </c>
       <c r="H10" t="str">
         <v>B+</v>
@@ -1012,30 +1013,27 @@
         <v>available</v>
       </c>
       <c r="J10" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
-      </c>
-      <c r="M10" t="str">
-        <v>NA</v>
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
       </c>
       <c r="B11" t="str">
-        <v>Troy Smith</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C11">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E11" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F11" t="str">
-        <v>429354308</v>
+        <v>448545599</v>
       </c>
       <c r="G11" t="str">
         <v>Melbourne</v>
@@ -1047,13 +1045,7 @@
         <v>available</v>
       </c>
       <c r="J11" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="K11" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-      <c r="L11" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
       </c>
       <c r="M11" t="str">
         <v>NA</v>
@@ -1061,34 +1053,43 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B12" t="str">
+        <v>Troy Smith</v>
+      </c>
+      <c r="C12">
+        <v>31</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Troyssmith94@gmail.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>429354308</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H12" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I12" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J12" t="str">
         <v>Tayla Huxtable</v>
-      </c>
-      <c r="C12">
-        <v>28</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Taylahuxtable@gmail.com</v>
-      </c>
-      <c r="F12" t="str">
-        <v>435320280</v>
-      </c>
-      <c r="G12" t="str">
-        <v>FERNTREE GULLY</v>
-      </c>
-      <c r="I12" t="str">
-        <v>available</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Troy Smith</v>
       </c>
       <c r="K12" t="str">
         <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L12" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M12" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="13">
@@ -2389,6 +2390,77 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RecordDayID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ContestantID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Block</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Seat</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BookingEmailSent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ConfirmedRSVP</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>73d6afb0-cfb6-4853-ba4e-78207c8c06d5</v>
+      </c>
+      <c r="B2" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>E2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>cd112197-9251-4276-b185-2ade91c758f2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="str">
+        <v>E3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
@@ -2422,7 +2494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,9 +5,8 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
-    <sheet name="Groups" sheetId="4" r:id="rId4"/>
-    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
+    <sheet name="Groups" sheetId="3" r:id="rId3"/>
+    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -954,89 +953,98 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B9" t="str">
+        <v>Troy Smith</v>
+      </c>
+      <c r="C9">
+        <v>31</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Troyssmith94@gmail.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>429354308</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H9" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I9" t="str">
+        <v>available</v>
+      </c>
+      <c r="J9" t="str">
         <v>Tayla Huxtable</v>
-      </c>
-      <c r="C9">
-        <v>28</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Taylahuxtable@gmail.com</v>
-      </c>
-      <c r="F9" t="str">
-        <v>435320280</v>
-      </c>
-      <c r="G9" t="str">
-        <v>FERNTREE GULLY</v>
-      </c>
-      <c r="I9" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Troy Smith</v>
       </c>
       <c r="K9" t="str">
         <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
       </c>
+      <c r="L9" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M9" t="str">
+        <v>NA</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B10" t="str">
-        <v>Brent Barnett</v>
+        <v>Tayla Huxtable</v>
       </c>
       <c r="C10">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D10" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E10" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>Taylahuxtable@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>423530043</v>
+        <v>435320280</v>
       </c>
       <c r="G10" t="str">
-        <v>Preston</v>
-      </c>
-      <c r="H10" t="str">
-        <v>B+</v>
+        <v>FERNTREE GULLY</v>
       </c>
       <c r="I10" t="str">
         <v>available</v>
       </c>
       <c r="J10" t="str">
-        <v>Stephanie Squillacioti</v>
+        <v>Troy Smith</v>
+      </c>
+      <c r="K10" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
       </c>
       <c r="B11" t="str">
-        <v>Tara Saltzman</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D11" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E11" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>448545599</v>
+        <v>423530043</v>
       </c>
       <c r="G11" t="str">
-        <v>Melbourne</v>
+        <v>Preston</v>
       </c>
       <c r="H11" t="str">
         <v>B+</v>
@@ -1045,30 +1053,27 @@
         <v>available</v>
       </c>
       <c r="J11" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
-      </c>
-      <c r="M11" t="str">
-        <v>NA</v>
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
       </c>
       <c r="B12" t="str">
-        <v>Troy Smith</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C12">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E12" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F12" t="str">
-        <v>429354308</v>
+        <v>448545599</v>
       </c>
       <c r="G12" t="str">
         <v>Melbourne</v>
@@ -1077,16 +1082,10 @@
         <v>B+</v>
       </c>
       <c r="I12" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J12" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="K12" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-      <c r="L12" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
       </c>
       <c r="M12" t="str">
         <v>NA</v>
@@ -2390,77 +2389,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>RecordDayID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>ContestantID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Block</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Seat</v>
-      </c>
-      <c r="F1" t="str">
-        <v>BookingEmailSent</v>
-      </c>
-      <c r="G1" t="str">
-        <v>ConfirmedRSVP</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>73d6afb0-cfb6-4853-ba4e-78207c8c06d5</v>
-      </c>
-      <c r="B2" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C2" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>E2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>cd112197-9251-4276-b185-2ade91c758f2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C3" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="str">
-        <v>E3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
@@ -2494,7 +2422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,8 +5,9 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" r:id="rId3"/>
-    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
+    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
+    <sheet name="Groups" sheetId="4" r:id="rId4"/>
+    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -953,25 +954,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
       </c>
       <c r="B9" t="str">
-        <v>Troy Smith</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C9">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D9" t="str">
         <v>Male</v>
       </c>
       <c r="E9" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F9" t="str">
-        <v>429354308</v>
+        <v>423530043</v>
       </c>
       <c r="G9" t="str">
-        <v>Melbourne</v>
+        <v>Preston</v>
       </c>
       <c r="H9" t="str">
         <v>B+</v>
@@ -980,115 +981,115 @@
         <v>available</v>
       </c>
       <c r="J9" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="K9" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-      <c r="L9" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
-      </c>
-      <c r="M9" t="str">
-        <v>NA</v>
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
       </c>
       <c r="B10" t="str">
-        <v>Tayla Huxtable</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="str">
         <v>Female</v>
       </c>
       <c r="E10" t="str">
-        <v>Taylahuxtable@gmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F10" t="str">
-        <v>435320280</v>
+        <v>448545599</v>
       </c>
       <c r="G10" t="str">
-        <v>FERNTREE GULLY</v>
+        <v>Melbourne</v>
+      </c>
+      <c r="H10" t="str">
+        <v>B+</v>
       </c>
       <c r="I10" t="str">
         <v>available</v>
       </c>
       <c r="J10" t="str">
-        <v>Troy Smith</v>
-      </c>
-      <c r="K10" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+      </c>
+      <c r="M10" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B11" t="str">
-        <v>Brent Barnett</v>
+        <v>Troy Smith</v>
       </c>
       <c r="C11">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D11" t="str">
         <v>Male</v>
       </c>
       <c r="E11" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>Troyssmith94@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>423530043</v>
+        <v>429354308</v>
       </c>
       <c r="G11" t="str">
-        <v>Preston</v>
+        <v>Melbourne</v>
       </c>
       <c r="H11" t="str">
         <v>B+</v>
       </c>
       <c r="I11" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J11" t="str">
-        <v>Stephanie Squillacioti</v>
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="K11" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L11" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M11" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B12" t="str">
-        <v>Tara Saltzman</v>
+        <v>Tayla Huxtable</v>
       </c>
       <c r="C12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" t="str">
         <v>Female</v>
       </c>
       <c r="E12" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>Taylahuxtable@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>448545599</v>
+        <v>435320280</v>
       </c>
       <c r="G12" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H12" t="str">
-        <v>B+</v>
+        <v>FERNTREE GULLY</v>
       </c>
       <c r="I12" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J12" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
-      </c>
-      <c r="M12" t="str">
-        <v>NA</v>
+        <v>Troy Smith</v>
+      </c>
+      <c r="K12" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
       </c>
     </row>
     <row r="13">
@@ -2389,6 +2390,77 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RecordDayID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ContestantID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Block</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Seat</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BookingEmailSent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ConfirmedRSVP</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ad340cba-9702-4a35-9a1f-7098bb2792d2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>A1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>055b0eeb-95e3-48d2-bab8-608bbe0173ce</v>
+      </c>
+      <c r="B3" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="str">
+        <v>A2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
@@ -2422,7 +2494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -736,7 +736,7 @@
         <v>B</v>
       </c>
       <c r="I2" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J2" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -769,242 +769,245 @@
         <v>B</v>
       </c>
       <c r="I3" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J3" t="str">
         <v>Donna Collins, Tom Collins</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
+        <v>8a905dfd-647c-4d96-a741-f7f1517a5136</v>
       </c>
       <c r="B4" t="str">
-        <v>Sharon King</v>
+        <v>Deanna Hay</v>
       </c>
       <c r="C4">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D4" t="str">
         <v>Female</v>
       </c>
       <c r="E4" t="str">
-        <v>dreamweaversixtyseven@gmail.com</v>
+        <v>dee_hay24@hotmail.com</v>
       </c>
       <c r="F4" t="str">
-        <v>611488000000</v>
+        <v>424504430</v>
       </c>
       <c r="G4" t="str">
-        <v xml:space="preserve">Mooroopna </v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H4" t="str">
-        <v>A</v>
+        <v>DNU</v>
       </c>
       <c r="I4" t="str">
         <v>available</v>
       </c>
-      <c r="J4" t="str" xml:space="preserve">
+      <c r="J4" t="str">
+        <v>Lynetta Shan Faoa</v>
+      </c>
+      <c r="L4" t="str">
+        <v xml:space="preserve">Cerebral palsy in a wheelchair </v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>efd8ab2e-988b-4afb-9374-3c3e3676f43a</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Matilda Sutherland</v>
+      </c>
+      <c r="C5">
+        <v>26</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E5" t="str">
+        <v>matilda.sutherland@hotmail.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>0467 165 012</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Bundoora</v>
+      </c>
+      <c r="H5" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I5" t="str">
+        <v>available</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Grace Mann</v>
+      </c>
+      <c r="M5" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>96d2c8ad-1e67-4659-b3d0-a3bbd4fe40cb</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Karina  Richmond</v>
+      </c>
+      <c r="C6">
+        <v>38</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E6" t="str">
+        <v>richmondkarina@yahoo.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>400554609</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Newcomb</v>
+      </c>
+      <c r="H6" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I6" t="str">
+        <v>available</v>
+      </c>
+      <c r="J6" t="str">
+        <v>AMY DILLON</v>
+      </c>
+      <c r="M6" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>7a05a613-1880-40c5-ab6a-cc078b418b6e</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Deb  Jones</v>
+      </c>
+      <c r="C7">
+        <v>66</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E7" t="str">
+        <v>fullhouse5@optusnet.com.au</v>
+      </c>
+      <c r="F7" t="str">
+        <v>438561474</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Bayswater North</v>
+      </c>
+      <c r="H7" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I7" t="str">
+        <v>available</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Daryl Jones</v>
+      </c>
+      <c r="M7" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sharon King</v>
+      </c>
+      <c r="C8">
+        <v>58</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E8" t="str">
+        <v>dreamweaversixtyseven@gmail.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>611488000000</v>
+      </c>
+      <c r="G8" t="str">
+        <v xml:space="preserve">Mooroopna </v>
+      </c>
+      <c r="H8" t="str">
+        <v>A</v>
+      </c>
+      <c r="I8" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J8" t="str" xml:space="preserve">
         <v xml:space="preserve">
 Friend :Jacinda Austin
 ID:b6042a-1-1936475</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M8" t="str">
         <v xml:space="preserve">No </v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>8a905dfd-647c-4d96-a741-f7f1517a5136</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Deanna Hay</v>
-      </c>
-      <c r="C5">
-        <v>38</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E5" t="str">
-        <v>dee_hay24@hotmail.com</v>
-      </c>
-      <c r="F5" t="str">
-        <v>424504430</v>
-      </c>
-      <c r="G5" t="str">
-        <v xml:space="preserve">Melbourne </v>
-      </c>
-      <c r="H5" t="str">
-        <v>DNU</v>
-      </c>
-      <c r="I5" t="str">
-        <v>available</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Lynetta Shan Faoa</v>
-      </c>
-      <c r="L5" t="str">
-        <v xml:space="preserve">Cerebral palsy in a wheelchair </v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>efd8ab2e-988b-4afb-9374-3c3e3676f43a</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Matilda Sutherland</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E6" t="str">
-        <v>matilda.sutherland@hotmail.com</v>
-      </c>
-      <c r="F6" t="str">
-        <v>0467 165 012</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Bundoora</v>
-      </c>
-      <c r="H6" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I6" t="str">
-        <v>available</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Grace Mann</v>
-      </c>
-      <c r="M6" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>96d2c8ad-1e67-4659-b3d0-a3bbd4fe40cb</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Karina  Richmond</v>
-      </c>
-      <c r="C7">
-        <v>38</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E7" t="str">
-        <v>richmondkarina@yahoo.com</v>
-      </c>
-      <c r="F7" t="str">
-        <v>400554609</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Newcomb</v>
-      </c>
-      <c r="H7" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I7" t="str">
-        <v>available</v>
-      </c>
-      <c r="J7" t="str">
-        <v>AMY DILLON</v>
-      </c>
-      <c r="M7" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>7a05a613-1880-40c5-ab6a-cc078b418b6e</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Deb  Jones</v>
-      </c>
-      <c r="C8">
-        <v>66</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E8" t="str">
-        <v>fullhouse5@optusnet.com.au</v>
-      </c>
-      <c r="F8" t="str">
-        <v>438561474</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Bayswater North</v>
-      </c>
-      <c r="H8" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I8" t="str">
-        <v>available</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Daryl Jones</v>
-      </c>
-      <c r="M8" t="str">
-        <v>No</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
       </c>
       <c r="B9" t="str">
-        <v>Brent Barnett</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C9">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D9" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E9" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F9" t="str">
-        <v>423530043</v>
+        <v>448545599</v>
       </c>
       <c r="G9" t="str">
-        <v>Preston</v>
+        <v>Melbourne</v>
       </c>
       <c r="H9" t="str">
         <v>B+</v>
       </c>
       <c r="I9" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J9" t="str">
-        <v>Stephanie Squillacioti</v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+      </c>
+      <c r="M9" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
       </c>
       <c r="B10" t="str">
-        <v>Tara Saltzman</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C10">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D10" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E10" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>448545599</v>
+        <v>423530043</v>
       </c>
       <c r="G10" t="str">
-        <v>Melbourne</v>
+        <v>Preston</v>
       </c>
       <c r="H10" t="str">
         <v>B+</v>
@@ -1013,10 +1016,7 @@
         <v>available</v>
       </c>
       <c r="J10" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
-      </c>
-      <c r="M10" t="str">
-        <v>NA</v>
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="11">
@@ -1160,127 +1160,124 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
+        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
       </c>
       <c r="B15" t="str">
-        <v>Sarah Desira</v>
+        <v>Thomas Mckenna</v>
       </c>
       <c r="C15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E15" t="str">
-        <v>unicornwolf11@gmail.com</v>
+        <v>mckenna.6@yahoo.com</v>
       </c>
       <c r="F15" t="str">
-        <v>450765125</v>
+        <v>421758700</v>
       </c>
       <c r="G15" t="str">
-        <v>Lara</v>
+        <v xml:space="preserve">Officer South </v>
       </c>
       <c r="H15" t="str">
         <v>B</v>
       </c>
       <c r="I15" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J15" t="str">
-        <v>Husband Daniel Desira b6042a-1-1936280</v>
-      </c>
-      <c r="M15" t="str">
-        <v xml:space="preserve">No </v>
+        <v>thomas mckenna, Carolyn (Caz) Wilby</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
+        <v>1d96e742-18bb-4fc0-b741-154d1a4d9487</v>
       </c>
       <c r="B16" t="str">
-        <v>Anna Fonua</v>
+        <v>James Butler</v>
       </c>
       <c r="C16">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D16" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E16" t="str">
-        <v>Annawallace89@hotmail.com</v>
+        <v>butlerjg1509@gmail.com</v>
       </c>
       <c r="F16" t="str">
-        <v>452452442</v>
+        <v>428400584</v>
       </c>
       <c r="G16" t="str">
-        <v>Truganina</v>
+        <v>Mentone</v>
       </c>
       <c r="H16" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I16" t="str">
         <v>available</v>
       </c>
       <c r="J16" t="str">
-        <v>Dad Michael Wallace - b6042a-1-1936372</v>
-      </c>
-      <c r="M16" t="str">
-        <v xml:space="preserve">no </v>
+        <v>Issy McReynolds</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
       </c>
       <c r="B17" t="str">
-        <v>David Fenwick</v>
+        <v>Mara Baumgardner</v>
       </c>
       <c r="C17">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D17" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E17" t="str">
-        <v>David.s.fenwick@gmail.com</v>
+        <v>Granic@hotmail.com</v>
       </c>
       <c r="F17" t="str">
-        <v>429811171</v>
+        <v>407364450</v>
       </c>
       <c r="G17" t="str">
-        <v>Teesdale</v>
+        <v>Cockatoo</v>
       </c>
       <c r="H17" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I17" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J17" t="str">
-        <v>Solo</v>
+        <v xml:space="preserve">Mum - Mira Granic </v>
+      </c>
+      <c r="M17" t="str">
+        <v xml:space="preserve">No </v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1d96e742-18bb-4fc0-b741-154d1a4d9487</v>
+        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
       </c>
       <c r="B18" t="str">
-        <v>James Butler</v>
+        <v>Eden Hayes</v>
       </c>
       <c r="C18">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D18" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E18" t="str">
-        <v>butlerjg1509@gmail.com</v>
+        <v>edenhayes19@gmail.com</v>
       </c>
       <c r="F18" t="str">
-        <v>428400584</v>
+        <v>448096139</v>
       </c>
       <c r="G18" t="str">
-        <v>Mentone</v>
+        <v>Elwood</v>
       </c>
       <c r="H18" t="str">
         <v>B+</v>
@@ -1289,74 +1286,71 @@
         <v>available</v>
       </c>
       <c r="J18" t="str">
-        <v>Issy McReynolds</v>
+        <v>Jackson Harris</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
       </c>
       <c r="B19" t="str">
-        <v>Mara Baumgardner</v>
+        <v>Antonio Freno</v>
       </c>
       <c r="C19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E19" t="str">
-        <v>Granic@hotmail.com</v>
+        <v>frenoantonio@hotmail.it</v>
       </c>
       <c r="F19" t="str">
-        <v>407364450</v>
+        <v>422177371</v>
       </c>
       <c r="G19" t="str">
-        <v>Cockatoo</v>
+        <v>Glenroy</v>
       </c>
       <c r="H19" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I19" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J19" t="str">
-        <v xml:space="preserve">Mum - Mira Granic </v>
-      </c>
-      <c r="M19" t="str">
-        <v xml:space="preserve">No </v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
       </c>
       <c r="B20" t="str">
-        <v>Eden Hayes</v>
+        <v>David Fenwick</v>
       </c>
       <c r="C20">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D20" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E20" t="str">
-        <v>edenhayes19@gmail.com</v>
+        <v>David.s.fenwick@gmail.com</v>
       </c>
       <c r="F20" t="str">
-        <v>448096139</v>
+        <v>429811171</v>
       </c>
       <c r="G20" t="str">
-        <v>Elwood</v>
+        <v>Teesdale</v>
       </c>
       <c r="H20" t="str">
         <v>B+</v>
       </c>
       <c r="I20" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J20" t="str">
-        <v>Jackson Harris</v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="21">
@@ -1385,7 +1379,7 @@
         <v>B+</v>
       </c>
       <c r="I21" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J21" t="str">
         <v>SOLO</v>
@@ -1394,365 +1388,371 @@
         <v>NA</v>
       </c>
     </row>
-    <row r="22" xml:space="preserve">
+    <row r="22">
       <c r="A22" t="str">
-        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
       </c>
       <c r="B22" t="str">
-        <v>Kayla Lorenzini</v>
+        <v>Tamara Mifsud</v>
       </c>
       <c r="C22">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D22" t="str">
         <v>Female</v>
       </c>
       <c r="E22" t="str">
-        <v>kaylalorenzini_@hotmail.com</v>
+        <v>tamara.mifsud@hotmail.com</v>
       </c>
       <c r="F22" t="str">
-        <v>430517653</v>
+        <v>416552122</v>
       </c>
       <c r="G22" t="str">
-        <v>Melbourne</v>
+        <v>Aintree</v>
       </c>
       <c r="H22" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I22" t="str">
         <v>available</v>
       </c>
-      <c r="J22" t="str" xml:space="preserve">
+      <c r="J22" t="str">
+        <v>Aliye Abcilar</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Philip Natoli</v>
+      </c>
+      <c r="C23">
+        <v>29</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Philip.natoli@outlook.com</v>
+      </c>
+      <c r="F23" t="str">
+        <v>466021882</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Caulfield South</v>
+      </c>
+      <c r="H23" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I23" t="str">
+        <v>available</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Hayley Wright</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Ricky Steve</v>
+      </c>
+      <c r="C24">
+        <v>31</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E24" t="str">
+        <v>tj-c-a@hotmail.com</v>
+      </c>
+      <c r="F24" t="str">
+        <v>411360449</v>
+      </c>
+      <c r="G24" t="str">
+        <v xml:space="preserve">Wangaratta </v>
+      </c>
+      <c r="H24" t="str">
+        <v>A</v>
+      </c>
+      <c r="I24" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Taylah-Jayne Lockery</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Jeanette Quy</v>
+      </c>
+      <c r="C25">
+        <v>74</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E25" t="str">
+        <v>quyfamily@tpg.com.au</v>
+      </c>
+      <c r="F25" t="str">
+        <v>402902273</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Rowville</v>
+      </c>
+      <c r="H25" t="str">
+        <v>C</v>
+      </c>
+      <c r="I25" t="str">
+        <v>available</v>
+      </c>
+      <c r="M25" t="str">
+        <v xml:space="preserve">nothing of note </v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>dcd305dd-c710-4a1e-859c-835031154035</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Nicholas Boicos</v>
+      </c>
+      <c r="C26">
+        <v>22</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E26" t="str">
+        <v>nboicos@hotmail.com</v>
+      </c>
+      <c r="F26" t="str">
+        <v>429556400</v>
+      </c>
+      <c r="G26" t="str">
+        <v xml:space="preserve">Altona Meadows </v>
+      </c>
+      <c r="H26" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I26" t="str">
+        <v>available</v>
+      </c>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nick Boicos 
+Matthew Boicos
+Brothers</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Mozgda  Alime</v>
+      </c>
+      <c r="C27">
+        <v>39</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E27" t="str">
+        <v>smalimi@hotmail.com</v>
+      </c>
+      <c r="F27" t="str">
+        <v>402010235</v>
+      </c>
+      <c r="G27" t="str">
+        <v xml:space="preserve">Melbourne </v>
+      </c>
+      <c r="H27" t="str">
+        <v>C</v>
+      </c>
+      <c r="I27" t="str">
+        <v>available</v>
+      </c>
+      <c r="J27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Sadaf Almini - I believe this is her cousin 
+Lida Alime - I believe this is her cousin or sister 
+Ahmad Alime - Ahmad is Lina's husband </v>
+      </c>
+      <c r="M27" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Kayla Lorenzini</v>
+      </c>
+      <c r="C28">
+        <v>29</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E28" t="str">
+        <v>kaylalorenzini_@hotmail.com</v>
+      </c>
+      <c r="F28" t="str">
+        <v>430517653</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H28" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I28" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J28" t="str" xml:space="preserve">
         <v xml:space="preserve">Kayla Lorenzini
 James Lorenzini
 Deanna Gramola</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Kerrie Donald</v>
-      </c>
-      <c r="C23">
-        <v>47</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E23" t="str">
-        <v>kerrieldonald@hotmail.com</v>
-      </c>
-      <c r="F23" t="str">
-        <v>61400826565</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Mailor's Flat</v>
-      </c>
-      <c r="H23" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I23" t="str">
-        <v>available</v>
-      </c>
-      <c r="J23" t="str">
-        <v>kerrie donald, alistair donald</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Tamara Mifsud</v>
-      </c>
-      <c r="C24">
-        <v>32</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E24" t="str">
-        <v>tamara.mifsud@hotmail.com</v>
-      </c>
-      <c r="F24" t="str">
-        <v>416552122</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Aintree</v>
-      </c>
-      <c r="H24" t="str">
-        <v>B</v>
-      </c>
-      <c r="I24" t="str">
-        <v>available</v>
-      </c>
-      <c r="J24" t="str">
-        <v>Aliye Abcilar</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Philip Natoli</v>
-      </c>
-      <c r="C25">
-        <v>29</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E25" t="str">
-        <v>Philip.natoli@outlook.com</v>
-      </c>
-      <c r="F25" t="str">
-        <v>466021882</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Caulfield South</v>
-      </c>
-      <c r="H25" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I25" t="str">
-        <v>available</v>
-      </c>
-      <c r="J25" t="str">
-        <v>Hayley Wright</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Jeanette Quy</v>
-      </c>
-      <c r="C26">
-        <v>74</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E26" t="str">
-        <v>quyfamily@tpg.com.au</v>
-      </c>
-      <c r="F26" t="str">
-        <v>402902273</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Rowville</v>
-      </c>
-      <c r="H26" t="str">
-        <v>C</v>
-      </c>
-      <c r="I26" t="str">
-        <v>available</v>
-      </c>
-      <c r="M26" t="str">
-        <v xml:space="preserve">nothing of note </v>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
-        <v>dcd305dd-c710-4a1e-859c-835031154035</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Nicholas Boicos</v>
-      </c>
-      <c r="C27">
+    <row r="29">
+      <c r="A29" t="str">
+        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Natasha Devers</v>
+      </c>
+      <c r="C29">
         <v>22</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E27" t="str">
-        <v>nboicos@hotmail.com</v>
-      </c>
-      <c r="F27" t="str">
-        <v>429556400</v>
-      </c>
-      <c r="G27" t="str">
-        <v xml:space="preserve">Altona Meadows </v>
-      </c>
-      <c r="H27" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I27" t="str">
-        <v>available</v>
-      </c>
-      <c r="J27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nick Boicos 
-Matthew Boicos
-Brothers</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Ricky Steve</v>
-      </c>
-      <c r="C28">
-        <v>31</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E28" t="str">
-        <v>tj-c-a@hotmail.com</v>
-      </c>
-      <c r="F28" t="str">
-        <v>411360449</v>
-      </c>
-      <c r="G28" t="str">
-        <v xml:space="preserve">Wangaratta </v>
-      </c>
-      <c r="H28" t="str">
-        <v>A</v>
-      </c>
-      <c r="I28" t="str">
-        <v>available</v>
-      </c>
-      <c r="J28" t="str">
-        <v>Taylah-Jayne Lockery</v>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29" t="str">
-        <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Mozgda  Alime</v>
-      </c>
-      <c r="C29">
-        <v>39</v>
       </c>
       <c r="D29" t="str">
         <v>Female</v>
       </c>
       <c r="E29" t="str">
-        <v>smalimi@hotmail.com</v>
+        <v>natashadevers@gmail.com</v>
       </c>
       <c r="F29" t="str">
-        <v>402010235</v>
+        <v>484003770</v>
       </c>
       <c r="G29" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v xml:space="preserve">Waterways </v>
       </c>
       <c r="H29" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="I29" t="str">
         <v>available</v>
       </c>
-      <c r="J29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Sadaf Almini - I believe this is her cousin 
-Lida Alime - I believe this is her cousin or sister 
-Ahmad Alime - Ahmad is Lina's husband </v>
-      </c>
-      <c r="M29" t="str">
-        <v xml:space="preserve">No </v>
+      <c r="J29" t="str">
+        <v>Oliver Moran</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
+        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
       </c>
       <c r="B30" t="str">
-        <v>Thomas Mckenna</v>
+        <v>Sarah Desira</v>
       </c>
       <c r="C30">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E30" t="str">
-        <v>mckenna.6@yahoo.com</v>
+        <v>unicornwolf11@gmail.com</v>
       </c>
       <c r="F30" t="str">
-        <v>421758700</v>
+        <v>450765125</v>
       </c>
       <c r="G30" t="str">
-        <v xml:space="preserve">Officer South </v>
+        <v>Lara</v>
       </c>
       <c r="H30" t="str">
         <v>B</v>
       </c>
       <c r="I30" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J30" t="str">
-        <v>thomas mckenna, Carolyn (Caz) Wilby</v>
+        <v>Husband Daniel Desira b6042a-1-1936280</v>
+      </c>
+      <c r="M30" t="str">
+        <v xml:space="preserve">No </v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
+        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
       </c>
       <c r="B31" t="str">
-        <v>Natasha Devers</v>
+        <v>Anna Fonua</v>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D31" t="str">
         <v>Female</v>
       </c>
       <c r="E31" t="str">
-        <v>natashadevers@gmail.com</v>
+        <v>Annawallace89@hotmail.com</v>
       </c>
       <c r="F31" t="str">
-        <v>484003770</v>
+        <v>452452442</v>
       </c>
       <c r="G31" t="str">
-        <v xml:space="preserve">Waterways </v>
+        <v>Truganina</v>
       </c>
       <c r="H31" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I31" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J31" t="str">
-        <v>Oliver Moran</v>
+        <v>Dad Michael Wallace - b6042a-1-1936372</v>
+      </c>
+      <c r="M31" t="str">
+        <v xml:space="preserve">no </v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
       </c>
       <c r="B32" t="str">
-        <v>Antonio Freno</v>
+        <v>Kerrie Donald</v>
       </c>
       <c r="C32">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D32" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E32" t="str">
-        <v>frenoantonio@hotmail.it</v>
+        <v>kerrieldonald@hotmail.com</v>
       </c>
       <c r="F32" t="str">
-        <v>422177371</v>
+        <v>61400826565</v>
       </c>
       <c r="G32" t="str">
-        <v>Glenroy</v>
+        <v>Mailor's Flat</v>
       </c>
       <c r="H32" t="str">
         <v>B+</v>
       </c>
       <c r="I32" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J32" t="str">
-        <v>Solo</v>
+        <v>kerrie donald, alistair donald</v>
       </c>
     </row>
     <row r="33">
@@ -1789,10 +1789,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
       </c>
       <c r="B34" t="str">
-        <v>Sherif Haggag</v>
+        <v>Alexander Leonard</v>
       </c>
       <c r="C34">
         <v>38</v>
@@ -1801,45 +1801,45 @@
         <v>Male</v>
       </c>
       <c r="E34" t="str">
-        <v>Shaggag87@gmail.com</v>
+        <v>alexleonardedit@gmail.com</v>
       </c>
       <c r="F34" t="str">
-        <v>426233449</v>
+        <v>421834476</v>
       </c>
       <c r="G34" t="str">
-        <v>Belmont</v>
+        <v>Croydon</v>
       </c>
       <c r="H34" t="str">
-        <v>B+</v>
+        <v>A+</v>
       </c>
       <c r="I34" t="str">
         <v>available</v>
       </c>
       <c r="J34" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>melissa francis, Alexander Leonard</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
       <c r="A35" t="str">
-        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
+        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
       </c>
       <c r="B35" t="str">
-        <v>Alexander Leonard</v>
+        <v>Bronwyn Parsons</v>
       </c>
       <c r="C35">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D35" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E35" t="str">
-        <v>alexleonardedit@gmail.com</v>
+        <v>Babybear61153@gmail.com</v>
       </c>
       <c r="F35" t="str">
-        <v>421834476</v>
+        <v>432543647</v>
       </c>
       <c r="G35" t="str">
-        <v>Croydon</v>
+        <v>Rosebud</v>
       </c>
       <c r="H35" t="str">
         <v>A+</v>
@@ -1847,180 +1847,180 @@
       <c r="I35" t="str">
         <v>available</v>
       </c>
-      <c r="J35" t="str">
-        <v>melissa francis, Alexander Leonard</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="J35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yolette Huon - yol-et Hue on
+Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
       <c r="A36" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
       </c>
       <c r="B36" t="str">
-        <v>Leanne Bryant</v>
+        <v>Paige Greig</v>
       </c>
       <c r="C36">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D36" t="str">
         <v>Female</v>
       </c>
       <c r="E36" t="str">
-        <v>blazeandcougar@gmail.com</v>
+        <v>paigegreig@hotmail.com</v>
       </c>
       <c r="F36" t="str">
-        <v>61415438228</v>
+        <v>406598552</v>
       </c>
       <c r="G36" t="str">
-        <v xml:space="preserve">Hampton Park </v>
+        <v>Mooroolbark</v>
       </c>
       <c r="H36" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="I36" t="str">
         <v>available</v>
       </c>
-      <c r="J36" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Erin
+Morgan (sister) - need to do application</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="str">
-        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
       </c>
       <c r="B37" t="str">
-        <v>Bronwyn Parsons</v>
+        <v>Tamika Colville</v>
       </c>
       <c r="C37">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D37" t="str">
         <v>Female</v>
       </c>
       <c r="E37" t="str">
-        <v>Babybear61153@gmail.com</v>
+        <v>tamika.colville@gmail.com</v>
       </c>
       <c r="F37" t="str">
-        <v>432543647</v>
+        <v>409132141</v>
       </c>
       <c r="G37" t="str">
-        <v>Rosebud</v>
+        <v>Golden square</v>
       </c>
       <c r="H37" t="str">
-        <v>A+</v>
+        <v>B+</v>
       </c>
       <c r="I37" t="str">
-        <v>available</v>
-      </c>
-      <c r="J37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Yolette Huon - yol-et Hue on
-Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>assigned</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Shinae Colville</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Diagnosed with MS in 2018</v>
+      </c>
+      <c r="M37" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
       </c>
       <c r="B38" t="str">
-        <v>Tamika Colville</v>
+        <v>Linda Browne</v>
       </c>
       <c r="C38">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D38" t="str">
         <v>Female</v>
       </c>
       <c r="E38" t="str">
-        <v>tamika.colville@gmail.com</v>
+        <v>Lindabrowne@iprimus.com.au</v>
       </c>
       <c r="F38" t="str">
-        <v>409132141</v>
+        <v>429570177</v>
       </c>
       <c r="G38" t="str">
-        <v>Golden square</v>
+        <v>OFFICER</v>
       </c>
       <c r="H38" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I38" t="str">
-        <v>available</v>
-      </c>
-      <c r="J38" t="str">
-        <v>Shinae Colville</v>
-      </c>
-      <c r="L38" t="str">
-        <v>Diagnosed with MS in 2018</v>
-      </c>
-      <c r="M38" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
-        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Paige Greig</v>
-      </c>
-      <c r="C39">
-        <v>31</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E39" t="str">
-        <v>paigegreig@hotmail.com</v>
-      </c>
-      <c r="F39" t="str">
-        <v>406598552</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Mooroolbark</v>
-      </c>
-      <c r="H39" t="str">
-        <v>C</v>
-      </c>
-      <c r="I39" t="str">
-        <v>available</v>
-      </c>
-      <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Erin
-Morgan (sister) - need to do application</v>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
-        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Linda Browne</v>
-      </c>
-      <c r="C40">
-        <v>54</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E40" t="str">
-        <v>Lindabrowne@iprimus.com.au</v>
-      </c>
-      <c r="F40" t="str">
-        <v>429570177</v>
-      </c>
-      <c r="G40" t="str">
-        <v>OFFICER</v>
-      </c>
-      <c r="H40" t="str">
-        <v>B</v>
-      </c>
-      <c r="I40" t="str">
-        <v>available</v>
-      </c>
-      <c r="J40" t="str" xml:space="preserve">
+        <v>assigned</v>
+      </c>
+      <c r="J38" t="str" xml:space="preserve">
         <v xml:space="preserve">Natalie Browne
 Linda Browne
 Aidan Miler</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Sherif Haggag</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Shaggag87@gmail.com</v>
+      </c>
+      <c r="F39" t="str">
+        <v>426233449</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Belmont</v>
+      </c>
+      <c r="H39" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I39" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Leanne Bryant</v>
+      </c>
+      <c r="C40">
+        <v>63</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E40" t="str">
+        <v>blazeandcougar@gmail.com</v>
+      </c>
+      <c r="F40" t="str">
+        <v>61415438228</v>
+      </c>
+      <c r="G40" t="str">
+        <v xml:space="preserve">Hampton Park </v>
+      </c>
+      <c r="H40" t="str">
+        <v>B</v>
+      </c>
+      <c r="I40" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
     <row r="41">
       <c r="A41" t="str">
         <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
@@ -2079,7 +2079,7 @@
         <v>B+</v>
       </c>
       <c r="I42" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J42" t="str">
         <v>Solo</v>
@@ -2144,7 +2144,7 @@
         <v>B</v>
       </c>
       <c r="I44" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J44" t="str">
         <v>SOLO</v>
@@ -2179,7 +2179,7 @@
         <v>B</v>
       </c>
       <c r="I45" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J45" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -2390,7 +2390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2452,9 +2452,366 @@
         <v>A2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>69e786fd-e21d-4e14-88da-7125c5f4a1d2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C4" t="str">
+        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>A3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>eb8bfbdd-63a6-4079-aba9-5800fb7a540b</v>
+      </c>
+      <c r="B5" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C5" t="str">
+        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>B1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>a3858d3d-55d1-4fdb-97d8-320bba44e137</v>
+      </c>
+      <c r="B6" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C6" t="str">
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>B2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>b52bba5a-5df3-4857-bd40-94b252176098</v>
+      </c>
+      <c r="B7" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C7" t="str">
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>B3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>4f0e1cd0-0b97-41cf-8546-066d8aacaa18</v>
+      </c>
+      <c r="B8" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C8" t="str">
+        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>B4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>e1a80551-d2da-4874-91db-588715a4fac4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C9" t="str">
+        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <v>B5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>abc48d6d-e2be-45f3-b39d-aab68fd3a887</v>
+      </c>
+      <c r="B10" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C10" t="str">
+        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>C1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1996d94e-e4b6-41eb-9c86-6f2ce57c0d3e</v>
+      </c>
+      <c r="B11" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C11" t="str">
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v>C2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>15371ee3-0b7e-4086-84f6-3720ca1ff543</v>
+      </c>
+      <c r="B12" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C12" t="str">
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>C3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9c31ffbb-2789-43bb-a60e-90c4b8100cef</v>
+      </c>
+      <c r="B13" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C13" t="str">
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>C4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>bc578b4a-ddea-41c3-9540-e88f6659f18c</v>
+      </c>
+      <c r="B14" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C14" t="str">
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>D1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>72473e20-842c-4521-a6c8-ba7c2d625b26</v>
+      </c>
+      <c r="B15" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>D2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>cdfce1b8-2ada-4f40-a965-ec4421f32195</v>
+      </c>
+      <c r="B16" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C16" t="str">
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="str">
+        <v>D3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>0bafba7c-79a0-4bae-b175-028f5c764b20</v>
+      </c>
+      <c r="B17" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C17" t="str">
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="str">
+        <v>D4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>94521f77-45d2-4af9-952a-a692cd7c7aa8</v>
+      </c>
+      <c r="B18" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C18" t="str">
+        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
+        <v>E1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>38e2c0fc-5873-43aa-9394-f7c2709f8a83</v>
+      </c>
+      <c r="B19" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C19" t="str">
+        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>E2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>c21a4154-3157-46c8-a878-b599e0689d93</v>
+      </c>
+      <c r="B20" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C20" t="str">
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="str">
+        <v>A1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>ffc84c94-f1d0-4b10-aa29-30dc6ffbda57</v>
+      </c>
+      <c r="B21" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C21" t="str">
+        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="str">
+        <v>A2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>b27d2d06-2e2c-4115-9995-db7dd2a60c77</v>
+      </c>
+      <c r="B22" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C22" t="str">
+        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="str">
+        <v>A3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>7a2cb7e6-2374-470d-916d-9e0890d7fde8</v>
+      </c>
+      <c r="B23" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C23" t="str">
+        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="str">
+        <v>A4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>36893ad6-bfef-4de4-b6f2-a5c5f1b825b0</v>
+      </c>
+      <c r="B24" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C24" t="str">
+        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="str">
+        <v>A5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H24"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -736,7 +736,7 @@
         <v>B</v>
       </c>
       <c r="I2" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J2" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -769,7 +769,7 @@
         <v>B</v>
       </c>
       <c r="I3" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J3" t="str">
         <v>Donna Collins, Tom Collins</v>
@@ -941,7 +941,7 @@
         <v>A</v>
       </c>
       <c r="I8" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J8" t="str" xml:space="preserve">
         <v xml:space="preserve">
@@ -978,7 +978,7 @@
         <v>B+</v>
       </c>
       <c r="I9" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J9" t="str">
         <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
@@ -1021,75 +1021,75 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B11" t="str">
-        <v>Troy Smith</v>
+        <v>Tayla Huxtable</v>
       </c>
       <c r="C11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D11" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E11" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>Taylahuxtable@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>429354308</v>
+        <v>435320280</v>
       </c>
       <c r="G11" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H11" t="str">
-        <v>B+</v>
+        <v>FERNTREE GULLY</v>
       </c>
       <c r="I11" t="str">
         <v>assigned</v>
       </c>
       <c r="J11" t="str">
-        <v>Tayla Huxtable</v>
+        <v>Troy Smith</v>
       </c>
       <c r="K11" t="str">
         <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
       </c>
-      <c r="L11" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
-      </c>
-      <c r="M11" t="str">
-        <v>NA</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B12" t="str">
-        <v>Tayla Huxtable</v>
+        <v>Troy Smith</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D12" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E12" t="str">
-        <v>Taylahuxtable@gmail.com</v>
+        <v>Troyssmith94@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>435320280</v>
+        <v>429354308</v>
       </c>
       <c r="G12" t="str">
-        <v>FERNTREE GULLY</v>
+        <v>Melbourne</v>
+      </c>
+      <c r="H12" t="str">
+        <v>B+</v>
       </c>
       <c r="I12" t="str">
         <v>assigned</v>
       </c>
       <c r="J12" t="str">
-        <v>Troy Smith</v>
+        <v>Tayla Huxtable</v>
       </c>
       <c r="K12" t="str">
         <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L12" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M12" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="13">
@@ -1160,98 +1160,98 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
+        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
       </c>
       <c r="B15" t="str">
-        <v>Thomas Mckenna</v>
+        <v>Kerrie Donald</v>
       </c>
       <c r="C15">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D15" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E15" t="str">
-        <v>mckenna.6@yahoo.com</v>
+        <v>kerrieldonald@hotmail.com</v>
       </c>
       <c r="F15" t="str">
-        <v>421758700</v>
+        <v>61400826565</v>
       </c>
       <c r="G15" t="str">
-        <v xml:space="preserve">Officer South </v>
+        <v>Mailor's Flat</v>
       </c>
       <c r="H15" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I15" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J15" t="str">
-        <v>thomas mckenna, Carolyn (Caz) Wilby</v>
+        <v>kerrie donald, alistair donald</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1d96e742-18bb-4fc0-b741-154d1a4d9487</v>
+        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
       </c>
       <c r="B16" t="str">
-        <v>James Butler</v>
+        <v>Thomas Mckenna</v>
       </c>
       <c r="C16">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D16" t="str">
         <v>Male</v>
       </c>
       <c r="E16" t="str">
-        <v>butlerjg1509@gmail.com</v>
+        <v>mckenna.6@yahoo.com</v>
       </c>
       <c r="F16" t="str">
-        <v>428400584</v>
+        <v>421758700</v>
       </c>
       <c r="G16" t="str">
-        <v>Mentone</v>
+        <v xml:space="preserve">Officer South </v>
       </c>
       <c r="H16" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I16" t="str">
         <v>available</v>
       </c>
       <c r="J16" t="str">
-        <v>Issy McReynolds</v>
+        <v>thomas mckenna, Carolyn (Caz) Wilby</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
+        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
       </c>
       <c r="B17" t="str">
-        <v>Mara Baumgardner</v>
+        <v>Sarah Desira</v>
       </c>
       <c r="C17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="str">
         <v>Female</v>
       </c>
       <c r="E17" t="str">
-        <v>Granic@hotmail.com</v>
+        <v>unicornwolf11@gmail.com</v>
       </c>
       <c r="F17" t="str">
-        <v>407364450</v>
+        <v>450765125</v>
       </c>
       <c r="G17" t="str">
-        <v>Cockatoo</v>
+        <v>Lara</v>
       </c>
       <c r="H17" t="str">
         <v>B</v>
       </c>
       <c r="I17" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J17" t="str">
-        <v xml:space="preserve">Mum - Mira Granic </v>
+        <v>Husband Daniel Desira b6042a-1-1936280</v>
       </c>
       <c r="M17" t="str">
         <v xml:space="preserve">No </v>
@@ -1259,25 +1259,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
+        <v>1d96e742-18bb-4fc0-b741-154d1a4d9487</v>
       </c>
       <c r="B18" t="str">
-        <v>Eden Hayes</v>
+        <v>James Butler</v>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D18" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E18" t="str">
-        <v>edenhayes19@gmail.com</v>
+        <v>butlerjg1509@gmail.com</v>
       </c>
       <c r="F18" t="str">
-        <v>448096139</v>
+        <v>428400584</v>
       </c>
       <c r="G18" t="str">
-        <v>Elwood</v>
+        <v>Mentone</v>
       </c>
       <c r="H18" t="str">
         <v>B+</v>
@@ -1286,30 +1286,30 @@
         <v>available</v>
       </c>
       <c r="J18" t="str">
-        <v>Jackson Harris</v>
+        <v>Issy McReynolds</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
       </c>
       <c r="B19" t="str">
-        <v>Antonio Freno</v>
+        <v>David Fenwick</v>
       </c>
       <c r="C19">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D19" t="str">
         <v>Male</v>
       </c>
       <c r="E19" t="str">
-        <v>frenoantonio@hotmail.it</v>
+        <v>David.s.fenwick@gmail.com</v>
       </c>
       <c r="F19" t="str">
-        <v>422177371</v>
+        <v>429811171</v>
       </c>
       <c r="G19" t="str">
-        <v>Glenroy</v>
+        <v>Teesdale</v>
       </c>
       <c r="H19" t="str">
         <v>B+</v>
@@ -1323,325 +1323,328 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
       </c>
       <c r="B20" t="str">
-        <v>David Fenwick</v>
+        <v>Eden Hayes</v>
       </c>
       <c r="C20">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D20" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E20" t="str">
-        <v>David.s.fenwick@gmail.com</v>
+        <v>edenhayes19@gmail.com</v>
       </c>
       <c r="F20" t="str">
-        <v>429811171</v>
+        <v>448096139</v>
       </c>
       <c r="G20" t="str">
-        <v>Teesdale</v>
+        <v>Elwood</v>
       </c>
       <c r="H20" t="str">
         <v>B+</v>
       </c>
       <c r="I20" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J20" t="str">
-        <v>Solo</v>
+        <v>Jackson Harris</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
       </c>
       <c r="B21" t="str">
-        <v>Kiran Rao</v>
+        <v>Anna Fonua</v>
       </c>
       <c r="C21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E21" t="str">
-        <v>kiran.rao07@gmail.com</v>
+        <v>Annawallace89@hotmail.com</v>
       </c>
       <c r="F21" t="str">
-        <v>420486042</v>
+        <v>452452442</v>
       </c>
       <c r="G21" t="str">
-        <v>Southbank</v>
+        <v>Truganina</v>
       </c>
       <c r="H21" t="str">
+        <v>A</v>
+      </c>
+      <c r="I21" t="str">
+        <v>available</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Dad Michael Wallace - b6042a-1-1936372</v>
+      </c>
+      <c r="M21" t="str">
+        <v xml:space="preserve">no </v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Kayla Lorenzini</v>
+      </c>
+      <c r="C22">
+        <v>29</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E22" t="str">
+        <v>kaylalorenzini_@hotmail.com</v>
+      </c>
+      <c r="F22" t="str">
+        <v>430517653</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H22" t="str">
         <v>B+</v>
       </c>
-      <c r="I21" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J21" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M21" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Tamara Mifsud</v>
-      </c>
-      <c r="C22">
-        <v>32</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E22" t="str">
-        <v>tamara.mifsud@hotmail.com</v>
-      </c>
-      <c r="F22" t="str">
-        <v>416552122</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Aintree</v>
-      </c>
-      <c r="H22" t="str">
-        <v>B</v>
-      </c>
       <c r="I22" t="str">
         <v>available</v>
       </c>
-      <c r="J22" t="str">
-        <v>Aliye Abcilar</v>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Kayla Lorenzini
+James Lorenzini
+Deanna Gramola</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
       </c>
       <c r="B23" t="str">
-        <v>Philip Natoli</v>
+        <v>Kiran Rao</v>
       </c>
       <c r="C23">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D23" t="str">
         <v>Male</v>
       </c>
       <c r="E23" t="str">
-        <v>Philip.natoli@outlook.com</v>
+        <v>kiran.rao07@gmail.com</v>
       </c>
       <c r="F23" t="str">
-        <v>466021882</v>
+        <v>420486042</v>
       </c>
       <c r="G23" t="str">
-        <v>Caulfield South</v>
+        <v>Southbank</v>
       </c>
       <c r="H23" t="str">
         <v>B+</v>
       </c>
       <c r="I23" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J23" t="str">
-        <v>Hayley Wright</v>
+        <v>SOLO</v>
+      </c>
+      <c r="M23" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
+        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
       </c>
       <c r="B24" t="str">
-        <v>Ricky Steve</v>
+        <v>Tamara Mifsud</v>
       </c>
       <c r="C24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" t="str">
         <v>Female</v>
       </c>
       <c r="E24" t="str">
-        <v>tj-c-a@hotmail.com</v>
+        <v>tamara.mifsud@hotmail.com</v>
       </c>
       <c r="F24" t="str">
-        <v>411360449</v>
+        <v>416552122</v>
       </c>
       <c r="G24" t="str">
-        <v xml:space="preserve">Wangaratta </v>
+        <v>Aintree</v>
       </c>
       <c r="H24" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I24" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J24" t="str">
-        <v>Taylah-Jayne Lockery</v>
+        <v>Aliye Abcilar</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Philip Natoli</v>
+      </c>
+      <c r="C25">
+        <v>29</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Philip.natoli@outlook.com</v>
+      </c>
+      <c r="F25" t="str">
+        <v>466021882</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Caulfield South</v>
+      </c>
+      <c r="H25" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I25" t="str">
+        <v>available</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Hayley Wright</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
         <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B26" t="str">
         <v>Jeanette Quy</v>
       </c>
-      <c r="C25">
+      <c r="C26">
         <v>74</v>
       </c>
-      <c r="D25" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E25" t="str">
+      <c r="D26" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E26" t="str">
         <v>quyfamily@tpg.com.au</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F26" t="str">
         <v>402902273</v>
       </c>
-      <c r="G25" t="str">
+      <c r="G26" t="str">
         <v>Rowville</v>
       </c>
-      <c r="H25" t="str">
+      <c r="H26" t="str">
         <v>C</v>
       </c>
-      <c r="I25" t="str">
-        <v>available</v>
-      </c>
-      <c r="M25" t="str">
+      <c r="I26" t="str">
+        <v>available</v>
+      </c>
+      <c r="M26" t="str">
         <v xml:space="preserve">nothing of note </v>
       </c>
     </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26" t="str">
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
         <v>dcd305dd-c710-4a1e-859c-835031154035</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B27" t="str">
         <v>Nicholas Boicos</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>22</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D27" t="str">
         <v>Male</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E27" t="str">
         <v>nboicos@hotmail.com</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F27" t="str">
         <v>429556400</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G27" t="str">
         <v xml:space="preserve">Altona Meadows </v>
       </c>
-      <c r="H26" t="str">
+      <c r="H27" t="str">
         <v>B+</v>
       </c>
-      <c r="I26" t="str">
-        <v>available</v>
-      </c>
-      <c r="J26" t="str" xml:space="preserve">
+      <c r="I27" t="str">
+        <v>available</v>
+      </c>
+      <c r="J27" t="str" xml:space="preserve">
         <v xml:space="preserve">Nick Boicos 
 Matthew Boicos
 Brothers</v>
       </c>
     </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
         <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B28" t="str">
         <v>Mozgda  Alime</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>39</v>
       </c>
-      <c r="D27" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E27" t="str">
+      <c r="D28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E28" t="str">
         <v>smalimi@hotmail.com</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F28" t="str">
         <v>402010235</v>
       </c>
-      <c r="G27" t="str">
+      <c r="G28" t="str">
         <v xml:space="preserve">Melbourne </v>
       </c>
-      <c r="H27" t="str">
+      <c r="H28" t="str">
         <v>C</v>
       </c>
-      <c r="I27" t="str">
-        <v>available</v>
-      </c>
-      <c r="J27" t="str" xml:space="preserve">
+      <c r="I28" t="str">
+        <v>available</v>
+      </c>
+      <c r="J28" t="str" xml:space="preserve">
         <v xml:space="preserve">Sadaf Almini - I believe this is her cousin 
 Lida Alime - I believe this is her cousin or sister 
 Ahmad Alime - Ahmad is Lina's husband </v>
       </c>
-      <c r="M27" t="str">
+      <c r="M28" t="str">
         <v xml:space="preserve">No </v>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28" t="str">
-        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Kayla Lorenzini</v>
-      </c>
-      <c r="C28">
-        <v>29</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E28" t="str">
-        <v>kaylalorenzini_@hotmail.com</v>
-      </c>
-      <c r="F28" t="str">
-        <v>430517653</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H28" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I28" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Kayla Lorenzini
-James Lorenzini
-Deanna Gramola</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
+        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
       </c>
       <c r="B29" t="str">
-        <v>Natasha Devers</v>
+        <v>Mara Baumgardner</v>
       </c>
       <c r="C29">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D29" t="str">
         <v>Female</v>
       </c>
       <c r="E29" t="str">
-        <v>natashadevers@gmail.com</v>
+        <v>Granic@hotmail.com</v>
       </c>
       <c r="F29" t="str">
-        <v>484003770</v>
+        <v>407364450</v>
       </c>
       <c r="G29" t="str">
-        <v xml:space="preserve">Waterways </v>
+        <v>Cockatoo</v>
       </c>
       <c r="H29" t="str">
         <v>B</v>
@@ -1650,109 +1653,106 @@
         <v>available</v>
       </c>
       <c r="J29" t="str">
-        <v>Oliver Moran</v>
+        <v xml:space="preserve">Mum - Mira Granic </v>
+      </c>
+      <c r="M29" t="str">
+        <v xml:space="preserve">No </v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
+        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
       </c>
       <c r="B30" t="str">
-        <v>Sarah Desira</v>
+        <v>Natasha Devers</v>
       </c>
       <c r="C30">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D30" t="str">
         <v>Female</v>
       </c>
       <c r="E30" t="str">
-        <v>unicornwolf11@gmail.com</v>
+        <v>natashadevers@gmail.com</v>
       </c>
       <c r="F30" t="str">
-        <v>450765125</v>
+        <v>484003770</v>
       </c>
       <c r="G30" t="str">
-        <v>Lara</v>
+        <v xml:space="preserve">Waterways </v>
       </c>
       <c r="H30" t="str">
         <v>B</v>
       </c>
       <c r="I30" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J30" t="str">
-        <v>Husband Daniel Desira b6042a-1-1936280</v>
-      </c>
-      <c r="M30" t="str">
-        <v xml:space="preserve">No </v>
+        <v>Oliver Moran</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
       </c>
       <c r="B31" t="str">
-        <v>Anna Fonua</v>
+        <v>Antonio Freno</v>
       </c>
       <c r="C31">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D31" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E31" t="str">
-        <v>Annawallace89@hotmail.com</v>
+        <v>frenoantonio@hotmail.it</v>
       </c>
       <c r="F31" t="str">
-        <v>452452442</v>
+        <v>422177371</v>
       </c>
       <c r="G31" t="str">
-        <v>Truganina</v>
+        <v>Glenroy</v>
       </c>
       <c r="H31" t="str">
-        <v>A</v>
+        <v>B+</v>
       </c>
       <c r="I31" t="str">
         <v>assigned</v>
       </c>
       <c r="J31" t="str">
-        <v>Dad Michael Wallace - b6042a-1-1936372</v>
-      </c>
-      <c r="M31" t="str">
-        <v xml:space="preserve">no </v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
+        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
       </c>
       <c r="B32" t="str">
-        <v>Kerrie Donald</v>
+        <v>Ricky Steve</v>
       </c>
       <c r="C32">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D32" t="str">
         <v>Female</v>
       </c>
       <c r="E32" t="str">
-        <v>kerrieldonald@hotmail.com</v>
+        <v>tj-c-a@hotmail.com</v>
       </c>
       <c r="F32" t="str">
-        <v>61400826565</v>
+        <v>411360449</v>
       </c>
       <c r="G32" t="str">
-        <v>Mailor's Flat</v>
+        <v xml:space="preserve">Wangaratta </v>
       </c>
       <c r="H32" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I32" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J32" t="str">
-        <v>kerrie donald, alistair donald</v>
+        <v>Taylah-Jayne Lockery</v>
       </c>
     </row>
     <row r="33">
@@ -1789,10 +1789,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
       </c>
       <c r="B34" t="str">
-        <v>Alexander Leonard</v>
+        <v>Sherif Haggag</v>
       </c>
       <c r="C34">
         <v>38</v>
@@ -1801,45 +1801,45 @@
         <v>Male</v>
       </c>
       <c r="E34" t="str">
+        <v>Shaggag87@gmail.com</v>
+      </c>
+      <c r="F34" t="str">
+        <v>426233449</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Belmont</v>
+      </c>
+      <c r="H34" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I34" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Alexander Leonard</v>
+      </c>
+      <c r="C35">
+        <v>38</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E35" t="str">
         <v>alexleonardedit@gmail.com</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F35" t="str">
         <v>421834476</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G35" t="str">
         <v>Croydon</v>
-      </c>
-      <c r="H34" t="str">
-        <v>A+</v>
-      </c>
-      <c r="I34" t="str">
-        <v>available</v>
-      </c>
-      <c r="J34" t="str">
-        <v>melissa francis, Alexander Leonard</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str">
-        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Bronwyn Parsons</v>
-      </c>
-      <c r="C35">
-        <v>72</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E35" t="str">
-        <v>Babybear61153@gmail.com</v>
-      </c>
-      <c r="F35" t="str">
-        <v>432543647</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Rosebud</v>
       </c>
       <c r="H35" t="str">
         <v>A+</v>
@@ -1847,178 +1847,179 @@
       <c r="I35" t="str">
         <v>available</v>
       </c>
-      <c r="J35" t="str" xml:space="preserve">
-        <v xml:space="preserve">Yolette Huon - yol-et Hue on
-Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
+      <c r="J35" t="str">
+        <v>melissa francis, Alexander Leonard</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
-        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
+        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
       </c>
       <c r="B36" t="str">
-        <v>Paige Greig</v>
+        <v>Linda Browne</v>
       </c>
       <c r="C36">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D36" t="str">
         <v>Female</v>
       </c>
       <c r="E36" t="str">
-        <v>paigegreig@hotmail.com</v>
+        <v>Lindabrowne@iprimus.com.au</v>
       </c>
       <c r="F36" t="str">
-        <v>406598552</v>
+        <v>429570177</v>
       </c>
       <c r="G36" t="str">
-        <v>Mooroolbark</v>
+        <v>OFFICER</v>
       </c>
       <c r="H36" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="I36" t="str">
         <v>available</v>
       </c>
       <c r="J36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Erin
-Morgan (sister) - need to do application</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Tamika Colville</v>
-      </c>
-      <c r="C37">
-        <v>31</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E37" t="str">
-        <v>tamika.colville@gmail.com</v>
-      </c>
-      <c r="F37" t="str">
-        <v>409132141</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Golden square</v>
-      </c>
-      <c r="H37" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I37" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J37" t="str">
-        <v>Shinae Colville</v>
-      </c>
-      <c r="L37" t="str">
-        <v>Diagnosed with MS in 2018</v>
-      </c>
-      <c r="M37" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str">
-        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Linda Browne</v>
-      </c>
-      <c r="C38">
-        <v>54</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Lindabrowne@iprimus.com.au</v>
-      </c>
-      <c r="F38" t="str">
-        <v>429570177</v>
-      </c>
-      <c r="G38" t="str">
-        <v>OFFICER</v>
-      </c>
-      <c r="H38" t="str">
-        <v>B</v>
-      </c>
-      <c r="I38" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J38" t="str" xml:space="preserve">
         <v xml:space="preserve">Natalie Browne
 Linda Browne
 Aidan Miler</v>
       </c>
     </row>
-    <row r="39">
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Dhananjay  Mehra</v>
+      </c>
+      <c r="C37">
+        <v>68</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Dmehra@bigpond.net.au</v>
+      </c>
+      <c r="F37" t="str">
+        <v>419353328</v>
+      </c>
+      <c r="G37" t="str">
+        <v xml:space="preserve">Point Cook </v>
+      </c>
+      <c r="H37" t="str">
+        <v>B</v>
+      </c>
+      <c r="I37" t="str">
+        <v>available</v>
+      </c>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Meenakshi Mehra
+Dhananjay Mehra</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Bronwyn Parsons</v>
+      </c>
+      <c r="C38">
+        <v>72</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Babybear61153@gmail.com</v>
+      </c>
+      <c r="F38" t="str">
+        <v>432543647</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Rosebud</v>
+      </c>
+      <c r="H38" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I38" t="str">
+        <v>available</v>
+      </c>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yolette Huon - yol-et Hue on
+Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
       </c>
       <c r="B39" t="str">
-        <v>Sherif Haggag</v>
+        <v>Paige Greig</v>
       </c>
       <c r="C39">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D39" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E39" t="str">
-        <v>Shaggag87@gmail.com</v>
+        <v>paigegreig@hotmail.com</v>
       </c>
       <c r="F39" t="str">
-        <v>426233449</v>
+        <v>406598552</v>
       </c>
       <c r="G39" t="str">
-        <v>Belmont</v>
+        <v>Mooroolbark</v>
       </c>
       <c r="H39" t="str">
-        <v>B+</v>
+        <v>C</v>
       </c>
       <c r="I39" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J39" t="str">
-        <v>Solo</v>
+        <v>available</v>
+      </c>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Erin
+Morgan (sister) - need to do application</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
       </c>
       <c r="B40" t="str">
-        <v>Leanne Bryant</v>
+        <v>Tamika Colville</v>
       </c>
       <c r="C40">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D40" t="str">
         <v>Female</v>
       </c>
       <c r="E40" t="str">
-        <v>blazeandcougar@gmail.com</v>
+        <v>tamika.colville@gmail.com</v>
       </c>
       <c r="F40" t="str">
-        <v>61415438228</v>
+        <v>409132141</v>
       </c>
       <c r="G40" t="str">
-        <v xml:space="preserve">Hampton Park </v>
+        <v>Golden square</v>
       </c>
       <c r="H40" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I40" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J40" t="str">
-        <v>Solo</v>
+        <v>Shinae Colville</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Diagnosed with MS in 2018</v>
+      </c>
+      <c r="M40" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="41">
@@ -2055,28 +2056,28 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
       </c>
       <c r="B42" t="str">
-        <v>Bashar Mona</v>
+        <v>Leanne Bryant</v>
       </c>
       <c r="C42">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D42" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E42" t="str">
-        <v>bashar.mona92@gmail.com</v>
+        <v>blazeandcougar@gmail.com</v>
       </c>
       <c r="F42" t="str">
-        <v>490871416</v>
+        <v>61415438228</v>
       </c>
       <c r="G42" t="str">
-        <v>Roxburgh park</v>
+        <v xml:space="preserve">Hampton Park </v>
       </c>
       <c r="H42" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I42" t="str">
         <v>assigned</v>
@@ -2153,37 +2154,36 @@
         <v>NA</v>
       </c>
     </row>
-    <row r="45" xml:space="preserve">
+    <row r="45">
       <c r="A45" t="str">
-        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
       </c>
       <c r="B45" t="str">
-        <v>Dhananjay  Mehra</v>
+        <v>Bashar Mona</v>
       </c>
       <c r="C45">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D45" t="str">
         <v>Male</v>
       </c>
       <c r="E45" t="str">
-        <v>Dmehra@bigpond.net.au</v>
+        <v>bashar.mona92@gmail.com</v>
       </c>
       <c r="F45" t="str">
-        <v>419353328</v>
+        <v>490871416</v>
       </c>
       <c r="G45" t="str">
-        <v xml:space="preserve">Point Cook </v>
+        <v>Roxburgh park</v>
       </c>
       <c r="H45" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I45" t="str">
         <v>assigned</v>
       </c>
-      <c r="J45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Meenakshi Mehra
-Dhananjay Mehra</v>
+      <c r="J45" t="str">
+        <v>Solo</v>
       </c>
     </row>
     <row r="46">
@@ -2390,7 +2390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2420,64 +2420,64 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ad340cba-9702-4a35-9a1f-7098bb2792d2</v>
+        <v>57d358cb-d720-4484-8903-846208a88129</v>
       </c>
       <c r="B2" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C2" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>A1</v>
+        <v>A3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>055b0eeb-95e3-48d2-bab8-608bbe0173ce</v>
+        <v>90a868f7-87c2-4b18-888a-1b0729aafd57</v>
       </c>
       <c r="B3" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C3" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>A2</v>
+        <v>A4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>69e786fd-e21d-4e14-88da-7125c5f4a1d2</v>
+        <v>f569744b-ca7b-46c3-b54f-b206d35d07d0</v>
       </c>
       <c r="B4" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C4" t="str">
-        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>A3</v>
+        <v>A5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>eb8bfbdd-63a6-4079-aba9-5800fb7a540b</v>
+        <v>19fd7f06-6147-4090-b47d-4769aeb855ce</v>
       </c>
       <c r="B5" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C5" t="str">
-        <v>34b3d848-f096-4bc9-bd55-dc4dd85ad1b3</v>
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2488,330 +2488,92 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>a3858d3d-55d1-4fdb-97d8-320bba44e137</v>
+        <v>01417c60-8dda-4286-a14c-ec8309236d41</v>
       </c>
       <c r="B6" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C6" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>B2</v>
+        <v>B4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>b52bba5a-5df3-4857-bd40-94b252176098</v>
+        <v>7d428f41-6701-460f-8c5e-fcf5f9f1e673</v>
       </c>
       <c r="B7" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C7" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>B3</v>
+        <v>B5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4f0e1cd0-0b97-41cf-8546-066d8aacaa18</v>
+        <v>2b9aa451-0238-45e5-96cd-ebd805d71c7b</v>
       </c>
       <c r="B8" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C8" t="str">
-        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>B4</v>
+        <v>C1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>e1a80551-d2da-4874-91db-588715a4fac4</v>
+        <v>3c5d1dfd-7f7d-4eec-b21f-5596ec0c9e4a</v>
       </c>
       <c r="B9" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C9" t="str">
-        <v>9f63aad3-aae1-4220-825c-8964694ec5d8</v>
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>B5</v>
+        <v>C2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>abc48d6d-e2be-45f3-b39d-aab68fd3a887</v>
+        <v>51037cc9-d563-444d-91e7-4c94330a4d63</v>
       </c>
       <c r="B10" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C10" t="str">
-        <v>97e81b41-1b8d-4562-9e12-3747f87663a9</v>
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>C1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1996d94e-e4b6-41eb-9c86-6f2ce57c0d3e</v>
-      </c>
-      <c r="B11" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C11" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="str">
-        <v>C2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>15371ee3-0b7e-4086-84f6-3720ca1ff543</v>
-      </c>
-      <c r="B12" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C12" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="str">
         <v>C3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>9c31ffbb-2789-43bb-a60e-90c4b8100cef</v>
-      </c>
-      <c r="B13" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C13" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="str">
-        <v>C4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>bc578b4a-ddea-41c3-9540-e88f6659f18c</v>
-      </c>
-      <c r="B14" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C14" t="str">
-        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="str">
-        <v>D1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>72473e20-842c-4521-a6c8-ba7c2d625b26</v>
-      </c>
-      <c r="B15" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C15" t="str">
-        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="str">
-        <v>D2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>cdfce1b8-2ada-4f40-a965-ec4421f32195</v>
-      </c>
-      <c r="B16" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C16" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="str">
-        <v>D3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>0bafba7c-79a0-4bae-b175-028f5c764b20</v>
-      </c>
-      <c r="B17" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C17" t="str">
-        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="str">
-        <v>D4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>94521f77-45d2-4af9-952a-a692cd7c7aa8</v>
-      </c>
-      <c r="B18" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C18" t="str">
-        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="str">
-        <v>E1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>38e2c0fc-5873-43aa-9394-f7c2709f8a83</v>
-      </c>
-      <c r="B19" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C19" t="str">
-        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="str">
-        <v>E2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>c21a4154-3157-46c8-a878-b599e0689d93</v>
-      </c>
-      <c r="B20" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C20" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20" t="str">
-        <v>A1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>ffc84c94-f1d0-4b10-aa29-30dc6ffbda57</v>
-      </c>
-      <c r="B21" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C21" t="str">
-        <v>4f08069b-d828-429c-af5e-b1eee2c123df</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="str">
-        <v>A2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>b27d2d06-2e2c-4115-9995-db7dd2a60c77</v>
-      </c>
-      <c r="B22" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C22" t="str">
-        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22" t="str">
-        <v>A3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>7a2cb7e6-2374-470d-916d-9e0890d7fde8</v>
-      </c>
-      <c r="B23" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C23" t="str">
-        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23" t="str">
-        <v>A4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>36893ad6-bfef-4de4-b6f2-a5c5f1b825b0</v>
-      </c>
-      <c r="B24" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C24" t="str">
-        <v>de606917-da6f-4fde-881b-7cbfd45cfe56</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24" t="str">
-        <v>A5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -736,7 +736,7 @@
         <v>B</v>
       </c>
       <c r="I2" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J2" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -1424,167 +1424,167 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
       </c>
       <c r="B23" t="str">
-        <v>Kiran Rao</v>
+        <v>Tamara Mifsud</v>
       </c>
       <c r="C23">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D23" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E23" t="str">
-        <v>kiran.rao07@gmail.com</v>
+        <v>tamara.mifsud@hotmail.com</v>
       </c>
       <c r="F23" t="str">
-        <v>420486042</v>
+        <v>416552122</v>
       </c>
       <c r="G23" t="str">
-        <v>Southbank</v>
+        <v>Aintree</v>
       </c>
       <c r="H23" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I23" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J23" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M23" t="str">
-        <v>NA</v>
+        <v>Aliye Abcilar</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
+        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
       </c>
       <c r="B24" t="str">
-        <v>Tamara Mifsud</v>
+        <v>Philip Natoli</v>
       </c>
       <c r="C24">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D24" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E24" t="str">
-        <v>tamara.mifsud@hotmail.com</v>
+        <v>Philip.natoli@outlook.com</v>
       </c>
       <c r="F24" t="str">
-        <v>416552122</v>
+        <v>466021882</v>
       </c>
       <c r="G24" t="str">
-        <v>Aintree</v>
+        <v>Caulfield South</v>
       </c>
       <c r="H24" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I24" t="str">
         <v>available</v>
       </c>
       <c r="J24" t="str">
-        <v>Aliye Abcilar</v>
+        <v>Hayley Wright</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
       </c>
       <c r="B25" t="str">
-        <v>Philip Natoli</v>
+        <v>Jeanette Quy</v>
       </c>
       <c r="C25">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="D25" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E25" t="str">
+        <v>quyfamily@tpg.com.au</v>
+      </c>
+      <c r="F25" t="str">
+        <v>402902273</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Rowville</v>
+      </c>
+      <c r="H25" t="str">
+        <v>C</v>
+      </c>
+      <c r="I25" t="str">
+        <v>available</v>
+      </c>
+      <c r="M25" t="str">
+        <v xml:space="preserve">nothing of note </v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>dcd305dd-c710-4a1e-859c-835031154035</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Nicholas Boicos</v>
+      </c>
+      <c r="C26">
+        <v>22</v>
+      </c>
+      <c r="D26" t="str">
         <v>Male</v>
       </c>
-      <c r="E25" t="str">
-        <v>Philip.natoli@outlook.com</v>
-      </c>
-      <c r="F25" t="str">
-        <v>466021882</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Caulfield South</v>
-      </c>
-      <c r="H25" t="str">
+      <c r="E26" t="str">
+        <v>nboicos@hotmail.com</v>
+      </c>
+      <c r="F26" t="str">
+        <v>429556400</v>
+      </c>
+      <c r="G26" t="str">
+        <v xml:space="preserve">Altona Meadows </v>
+      </c>
+      <c r="H26" t="str">
         <v>B+</v>
       </c>
-      <c r="I25" t="str">
-        <v>available</v>
-      </c>
-      <c r="J25" t="str">
-        <v>Hayley Wright</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Jeanette Quy</v>
-      </c>
-      <c r="C26">
-        <v>74</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E26" t="str">
-        <v>quyfamily@tpg.com.au</v>
-      </c>
-      <c r="F26" t="str">
-        <v>402902273</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Rowville</v>
-      </c>
-      <c r="H26" t="str">
-        <v>C</v>
-      </c>
       <c r="I26" t="str">
         <v>available</v>
       </c>
-      <c r="M26" t="str">
-        <v xml:space="preserve">nothing of note </v>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
-        <v>dcd305dd-c710-4a1e-859c-835031154035</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Nicholas Boicos</v>
-      </c>
-      <c r="C27">
-        <v>22</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E27" t="str">
-        <v>nboicos@hotmail.com</v>
-      </c>
-      <c r="F27" t="str">
-        <v>429556400</v>
-      </c>
-      <c r="G27" t="str">
-        <v xml:space="preserve">Altona Meadows </v>
-      </c>
-      <c r="H27" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I27" t="str">
-        <v>available</v>
-      </c>
-      <c r="J27" t="str" xml:space="preserve">
+      <c r="J26" t="str" xml:space="preserve">
         <v xml:space="preserve">Nick Boicos 
 Matthew Boicos
 Brothers</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Kiran Rao</v>
+      </c>
+      <c r="C27">
+        <v>35</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E27" t="str">
+        <v>kiran.rao07@gmail.com</v>
+      </c>
+      <c r="F27" t="str">
+        <v>420486042</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Southbank</v>
+      </c>
+      <c r="H27" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I27" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J27" t="str">
+        <v>SOLO</v>
+      </c>
+      <c r="M27" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
@@ -1789,25 +1789,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
       </c>
       <c r="B34" t="str">
-        <v>Sherif Haggag</v>
+        <v>Bashar Mona</v>
       </c>
       <c r="C34">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D34" t="str">
         <v>Male</v>
       </c>
       <c r="E34" t="str">
-        <v>Shaggag87@gmail.com</v>
+        <v>bashar.mona92@gmail.com</v>
       </c>
       <c r="F34" t="str">
-        <v>426233449</v>
+        <v>490871416</v>
       </c>
       <c r="G34" t="str">
-        <v>Belmont</v>
+        <v>Roxburgh park</v>
       </c>
       <c r="H34" t="str">
         <v>B+</v>
@@ -1887,136 +1887,133 @@
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37" t="str">
+        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Bronwyn Parsons</v>
+      </c>
+      <c r="C37">
+        <v>72</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Babybear61153@gmail.com</v>
+      </c>
+      <c r="F37" t="str">
+        <v>432543647</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Rosebud</v>
+      </c>
+      <c r="H37" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I37" t="str">
+        <v>available</v>
+      </c>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yolette Huon - yol-et Hue on
+Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Paige Greig</v>
+      </c>
+      <c r="C38">
+        <v>31</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E38" t="str">
+        <v>paigegreig@hotmail.com</v>
+      </c>
+      <c r="F38" t="str">
+        <v>406598552</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Mooroolbark</v>
+      </c>
+      <c r="H38" t="str">
+        <v>C</v>
+      </c>
+      <c r="I38" t="str">
+        <v>available</v>
+      </c>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Erin
+Morgan (sister) - need to do application</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
         <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B39" t="str">
         <v>Dhananjay  Mehra</v>
       </c>
-      <c r="C37">
+      <c r="C39">
         <v>68</v>
       </c>
-      <c r="D37" t="str">
+      <c r="D39" t="str">
         <v>Male</v>
       </c>
-      <c r="E37" t="str">
+      <c r="E39" t="str">
         <v>Dmehra@bigpond.net.au</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F39" t="str">
         <v>419353328</v>
       </c>
-      <c r="G37" t="str">
+      <c r="G39" t="str">
         <v xml:space="preserve">Point Cook </v>
       </c>
-      <c r="H37" t="str">
+      <c r="H39" t="str">
         <v>B</v>
       </c>
-      <c r="I37" t="str">
-        <v>available</v>
-      </c>
-      <c r="J37" t="str" xml:space="preserve">
+      <c r="I39" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J39" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
 Dhananjay Mehra</v>
       </c>
     </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str">
-        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Bronwyn Parsons</v>
-      </c>
-      <c r="C38">
-        <v>72</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Babybear61153@gmail.com</v>
-      </c>
-      <c r="F38" t="str">
-        <v>432543647</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Rosebud</v>
-      </c>
-      <c r="H38" t="str">
-        <v>A+</v>
-      </c>
-      <c r="I38" t="str">
-        <v>available</v>
-      </c>
-      <c r="J38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Yolette Huon - yol-et Hue on
-Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
-        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Paige Greig</v>
-      </c>
-      <c r="C39">
-        <v>31</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E39" t="str">
-        <v>paigegreig@hotmail.com</v>
-      </c>
-      <c r="F39" t="str">
-        <v>406598552</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Mooroolbark</v>
-      </c>
-      <c r="H39" t="str">
-        <v>C</v>
-      </c>
-      <c r="I39" t="str">
-        <v>available</v>
-      </c>
-      <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Erin
-Morgan (sister) - need to do application</v>
-      </c>
-    </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
       </c>
       <c r="B40" t="str">
-        <v>Tamika Colville</v>
+        <v>Angela Verspay</v>
       </c>
       <c r="C40">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D40" t="str">
         <v>Female</v>
       </c>
       <c r="E40" t="str">
-        <v>tamika.colville@gmail.com</v>
+        <v>angelarileysmyth@hotmail.com</v>
       </c>
       <c r="F40" t="str">
-        <v>409132141</v>
+        <v>477660119</v>
       </c>
       <c r="G40" t="str">
-        <v>Golden square</v>
+        <v>Warrnambool</v>
       </c>
       <c r="H40" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I40" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J40" t="str">
-        <v>Shinae Colville</v>
-      </c>
-      <c r="L40" t="str">
-        <v>Diagnosed with MS in 2018</v>
+        <v>SOLO</v>
       </c>
       <c r="M40" t="str">
         <v>NA</v>
@@ -2024,25 +2021,25 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
       </c>
       <c r="B41" t="str">
-        <v>Kadisha  Bruton</v>
+        <v>Tamika Colville</v>
       </c>
       <c r="C41">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D41" t="str">
         <v>Female</v>
       </c>
       <c r="E41" t="str">
-        <v>kadishaann@icloud.com</v>
+        <v>tamika.colville@gmail.com</v>
       </c>
       <c r="F41" t="str">
-        <v>434829249</v>
+        <v>409132141</v>
       </c>
       <c r="G41" t="str">
-        <v xml:space="preserve">Kurunjang </v>
+        <v>Golden square</v>
       </c>
       <c r="H41" t="str">
         <v>B+</v>
@@ -2051,33 +2048,39 @@
         <v>available</v>
       </c>
       <c r="J41" t="str">
-        <v>Jacob Steele</v>
+        <v>Shinae Colville</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Diagnosed with MS in 2018</v>
+      </c>
+      <c r="M41" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
       </c>
       <c r="B42" t="str">
-        <v>Leanne Bryant</v>
+        <v>Sherif Haggag</v>
       </c>
       <c r="C42">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D42" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E42" t="str">
-        <v>blazeandcougar@gmail.com</v>
+        <v>Shaggag87@gmail.com</v>
       </c>
       <c r="F42" t="str">
-        <v>61415438228</v>
+        <v>426233449</v>
       </c>
       <c r="G42" t="str">
-        <v xml:space="preserve">Hampton Park </v>
+        <v>Belmont</v>
       </c>
       <c r="H42" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I42" t="str">
         <v>assigned</v>
@@ -2086,27 +2089,27 @@
         <v>Solo</v>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
+    <row r="43">
       <c r="A43" t="str">
-        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
+        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
       </c>
       <c r="B43" t="str">
-        <v>Sharyn  McKinnis</v>
+        <v>Kadisha  Bruton</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D43" t="str">
         <v>Female</v>
       </c>
       <c r="E43" t="str">
-        <v>s.lmckinnis@bigpond.com</v>
+        <v>kadishaann@icloud.com</v>
       </c>
       <c r="F43" t="str">
-        <v>419880873</v>
+        <v>434829249</v>
       </c>
       <c r="G43" t="str">
-        <v>Newtown</v>
+        <v xml:space="preserve">Kurunjang </v>
       </c>
       <c r="H43" t="str">
         <v>B+</v>
@@ -2114,70 +2117,67 @@
       <c r="I43" t="str">
         <v>available</v>
       </c>
-      <c r="J43" t="str" xml:space="preserve">
+      <c r="J43" t="str">
+        <v>Jacob Steele</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Sharyn  McKinnis</v>
+      </c>
+      <c r="C44">
+        <v>50</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E44" t="str">
+        <v>s.lmckinnis@bigpond.com</v>
+      </c>
+      <c r="F44" t="str">
+        <v>419880873</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Newtown</v>
+      </c>
+      <c r="H44" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I44" t="str">
+        <v>available</v>
+      </c>
+      <c r="J44" t="str" xml:space="preserve">
         <v xml:space="preserve">Isabelle McKinnis, Sharyn McKinnis
 </v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Angela Verspay</v>
-      </c>
-      <c r="C44">
-        <v>45</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E44" t="str">
-        <v>angelarileysmyth@hotmail.com</v>
-      </c>
-      <c r="F44" t="str">
-        <v>477660119</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Warrnambool</v>
-      </c>
-      <c r="H44" t="str">
-        <v>B</v>
-      </c>
-      <c r="I44" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J44" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M44" t="str">
-        <v>NA</v>
-      </c>
-    </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
       </c>
       <c r="B45" t="str">
-        <v>Bashar Mona</v>
+        <v>Leanne Bryant</v>
       </c>
       <c r="C45">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D45" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E45" t="str">
-        <v>bashar.mona92@gmail.com</v>
+        <v>blazeandcougar@gmail.com</v>
       </c>
       <c r="F45" t="str">
-        <v>490871416</v>
+        <v>61415438228</v>
       </c>
       <c r="G45" t="str">
-        <v>Roxburgh park</v>
+        <v xml:space="preserve">Hampton Park </v>
       </c>
       <c r="H45" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I45" t="str">
         <v>assigned</v>
@@ -2390,7 +2390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>57d358cb-d720-4484-8903-846208a88129</v>
+        <v>9b1755ab-387a-460f-adf3-45b9fddc11fd</v>
       </c>
       <c r="B2" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2432,12 +2432,12 @@
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>A3</v>
+        <v>A1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>90a868f7-87c2-4b18-888a-1b0729aafd57</v>
+        <v>86c92277-1eb6-4579-800f-d1569c0254b3</v>
       </c>
       <c r="B3" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2449,131 +2449,165 @@
         <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>A4</v>
+        <v>A2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>f569744b-ca7b-46c3-b54f-b206d35d07d0</v>
+        <v>9f6a0125-b8ba-43db-a2a1-afac55ddf6e8</v>
       </c>
       <c r="B4" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C4" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>A5</v>
+        <v>A3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>19fd7f06-6147-4090-b47d-4769aeb855ce</v>
+        <v>83af9978-0312-4c27-8d18-8d049ea42655</v>
       </c>
       <c r="B5" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C5" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>B1</v>
+        <v>A4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>01417c60-8dda-4286-a14c-ec8309236d41</v>
+        <v>3b00db5a-6d9a-4a93-a960-aaabe789f4f7</v>
       </c>
       <c r="B6" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C6" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>B4</v>
+        <v>A5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>7d428f41-6701-460f-8c5e-fcf5f9f1e673</v>
+        <v>99a23277-750a-4b95-a5ac-09f1fe6151c6</v>
       </c>
       <c r="B7" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C7" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>B5</v>
+        <v>B1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2b9aa451-0238-45e5-96cd-ebd805d71c7b</v>
+        <v>fe0a3a15-8530-43f2-9d77-806462029506</v>
       </c>
       <c r="B8" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C8" t="str">
-        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>C1</v>
+        <v>B2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3c5d1dfd-7f7d-4eec-b21f-5596ec0c9e4a</v>
+        <v>2ee524eb-d4b2-4297-bc94-bf79bc90fc39</v>
       </c>
       <c r="B9" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C9" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>C2</v>
+        <v>B3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>51037cc9-d563-444d-91e7-4c94330a4d63</v>
+        <v>43336515-ba8a-43ea-ac49-7c4a2bcac7d2</v>
       </c>
       <c r="B10" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C10" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>C3</v>
+        <v>B4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>759931ad-4413-4ca1-8dc6-d240e042cfb1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C11" t="str">
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v>B5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>a1bf8297-f865-4bc4-acb3-0900a2992ff9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C12" t="str">
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>C1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -742,6 +742,9 @@
         <v xml:space="preserve">Meenakshi Mehra
 Dhananjay Mehra</v>
       </c>
+      <c r="K2" t="str">
+        <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -915,181 +918,181 @@
         <v>No</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
+    <row r="8">
       <c r="A8" t="str">
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Taylahuxtable@gmail.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>435320280</v>
+      </c>
+      <c r="G8" t="str">
+        <v>FERNTREE GULLY</v>
+      </c>
+      <c r="I8" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Troy Smith</v>
+      </c>
+      <c r="K8" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Troy Smith</v>
+      </c>
+      <c r="C9">
+        <v>31</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Troyssmith94@gmail.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>429354308</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H9" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I9" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="K9" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L9" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M9" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
         <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B10" t="str">
         <v>Sharon King</v>
       </c>
-      <c r="C8">
+      <c r="C10">
         <v>58</v>
       </c>
-      <c r="D8" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E8" t="str">
+      <c r="D10" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E10" t="str">
         <v>dreamweaversixtyseven@gmail.com</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F10" t="str">
         <v>611488000000</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G10" t="str">
         <v xml:space="preserve">Mooroopna </v>
       </c>
-      <c r="H8" t="str">
+      <c r="H10" t="str">
         <v>A</v>
       </c>
-      <c r="I8" t="str">
-        <v>available</v>
-      </c>
-      <c r="J8" t="str" xml:space="preserve">
+      <c r="I10" t="str">
+        <v>available</v>
+      </c>
+      <c r="J10" t="str" xml:space="preserve">
         <v xml:space="preserve">
 Friend :Jacinda Austin
 ID:b6042a-1-1936475</v>
       </c>
-      <c r="M8" t="str">
+      <c r="M10" t="str">
         <v xml:space="preserve">No </v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Tara Saltzman</v>
-      </c>
-      <c r="C9">
-        <v>29</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E9" t="str">
-        <v>tarasaltzman@bigpond.com</v>
-      </c>
-      <c r="F9" t="str">
-        <v>448545599</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H9" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I9" t="str">
-        <v>available</v>
-      </c>
-      <c r="J9" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
-      </c>
-      <c r="M9" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Brent Barnett</v>
-      </c>
-      <c r="C10">
-        <v>37</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E10" t="str">
-        <v>brentbarnett88@gmail.com</v>
-      </c>
-      <c r="F10" t="str">
-        <v>423530043</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Preston</v>
-      </c>
-      <c r="H10" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I10" t="str">
-        <v>available</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
       </c>
       <c r="B11" t="str">
-        <v>Tayla Huxtable</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="str">
         <v>Female</v>
       </c>
       <c r="E11" t="str">
-        <v>Taylahuxtable@gmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F11" t="str">
-        <v>435320280</v>
+        <v>448545599</v>
       </c>
       <c r="G11" t="str">
-        <v>FERNTREE GULLY</v>
+        <v>Melbourne</v>
+      </c>
+      <c r="H11" t="str">
+        <v>B+</v>
       </c>
       <c r="I11" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J11" t="str">
-        <v>Troy Smith</v>
-      </c>
-      <c r="K11" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+      </c>
+      <c r="M11" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
       </c>
       <c r="B12" t="str">
-        <v>Troy Smith</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C12">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D12" t="str">
         <v>Male</v>
       </c>
       <c r="E12" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>429354308</v>
+        <v>423530043</v>
       </c>
       <c r="G12" t="str">
-        <v>Melbourne</v>
+        <v>Preston</v>
       </c>
       <c r="H12" t="str">
         <v>B+</v>
       </c>
       <c r="I12" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J12" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="K12" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-      <c r="L12" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
-      </c>
-      <c r="M12" t="str">
-        <v>NA</v>
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="13">
@@ -1291,25 +1294,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
       </c>
       <c r="B19" t="str">
-        <v>David Fenwick</v>
+        <v>Kiran Rao</v>
       </c>
       <c r="C19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" t="str">
         <v>Male</v>
       </c>
       <c r="E19" t="str">
-        <v>David.s.fenwick@gmail.com</v>
+        <v>kiran.rao07@gmail.com</v>
       </c>
       <c r="F19" t="str">
-        <v>429811171</v>
+        <v>420486042</v>
       </c>
       <c r="G19" t="str">
-        <v>Teesdale</v>
+        <v>Southbank</v>
       </c>
       <c r="H19" t="str">
         <v>B+</v>
@@ -1318,7 +1321,10 @@
         <v>assigned</v>
       </c>
       <c r="J19" t="str">
-        <v>Solo</v>
+        <v>SOLO</v>
+      </c>
+      <c r="M19" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="20">
@@ -1554,25 +1560,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
       </c>
       <c r="B27" t="str">
-        <v>Kiran Rao</v>
+        <v>David Fenwick</v>
       </c>
       <c r="C27">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D27" t="str">
         <v>Male</v>
       </c>
       <c r="E27" t="str">
-        <v>kiran.rao07@gmail.com</v>
+        <v>David.s.fenwick@gmail.com</v>
       </c>
       <c r="F27" t="str">
-        <v>420486042</v>
+        <v>429811171</v>
       </c>
       <c r="G27" t="str">
-        <v>Southbank</v>
+        <v>Teesdale</v>
       </c>
       <c r="H27" t="str">
         <v>B+</v>
@@ -1581,10 +1587,7 @@
         <v>assigned</v>
       </c>
       <c r="J27" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M27" t="str">
-        <v>NA</v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
@@ -1789,28 +1792,28 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
       </c>
       <c r="B34" t="str">
-        <v>Bashar Mona</v>
+        <v>Leanne Bryant</v>
       </c>
       <c r="C34">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D34" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E34" t="str">
-        <v>bashar.mona92@gmail.com</v>
+        <v>blazeandcougar@gmail.com</v>
       </c>
       <c r="F34" t="str">
-        <v>490871416</v>
+        <v>61415438228</v>
       </c>
       <c r="G34" t="str">
-        <v>Roxburgh park</v>
+        <v xml:space="preserve">Hampton Park </v>
       </c>
       <c r="H34" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I34" t="str">
         <v>assigned</v>
@@ -1885,103 +1888,102 @@
 Aidan Miler</v>
       </c>
     </row>
-    <row r="37" xml:space="preserve">
+    <row r="37">
       <c r="A37" t="str">
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Bashar Mona</v>
+      </c>
+      <c r="C37">
+        <v>33</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E37" t="str">
+        <v>bashar.mona92@gmail.com</v>
+      </c>
+      <c r="F37" t="str">
+        <v>490871416</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Roxburgh park</v>
+      </c>
+      <c r="H37" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I37" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
         <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B38" t="str">
         <v>Bronwyn Parsons</v>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>72</v>
       </c>
-      <c r="D37" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E37" t="str">
+      <c r="D38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E38" t="str">
         <v>Babybear61153@gmail.com</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F38" t="str">
         <v>432543647</v>
       </c>
-      <c r="G37" t="str">
+      <c r="G38" t="str">
         <v>Rosebud</v>
       </c>
-      <c r="H37" t="str">
+      <c r="H38" t="str">
         <v>A+</v>
       </c>
-      <c r="I37" t="str">
-        <v>available</v>
-      </c>
-      <c r="J37" t="str" xml:space="preserve">
+      <c r="I38" t="str">
+        <v>available</v>
+      </c>
+      <c r="J38" t="str" xml:space="preserve">
         <v xml:space="preserve">Yolette Huon - yol-et Hue on
 Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
       </c>
     </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str">
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
         <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B39" t="str">
         <v>Paige Greig</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>31</v>
       </c>
-      <c r="D38" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E38" t="str">
+      <c r="D39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E39" t="str">
         <v>paigegreig@hotmail.com</v>
       </c>
-      <c r="F38" t="str">
+      <c r="F39" t="str">
         <v>406598552</v>
       </c>
-      <c r="G38" t="str">
+      <c r="G39" t="str">
         <v>Mooroolbark</v>
       </c>
-      <c r="H38" t="str">
+      <c r="H39" t="str">
         <v>C</v>
       </c>
-      <c r="I38" t="str">
-        <v>available</v>
-      </c>
-      <c r="J38" t="str" xml:space="preserve">
+      <c r="I39" t="str">
+        <v>available</v>
+      </c>
+      <c r="J39" t="str" xml:space="preserve">
         <v xml:space="preserve">Erin
 Morgan (sister) - need to do application</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
-        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Dhananjay  Mehra</v>
-      </c>
-      <c r="C39">
-        <v>68</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E39" t="str">
-        <v>Dmehra@bigpond.net.au</v>
-      </c>
-      <c r="F39" t="str">
-        <v>419353328</v>
-      </c>
-      <c r="G39" t="str">
-        <v xml:space="preserve">Point Cook </v>
-      </c>
-      <c r="H39" t="str">
-        <v>B</v>
-      </c>
-      <c r="I39" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Meenakshi Mehra
-Dhananjay Mehra</v>
       </c>
     </row>
     <row r="40">
@@ -2057,36 +2059,40 @@
         <v>NA</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
       </c>
       <c r="B42" t="str">
-        <v>Sherif Haggag</v>
+        <v>Dhananjay  Mehra</v>
       </c>
       <c r="C42">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D42" t="str">
         <v>Male</v>
       </c>
       <c r="E42" t="str">
-        <v>Shaggag87@gmail.com</v>
+        <v>Dmehra@bigpond.net.au</v>
       </c>
       <c r="F42" t="str">
-        <v>426233449</v>
+        <v>419353328</v>
       </c>
       <c r="G42" t="str">
-        <v>Belmont</v>
+        <v xml:space="preserve">Point Cook </v>
       </c>
       <c r="H42" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I42" t="str">
         <v>assigned</v>
       </c>
-      <c r="J42" t="str">
-        <v>Solo</v>
+      <c r="J42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Meenakshi Mehra
+Dhananjay Mehra</v>
+      </c>
+      <c r="K42" t="str">
+        <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
       </c>
     </row>
     <row r="43">
@@ -2156,28 +2162,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
       </c>
       <c r="B45" t="str">
-        <v>Leanne Bryant</v>
+        <v>Sherif Haggag</v>
       </c>
       <c r="C45">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D45" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E45" t="str">
-        <v>blazeandcougar@gmail.com</v>
+        <v>Shaggag87@gmail.com</v>
       </c>
       <c r="F45" t="str">
-        <v>61415438228</v>
+        <v>426233449</v>
       </c>
       <c r="G45" t="str">
-        <v xml:space="preserve">Hampton Park </v>
+        <v>Belmont</v>
       </c>
       <c r="H45" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I45" t="str">
         <v>assigned</v>
@@ -2420,7 +2426,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>9b1755ab-387a-460f-adf3-45b9fddc11fd</v>
+        <v>cbb914d8-4355-4eae-8e6a-d916e6eeab9c</v>
       </c>
       <c r="B2" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2437,7 +2443,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>86c92277-1eb6-4579-800f-d1569c0254b3</v>
+        <v>72ec2db4-7ad6-48e7-aada-ebcd77e964de</v>
       </c>
       <c r="B3" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2454,7 +2460,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>9f6a0125-b8ba-43db-a2a1-afac55ddf6e8</v>
+        <v>3c715c30-77ec-4327-a1dc-77e587684309</v>
       </c>
       <c r="B4" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2471,7 +2477,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>83af9978-0312-4c27-8d18-8d049ea42655</v>
+        <v>98131f5a-2b3c-46c8-876a-215c01d25450</v>
       </c>
       <c r="B5" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2488,7 +2494,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3b00db5a-6d9a-4a93-a960-aaabe789f4f7</v>
+        <v>cd4bdfd0-1ea2-465c-9a88-0c4e8be41c46</v>
       </c>
       <c r="B6" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2505,13 +2511,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>99a23277-750a-4b95-a5ac-09f1fe6151c6</v>
+        <v>e3f866e4-5581-4731-8857-0d4dad4cee98</v>
       </c>
       <c r="B7" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C7" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2522,13 +2528,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>fe0a3a15-8530-43f2-9d77-806462029506</v>
+        <v>525e206b-a4dc-4cb0-bb8d-350087facf3e</v>
       </c>
       <c r="B8" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C8" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2539,7 +2545,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2ee524eb-d4b2-4297-bc94-bf79bc90fc39</v>
+        <v>8d7a05d2-98e8-40f7-b7ff-a8b4cbbfcb46</v>
       </c>
       <c r="B9" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2556,7 +2562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>43336515-ba8a-43ea-ac49-7c4a2bcac7d2</v>
+        <v>8d8eddd8-180f-4a64-af6b-a1e848b325b0</v>
       </c>
       <c r="B10" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2573,7 +2579,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>759931ad-4413-4ca1-8dc6-d240e042cfb1</v>
+        <v>0b61d3fc-daf3-492d-b9a1-6070b61f0235</v>
       </c>
       <c r="B11" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2590,7 +2596,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>a1bf8297-f865-4bc4-acb3-0900a2992ff9</v>
+        <v>cd6ab2c2-d134-4f10-95c6-caa3b4590d32</v>
       </c>
       <c r="B12" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -2602,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="str">
-        <v>C1</v>
+        <v>D1</v>
       </c>
     </row>
   </sheetData>
@@ -2614,7 +2620,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2640,9 +2646,17 @@
         <v>GRP002</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AUTO-MK2NF2KE-kuoa</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,9 +5,8 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
-    <sheet name="Groups" sheetId="4" r:id="rId4"/>
-    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
+    <sheet name="Groups" sheetId="3" r:id="rId3"/>
+    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -736,7 +735,7 @@
         <v>B</v>
       </c>
       <c r="I2" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J2" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -920,75 +919,75 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B8" t="str">
+        <v>Troy Smith</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Troyssmith94@gmail.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>429354308</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H8" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I8" t="str">
+        <v>available</v>
+      </c>
+      <c r="J8" t="str">
         <v>Tayla Huxtable</v>
-      </c>
-      <c r="C8">
-        <v>28</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Taylahuxtable@gmail.com</v>
-      </c>
-      <c r="F8" t="str">
-        <v>435320280</v>
-      </c>
-      <c r="G8" t="str">
-        <v>FERNTREE GULLY</v>
-      </c>
-      <c r="I8" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Troy Smith</v>
       </c>
       <c r="K8" t="str">
         <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
       </c>
+      <c r="L8" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
+      </c>
+      <c r="M8" t="str">
+        <v>NA</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B9" t="str">
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="C9">
+        <v>28</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Taylahuxtable@gmail.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>435320280</v>
+      </c>
+      <c r="G9" t="str">
+        <v>FERNTREE GULLY</v>
+      </c>
+      <c r="I9" t="str">
+        <v>available</v>
+      </c>
+      <c r="J9" t="str">
         <v>Troy Smith</v>
-      </c>
-      <c r="C9">
-        <v>31</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Troyssmith94@gmail.com</v>
-      </c>
-      <c r="F9" t="str">
-        <v>429354308</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H9" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I9" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Tayla Huxtable</v>
       </c>
       <c r="K9" t="str">
         <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-      <c r="L9" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
-      </c>
-      <c r="M9" t="str">
-        <v>NA</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -1294,193 +1293,190 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
       </c>
       <c r="B19" t="str">
-        <v>Kiran Rao</v>
+        <v>Eden Hayes</v>
       </c>
       <c r="C19">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D19" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E19" t="str">
-        <v>kiran.rao07@gmail.com</v>
+        <v>edenhayes19@gmail.com</v>
       </c>
       <c r="F19" t="str">
-        <v>420486042</v>
+        <v>448096139</v>
       </c>
       <c r="G19" t="str">
-        <v>Southbank</v>
+        <v>Elwood</v>
       </c>
       <c r="H19" t="str">
         <v>B+</v>
       </c>
       <c r="I19" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J19" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M19" t="str">
-        <v>NA</v>
+        <v>Jackson Harris</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1bc7d8fc-def3-4f9f-8376-80b79696d1a5</v>
+        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
       </c>
       <c r="B20" t="str">
-        <v>Eden Hayes</v>
+        <v>Anna Fonua</v>
       </c>
       <c r="C20">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D20" t="str">
         <v>Female</v>
       </c>
       <c r="E20" t="str">
-        <v>edenhayes19@gmail.com</v>
+        <v>Annawallace89@hotmail.com</v>
       </c>
       <c r="F20" t="str">
-        <v>448096139</v>
+        <v>452452442</v>
       </c>
       <c r="G20" t="str">
-        <v>Elwood</v>
+        <v>Truganina</v>
       </c>
       <c r="H20" t="str">
+        <v>A</v>
+      </c>
+      <c r="I20" t="str">
+        <v>available</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Dad Michael Wallace - b6042a-1-1936372</v>
+      </c>
+      <c r="M20" t="str">
+        <v xml:space="preserve">no </v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Kayla Lorenzini</v>
+      </c>
+      <c r="C21">
+        <v>29</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E21" t="str">
+        <v>kaylalorenzini_@hotmail.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v>430517653</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H21" t="str">
         <v>B+</v>
       </c>
-      <c r="I20" t="str">
-        <v>available</v>
-      </c>
-      <c r="J20" t="str">
-        <v>Jackson Harris</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>419afd3f-2406-423d-942f-2dfafe875f96</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Anna Fonua</v>
-      </c>
-      <c r="C21">
-        <v>36</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Annawallace89@hotmail.com</v>
-      </c>
-      <c r="F21" t="str">
-        <v>452452442</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Truganina</v>
-      </c>
-      <c r="H21" t="str">
-        <v>A</v>
-      </c>
       <c r="I21" t="str">
         <v>available</v>
       </c>
-      <c r="J21" t="str">
-        <v>Dad Michael Wallace - b6042a-1-1936372</v>
-      </c>
-      <c r="M21" t="str">
-        <v xml:space="preserve">no </v>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22" t="str">
-        <v>d9b76f1c-0867-44fc-9215-6ef7b1184af6</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Kayla Lorenzini</v>
-      </c>
-      <c r="C22">
-        <v>29</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E22" t="str">
-        <v>kaylalorenzini_@hotmail.com</v>
-      </c>
-      <c r="F22" t="str">
-        <v>430517653</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Melbourne</v>
-      </c>
-      <c r="H22" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I22" t="str">
-        <v>available</v>
-      </c>
-      <c r="J22" t="str" xml:space="preserve">
+      <c r="J21" t="str" xml:space="preserve">
         <v xml:space="preserve">Kayla Lorenzini
 James Lorenzini
 Deanna Gramola</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Tamara Mifsud</v>
+      </c>
+      <c r="C22">
+        <v>32</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E22" t="str">
+        <v>tamara.mifsud@hotmail.com</v>
+      </c>
+      <c r="F22" t="str">
+        <v>416552122</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Aintree</v>
+      </c>
+      <c r="H22" t="str">
+        <v>B</v>
+      </c>
+      <c r="I22" t="str">
+        <v>available</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Aliye Abcilar</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
+        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
       </c>
       <c r="B23" t="str">
-        <v>Tamara Mifsud</v>
+        <v>Philip Natoli</v>
       </c>
       <c r="C23">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D23" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E23" t="str">
-        <v>tamara.mifsud@hotmail.com</v>
+        <v>Philip.natoli@outlook.com</v>
       </c>
       <c r="F23" t="str">
-        <v>416552122</v>
+        <v>466021882</v>
       </c>
       <c r="G23" t="str">
-        <v>Aintree</v>
+        <v>Caulfield South</v>
       </c>
       <c r="H23" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I23" t="str">
         <v>available</v>
       </c>
       <c r="J23" t="str">
-        <v>Aliye Abcilar</v>
+        <v>Hayley Wright</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
       </c>
       <c r="B24" t="str">
-        <v>Philip Natoli</v>
+        <v>Antonio Freno</v>
       </c>
       <c r="C24">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D24" t="str">
         <v>Male</v>
       </c>
       <c r="E24" t="str">
-        <v>Philip.natoli@outlook.com</v>
+        <v>frenoantonio@hotmail.it</v>
       </c>
       <c r="F24" t="str">
-        <v>466021882</v>
+        <v>422177371</v>
       </c>
       <c r="G24" t="str">
-        <v>Caulfield South</v>
+        <v>Glenroy</v>
       </c>
       <c r="H24" t="str">
         <v>B+</v>
@@ -1489,7 +1485,7 @@
         <v>available</v>
       </c>
       <c r="J24" t="str">
-        <v>Hayley Wright</v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="25">
@@ -1558,96 +1554,99 @@
 Brothers</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+        <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
       </c>
       <c r="B27" t="str">
-        <v>David Fenwick</v>
+        <v>Mozgda  Alime</v>
       </c>
       <c r="C27">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D27" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E27" t="str">
-        <v>David.s.fenwick@gmail.com</v>
+        <v>smalimi@hotmail.com</v>
       </c>
       <c r="F27" t="str">
-        <v>429811171</v>
+        <v>402010235</v>
       </c>
       <c r="G27" t="str">
-        <v>Teesdale</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H27" t="str">
-        <v>B+</v>
+        <v>C</v>
       </c>
       <c r="I27" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J27" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28" t="str">
-        <v>15fb53d0-3916-4c9a-9f73-c28c879dec33</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Mozgda  Alime</v>
-      </c>
-      <c r="C28">
-        <v>39</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E28" t="str">
-        <v>smalimi@hotmail.com</v>
-      </c>
-      <c r="F28" t="str">
-        <v>402010235</v>
-      </c>
-      <c r="G28" t="str">
-        <v xml:space="preserve">Melbourne </v>
-      </c>
-      <c r="H28" t="str">
-        <v>C</v>
-      </c>
-      <c r="I28" t="str">
-        <v>available</v>
-      </c>
-      <c r="J28" t="str" xml:space="preserve">
+        <v>available</v>
+      </c>
+      <c r="J27" t="str" xml:space="preserve">
         <v xml:space="preserve">Sadaf Almini - I believe this is her cousin 
 Lida Alime - I believe this is her cousin or sister 
 Ahmad Alime - Ahmad is Lina's husband </v>
       </c>
+      <c r="M27" t="str">
+        <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Mara Baumgardner</v>
+      </c>
+      <c r="C28">
+        <v>40</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Granic@hotmail.com</v>
+      </c>
+      <c r="F28" t="str">
+        <v>407364450</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Cockatoo</v>
+      </c>
+      <c r="H28" t="str">
+        <v>B</v>
+      </c>
+      <c r="I28" t="str">
+        <v>available</v>
+      </c>
+      <c r="J28" t="str">
+        <v xml:space="preserve">Mum - Mira Granic </v>
+      </c>
       <c r="M28" t="str">
         <v xml:space="preserve">No </v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>f7b766dc-a0d0-4a91-98ef-47472cdca803</v>
+        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
       </c>
       <c r="B29" t="str">
-        <v>Mara Baumgardner</v>
+        <v>Natasha Devers</v>
       </c>
       <c r="C29">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D29" t="str">
         <v>Female</v>
       </c>
       <c r="E29" t="str">
-        <v>Granic@hotmail.com</v>
+        <v>natashadevers@gmail.com</v>
       </c>
       <c r="F29" t="str">
-        <v>407364450</v>
+        <v>484003770</v>
       </c>
       <c r="G29" t="str">
-        <v>Cockatoo</v>
+        <v xml:space="preserve">Waterways </v>
       </c>
       <c r="H29" t="str">
         <v>B</v>
@@ -1656,74 +1655,74 @@
         <v>available</v>
       </c>
       <c r="J29" t="str">
-        <v xml:space="preserve">Mum - Mira Granic </v>
-      </c>
-      <c r="M29" t="str">
-        <v xml:space="preserve">No </v>
+        <v>Oliver Moran</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>607e3750-92e2-4480-b39d-1cb0e026cd4b</v>
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
       </c>
       <c r="B30" t="str">
-        <v>Natasha Devers</v>
+        <v>David Fenwick</v>
       </c>
       <c r="C30">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D30" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E30" t="str">
-        <v>natashadevers@gmail.com</v>
+        <v>David.s.fenwick@gmail.com</v>
       </c>
       <c r="F30" t="str">
-        <v>484003770</v>
+        <v>429811171</v>
       </c>
       <c r="G30" t="str">
-        <v xml:space="preserve">Waterways </v>
+        <v>Teesdale</v>
       </c>
       <c r="H30" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I30" t="str">
         <v>available</v>
       </c>
       <c r="J30" t="str">
-        <v>Oliver Moran</v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
       </c>
       <c r="B31" t="str">
-        <v>Antonio Freno</v>
+        <v>Kiran Rao</v>
       </c>
       <c r="C31">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D31" t="str">
         <v>Male</v>
       </c>
       <c r="E31" t="str">
-        <v>frenoantonio@hotmail.it</v>
+        <v>kiran.rao07@gmail.com</v>
       </c>
       <c r="F31" t="str">
-        <v>422177371</v>
+        <v>420486042</v>
       </c>
       <c r="G31" t="str">
-        <v>Glenroy</v>
+        <v>Southbank</v>
       </c>
       <c r="H31" t="str">
         <v>B+</v>
       </c>
       <c r="I31" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J31" t="str">
-        <v>Solo</v>
+        <v>SOLO</v>
+      </c>
+      <c r="M31" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="32">
@@ -1792,129 +1791,130 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
       </c>
       <c r="B34" t="str">
-        <v>Leanne Bryant</v>
+        <v>Alexander Leonard</v>
       </c>
       <c r="C34">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D34" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E34" t="str">
-        <v>blazeandcougar@gmail.com</v>
+        <v>alexleonardedit@gmail.com</v>
       </c>
       <c r="F34" t="str">
-        <v>61415438228</v>
+        <v>421834476</v>
       </c>
       <c r="G34" t="str">
-        <v xml:space="preserve">Hampton Park </v>
+        <v>Croydon</v>
       </c>
       <c r="H34" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I34" t="str">
+        <v>available</v>
+      </c>
+      <c r="J34" t="str">
+        <v>melissa francis, Alexander Leonard</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Linda Browne</v>
+      </c>
+      <c r="C35">
+        <v>54</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Lindabrowne@iprimus.com.au</v>
+      </c>
+      <c r="F35" t="str">
+        <v>429570177</v>
+      </c>
+      <c r="G35" t="str">
+        <v>OFFICER</v>
+      </c>
+      <c r="H35" t="str">
         <v>B</v>
       </c>
-      <c r="I34" t="str">
-        <v>assigned</v>
-      </c>
-      <c r="J34" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Alexander Leonard</v>
-      </c>
-      <c r="C35">
-        <v>38</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E35" t="str">
-        <v>alexleonardedit@gmail.com</v>
-      </c>
-      <c r="F35" t="str">
-        <v>421834476</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Croydon</v>
-      </c>
-      <c r="H35" t="str">
-        <v>A+</v>
-      </c>
       <c r="I35" t="str">
         <v>available</v>
       </c>
-      <c r="J35" t="str">
-        <v>melissa francis, Alexander Leonard</v>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36" t="str">
-        <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Linda Browne</v>
-      </c>
-      <c r="C36">
-        <v>54</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E36" t="str">
-        <v>Lindabrowne@iprimus.com.au</v>
-      </c>
-      <c r="F36" t="str">
-        <v>429570177</v>
-      </c>
-      <c r="G36" t="str">
-        <v>OFFICER</v>
-      </c>
-      <c r="H36" t="str">
-        <v>B</v>
-      </c>
-      <c r="I36" t="str">
-        <v>available</v>
-      </c>
-      <c r="J36" t="str" xml:space="preserve">
+      <c r="J35" t="str" xml:space="preserve">
         <v xml:space="preserve">Natalie Browne
 Linda Browne
 Aidan Miler</v>
       </c>
     </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Bronwyn Parsons</v>
+      </c>
+      <c r="C36">
+        <v>72</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Babybear61153@gmail.com</v>
+      </c>
+      <c r="F36" t="str">
+        <v>432543647</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Rosebud</v>
+      </c>
+      <c r="H36" t="str">
+        <v>A+</v>
+      </c>
+      <c r="I36" t="str">
+        <v>available</v>
+      </c>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yolette Huon - yol-et Hue on
+Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
+      </c>
+    </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
       </c>
       <c r="B37" t="str">
-        <v>Bashar Mona</v>
+        <v>Sherif Haggag</v>
       </c>
       <c r="C37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D37" t="str">
         <v>Male</v>
       </c>
       <c r="E37" t="str">
-        <v>bashar.mona92@gmail.com</v>
+        <v>Shaggag87@gmail.com</v>
       </c>
       <c r="F37" t="str">
-        <v>490871416</v>
+        <v>426233449</v>
       </c>
       <c r="G37" t="str">
-        <v>Roxburgh park</v>
+        <v>Belmont</v>
       </c>
       <c r="H37" t="str">
         <v>B+</v>
       </c>
       <c r="I37" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J37" t="str">
         <v>Solo</v>
@@ -1922,100 +1922,102 @@
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
+        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
       </c>
       <c r="B38" t="str">
-        <v>Bronwyn Parsons</v>
+        <v>Paige Greig</v>
       </c>
       <c r="C38">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D38" t="str">
         <v>Female</v>
       </c>
       <c r="E38" t="str">
-        <v>Babybear61153@gmail.com</v>
+        <v>paigegreig@hotmail.com</v>
       </c>
       <c r="F38" t="str">
-        <v>432543647</v>
+        <v>406598552</v>
       </c>
       <c r="G38" t="str">
-        <v>Rosebud</v>
+        <v>Mooroolbark</v>
       </c>
       <c r="H38" t="str">
-        <v>A+</v>
+        <v>C</v>
       </c>
       <c r="I38" t="str">
         <v>available</v>
       </c>
       <c r="J38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Yolette Huon - yol-et Hue on
-Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
-        <v>23f118f9-20db-422c-8cef-939dc73dd803</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Paige Greig</v>
-      </c>
-      <c r="C39">
-        <v>31</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E39" t="str">
-        <v>paigegreig@hotmail.com</v>
-      </c>
-      <c r="F39" t="str">
-        <v>406598552</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Mooroolbark</v>
-      </c>
-      <c r="H39" t="str">
-        <v>C</v>
-      </c>
-      <c r="I39" t="str">
-        <v>available</v>
-      </c>
-      <c r="J39" t="str" xml:space="preserve">
         <v xml:space="preserve">Erin
 Morgan (sister) - need to do application</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Bashar Mona</v>
+      </c>
+      <c r="C39">
+        <v>33</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E39" t="str">
+        <v>bashar.mona92@gmail.com</v>
+      </c>
+      <c r="F39" t="str">
+        <v>490871416</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Roxburgh park</v>
+      </c>
+      <c r="H39" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I39" t="str">
+        <v>available</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
       </c>
       <c r="B40" t="str">
-        <v>Angela Verspay</v>
+        <v>Tamika Colville</v>
       </c>
       <c r="C40">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D40" t="str">
         <v>Female</v>
       </c>
       <c r="E40" t="str">
-        <v>angelarileysmyth@hotmail.com</v>
+        <v>tamika.colville@gmail.com</v>
       </c>
       <c r="F40" t="str">
-        <v>477660119</v>
+        <v>409132141</v>
       </c>
       <c r="G40" t="str">
-        <v>Warrnambool</v>
+        <v>Golden square</v>
       </c>
       <c r="H40" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I40" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J40" t="str">
-        <v>SOLO</v>
+        <v>Shinae Colville</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Diagnosed with MS in 2018</v>
       </c>
       <c r="M40" t="str">
         <v>NA</v>
@@ -2023,25 +2025,25 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
       </c>
       <c r="B41" t="str">
-        <v>Tamika Colville</v>
+        <v>Kadisha  Bruton</v>
       </c>
       <c r="C41">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D41" t="str">
         <v>Female</v>
       </c>
       <c r="E41" t="str">
-        <v>tamika.colville@gmail.com</v>
+        <v>kadishaann@icloud.com</v>
       </c>
       <c r="F41" t="str">
-        <v>409132141</v>
+        <v>434829249</v>
       </c>
       <c r="G41" t="str">
-        <v>Golden square</v>
+        <v xml:space="preserve">Kurunjang </v>
       </c>
       <c r="H41" t="str">
         <v>B+</v>
@@ -2050,13 +2052,7 @@
         <v>available</v>
       </c>
       <c r="J41" t="str">
-        <v>Shinae Colville</v>
-      </c>
-      <c r="L41" t="str">
-        <v>Diagnosed with MS in 2018</v>
-      </c>
-      <c r="M41" t="str">
-        <v>NA</v>
+        <v>Jacob Steele</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
@@ -2085,7 +2081,7 @@
         <v>B</v>
       </c>
       <c r="I42" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J42" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -2095,27 +2091,27 @@
         <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
+        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
       </c>
       <c r="B43" t="str">
-        <v>Kadisha  Bruton</v>
+        <v>Sharyn  McKinnis</v>
       </c>
       <c r="C43">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D43" t="str">
         <v>Female</v>
       </c>
       <c r="E43" t="str">
-        <v>kadishaann@icloud.com</v>
+        <v>s.lmckinnis@bigpond.com</v>
       </c>
       <c r="F43" t="str">
-        <v>434829249</v>
+        <v>419880873</v>
       </c>
       <c r="G43" t="str">
-        <v xml:space="preserve">Kurunjang </v>
+        <v>Newtown</v>
       </c>
       <c r="H43" t="str">
         <v>B+</v>
@@ -2123,192 +2119,192 @@
       <c r="I43" t="str">
         <v>available</v>
       </c>
-      <c r="J43" t="str">
-        <v>Jacob Steele</v>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
-      <c r="A44" t="str">
-        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Sharyn  McKinnis</v>
-      </c>
-      <c r="C44">
-        <v>50</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E44" t="str">
-        <v>s.lmckinnis@bigpond.com</v>
-      </c>
-      <c r="F44" t="str">
-        <v>419880873</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Newtown</v>
-      </c>
-      <c r="H44" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I44" t="str">
-        <v>available</v>
-      </c>
-      <c r="J44" t="str" xml:space="preserve">
+      <c r="J43" t="str" xml:space="preserve">
         <v xml:space="preserve">Isabelle McKinnis, Sharyn McKinnis
 </v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Leanne Bryant</v>
+      </c>
+      <c r="C44">
+        <v>63</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E44" t="str">
+        <v>blazeandcougar@gmail.com</v>
+      </c>
+      <c r="F44" t="str">
+        <v>61415438228</v>
+      </c>
+      <c r="G44" t="str">
+        <v xml:space="preserve">Hampton Park </v>
+      </c>
+      <c r="H44" t="str">
+        <v>B</v>
+      </c>
+      <c r="I44" t="str">
+        <v>available</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+        <v>cfd3f567-ab69-4fa9-8a35-ca9c949fba91</v>
       </c>
       <c r="B45" t="str">
-        <v>Sherif Haggag</v>
+        <v>Michael Stevens</v>
       </c>
       <c r="C45">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D45" t="str">
         <v>Male</v>
       </c>
       <c r="E45" t="str">
-        <v>Shaggag87@gmail.com</v>
+        <v>mjstevens1306@gmail.com</v>
       </c>
       <c r="F45" t="str">
-        <v>426233449</v>
+        <v>424659733</v>
       </c>
       <c r="G45" t="str">
-        <v>Belmont</v>
+        <v xml:space="preserve">Heathcote Junction </v>
       </c>
       <c r="H45" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I45" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J45" t="str">
-        <v>Solo</v>
+        <v>Libby Dunbar</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>cfd3f567-ab69-4fa9-8a35-ca9c949fba91</v>
+        <v>f50d5074-9b3e-4386-9039-5e4cbd121267</v>
       </c>
       <c r="B46" t="str">
-        <v>Michael Stevens</v>
+        <v>Keera Bell</v>
       </c>
       <c r="C46">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D46" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E46" t="str">
-        <v>mjstevens1306@gmail.com</v>
+        <v>Keera_b@hotmail.com</v>
       </c>
       <c r="F46" t="str">
-        <v>424659733</v>
+        <v>404754383</v>
       </c>
       <c r="G46" t="str">
-        <v xml:space="preserve">Heathcote Junction </v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H46" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I46" t="str">
         <v>available</v>
       </c>
       <c r="J46" t="str">
-        <v>Libby Dunbar</v>
+        <v>Dek Bell</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>f50d5074-9b3e-4386-9039-5e4cbd121267</v>
+        <v>0b96f877-e1c4-4c17-aa89-21b4a5f7f002</v>
       </c>
       <c r="B47" t="str">
-        <v>Keera Bell</v>
+        <v>Stephen Deacon</v>
       </c>
       <c r="C47">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D47" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E47" t="str">
-        <v>Keera_b@hotmail.com</v>
+        <v>StephenDeacon@duck.com</v>
       </c>
       <c r="F47" t="str">
-        <v>404754383</v>
+        <v>435353108</v>
       </c>
       <c r="G47" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v>St Kilda</v>
       </c>
       <c r="H47" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I47" t="str">
         <v>available</v>
       </c>
       <c r="J47" t="str">
-        <v>Dek Bell</v>
+        <v>Chanyapach Deacon</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0b96f877-e1c4-4c17-aa89-21b4a5f7f002</v>
+        <v>eb3b2a7d-e6b0-421b-8987-00bfff95dda9</v>
       </c>
       <c r="B48" t="str">
-        <v>Stephen Deacon</v>
+        <v>Jasmine Miller</v>
       </c>
       <c r="C48">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D48" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E48" t="str">
-        <v>StephenDeacon@duck.com</v>
+        <v>jasmine_courtney@hotmail.com</v>
       </c>
       <c r="F48" t="str">
-        <v>435353108</v>
+        <v>0432 387 712</v>
       </c>
       <c r="G48" t="str">
-        <v>St Kilda</v>
+        <v>Hughesdale</v>
       </c>
       <c r="H48" t="str">
-        <v>B+</v>
+        <v>C</v>
       </c>
       <c r="I48" t="str">
         <v>available</v>
       </c>
       <c r="J48" t="str">
-        <v>Chanyapach Deacon</v>
+        <v>ablo - partner</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>eb3b2a7d-e6b0-421b-8987-00bfff95dda9</v>
+        <v>300ac025-db3a-42ba-a9dd-777f02fb3454</v>
       </c>
       <c r="B49" t="str">
-        <v>Jasmine Miller</v>
+        <v>Jeanette Quy</v>
       </c>
       <c r="C49">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D49" t="str">
         <v>Female</v>
       </c>
       <c r="E49" t="str">
-        <v>jasmine_courtney@hotmail.com</v>
+        <v>koalaleaf@hotmail.com</v>
       </c>
       <c r="F49" t="str">
-        <v>0432 387 712</v>
+        <v>402902273</v>
       </c>
       <c r="G49" t="str">
-        <v>Hughesdale</v>
+        <v>Rowville</v>
       </c>
       <c r="H49" t="str">
         <v>C</v>
@@ -2317,30 +2313,33 @@
         <v>available</v>
       </c>
       <c r="J49" t="str">
-        <v>ablo - partner</v>
+        <v>Husband Ted Quy b6042a-1-1872960</v>
+      </c>
+      <c r="M49" t="str">
+        <v xml:space="preserve">Nothing of note </v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>300ac025-db3a-42ba-a9dd-777f02fb3454</v>
+        <v>0ea22efb-f85f-400a-b28d-d1312568ba67</v>
       </c>
       <c r="B50" t="str">
-        <v>Jeanette Quy</v>
+        <v>Jess Cossari</v>
       </c>
       <c r="C50">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="D50" t="str">
         <v>Female</v>
       </c>
       <c r="E50" t="str">
-        <v>koalaleaf@hotmail.com</v>
+        <v>Jcossari@hotmail.com</v>
       </c>
       <c r="F50" t="str">
-        <v>402902273</v>
+        <v xml:space="preserve">0458 746 551 </v>
       </c>
       <c r="G50" t="str">
-        <v>Rowville</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H50" t="str">
         <v>C</v>
@@ -2349,42 +2348,42 @@
         <v>available</v>
       </c>
       <c r="J50" t="str">
-        <v>Husband Ted Quy b6042a-1-1872960</v>
-      </c>
-      <c r="M50" t="str">
-        <v xml:space="preserve">Nothing of note </v>
+        <v>Andrea Cocco</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0ea22efb-f85f-400a-b28d-d1312568ba67</v>
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
       </c>
       <c r="B51" t="str">
-        <v>Jess Cossari</v>
+        <v>Angela Verspay</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D51" t="str">
         <v>Female</v>
       </c>
       <c r="E51" t="str">
-        <v>Jcossari@hotmail.com</v>
+        <v>angelarileysmyth@hotmail.com</v>
       </c>
       <c r="F51" t="str">
-        <v xml:space="preserve">0458 746 551 </v>
+        <v>477660119</v>
       </c>
       <c r="G51" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v>Warrnambool</v>
       </c>
       <c r="H51" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="I51" t="str">
         <v>available</v>
       </c>
       <c r="J51" t="str">
-        <v>Andrea Cocco</v>
+        <v>SOLO</v>
+      </c>
+      <c r="M51" t="str">
+        <v>NA</v>
       </c>
     </row>
   </sheetData>
@@ -2396,230 +2395,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>RecordDayID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>ContestantID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Block</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Seat</v>
-      </c>
-      <c r="F1" t="str">
-        <v>BookingEmailSent</v>
-      </c>
-      <c r="G1" t="str">
-        <v>ConfirmedRSVP</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>cbb914d8-4355-4eae-8e6a-d916e6eeab9c</v>
-      </c>
-      <c r="B2" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C2" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>A1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>72ec2db4-7ad6-48e7-aada-ebcd77e964de</v>
-      </c>
-      <c r="B3" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C3" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="str">
-        <v>A2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3c715c30-77ec-4327-a1dc-77e587684309</v>
-      </c>
-      <c r="B4" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C4" t="str">
-        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>98131f5a-2b3c-46c8-876a-215c01d25450</v>
-      </c>
-      <c r="B5" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C5" t="str">
-        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="str">
-        <v>A4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>cd4bdfd0-1ea2-465c-9a88-0c4e8be41c46</v>
-      </c>
-      <c r="B6" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C6" t="str">
-        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="str">
-        <v>A5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>e3f866e4-5581-4731-8857-0d4dad4cee98</v>
-      </c>
-      <c r="B7" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C7" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="str">
-        <v>B1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>525e206b-a4dc-4cb0-bb8d-350087facf3e</v>
-      </c>
-      <c r="B8" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C8" t="str">
-        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="str">
-        <v>B2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>8d7a05d2-98e8-40f7-b7ff-a8b4cbbfcb46</v>
-      </c>
-      <c r="B9" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C9" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="str">
-        <v>B3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>8d8eddd8-180f-4a64-af6b-a1e848b325b0</v>
-      </c>
-      <c r="B10" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C10" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="str">
-        <v>B4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>0b61d3fc-daf3-492d-b9a1-6070b61f0235</v>
-      </c>
-      <c r="B11" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C11" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="str">
-        <v>B5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>cd6ab2c2-d134-4f10-95c6-caa3b4590d32</v>
-      </c>
-      <c r="B12" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C12" t="str">
-        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="str">
-        <v>D1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
@@ -2661,7 +2436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -5,8 +5,9 @@
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" r:id="rId3"/>
-    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
+    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
+    <sheet name="Groups" sheetId="4" r:id="rId4"/>
+    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -735,7 +736,7 @@
         <v>B</v>
       </c>
       <c r="I2" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J2" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -917,134 +918,128 @@
         <v>No</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
       </c>
       <c r="B8" t="str">
-        <v>Troy Smith</v>
+        <v>Sharon King</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D8" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E8" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>dreamweaversixtyseven@gmail.com</v>
       </c>
       <c r="F8" t="str">
-        <v>429354308</v>
+        <v>611488000000</v>
       </c>
       <c r="G8" t="str">
-        <v>Melbourne</v>
+        <v xml:space="preserve">Mooroopna </v>
       </c>
       <c r="H8" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I8" t="str">
         <v>available</v>
       </c>
-      <c r="J8" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="K8" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-      <c r="L8" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
-      </c>
-      <c r="M8" t="str">
-        <v>NA</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="C9">
-        <v>28</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Taylahuxtable@gmail.com</v>
-      </c>
-      <c r="F9" t="str">
-        <v>435320280</v>
-      </c>
-      <c r="G9" t="str">
-        <v>FERNTREE GULLY</v>
-      </c>
-      <c r="I9" t="str">
-        <v>available</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Troy Smith</v>
-      </c>
-      <c r="K9" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
-        <v>1fe25fd6-dc69-4d29-b22f-9a15ad3d457f</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Sharon King</v>
-      </c>
-      <c r="C10">
-        <v>58</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E10" t="str">
-        <v>dreamweaversixtyseven@gmail.com</v>
-      </c>
-      <c r="F10" t="str">
-        <v>611488000000</v>
-      </c>
-      <c r="G10" t="str">
-        <v xml:space="preserve">Mooroopna </v>
-      </c>
-      <c r="H10" t="str">
-        <v>A</v>
-      </c>
-      <c r="I10" t="str">
-        <v>available</v>
-      </c>
-      <c r="J10" t="str" xml:space="preserve">
+      <c r="J8" t="str" xml:space="preserve">
         <v xml:space="preserve">
 Friend :Jacinda Austin
 ID:b6042a-1-1936475</v>
       </c>
-      <c r="M10" t="str">
+      <c r="M8" t="str">
         <v xml:space="preserve">No </v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Tara Saltzman</v>
+      </c>
+      <c r="C9">
+        <v>29</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E9" t="str">
+        <v>tarasaltzman@bigpond.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>448545599</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="H9" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I9" t="str">
+        <v>available</v>
+      </c>
+      <c r="J9" t="str">
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+      </c>
+      <c r="M9" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Brent Barnett</v>
+      </c>
+      <c r="C10">
+        <v>37</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E10" t="str">
+        <v>brentbarnett88@gmail.com</v>
+      </c>
+      <c r="F10" t="str">
+        <v>423530043</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Preston</v>
+      </c>
+      <c r="H10" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I10" t="str">
+        <v>available</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Stephanie Squillacioti</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>82960b61-d36b-49e2-9ddf-a7b8e0b02a63</v>
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
       </c>
       <c r="B11" t="str">
-        <v>Tara Saltzman</v>
+        <v>Troy Smith</v>
       </c>
       <c r="C11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E11" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>Troyssmith94@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>448545599</v>
+        <v>429354308</v>
       </c>
       <c r="G11" t="str">
         <v>Melbourne</v>
@@ -1053,10 +1048,16 @@
         <v>B+</v>
       </c>
       <c r="I11" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J11" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="K11" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="L11" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
       </c>
       <c r="M11" t="str">
         <v>NA</v>
@@ -1064,34 +1065,34 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>f693566d-ea7c-40d1-89aa-158e842961d0</v>
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
       </c>
       <c r="B12" t="str">
-        <v>Brent Barnett</v>
+        <v>Tayla Huxtable</v>
       </c>
       <c r="C12">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D12" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E12" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>Taylahuxtable@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>423530043</v>
+        <v>435320280</v>
       </c>
       <c r="G12" t="str">
-        <v>Preston</v>
-      </c>
-      <c r="H12" t="str">
-        <v>B+</v>
+        <v>FERNTREE GULLY</v>
       </c>
       <c r="I12" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J12" t="str">
-        <v>Stephanie Squillacioti</v>
+        <v>Troy Smith</v>
+      </c>
+      <c r="K12" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
       </c>
     </row>
     <row r="13">
@@ -1394,89 +1395,89 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
+        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
       </c>
       <c r="B22" t="str">
-        <v>Tamara Mifsud</v>
+        <v>Jeanette Quy</v>
       </c>
       <c r="C22">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D22" t="str">
         <v>Female</v>
       </c>
       <c r="E22" t="str">
-        <v>tamara.mifsud@hotmail.com</v>
+        <v>quyfamily@tpg.com.au</v>
       </c>
       <c r="F22" t="str">
-        <v>416552122</v>
+        <v>402902273</v>
       </c>
       <c r="G22" t="str">
-        <v>Aintree</v>
+        <v>Rowville</v>
       </c>
       <c r="H22" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="I22" t="str">
-        <v>available</v>
-      </c>
-      <c r="J22" t="str">
-        <v>Aliye Abcilar</v>
+        <v>assigned</v>
+      </c>
+      <c r="M22" t="str">
+        <v xml:space="preserve">nothing of note </v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
+        <v>f048c8fe-e8c9-4357-8ec8-ef76793e5bc1</v>
       </c>
       <c r="B23" t="str">
-        <v>Philip Natoli</v>
+        <v>Tamara Mifsud</v>
       </c>
       <c r="C23">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D23" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E23" t="str">
-        <v>Philip.natoli@outlook.com</v>
+        <v>tamara.mifsud@hotmail.com</v>
       </c>
       <c r="F23" t="str">
-        <v>466021882</v>
+        <v>416552122</v>
       </c>
       <c r="G23" t="str">
-        <v>Caulfield South</v>
+        <v>Aintree</v>
       </c>
       <c r="H23" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I23" t="str">
         <v>available</v>
       </c>
       <c r="J23" t="str">
-        <v>Hayley Wright</v>
+        <v>Aliye Abcilar</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+        <v>6bbdadcb-23a8-41c9-964b-6152e234cb33</v>
       </c>
       <c r="B24" t="str">
-        <v>Antonio Freno</v>
+        <v>Philip Natoli</v>
       </c>
       <c r="C24">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D24" t="str">
         <v>Male</v>
       </c>
       <c r="E24" t="str">
-        <v>frenoantonio@hotmail.it</v>
+        <v>Philip.natoli@outlook.com</v>
       </c>
       <c r="F24" t="str">
-        <v>422177371</v>
+        <v>466021882</v>
       </c>
       <c r="G24" t="str">
-        <v>Glenroy</v>
+        <v>Caulfield South</v>
       </c>
       <c r="H24" t="str">
         <v>B+</v>
@@ -1485,39 +1486,39 @@
         <v>available</v>
       </c>
       <c r="J24" t="str">
-        <v>Solo</v>
+        <v>Hayley Wright</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
       </c>
       <c r="B25" t="str">
-        <v>Jeanette Quy</v>
+        <v>Antonio Freno</v>
       </c>
       <c r="C25">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="D25" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E25" t="str">
-        <v>quyfamily@tpg.com.au</v>
+        <v>frenoantonio@hotmail.it</v>
       </c>
       <c r="F25" t="str">
-        <v>402902273</v>
+        <v>422177371</v>
       </c>
       <c r="G25" t="str">
-        <v>Rowville</v>
+        <v>Glenroy</v>
       </c>
       <c r="H25" t="str">
-        <v>C</v>
+        <v>B+</v>
       </c>
       <c r="I25" t="str">
-        <v>available</v>
-      </c>
-      <c r="M25" t="str">
-        <v xml:space="preserve">nothing of note </v>
+        <v>assigned</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Solo</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
@@ -1684,7 +1685,7 @@
         <v>B+</v>
       </c>
       <c r="I30" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J30" t="str">
         <v>Solo</v>
@@ -1716,7 +1717,7 @@
         <v>B+</v>
       </c>
       <c r="I31" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J31" t="str">
         <v>SOLO</v>
@@ -1791,133 +1792,136 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Angela Verspay</v>
+      </c>
+      <c r="C34">
+        <v>45</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E34" t="str">
+        <v>angelarileysmyth@hotmail.com</v>
+      </c>
+      <c r="F34" t="str">
+        <v>477660119</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Warrnambool</v>
+      </c>
+      <c r="H34" t="str">
+        <v>B</v>
+      </c>
+      <c r="I34" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J34" t="str">
+        <v>SOLO</v>
+      </c>
+      <c r="M34" t="str">
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
         <v>2aadb3db-ad8e-4edd-a81d-f045a926ceb9</v>
       </c>
-      <c r="B34" t="str">
+      <c r="B35" t="str">
         <v>Alexander Leonard</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <v>38</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D35" t="str">
         <v>Male</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E35" t="str">
         <v>alexleonardedit@gmail.com</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F35" t="str">
         <v>421834476</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G35" t="str">
         <v>Croydon</v>
       </c>
-      <c r="H34" t="str">
+      <c r="H35" t="str">
         <v>A+</v>
       </c>
-      <c r="I34" t="str">
-        <v>available</v>
-      </c>
-      <c r="J34" t="str">
+      <c r="I35" t="str">
+        <v>available</v>
+      </c>
+      <c r="J35" t="str">
         <v>melissa francis, Alexander Leonard</v>
       </c>
     </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str">
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
         <v>ed91813b-2f74-4638-9d1a-ef8c54cff447</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B36" t="str">
         <v>Linda Browne</v>
       </c>
-      <c r="C35">
+      <c r="C36">
         <v>54</v>
       </c>
-      <c r="D35" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E35" t="str">
+      <c r="D36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E36" t="str">
         <v>Lindabrowne@iprimus.com.au</v>
       </c>
-      <c r="F35" t="str">
+      <c r="F36" t="str">
         <v>429570177</v>
       </c>
-      <c r="G35" t="str">
+      <c r="G36" t="str">
         <v>OFFICER</v>
       </c>
-      <c r="H35" t="str">
+      <c r="H36" t="str">
         <v>B</v>
       </c>
-      <c r="I35" t="str">
-        <v>available</v>
-      </c>
-      <c r="J35" t="str" xml:space="preserve">
+      <c r="I36" t="str">
+        <v>available</v>
+      </c>
+      <c r="J36" t="str" xml:space="preserve">
         <v xml:space="preserve">Natalie Browne
 Linda Browne
 Aidan Miler</v>
       </c>
     </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36" t="str">
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
         <v>1211456d-ea92-4a7b-9d94-885982cf345c</v>
       </c>
-      <c r="B36" t="str">
+      <c r="B37" t="str">
         <v>Bronwyn Parsons</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>72</v>
       </c>
-      <c r="D36" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E36" t="str">
+      <c r="D37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E37" t="str">
         <v>Babybear61153@gmail.com</v>
       </c>
-      <c r="F36" t="str">
+      <c r="F37" t="str">
         <v>432543647</v>
       </c>
-      <c r="G36" t="str">
+      <c r="G37" t="str">
         <v>Rosebud</v>
       </c>
-      <c r="H36" t="str">
+      <c r="H37" t="str">
         <v>A+</v>
       </c>
-      <c r="I36" t="str">
-        <v>available</v>
-      </c>
-      <c r="J36" t="str" xml:space="preserve">
+      <c r="I37" t="str">
+        <v>available</v>
+      </c>
+      <c r="J37" t="str" xml:space="preserve">
         <v xml:space="preserve">Yolette Huon - yol-et Hue on
 Bronwyn Parsons - Would like to be called Bron Emmerson - maiden name</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Sherif Haggag</v>
-      </c>
-      <c r="C37">
-        <v>38</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E37" t="str">
-        <v>Shaggag87@gmail.com</v>
-      </c>
-      <c r="F37" t="str">
-        <v>426233449</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Belmont</v>
-      </c>
-      <c r="H37" t="str">
-        <v>B+</v>
-      </c>
-      <c r="I37" t="str">
-        <v>available</v>
-      </c>
-      <c r="J37" t="str">
-        <v>Solo</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
@@ -1955,31 +1959,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
       </c>
       <c r="B39" t="str">
-        <v>Bashar Mona</v>
+        <v>Sherif Haggag</v>
       </c>
       <c r="C39">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D39" t="str">
         <v>Male</v>
       </c>
       <c r="E39" t="str">
-        <v>bashar.mona92@gmail.com</v>
+        <v>Shaggag87@gmail.com</v>
       </c>
       <c r="F39" t="str">
-        <v>490871416</v>
+        <v>426233449</v>
       </c>
       <c r="G39" t="str">
-        <v>Roxburgh park</v>
+        <v>Belmont</v>
       </c>
       <c r="H39" t="str">
         <v>B+</v>
       </c>
       <c r="I39" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J39" t="str">
         <v>Solo</v>
@@ -1987,63 +1991,57 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
       </c>
       <c r="B40" t="str">
-        <v>Tamika Colville</v>
+        <v>Bashar Mona</v>
       </c>
       <c r="C40">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D40" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E40" t="str">
-        <v>tamika.colville@gmail.com</v>
+        <v>bashar.mona92@gmail.com</v>
       </c>
       <c r="F40" t="str">
-        <v>409132141</v>
+        <v>490871416</v>
       </c>
       <c r="G40" t="str">
-        <v>Golden square</v>
+        <v>Roxburgh park</v>
       </c>
       <c r="H40" t="str">
         <v>B+</v>
       </c>
       <c r="I40" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J40" t="str">
-        <v>Shinae Colville</v>
-      </c>
-      <c r="L40" t="str">
-        <v>Diagnosed with MS in 2018</v>
-      </c>
-      <c r="M40" t="str">
-        <v>NA</v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
+        <v>cbfeb8b0-bd5d-4614-a055-cbac047cf152</v>
       </c>
       <c r="B41" t="str">
-        <v>Kadisha  Bruton</v>
+        <v>Tamika Colville</v>
       </c>
       <c r="C41">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D41" t="str">
         <v>Female</v>
       </c>
       <c r="E41" t="str">
-        <v>kadishaann@icloud.com</v>
+        <v>tamika.colville@gmail.com</v>
       </c>
       <c r="F41" t="str">
-        <v>434829249</v>
+        <v>409132141</v>
       </c>
       <c r="G41" t="str">
-        <v xml:space="preserve">Kurunjang </v>
+        <v>Golden square</v>
       </c>
       <c r="H41" t="str">
         <v>B+</v>
@@ -2052,7 +2050,13 @@
         <v>available</v>
       </c>
       <c r="J41" t="str">
-        <v>Jacob Steele</v>
+        <v>Shinae Colville</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Diagnosed with MS in 2018</v>
+      </c>
+      <c r="M41" t="str">
+        <v>NA</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
@@ -2081,7 +2085,7 @@
         <v>B</v>
       </c>
       <c r="I42" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J42" t="str" xml:space="preserve">
         <v xml:space="preserve">Meenakshi Mehra
@@ -2091,27 +2095,27 @@
         <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
+    <row r="43">
       <c r="A43" t="str">
-        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
+        <v>441f345e-57a2-403b-a9a9-8284261eba7b</v>
       </c>
       <c r="B43" t="str">
-        <v>Sharyn  McKinnis</v>
+        <v>Kadisha  Bruton</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D43" t="str">
         <v>Female</v>
       </c>
       <c r="E43" t="str">
-        <v>s.lmckinnis@bigpond.com</v>
+        <v>kadishaann@icloud.com</v>
       </c>
       <c r="F43" t="str">
-        <v>419880873</v>
+        <v>434829249</v>
       </c>
       <c r="G43" t="str">
-        <v>Newtown</v>
+        <v xml:space="preserve">Kurunjang </v>
       </c>
       <c r="H43" t="str">
         <v>B+</v>
@@ -2119,192 +2123,192 @@
       <c r="I43" t="str">
         <v>available</v>
       </c>
-      <c r="J43" t="str" xml:space="preserve">
+      <c r="J43" t="str">
+        <v>Jacob Steele</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>37fadce4-5d89-4542-a6e1-5e3e50620b85</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Sharyn  McKinnis</v>
+      </c>
+      <c r="C44">
+        <v>50</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E44" t="str">
+        <v>s.lmckinnis@bigpond.com</v>
+      </c>
+      <c r="F44" t="str">
+        <v>419880873</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Newtown</v>
+      </c>
+      <c r="H44" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I44" t="str">
+        <v>available</v>
+      </c>
+      <c r="J44" t="str" xml:space="preserve">
         <v xml:space="preserve">Isabelle McKinnis, Sharyn McKinnis
 </v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Leanne Bryant</v>
-      </c>
-      <c r="C44">
-        <v>63</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E44" t="str">
-        <v>blazeandcougar@gmail.com</v>
-      </c>
-      <c r="F44" t="str">
-        <v>61415438228</v>
-      </c>
-      <c r="G44" t="str">
-        <v xml:space="preserve">Hampton Park </v>
-      </c>
-      <c r="H44" t="str">
-        <v>B</v>
-      </c>
-      <c r="I44" t="str">
-        <v>available</v>
-      </c>
-      <c r="J44" t="str">
-        <v>Solo</v>
-      </c>
-    </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>cfd3f567-ab69-4fa9-8a35-ca9c949fba91</v>
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
       </c>
       <c r="B45" t="str">
-        <v>Michael Stevens</v>
+        <v>Leanne Bryant</v>
       </c>
       <c r="C45">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D45" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E45" t="str">
-        <v>mjstevens1306@gmail.com</v>
+        <v>blazeandcougar@gmail.com</v>
       </c>
       <c r="F45" t="str">
-        <v>424659733</v>
+        <v>61415438228</v>
       </c>
       <c r="G45" t="str">
-        <v xml:space="preserve">Heathcote Junction </v>
+        <v xml:space="preserve">Hampton Park </v>
       </c>
       <c r="H45" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="I45" t="str">
-        <v>available</v>
+        <v>assigned</v>
       </c>
       <c r="J45" t="str">
-        <v>Libby Dunbar</v>
+        <v>Solo</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>f50d5074-9b3e-4386-9039-5e4cbd121267</v>
+        <v>cfd3f567-ab69-4fa9-8a35-ca9c949fba91</v>
       </c>
       <c r="B46" t="str">
-        <v>Keera Bell</v>
+        <v>Michael Stevens</v>
       </c>
       <c r="C46">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D46" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E46" t="str">
-        <v>Keera_b@hotmail.com</v>
+        <v>mjstevens1306@gmail.com</v>
       </c>
       <c r="F46" t="str">
-        <v>404754383</v>
+        <v>424659733</v>
       </c>
       <c r="G46" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v xml:space="preserve">Heathcote Junction </v>
       </c>
       <c r="H46" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="I46" t="str">
         <v>available</v>
       </c>
       <c r="J46" t="str">
-        <v>Dek Bell</v>
+        <v>Libby Dunbar</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0b96f877-e1c4-4c17-aa89-21b4a5f7f002</v>
+        <v>f50d5074-9b3e-4386-9039-5e4cbd121267</v>
       </c>
       <c r="B47" t="str">
-        <v>Stephen Deacon</v>
+        <v>Keera Bell</v>
       </c>
       <c r="C47">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D47" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E47" t="str">
-        <v>StephenDeacon@duck.com</v>
+        <v>Keera_b@hotmail.com</v>
       </c>
       <c r="F47" t="str">
-        <v>435353108</v>
+        <v>404754383</v>
       </c>
       <c r="G47" t="str">
-        <v>St Kilda</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H47" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I47" t="str">
         <v>available</v>
       </c>
       <c r="J47" t="str">
-        <v>Chanyapach Deacon</v>
+        <v>Dek Bell</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>eb3b2a7d-e6b0-421b-8987-00bfff95dda9</v>
+        <v>0b96f877-e1c4-4c17-aa89-21b4a5f7f002</v>
       </c>
       <c r="B48" t="str">
-        <v>Jasmine Miller</v>
+        <v>Stephen Deacon</v>
       </c>
       <c r="C48">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D48" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E48" t="str">
-        <v>jasmine_courtney@hotmail.com</v>
+        <v>StephenDeacon@duck.com</v>
       </c>
       <c r="F48" t="str">
-        <v>0432 387 712</v>
+        <v>435353108</v>
       </c>
       <c r="G48" t="str">
-        <v>Hughesdale</v>
+        <v>St Kilda</v>
       </c>
       <c r="H48" t="str">
-        <v>C</v>
+        <v>B+</v>
       </c>
       <c r="I48" t="str">
         <v>available</v>
       </c>
       <c r="J48" t="str">
-        <v>ablo - partner</v>
+        <v>Chanyapach Deacon</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>300ac025-db3a-42ba-a9dd-777f02fb3454</v>
+        <v>eb3b2a7d-e6b0-421b-8987-00bfff95dda9</v>
       </c>
       <c r="B49" t="str">
-        <v>Jeanette Quy</v>
+        <v>Jasmine Miller</v>
       </c>
       <c r="C49">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D49" t="str">
         <v>Female</v>
       </c>
       <c r="E49" t="str">
-        <v>koalaleaf@hotmail.com</v>
+        <v>jasmine_courtney@hotmail.com</v>
       </c>
       <c r="F49" t="str">
-        <v>402902273</v>
+        <v>0432 387 712</v>
       </c>
       <c r="G49" t="str">
-        <v>Rowville</v>
+        <v>Hughesdale</v>
       </c>
       <c r="H49" t="str">
         <v>C</v>
@@ -2313,33 +2317,30 @@
         <v>available</v>
       </c>
       <c r="J49" t="str">
-        <v>Husband Ted Quy b6042a-1-1872960</v>
-      </c>
-      <c r="M49" t="str">
-        <v xml:space="preserve">Nothing of note </v>
+        <v>ablo - partner</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0ea22efb-f85f-400a-b28d-d1312568ba67</v>
+        <v>300ac025-db3a-42ba-a9dd-777f02fb3454</v>
       </c>
       <c r="B50" t="str">
-        <v>Jess Cossari</v>
+        <v>Jeanette Quy</v>
       </c>
       <c r="C50">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D50" t="str">
         <v>Female</v>
       </c>
       <c r="E50" t="str">
-        <v>Jcossari@hotmail.com</v>
+        <v>koalaleaf@hotmail.com</v>
       </c>
       <c r="F50" t="str">
-        <v xml:space="preserve">0458 746 551 </v>
+        <v>402902273</v>
       </c>
       <c r="G50" t="str">
-        <v xml:space="preserve">Melbourne </v>
+        <v>Rowville</v>
       </c>
       <c r="H50" t="str">
         <v>C</v>
@@ -2348,42 +2349,42 @@
         <v>available</v>
       </c>
       <c r="J50" t="str">
-        <v>Andrea Cocco</v>
+        <v>Husband Ted Quy b6042a-1-1872960</v>
+      </c>
+      <c r="M50" t="str">
+        <v xml:space="preserve">Nothing of note </v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+        <v>0ea22efb-f85f-400a-b28d-d1312568ba67</v>
       </c>
       <c r="B51" t="str">
-        <v>Angela Verspay</v>
+        <v>Jess Cossari</v>
       </c>
       <c r="C51">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D51" t="str">
         <v>Female</v>
       </c>
       <c r="E51" t="str">
-        <v>angelarileysmyth@hotmail.com</v>
+        <v>Jcossari@hotmail.com</v>
       </c>
       <c r="F51" t="str">
-        <v>477660119</v>
+        <v xml:space="preserve">0458 746 551 </v>
       </c>
       <c r="G51" t="str">
-        <v>Warrnambool</v>
+        <v xml:space="preserve">Melbourne </v>
       </c>
       <c r="H51" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="I51" t="str">
         <v>available</v>
       </c>
       <c r="J51" t="str">
-        <v>SOLO</v>
-      </c>
-      <c r="M51" t="str">
-        <v>NA</v>
+        <v>Andrea Cocco</v>
       </c>
     </row>
   </sheetData>
@@ -2395,6 +2396,247 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RecordDayID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ContestantID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Block</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Seat</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BookingEmailSent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ConfirmedRSVP</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>c428090e-0851-4b9f-9cdf-b348454d0c4e</v>
+      </c>
+      <c r="B2" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>b1fc34e8-20cb-4607-9568-0761cf4520a6</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>A1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>f0011d52-8ade-4f64-8ae4-ac21e90ea107</v>
+      </c>
+      <c r="B3" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6b9ae7f0-4a81-4dda-8e55-e49415d98ec6</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="str">
+        <v>A2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>71557816-b068-469d-81bc-86890e16382c</v>
+      </c>
+      <c r="B4" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C4" t="str">
+        <v>614641dd-4e94-4c42-a1d9-db37c608dcbe</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>A3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>038813f4-6e6c-4514-a5d1-48ddd8b23b1a</v>
+      </c>
+      <c r="B5" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C5" t="str">
+        <v>e4a52d0d-9c54-4504-8a0f-85845cd88e27</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>A4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>9eff4738-21c1-4c84-a047-c967ca2455b8</v>
+      </c>
+      <c r="B6" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C6" t="str">
+        <v>96c75db9-b001-4abe-8ddb-d5a73cb04529</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>A5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>4d40a2f2-bd3f-4706-bf35-af6009f63454</v>
+      </c>
+      <c r="B7" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C7" t="str">
+        <v>45c7f69f-dd89-41d8-b7f0-a83f77fa9d12</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="str">
+        <v>A1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>d70bd36a-e512-49d1-a282-af50e4a270be</v>
+      </c>
+      <c r="B8" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C8" t="str">
+        <v>c60666dd-e08c-4aa0-8582-4e7a3ad280f8</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="str">
+        <v>A1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2a8393a8-50cd-4281-adca-3a3a3dc4ebd0</v>
+      </c>
+      <c r="B9" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C9" t="str">
+        <v>646d2ff7-803b-4c80-bdd6-09d44eec6929</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>A2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>e6be730c-352f-480e-a6ea-22218cf952b5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C10" t="str">
+        <v>917bd31e-7781-44cc-936c-980cb1f844aa</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="str">
+        <v>A3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>119c5658-ecfd-4a4f-a9eb-5ca7b7a6f5f7</v>
+      </c>
+      <c r="B11" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C11" t="str">
+        <v>6cada433-8344-4d95-97dc-33c9c173ce7c</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="str">
+        <v>A1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>d9f5032e-edab-4349-a70d-e4c64699eb6b</v>
+      </c>
+      <c r="B12" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C12" t="str">
+        <v>7fc083f6-6be3-42bf-b4e5-fc6412e1c559</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" t="str">
+        <v>A2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>115ba5a2-17a0-426b-8ed1-38ed2cb0bce3</v>
+      </c>
+      <c r="B13" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C13" t="str">
+        <v>54de1dd9-b7eb-489d-b4a1-8b3744a385c4</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" t="str">
+        <v>A3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
@@ -2436,7 +2678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
-    <sheet name="Groups" sheetId="2" r:id="rId2"/>
-    <sheet name="Block Types" sheetId="3" r:id="rId3"/>
+    <sheet name="Contestants" sheetId="2" r:id="rId2"/>
+    <sheet name="Groups" sheetId="3" r:id="rId3"/>
+    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -665,49 +666,163 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>ReferenceNumber</v>
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Age</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Location</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Rating</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>AttendingWith</v>
+      </c>
+      <c r="K1" t="str">
+        <v>GroupID</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MedicalInfo</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MobilityNotes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>f25a6094-c1a5-4eb4-a709-1cc3d9b3ab5e</v>
+        <v>test-link-a</v>
       </c>
       <c r="B2" t="str">
-        <v>GRP001</v>
+        <v>Alice Test</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E2" t="str">
+        <v>alice@test.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>555-1001</v>
+      </c>
+      <c r="I2" t="str">
+        <v>available</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+        <v>test-link-b</v>
       </c>
       <c r="B3" t="str">
-        <v>GRP002</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
-      </c>
-      <c r="B4" t="str">
-        <v>AUTO-MK2NF2KE-kuoa</v>
+        <v>Bob Test</v>
+      </c>
+      <c r="C3">
+        <v>32</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E3" t="str">
+        <v>bob@test.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v>555-1002</v>
+      </c>
+      <c r="I3" t="str">
+        <v>available</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ReferenceNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>f25a6094-c1a5-4eb4-a709-1cc3d9b3ab5e</v>
+      </c>
+      <c r="B2" t="str">
+        <v>GRP001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="B3" t="str">
+        <v>GRP002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AUTO-MK2NF2KE-kuoa</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>632fede5-4c1f-4f47-8a24-f4c94563915f</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MANUAL-MKB8V43C</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>d5513a17-247e-49c4-be46-eca3c0aa0c4c</v>
+      </c>
+      <c r="B6" t="str">
+        <v>MANUAL-MKB952R9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>
     <row r="1">

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -4,9 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
-    <sheet name="Contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" r:id="rId3"/>
-    <sheet name="Block Types" sheetId="4" r:id="rId4"/>
+    <sheet name="Groups" sheetId="2" r:id="rId2"/>
+    <sheet name="Block Types" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -666,104 +665,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Age</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Gender</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Location</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Rating</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="J1" t="str">
-        <v>AttendingWith</v>
-      </c>
-      <c r="K1" t="str">
-        <v>GroupID</v>
-      </c>
-      <c r="L1" t="str">
-        <v>MedicalInfo</v>
-      </c>
-      <c r="M1" t="str">
-        <v>MobilityNotes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>test-link-a</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Alice Test</v>
-      </c>
-      <c r="C2">
-        <v>28</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Female</v>
-      </c>
-      <c r="E2" t="str">
-        <v>alice@test.com</v>
-      </c>
-      <c r="F2" t="str">
-        <v>555-1001</v>
-      </c>
-      <c r="I2" t="str">
-        <v>available</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>test-link-b</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Bob Test</v>
-      </c>
-      <c r="C3">
-        <v>32</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Male</v>
-      </c>
-      <c r="E3" t="str">
-        <v>bob@test.com</v>
-      </c>
-      <c r="F3" t="str">
-        <v>555-1002</v>
-      </c>
-      <c r="I3" t="str">
-        <v>available</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
@@ -821,7 +722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -4,8 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
-    <sheet name="Groups" sheetId="2" r:id="rId2"/>
-    <sheet name="Block Types" sheetId="3" r:id="rId3"/>
+    <sheet name="Contestants" sheetId="2" r:id="rId2"/>
+    <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
+    <sheet name="Groups" sheetId="4" r:id="rId4"/>
+    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -665,65 +667,263 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>ReferenceNumber</v>
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Age</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Location</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Rating</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>AttendingWith</v>
+      </c>
+      <c r="K1" t="str">
+        <v>GroupID</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MedicalInfo</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MobilityNotes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>f25a6094-c1a5-4eb4-a709-1cc3d9b3ab5e</v>
+        <v>df1eee3b-9186-4dcb-8dff-b88f5ac053e5</v>
       </c>
       <c r="B2" t="str">
-        <v>GRP001</v>
+        <v>Kathleen Reynolds</v>
+      </c>
+      <c r="C2">
+        <v>33</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Female</v>
+      </c>
+      <c r="E2" t="str">
+        <v>kathleenmonicareynolds@gmail.com</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Footscray</v>
+      </c>
+      <c r="H2" t="str">
+        <v>A</v>
+      </c>
+      <c r="I2" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Peter Adamidis</v>
+      </c>
+      <c r="K2" t="str">
+        <v>44a98d78-5aac-4530-bb14-36dd87ed6cfb</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
       </c>
       <c r="B3" t="str">
-        <v>GRP002</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
-      </c>
-      <c r="B4" t="str">
-        <v>AUTO-MK2NF2KE-kuoa</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>632fede5-4c1f-4f47-8a24-f4c94563915f</v>
-      </c>
-      <c r="B5" t="str">
-        <v>MANUAL-MKB8V43C</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>d5513a17-247e-49c4-be46-eca3c0aa0c4c</v>
-      </c>
-      <c r="B6" t="str">
-        <v>MANUAL-MKB952R9</v>
+        <v>Peter Adamidis</v>
+      </c>
+      <c r="C3">
+        <v>34</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E3" t="str">
+        <v>peter.adamidis@gmail.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v>498086080</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Greenvale</v>
+      </c>
+      <c r="H3" t="str">
+        <v>B</v>
+      </c>
+      <c r="I3" t="str">
+        <v>assigned</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Kathleen Reynolds</v>
+      </c>
+      <c r="K3" t="str">
+        <v>44a98d78-5aac-4530-bb14-36dd87ed6cfb</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RecordDayID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ContestantID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Block</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Seat</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BookingEmailSent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ConfirmedRSVP</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>32a65917-9e14-41de-8f93-c9049de2b2fa</v>
+      </c>
+      <c r="B2" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>df1eee3b-9186-4dcb-8dff-b88f5ac053e5</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="str">
+        <v>D2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ed805d47-d9cc-43fe-b44b-d40e665ed5fd</v>
+      </c>
+      <c r="B3" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C3" t="str">
+        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="str">
+        <v>D3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ReferenceNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>f25a6094-c1a5-4eb4-a709-1cc3d9b3ab5e</v>
+      </c>
+      <c r="B2" t="str">
+        <v>GRP001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>6b341038-788f-4120-a2ca-16551bbc1d11</v>
+      </c>
+      <c r="B3" t="str">
+        <v>GRP002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>8c760df8-0e51-4b27-b1cb-0754c8b03595</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AUTO-MK2NF2KE-kuoa</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>632fede5-4c1f-4f47-8a24-f4c94563915f</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MANUAL-MKB8V43C</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>d5513a17-247e-49c4-be46-eca3c0aa0c4c</v>
+      </c>
+      <c r="B6" t="str">
+        <v>MANUAL-MKB952R9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>44a98d78-5aac-4530-bb14-36dd87ed6cfb</v>
+      </c>
+      <c r="B7" t="str">
+        <v>GRP003</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>
     <row r="1">

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -6,8 +6,9 @@
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
     <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
-    <sheet name="Groups" sheetId="4" r:id="rId4"/>
-    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
+    <sheet name="Standbys" sheetId="4" r:id="rId4"/>
+    <sheet name="Groups" sheetId="5" r:id="rId5"/>
+    <sheet name="Block Types" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -786,7 +787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -831,31 +832,56 @@
         <v>D2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ed805d47-d9cc-43fe-b44b-d40e665ed5fd</v>
-      </c>
-      <c r="B3" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C3" t="str">
-        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3" t="str">
-        <v>D3</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>RecordDayID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ContestantID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>55f716f6-1aea-4732-b4ff-deb3b65a8203</v>
+      </c>
+      <c r="B2" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
+      </c>
+      <c r="D2" t="str">
+        <v>pending</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
   <sheetData>
@@ -922,7 +948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -6,9 +6,8 @@
     <sheet name="Record Days" sheetId="1" r:id="rId1"/>
     <sheet name="Contestants" sheetId="2" r:id="rId2"/>
     <sheet name="Seat Assignments" sheetId="3" r:id="rId3"/>
-    <sheet name="Standbys" sheetId="4" r:id="rId4"/>
-    <sheet name="Groups" sheetId="5" r:id="rId5"/>
-    <sheet name="Block Types" sheetId="6" r:id="rId6"/>
+    <sheet name="Groups" sheetId="4" r:id="rId4"/>
+    <sheet name="Block Types" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -787,7 +786,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -817,7 +816,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>32a65917-9e14-41de-8f93-c9049de2b2fa</v>
+        <v>70f80dcf-ade2-4f1d-abe5-ea68a6443a19</v>
       </c>
       <c r="B2" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
@@ -826,62 +825,37 @@
         <v>df1eee3b-9186-4dcb-8dff-b88f5ac053e5</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="str">
         <v>D2</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>c9f9f9a5-223f-43c1-92c6-0f0a39ad4ab7</v>
+      </c>
+      <c r="B3" t="str">
+        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
+      </c>
+      <c r="C3" t="str">
+        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3" t="str">
+        <v>D3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>RecordDayID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>ContestantID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>55f716f6-1aea-4732-b4ff-deb3b65a8203</v>
-      </c>
-      <c r="B2" t="str">
-        <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
-      </c>
-      <c r="C2" t="str">
-        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
-      </c>
-      <c r="D2" t="str">
-        <v>pending</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
   <sheetData>
@@ -948,7 +922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -16558,7 +16558,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16912,10 +16912,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>badc1981-587e-4ebe-a4ca-d09f25a98a6b</v>
+        <v>4024cdf1-46c9-4af4-b451-6e106c607a2e</v>
       </c>
       <c r="B26" t="str">
-        <v>eec54567-3e21-424c-8d62-28772c0a6c25</v>
+        <v>59f9cd94-162d-413c-9797-5a881676a706</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -16926,21 +16926,35 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>321d3111-fcc3-4246-8800-231133dd823d</v>
+        <v>badc1981-587e-4ebe-a4ca-d09f25a98a6b</v>
       </c>
       <c r="B27" t="str">
         <v>eec54567-3e21-424c-8d62-28772c0a6c25</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="str">
         <v>PB</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>321d3111-fcc3-4246-8800-231133dd823d</v>
+      </c>
+      <c r="B28" t="str">
+        <v>eec54567-3e21-424c-8d62-28772c0a6c25</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="str">
+        <v>PB</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -15195,342 +15195,342 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>70f80dcf-ade2-4f1d-abe5-ea68a6443a19</v>
+        <v>c9f9f9a5-223f-43c1-92c6-0f0a39ad4ab7</v>
       </c>
       <c r="B2" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C2" t="str">
-        <v>df1eee3b-9186-4dcb-8dff-b88f5ac053e5</v>
+        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
       </c>
       <c r="D2">
         <v>7</v>
       </c>
       <c r="E2" t="str">
-        <v>D2</v>
+        <v>D3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>c9f9f9a5-223f-43c1-92c6-0f0a39ad4ab7</v>
+        <v>20e92b66-46e9-4eb7-80cf-b20ed2afa92c</v>
       </c>
       <c r="B3" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C3" t="str">
-        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
+        <v>1373bff6-1fa6-4e22-a5be-810587cb7056</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>D3</v>
+        <v>B1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>20e92b66-46e9-4eb7-80cf-b20ed2afa92c</v>
+        <v>d7d0a055-b2d4-4231-84ba-3a6049c57715</v>
       </c>
       <c r="B4" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C4" t="str">
-        <v>1373bff6-1fa6-4e22-a5be-810587cb7056</v>
+        <v>c2568561-9563-4f98-83f7-0658e14bed36</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>B1</v>
+        <v>B2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>d7d0a055-b2d4-4231-84ba-3a6049c57715</v>
+        <v>3a8396e9-22fd-4db5-b8d3-a791ee3f206e</v>
       </c>
       <c r="B5" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C5" t="str">
-        <v>c2568561-9563-4f98-83f7-0658e14bed36</v>
+        <v>f066c255-163d-4c17-8441-e7673d2646f3</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>B2</v>
+        <v>B3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3a8396e9-22fd-4db5-b8d3-a791ee3f206e</v>
+        <v>52696136-4d33-47a1-9605-aae3f328c29d</v>
       </c>
       <c r="B6" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C6" t="str">
-        <v>f066c255-163d-4c17-8441-e7673d2646f3</v>
+        <v>16a56913-24a5-4bd8-9c45-78f2ae55a11d</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>B3</v>
+        <v>B4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>52696136-4d33-47a1-9605-aae3f328c29d</v>
+        <v>bae99a6d-aa62-4e41-9a56-54aaf7d037d3</v>
       </c>
       <c r="B7" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C7" t="str">
-        <v>16a56913-24a5-4bd8-9c45-78f2ae55a11d</v>
+        <v>c4a59423-d8ff-4b63-aa35-62c78b050663</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>B4</v>
+        <v>C1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>bae99a6d-aa62-4e41-9a56-54aaf7d037d3</v>
+        <v>33778eb7-9030-4fea-b9c6-b2a4cf28b7ad</v>
       </c>
       <c r="B8" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C8" t="str">
-        <v>c4a59423-d8ff-4b63-aa35-62c78b050663</v>
+        <v>3c4c0dd0-e98b-449e-b2fe-38d8927a3f3a</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>C1</v>
+        <v>C2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>33778eb7-9030-4fea-b9c6-b2a4cf28b7ad</v>
+        <v>ed2c1c4b-610a-4f9c-92f8-353df202c677</v>
       </c>
       <c r="B9" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C9" t="str">
-        <v>3c4c0dd0-e98b-449e-b2fe-38d8927a3f3a</v>
+        <v>0ac07194-cfd3-43c3-93a4-e21b0470f833</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>C2</v>
+        <v>C3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ed2c1c4b-610a-4f9c-92f8-353df202c677</v>
+        <v>7fe3b0ab-fa8c-4993-b046-89982206ff8d</v>
       </c>
       <c r="B10" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C10" t="str">
-        <v>0ac07194-cfd3-43c3-93a4-e21b0470f833</v>
+        <v>65a7d185-32fb-4518-96c6-a8b8a0314939</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>C3</v>
+        <v>D3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>7fe3b0ab-fa8c-4993-b046-89982206ff8d</v>
+        <v>033e9966-1308-4b1e-9c87-7198d93b3c0f</v>
       </c>
       <c r="B11" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C11" t="str">
-        <v>65a7d185-32fb-4518-96c6-a8b8a0314939</v>
+        <v>b42f2517-90d3-4c2e-aec1-7338c18cd14f</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="str">
-        <v>D3</v>
+        <v>D4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>033e9966-1308-4b1e-9c87-7198d93b3c0f</v>
+        <v>d79f293f-1b26-4443-ac34-382a81fd09f3</v>
       </c>
       <c r="B12" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C12" t="str">
-        <v>b42f2517-90d3-4c2e-aec1-7338c18cd14f</v>
+        <v>8cb8a9bf-a712-4ad3-b537-f0eebc912e58</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="str">
-        <v>D4</v>
+        <v>E1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>d79f293f-1b26-4443-ac34-382a81fd09f3</v>
+        <v>49e57d2c-e52e-43d6-8105-8f8f87cd393e</v>
       </c>
       <c r="B13" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C13" t="str">
-        <v>8cb8a9bf-a712-4ad3-b537-f0eebc912e58</v>
+        <v>5fb55209-4753-4095-b21f-a62a5c711d7d</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="str">
-        <v>E1</v>
+        <v>E2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>49e57d2c-e52e-43d6-8105-8f8f87cd393e</v>
+        <v>3034a004-0f03-4137-bb27-d11448c0abdb</v>
       </c>
       <c r="B14" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C14" t="str">
-        <v>5fb55209-4753-4095-b21f-a62a5c711d7d</v>
+        <v>034c094f-f76d-434f-8b89-909c23c8ad42</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="str">
-        <v>E2</v>
+        <v>E3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3034a004-0f03-4137-bb27-d11448c0abdb</v>
+        <v>592fd454-318d-40aa-9e12-d3e6036e2e34</v>
       </c>
       <c r="B15" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C15" t="str">
-        <v>034c094f-f76d-434f-8b89-909c23c8ad42</v>
+        <v>c37d275c-1560-4d86-9b7a-22963f478a91</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="str">
-        <v>E3</v>
+        <v>E4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>592fd454-318d-40aa-9e12-d3e6036e2e34</v>
+        <v>4f2e9b92-f970-4f97-a5bf-31b2204c6dbb</v>
       </c>
       <c r="B16" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C16" t="str">
-        <v>c37d275c-1560-4d86-9b7a-22963f478a91</v>
+        <v>71d827af-973f-4c3a-a074-dd419b4a9c27</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="str">
-        <v>E4</v>
+        <v>A1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>4f2e9b92-f970-4f97-a5bf-31b2204c6dbb</v>
+        <v>32d58a77-f34a-4cd2-b9a7-559df3c555d1</v>
       </c>
       <c r="B17" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C17" t="str">
-        <v>71d827af-973f-4c3a-a074-dd419b4a9c27</v>
+        <v>7f88f66e-bf77-4937-bfe1-44d447960afc</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="str">
-        <v>A1</v>
+        <v>A2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>32d58a77-f34a-4cd2-b9a7-559df3c555d1</v>
+        <v>9d49646c-54a0-43cc-b5a8-9a42788aaf6f</v>
       </c>
       <c r="B18" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C18" t="str">
-        <v>7f88f66e-bf77-4937-bfe1-44d447960afc</v>
+        <v>9520e1b4-1889-4925-9628-eb625555036c</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="str">
-        <v>A2</v>
+        <v>A3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>9d49646c-54a0-43cc-b5a8-9a42788aaf6f</v>
+        <v>3411d007-571a-484a-a508-360fe9c6c33e</v>
       </c>
       <c r="B19" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C19" t="str">
-        <v>9520e1b4-1889-4925-9628-eb625555036c</v>
+        <v>293e11eb-227f-4247-8788-b270b2af2d63</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="str">
-        <v>A3</v>
+        <v>B5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>3411d007-571a-484a-a508-360fe9c6c33e</v>
+        <v>2457f5d9-ae65-4242-ab9c-2fb3902296fb</v>
       </c>
       <c r="B20" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C20" t="str">
-        <v>293e11eb-227f-4247-8788-b270b2af2d63</v>
+        <v>efcb7955-b4bc-487b-b45b-02a50d7f5ba2</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="str">
-        <v>B5</v>
+        <v>C4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2457f5d9-ae65-4242-ab9c-2fb3902296fb</v>
+        <v>70f80dcf-ade2-4f1d-abe5-ea68a6443a19</v>
       </c>
       <c r="B21" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C21" t="str">
-        <v>efcb7955-b4bc-487b-b45b-02a50d7f5ba2</v>
+        <v>df1eee3b-9186-4dcb-8dff-b88f5ac053e5</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E21" t="str">
-        <v>C4</v>
+        <v>D2</v>
       </c>
     </row>
   </sheetData>

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -712,25 +712,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>9528376e-b4d9-4b58-87ac-757ac76c3509</v>
+        <v>97ce0b2a-8b18-4079-8405-31b1a13ffdab</v>
       </c>
       <c r="B2" t="str">
-        <v>Michelle  Richardson</v>
+        <v>Chelsea  Fanning</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D2" t="str">
         <v>Female</v>
       </c>
       <c r="E2" t="str">
-        <v>mrichardson17@outlook.com.au</v>
+        <v>cmaryf01@icloud.com</v>
       </c>
       <c r="F2" t="str">
-        <v>0459150497</v>
+        <v>0401507791</v>
       </c>
       <c r="G2" t="str">
-        <v>Portland</v>
+        <v xml:space="preserve">Gladstone </v>
       </c>
       <c r="H2" t="str">
         <v>B+</v>
@@ -739,33 +739,33 @@
         <v>available</v>
       </c>
       <c r="J2" t="str">
-        <v>Chelsea Fanning</v>
+        <v>Michelle Richardson</v>
       </c>
       <c r="K2" t="str">
         <v>64c49e8a-746f-4336-b779-194a3e136339</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>97ce0b2a-8b18-4079-8405-31b1a13ffdab</v>
+        <v>2da73fbf-9373-4a15-98b4-1dc259db08b0</v>
       </c>
       <c r="B3" t="str">
-        <v>Chelsea  Fanning</v>
+        <v>Sandra  Anderson</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D3" t="str">
         <v>Female</v>
       </c>
       <c r="E3" t="str">
-        <v>cmaryf01@icloud.com</v>
+        <v>mathewsally1c@gmail.com</v>
       </c>
       <c r="F3" t="str">
-        <v>0401507791</v>
+        <v>0439352004</v>
       </c>
       <c r="G3" t="str">
-        <v xml:space="preserve">Gladstone </v>
+        <v xml:space="preserve">Dromana </v>
       </c>
       <c r="H3" t="str">
         <v>B+</v>
@@ -773,34 +773,38 @@
       <c r="I3" t="str">
         <v>available</v>
       </c>
-      <c r="J3" t="str">
-        <v>Michelle Richardson</v>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jessy Brown
+Matilda Davis
+Colin Anderson
+Sandra Anderson
+Sally Davis</v>
       </c>
       <c r="K3" t="str">
-        <v>64c49e8a-746f-4336-b779-194a3e136339</v>
+        <v>1b3b852f-d9f5-491a-86d6-2ebe1fdac3f9</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>2da73fbf-9373-4a15-98b4-1dc259db08b0</v>
+        <v>ef612e09-b066-4880-a01c-1aa0836a93aa</v>
       </c>
       <c r="B4" t="str">
-        <v>Sandra  Anderson</v>
+        <v>Sally Davis</v>
       </c>
       <c r="C4">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D4" t="str">
         <v>Female</v>
       </c>
       <c r="E4" t="str">
-        <v>mathewsally1c@gmail.com</v>
+        <v>matsal1c@bigpond.com</v>
       </c>
       <c r="F4" t="str">
-        <v>0439352004</v>
+        <v>0434871103</v>
       </c>
       <c r="G4" t="str">
-        <v xml:space="preserve">Dromana </v>
+        <v>My Martha</v>
       </c>
       <c r="H4" t="str">
         <v>B+</v>
@@ -819,66 +823,59 @@
         <v>1b3b852f-d9f5-491a-86d6-2ebe1fdac3f9</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>ef612e09-b066-4880-a01c-1aa0836a93aa</v>
+        <v>71d827af-973f-4c3a-a074-dd419b4a9c27</v>
       </c>
       <c r="B5" t="str">
-        <v>Sally Davis</v>
+        <v>Angela Verspay</v>
       </c>
       <c r="C5">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D5" t="str">
         <v>Female</v>
       </c>
       <c r="E5" t="str">
-        <v>matsal1c@bigpond.com</v>
+        <v>angelarileysmyth@hotmail.com</v>
       </c>
       <c r="F5" t="str">
-        <v>0434871103</v>
+        <v>0477660119</v>
       </c>
       <c r="G5" t="str">
-        <v>My Martha</v>
+        <v>Warrnambool</v>
       </c>
       <c r="H5" t="str">
-        <v>B+</v>
+        <v>B</v>
       </c>
       <c r="I5" t="str">
-        <v>available</v>
-      </c>
-      <c r="J5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jessy Brown
-Matilda Davis
-Colin Anderson
-Sandra Anderson
-Sally Davis</v>
-      </c>
-      <c r="K5" t="str">
-        <v>1b3b852f-d9f5-491a-86d6-2ebe1fdac3f9</v>
+        <v>assigned</v>
+      </c>
+      <c r="J5" t="str">
+        <v>SOLO</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>71d827af-973f-4c3a-a074-dd419b4a9c27</v>
+        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
       </c>
       <c r="B6" t="str">
-        <v>Angela Verspay</v>
+        <v>Peter Adamidis</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D6" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E6" t="str">
-        <v>angelarileysmyth@hotmail.com</v>
+        <v>peter.adamidis@gmail.com</v>
       </c>
       <c r="F6" t="str">
-        <v>0477660119</v>
+        <v>0498086080</v>
       </c>
       <c r="G6" t="str">
-        <v>Warrnambool</v>
+        <v>Greenvale</v>
       </c>
       <c r="H6" t="str">
         <v>B</v>
@@ -887,65 +884,68 @@
         <v>assigned</v>
       </c>
       <c r="J6" t="str">
-        <v>SOLO</v>
+        <v>Kathleen Reynolds</v>
+      </c>
+      <c r="K6" t="str">
+        <v>44a98d78-5aac-4530-bb14-36dd87ed6cfb</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
+        <v>08958291-6c32-49d6-a9ef-1aa84b760b54</v>
       </c>
       <c r="B7" t="str">
-        <v>Peter Adamidis</v>
+        <v>Brent Barnett</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" t="str">
         <v>Male</v>
       </c>
       <c r="E7" t="str">
-        <v>peter.adamidis@gmail.com</v>
+        <v>brentbarnett88@gmail.com</v>
       </c>
       <c r="F7" t="str">
-        <v>0498086080</v>
+        <v>0423530043</v>
       </c>
       <c r="G7" t="str">
-        <v>Greenvale</v>
+        <v>Preston</v>
       </c>
       <c r="H7" t="str">
-        <v>B</v>
+        <v>B+</v>
       </c>
       <c r="I7" t="str">
-        <v>assigned</v>
+        <v>available</v>
       </c>
       <c r="J7" t="str">
-        <v>Kathleen Reynolds</v>
+        <v>Stephanie Squillacioti</v>
       </c>
       <c r="K7" t="str">
-        <v>44a98d78-5aac-4530-bb14-36dd87ed6cfb</v>
+        <v>9b12e80e-a626-4481-95b4-484e64b6f474</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08958291-6c32-49d6-a9ef-1aa84b760b54</v>
+        <v>5e33fa3c-fe11-46d0-89b0-09389e33b12f</v>
       </c>
       <c r="B8" t="str">
-        <v>Brent Barnett</v>
+        <v>Tara Saltzman</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D8" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E8" t="str">
-        <v>brentbarnett88@gmail.com</v>
+        <v>tarasaltzman@bigpond.com</v>
       </c>
       <c r="F8" t="str">
-        <v>0423530043</v>
+        <v>0448545599</v>
       </c>
       <c r="G8" t="str">
-        <v>Preston</v>
+        <v>Melbourne</v>
       </c>
       <c r="H8" t="str">
         <v>B+</v>
@@ -954,33 +954,30 @@
         <v>available</v>
       </c>
       <c r="J8" t="str">
-        <v>Stephanie Squillacioti</v>
-      </c>
-      <c r="K8" t="str">
-        <v>9b12e80e-a626-4481-95b4-484e64b6f474</v>
+        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>5e33fa3c-fe11-46d0-89b0-09389e33b12f</v>
+        <v>01eae1ca-b0d3-4b95-8800-b73c7ccd999f</v>
       </c>
       <c r="B9" t="str">
-        <v>Tara Saltzman</v>
+        <v>Karina  Richmond</v>
       </c>
       <c r="C9">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D9" t="str">
         <v>Female</v>
       </c>
       <c r="E9" t="str">
-        <v>tarasaltzman@bigpond.com</v>
+        <v>richmondkarina@yahoo.com</v>
       </c>
       <c r="F9" t="str">
-        <v>0448545599</v>
+        <v>0400554609</v>
       </c>
       <c r="G9" t="str">
-        <v>Melbourne</v>
+        <v>Newcomb</v>
       </c>
       <c r="H9" t="str">
         <v>B+</v>
@@ -989,30 +986,30 @@
         <v>available</v>
       </c>
       <c r="J9" t="str">
-        <v xml:space="preserve">JACK AGIUS - NEEDS TO DO APPLICATION </v>
+        <v>AMY DILLON</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>01eae1ca-b0d3-4b95-8800-b73c7ccd999f</v>
+        <v>9cea8138-f43e-49b8-b2c7-849645bf2a59</v>
       </c>
       <c r="B10" t="str">
-        <v>Karina  Richmond</v>
+        <v>Troy Smith</v>
       </c>
       <c r="C10">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D10" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E10" t="str">
-        <v>richmondkarina@yahoo.com</v>
+        <v>Troyssmith94@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>0400554609</v>
+        <v>0429354308</v>
       </c>
       <c r="G10" t="str">
-        <v>Newcomb</v>
+        <v>Melbourne</v>
       </c>
       <c r="H10" t="str">
         <v>B+</v>
@@ -1021,30 +1018,33 @@
         <v>available</v>
       </c>
       <c r="J10" t="str">
-        <v>AMY DILLON</v>
+        <v>Tayla Huxtable</v>
+      </c>
+      <c r="L10" t="str">
+        <v xml:space="preserve">Peanut allergy </v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9cea8138-f43e-49b8-b2c7-849645bf2a59</v>
+        <v>e64cdfc2-e9c8-4ab5-84e1-c4b636b79efb</v>
       </c>
       <c r="B11" t="str">
-        <v>Troy Smith</v>
+        <v>Deb  Jones</v>
       </c>
       <c r="C11">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D11" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E11" t="str">
-        <v>Troyssmith94@gmail.com</v>
+        <v>fullhouse5@optusnet.com.au</v>
       </c>
       <c r="F11" t="str">
-        <v>0429354308</v>
+        <v>0438561474</v>
       </c>
       <c r="G11" t="str">
-        <v>Melbourne</v>
+        <v>Bayswater North</v>
       </c>
       <c r="H11" t="str">
         <v>B+</v>
@@ -1053,33 +1053,36 @@
         <v>available</v>
       </c>
       <c r="J11" t="str">
-        <v>Tayla Huxtable</v>
-      </c>
-      <c r="L11" t="str">
-        <v xml:space="preserve">Peanut allergy </v>
+        <v>Daryl Jones</v>
+      </c>
+      <c r="K11" t="str">
+        <v>3bd0ea54-9969-49c7-af92-796fd54643e7</v>
+      </c>
+      <c r="M11" t="str">
+        <v>No</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>e64cdfc2-e9c8-4ab5-84e1-c4b636b79efb</v>
+        <v>3d46906e-68f4-44ae-a430-a3225a7be977</v>
       </c>
       <c r="B12" t="str">
-        <v>Deb  Jones</v>
+        <v>Philip Natoli</v>
       </c>
       <c r="C12">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D12" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="E12" t="str">
-        <v>fullhouse5@optusnet.com.au</v>
+        <v>Philip.natoli@outlook.com</v>
       </c>
       <c r="F12" t="str">
-        <v>0438561474</v>
+        <v>0466021882</v>
       </c>
       <c r="G12" t="str">
-        <v>Bayswater North</v>
+        <v>Caulfield South</v>
       </c>
       <c r="H12" t="str">
         <v>B+</v>
@@ -1088,48 +1091,51 @@
         <v>available</v>
       </c>
       <c r="J12" t="str">
-        <v>Daryl Jones</v>
+        <v>Hayley Wright</v>
       </c>
       <c r="K12" t="str">
-        <v>3bd0ea54-9969-49c7-af92-796fd54643e7</v>
-      </c>
-      <c r="M12" t="str">
-        <v>No</v>
+        <v>7989cb62-884e-4e52-a28b-cca0e64f2a6f</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>3d46906e-68f4-44ae-a430-a3225a7be977</v>
+        <v>9528376e-b4d9-4b58-87ac-757ac76c3509</v>
       </c>
       <c r="B13" t="str">
-        <v>Philip Natoli</v>
+        <v>Michelle  Richardson</v>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="E13" t="str">
-        <v>Philip.natoli@outlook.com</v>
+        <v>mrichardson17@outlook.com.au</v>
       </c>
       <c r="F13" t="str">
-        <v>0466021882</v>
+        <v>0459150497</v>
       </c>
       <c r="G13" t="str">
-        <v>Caulfield South</v>
+        <v>Portland</v>
       </c>
       <c r="H13" t="str">
-        <v>B+</v>
+        <v>A</v>
       </c>
       <c r="I13" t="str">
         <v>available</v>
       </c>
       <c r="J13" t="str">
-        <v>Hayley Wright</v>
+        <v>Chelsea Fanning</v>
       </c>
       <c r="K13" t="str">
-        <v>7989cb62-884e-4e52-a28b-cca0e64f2a6f</v>
+        <v>64c49e8a-746f-4336-b779-194a3e136339</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">

--- a/storage/backups/automatic-backup.xlsx
+++ b/storage/backups/automatic-backup.xlsx
@@ -15201,342 +15201,342 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>c9f9f9a5-223f-43c1-92c6-0f0a39ad4ab7</v>
+        <v>70f80dcf-ade2-4f1d-abe5-ea68a6443a19</v>
       </c>
       <c r="B2" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C2" t="str">
-        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
+        <v>df1eee3b-9186-4dcb-8dff-b88f5ac053e5</v>
       </c>
       <c r="D2">
         <v>7</v>
       </c>
       <c r="E2" t="str">
-        <v>D3</v>
+        <v>D2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>20e92b66-46e9-4eb7-80cf-b20ed2afa92c</v>
+        <v>c9f9f9a5-223f-43c1-92c6-0f0a39ad4ab7</v>
       </c>
       <c r="B3" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C3" t="str">
-        <v>1373bff6-1fa6-4e22-a5be-810587cb7056</v>
+        <v>c9ff7c4e-e24d-43e0-844b-ccf99323c69a</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E3" t="str">
-        <v>B1</v>
+        <v>D3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>d7d0a055-b2d4-4231-84ba-3a6049c57715</v>
+        <v>20e92b66-46e9-4eb7-80cf-b20ed2afa92c</v>
       </c>
       <c r="B4" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C4" t="str">
-        <v>c2568561-9563-4f98-83f7-0658e14bed36</v>
+        <v>1373bff6-1fa6-4e22-a5be-810587cb7056</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>B2</v>
+        <v>B1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3a8396e9-22fd-4db5-b8d3-a791ee3f206e</v>
+        <v>d7d0a055-b2d4-4231-84ba-3a6049c57715</v>
       </c>
       <c r="B5" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C5" t="str">
-        <v>f066c255-163d-4c17-8441-e7673d2646f3</v>
+        <v>c2568561-9563-4f98-83f7-0658e14bed36</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>B3</v>
+        <v>B2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>52696136-4d33-47a1-9605-aae3f328c29d</v>
+        <v>3a8396e9-22fd-4db5-b8d3-a791ee3f206e</v>
       </c>
       <c r="B6" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C6" t="str">
-        <v>16a56913-24a5-4bd8-9c45-78f2ae55a11d</v>
+        <v>f066c255-163d-4c17-8441-e7673d2646f3</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>B4</v>
+        <v>B3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>bae99a6d-aa62-4e41-9a56-54aaf7d037d3</v>
+        <v>52696136-4d33-47a1-9605-aae3f328c29d</v>
       </c>
       <c r="B7" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C7" t="str">
-        <v>c4a59423-d8ff-4b63-aa35-62c78b050663</v>
+        <v>16a56913-24a5-4bd8-9c45-78f2ae55a11d</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>C1</v>
+        <v>B4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>33778eb7-9030-4fea-b9c6-b2a4cf28b7ad</v>
+        <v>bae99a6d-aa62-4e41-9a56-54aaf7d037d3</v>
       </c>
       <c r="B8" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C8" t="str">
-        <v>3c4c0dd0-e98b-449e-b2fe-38d8927a3f3a</v>
+        <v>c4a59423-d8ff-4b63-aa35-62c78b050663</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ed2c1c4b-610a-4f9c-92f8-353df202c677</v>
+        <v>33778eb7-9030-4fea-b9c6-b2a4cf28b7ad</v>
       </c>
       <c r="B9" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C9" t="str">
-        <v>0ac07194-cfd3-43c3-93a4-e21b0470f833</v>
+        <v>3c4c0dd0-e98b-449e-b2fe-38d8927a3f3a</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>7fe3b0ab-fa8c-4993-b046-89982206ff8d</v>
+        <v>ed2c1c4b-610a-4f9c-92f8-353df202c677</v>
       </c>
       <c r="B10" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C10" t="str">
-        <v>65a7d185-32fb-4518-96c6-a8b8a0314939</v>
+        <v>0ac07194-cfd3-43c3-93a4-e21b0470f833</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>D3</v>
+        <v>C3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>033e9966-1308-4b1e-9c87-7198d93b3c0f</v>
+        <v>7fe3b0ab-fa8c-4993-b046-89982206ff8d</v>
       </c>
       <c r="B11" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C11" t="str">
-        <v>b42f2517-90d3-4c2e-aec1-7338c18cd14f</v>
+        <v>65a7d185-32fb-4518-96c6-a8b8a0314939</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="str">
-        <v>D4</v>
+        <v>D3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>d79f293f-1b26-4443-ac34-382a81fd09f3</v>
+        <v>033e9966-1308-4b1e-9c87-7198d93b3c0f</v>
       </c>
       <c r="B12" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C12" t="str">
-        <v>8cb8a9bf-a712-4ad3-b537-f0eebc912e58</v>
+        <v>b42f2517-90d3-4c2e-aec1-7338c18cd14f</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="str">
-        <v>E1</v>
+        <v>D4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>49e57d2c-e52e-43d6-8105-8f8f87cd393e</v>
+        <v>d79f293f-1b26-4443-ac34-382a81fd09f3</v>
       </c>
       <c r="B13" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C13" t="str">
-        <v>5fb55209-4753-4095-b21f-a62a5c711d7d</v>
+        <v>8cb8a9bf-a712-4ad3-b537-f0eebc912e58</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="str">
-        <v>E2</v>
+        <v>E1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3034a004-0f03-4137-bb27-d11448c0abdb</v>
+        <v>49e57d2c-e52e-43d6-8105-8f8f87cd393e</v>
       </c>
       <c r="B14" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C14" t="str">
-        <v>034c094f-f76d-434f-8b89-909c23c8ad42</v>
+        <v>5fb55209-4753-4095-b21f-a62a5c711d7d</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="str">
-        <v>E3</v>
+        <v>E2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>592fd454-318d-40aa-9e12-d3e6036e2e34</v>
+        <v>3034a004-0f03-4137-bb27-d11448c0abdb</v>
       </c>
       <c r="B15" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C15" t="str">
-        <v>c37d275c-1560-4d86-9b7a-22963f478a91</v>
+        <v>034c094f-f76d-434f-8b89-909c23c8ad42</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="str">
-        <v>E4</v>
+        <v>E3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>4f2e9b92-f970-4f97-a5bf-31b2204c6dbb</v>
+        <v>592fd454-318d-40aa-9e12-d3e6036e2e34</v>
       </c>
       <c r="B16" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C16" t="str">
-        <v>71d827af-973f-4c3a-a074-dd419b4a9c27</v>
+        <v>c37d275c-1560-4d86-9b7a-22963f478a91</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="str">
-        <v>A1</v>
+        <v>E4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>32d58a77-f34a-4cd2-b9a7-559df3c555d1</v>
+        <v>4f2e9b92-f970-4f97-a5bf-31b2204c6dbb</v>
       </c>
       <c r="B17" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C17" t="str">
-        <v>7f88f66e-bf77-4937-bfe1-44d447960afc</v>
+        <v>71d827af-973f-4c3a-a074-dd419b4a9c27</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="str">
-        <v>A2</v>
+        <v>A1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>9d49646c-54a0-43cc-b5a8-9a42788aaf6f</v>
+        <v>32d58a77-f34a-4cd2-b9a7-559df3c555d1</v>
       </c>
       <c r="B18" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C18" t="str">
-        <v>9520e1b4-1889-4925-9628-eb625555036c</v>
+        <v>7f88f66e-bf77-4937-bfe1-44d447960afc</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="str">
-        <v>A3</v>
+        <v>A2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>3411d007-571a-484a-a508-360fe9c6c33e</v>
+        <v>9d49646c-54a0-43cc-b5a8-9a42788aaf6f</v>
       </c>
       <c r="B19" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C19" t="str">
-        <v>293e11eb-227f-4247-8788-b270b2af2d63</v>
+        <v>9520e1b4-1889-4925-9628-eb625555036c</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="str">
-        <v>B5</v>
+        <v>A3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2457f5d9-ae65-4242-ab9c-2fb3902296fb</v>
+        <v>3411d007-571a-484a-a508-360fe9c6c33e</v>
       </c>
       <c r="B20" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C20" t="str">
-        <v>efcb7955-b4bc-487b-b45b-02a50d7f5ba2</v>
+        <v>293e11eb-227f-4247-8788-b270b2af2d63</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="str">
-        <v>C4</v>
+        <v>B5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>70f80dcf-ade2-4f1d-abe5-ea68a6443a19</v>
+        <v>2457f5d9-ae65-4242-ab9c-2fb3902296fb</v>
       </c>
       <c r="B21" t="str">
         <v>e432f0fe-1383-44a2-990c-5f787da5008a</v>
       </c>
       <c r="C21" t="str">
-        <v>df1eee3b-9186-4dcb-8dff-b88f5ac053e5</v>
+        <v>efcb7955-b4bc-487b-b45b-02a50d7f5ba2</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E21" t="str">
-        <v>D2</v>
+        <v>C4</v>
       </c>
     </row>
   </sheetData>
